--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1428010C-6B6C-480E-B8BD-7F6A2946C024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988E393A-7BB3-4BAC-B9E5-85938DE98A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="147">
   <si>
     <t>User Story</t>
   </si>
@@ -190,18 +190,12 @@
     <t>Missing doctors page element(s)</t>
   </si>
   <si>
-    <t>Any specialty card navigates to wrong section of doctors page</t>
-  </si>
-  <si>
     <t>Missing element(s)</t>
   </si>
   <si>
     <t>Verify if new User can Register using own valid credentials</t>
   </si>
   <si>
-    <t>Verify if new User password is handeld securely</t>
-  </si>
-  <si>
     <t>Register without Selecting a country</t>
   </si>
   <si>
@@ -241,9 +235,6 @@
     <t>Extra sensitive personal data can be accessable by outsiders</t>
   </si>
   <si>
-    <t>Verify if a registered User cannot accept 'Remember me' at Log in and cannot stay logged in</t>
-  </si>
-  <si>
     <t xml:space="preserve">Check all logged in Homepage elements exist </t>
   </si>
   <si>
@@ -394,12 +385,6 @@
     <t>Appointment modification unavailable</t>
   </si>
   <si>
-    <t>As a registered User I want to Check and even Modify my booked appointment(s) saved in profile so that I can customize them to fit to my schedule</t>
-  </si>
-  <si>
-    <t>Verify if a registered User can check booked appointment(s) on personal Appointments Page after Login</t>
-  </si>
-  <si>
     <t>Risk of extra sensitive personal data access by outsiders</t>
   </si>
   <si>
@@ -409,24 +394,15 @@
     <t>Log in with Social Media / other app/site's credentials</t>
   </si>
   <si>
-    <t>Verify if new User can Log in using own valid credentials</t>
-  </si>
-  <si>
     <t xml:space="preserve">invalid </t>
   </si>
   <si>
     <t xml:space="preserve"> =&gt; </t>
   </si>
   <si>
-    <t>Verify if general User can Open the Homepage and the required elements of the page are visible</t>
-  </si>
-  <si>
     <t>Verify if new User can Open Register page and the required elements of the page are visible</t>
   </si>
   <si>
-    <t>Verify if new User can Open Login page and the required elements of the page are visible</t>
-  </si>
-  <si>
     <t>Verify if any (general / logged in) User can Navigate to Doctors Page and required elements of the page are visible</t>
   </si>
   <si>
@@ -457,8 +433,86 @@
     <t>Check that Logout button works properly closing the profile</t>
   </si>
   <si>
+    <t>Verify if any User can Search MDs by name/clinic/specailty in Doctors Page search field</t>
+  </si>
+  <si>
+    <t>Verify if Navigating to a specialty section Dislpays the required elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open any specialty section Displays the proper elements of section </t>
+  </si>
+  <si>
+    <t>Missing elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wrong sorted order</t>
+  </si>
+  <si>
+    <t>Booking page is unavailable via URL</t>
+  </si>
+  <si>
+    <t>Verify if any User can Open an MD's personal Booking Page</t>
+  </si>
+  <si>
+    <t>Click any Booking button Opens the MD's personal Booking Page</t>
+  </si>
+  <si>
+    <t>Booking page is unavailable via button(s)</t>
+  </si>
+  <si>
+    <t>Wrong dates/consultation hours available</t>
+  </si>
+  <si>
+    <t>Verify if any User can Book appointment</t>
+  </si>
+  <si>
+    <t>No reminder and no trace of booking</t>
+  </si>
+  <si>
+    <t>Appointment is not saved</t>
+  </si>
+  <si>
+    <t>Book appointment and calendar note / reminder email/text is sent</t>
+  </si>
+  <si>
+    <t>Book appointment and it is Saved into User's profile</t>
+  </si>
+  <si>
+    <t>Book appointment and it is not Saved / available from app</t>
+  </si>
+  <si>
+    <t>Leaking extra sensitive personal data</t>
+  </si>
+  <si>
+    <t>Login using credentials and Navigate to personal Appointments Page displays the proper User's appointments</t>
+  </si>
+  <si>
+    <t>Missing page elements and appointment details</t>
+  </si>
+  <si>
+    <t>Open personal Appointments Page displays booked appoinment(s) separated with basicrequired elements</t>
+  </si>
+  <si>
+    <t>Verify if User can Open Homepage and the required elements of the page are visible</t>
+  </si>
+  <si>
+    <t>Verify if new User password is handled securely</t>
+  </si>
+  <si>
+    <t>Verify if User can Open Login page and the required elements of the page are visible</t>
+  </si>
+  <si>
+    <t>Verify if registered User can Log in using own valid credentials</t>
+  </si>
+  <si>
+    <t>Verify if registered User cannot accept 'Remember me' at Log in and cannot stay logged in</t>
+  </si>
+  <si>
+    <t>Verify if any User can Navigate to a specialty section of Doctors Page via specialty cards</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">C lick any </t>
+      <t xml:space="preserve">Click a </t>
     </r>
     <r>
       <rPr>
@@ -479,77 +533,20 @@
         <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> card of Doctors Page Navigates to the selected specialty section of Doctors Page only the MDs with the selected specialty </t>
+      <t xml:space="preserve"> card of Doctors Page Navigates to the selected specialty section of Doctors Page</t>
     </r>
   </si>
   <si>
-    <t>Verify if any User can Search MDs by name/clinic/specailty in Doctors Page search field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify if any User can Navigate to a specialty section of  Doctors Page via specialty cards of Homepage </t>
-  </si>
-  <si>
-    <t>Verify if any User can Navigate to a specialty section of  Doctors Page via specialty cards of Doctors Page</t>
-  </si>
-  <si>
-    <t>Verify if Navigating to a specialty section Dislpays the required elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open any specialty section Displays the proper elements of section </t>
-  </si>
-  <si>
-    <t>Missing elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Wrong sorted order</t>
-  </si>
-  <si>
-    <t>Open any specialty section Displays MDs in the proper sorted order</t>
-  </si>
-  <si>
-    <t>Booking page is unavailable via URL</t>
-  </si>
-  <si>
-    <t>Verify if any User can Open an MD's personal Booking Page</t>
-  </si>
-  <si>
-    <t>Click any Booking button Opens the MD's personal Booking Page</t>
-  </si>
-  <si>
-    <t>Booking page is unavailable via button(s)</t>
-  </si>
-  <si>
-    <t>Wrong dates/consultation hours available</t>
-  </si>
-  <si>
-    <t>Verify if any User can Book appointment</t>
-  </si>
-  <si>
-    <t>No reminder and no trace of booking</t>
-  </si>
-  <si>
-    <t>Appointment is not saved</t>
-  </si>
-  <si>
-    <t>Book appointment and calendar note / reminder email/text is sent</t>
-  </si>
-  <si>
-    <t>Book appointment and it is Saved into User's profile</t>
-  </si>
-  <si>
-    <t>Book appointment and it is not Saved / available from app</t>
-  </si>
-  <si>
-    <t>Leaking extra sensitive personal data</t>
-  </si>
-  <si>
-    <t>Login using credentials and Navigate to personal Appointments Page displays the proper User's appointments</t>
-  </si>
-  <si>
-    <t>Missing page elements and appointment details</t>
-  </si>
-  <si>
-    <t>Open personal Appointments Page displays booked appoinment(s) separated with basicrequired elements</t>
+    <t>Open any specialty section Displays  only the MDs with the selected specialty and in the proper sorted order</t>
+  </si>
+  <si>
+    <t>As a registered User I want to Check and Modify my booked appointment(s) saved in profile so that I can customize them to fit to my schedule</t>
+  </si>
+  <si>
+    <t>Verify if a logged in User can Open personal Appointments Page after Login</t>
+  </si>
+  <si>
+    <t>Verify if a logged in User can check booked appointment(s) details on personal Appointments Page after Login</t>
   </si>
 </sst>
 </file>
@@ -861,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1068,80 +1065,76 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1535,20 +1528,20 @@
       <c r="I2" s="47"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="82" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>111</v>
+      <c r="B3" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>136</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F3" s="61" t="s">
         <v>9</v>
@@ -1558,9 +1551,9 @@
       <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="82"/>
       <c r="D4" s="12" t="s">
         <v>24</v>
       </c>
@@ -1586,20 +1579,20 @@
       <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>112</v>
+      <c r="C6" s="83" t="s">
+        <v>105</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F6" s="29" t="s">
         <v>11</v>
@@ -1609,14 +1602,14 @@
       <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="82"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="74"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="84"/>
       <c r="D7" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>9</v>
@@ -1626,14 +1619,14 @@
       <c r="I7" s="52"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="82"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="77"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>11</v>
@@ -1643,75 +1636,73 @@
       <c r="I8" s="53"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="82"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="75" t="s">
-        <v>37</v>
+      <c r="A9" s="81"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="83" t="s">
+        <v>36</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="75" t="s">
-        <v>46</v>
+        <v>78</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>44</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" s="29" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="46" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="J9" s="54" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="K9" s="54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="74"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="84"/>
       <c r="D10" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="77"/>
+        <v>83</v>
+      </c>
+      <c r="E10" s="76"/>
       <c r="F10" s="48" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="40"/>
       <c r="H10" s="37"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="87"/>
+      <c r="I10" s="70"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="77"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F11" s="48" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="41"/>
-      <c r="H11" s="88"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="52"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="56" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="D12" s="57" t="s">
         <v>5</v>
@@ -1727,18 +1718,18 @@
       <c r="I12" s="52"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="79" t="s">
-        <v>43</v>
+      <c r="A13" s="81"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="87" t="s">
+        <v>41</v>
       </c>
       <c r="D13" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="90" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="72" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="41"/>
@@ -1746,16 +1737,16 @@
       <c r="I13" s="52"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="80"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="92" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="79" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="41"/>
@@ -1763,14 +1754,14 @@
       <c r="I14" s="52"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="81"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="89"/>
       <c r="D15" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="83"/>
-      <c r="F15" s="85"/>
+        <v>39</v>
+      </c>
+      <c r="E15" s="78"/>
+      <c r="F15" s="80"/>
       <c r="G15" s="41"/>
       <c r="H15" s="1"/>
       <c r="I15" s="52"/>
@@ -1787,20 +1778,20 @@
       <c r="I16" s="52"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82" t="s">
+      <c r="A17" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="82" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>113</v>
+      <c r="B17" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>138</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F17" s="48" t="s">
         <v>11</v>
@@ -1810,14 +1801,14 @@
       <c r="I17" s="52"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="74"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>9</v>
@@ -1827,14 +1818,14 @@
       <c r="I18" s="52"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="77"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>11</v>
@@ -1843,23 +1834,23 @@
       <c r="H19" s="51"/>
       <c r="I19" s="53"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="75" t="s">
-        <v>108</v>
+    <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="81"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="83" t="s">
+        <v>139</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>47</v>
+        <v>77</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>45</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>28</v>
@@ -1869,13 +1860,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="74"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="77"/>
+        <v>102</v>
+      </c>
+      <c r="E21" s="76"/>
       <c r="F21" s="9" t="s">
         <v>11</v>
       </c>
@@ -1884,33 +1875,33 @@
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="83"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="77"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="41"/>
-      <c r="H22" s="88"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="52"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="83"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="78"/>
       <c r="C23" s="11" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>9</v>
@@ -1920,16 +1911,16 @@
       <c r="I23" s="52"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="83"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="78"/>
       <c r="C24" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>11</v>
@@ -1939,16 +1930,16 @@
       <c r="I24" s="52"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="84" t="s">
-        <v>56</v>
+      <c r="A25" s="78"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="83" t="s">
+        <v>53</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="84" t="s">
-        <v>51</v>
+        <v>115</v>
+      </c>
+      <c r="E25" s="82" t="s">
+        <v>49</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>9</v>
@@ -1958,13 +1949,13 @@
       <c r="I25" s="52"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="84"/>
+        <v>60</v>
+      </c>
+      <c r="E26" s="82"/>
       <c r="F26" s="10" t="s">
         <v>9</v>
       </c>
@@ -1984,20 +1975,20 @@
       <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="72" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="75" t="s">
-        <v>114</v>
+      <c r="B28" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="83" t="s">
+        <v>106</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F28" s="48" t="s">
         <v>15</v>
@@ -2007,14 +1998,14 @@
       <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="74"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="84"/>
       <c r="D29" s="27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F29" s="24" t="s">
         <v>9</v>
@@ -2024,11 +2015,11 @@
       <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="74"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="84"/>
       <c r="D30" s="12" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>34</v>
@@ -2041,14 +2032,14 @@
       <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="77"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F31" s="48" t="s">
         <v>15</v>
@@ -2058,13 +2049,13 @@
       <c r="I31" s="42"/>
     </row>
     <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="73"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>25</v>
@@ -2077,16 +2068,16 @@
       <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="73"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="75" t="s">
-        <v>126</v>
+      <c r="A33" s="85"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="83" t="s">
+        <v>141</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" s="89" t="s">
-        <v>117</v>
+        <v>108</v>
+      </c>
+      <c r="E33" s="75" t="s">
+        <v>109</v>
       </c>
       <c r="F33" s="48" t="s">
         <v>15</v>
@@ -2095,14 +2086,14 @@
       <c r="H33" s="3"/>
       <c r="I33" s="42"/>
     </row>
-    <row r="34" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="73"/>
-      <c r="B34" s="73"/>
-      <c r="C34" s="76"/>
+    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="85"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="86"/>
       <c r="D34" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="77"/>
+      <c r="E34" s="84"/>
       <c r="F34" s="48" t="s">
         <v>11</v>
       </c>
@@ -2110,18 +2101,14 @@
       <c r="H34" s="3"/>
       <c r="I34" s="42"/>
     </row>
-    <row r="35" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="73"/>
-      <c r="B35" s="73"/>
-      <c r="C35" s="11" t="s">
-        <v>127</v>
-      </c>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="76"/>
       <c r="D35" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>35</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="E35" s="76"/>
       <c r="F35" s="48" t="s">
         <v>11</v>
       </c>
@@ -2130,33 +2117,33 @@
       <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="73"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="75" t="s">
-        <v>128</v>
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="83" t="s">
+        <v>117</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G36" s="41"/>
-      <c r="H36" s="94"/>
+      <c r="H36" s="3"/>
       <c r="I36" s="42"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="73"/>
-      <c r="B37" s="73"/>
-      <c r="C37" s="77"/>
+    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="85"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="76"/>
       <c r="D37" s="12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>15</v>
@@ -2166,10 +2153,10 @@
       <c r="I37" s="44"/>
     </row>
     <row r="38" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="78"/>
-      <c r="B38" s="78"/>
+      <c r="A38" s="74"/>
+      <c r="B38" s="74"/>
       <c r="C38" s="33" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>31</v>
@@ -2202,20 +2189,20 @@
       <c r="I39" s="38"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="70" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="75" t="s">
-        <v>134</v>
+      <c r="A40" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="83" t="s">
+        <v>122</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>15</v>
@@ -2227,14 +2214,14 @@
       <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="71"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="76"/>
+      <c r="A41" s="91"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="86"/>
       <c r="D41" s="12" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>9</v>
@@ -2244,11 +2231,11 @@
       <c r="I41" s="42"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="71"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
+      <c r="A42" s="91"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
       <c r="D42" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>19</v>
@@ -2261,14 +2248,14 @@
       <c r="I42" s="44"/>
     </row>
     <row r="43" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="71"/>
-      <c r="B43" s="74"/>
-      <c r="C43" s="77"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="76"/>
       <c r="D43" s="12" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>9</v>
@@ -2284,16 +2271,16 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="71"/>
-      <c r="B44" s="74"/>
+      <c r="A44" s="91"/>
+      <c r="B44" s="84"/>
       <c r="C44" s="22" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F44" s="24" t="s">
         <v>9</v>
@@ -2305,20 +2292,20 @@
         <v>28</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="71"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="75" t="s">
-        <v>88</v>
+      <c r="A45" s="91"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="83" t="s">
+        <v>85</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F45" s="25" t="s">
         <v>9</v>
@@ -2328,52 +2315,52 @@
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="71"/>
-      <c r="B46" s="74"/>
-      <c r="C46" s="77"/>
+      <c r="A46" s="91"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="76"/>
       <c r="D46" s="27" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F46" s="55" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="64"/>
-      <c r="H46" s="94"/>
+      <c r="H46" s="3"/>
       <c r="I46" s="42"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="71"/>
-      <c r="B47" s="74"/>
-      <c r="C47" s="95" t="s">
-        <v>89</v>
+      <c r="A47" s="91"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="92" t="s">
+        <v>86</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="73" t="s">
         <v>9</v>
       </c>
       <c r="G47" s="64"/>
-      <c r="H47" s="94"/>
+      <c r="H47" s="3"/>
       <c r="I47" s="42"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="71"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="77"/>
+      <c r="A48" s="91"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="76"/>
       <c r="D48" s="27" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F48" s="78"/>
+        <v>127</v>
+      </c>
+      <c r="F48" s="74"/>
       <c r="G48" s="64"/>
       <c r="H48" s="3"/>
       <c r="I48" s="42"/>
@@ -2390,20 +2377,20 @@
       <c r="I49" s="42"/>
     </row>
     <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="72" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="75" t="s">
-        <v>104</v>
+      <c r="A50" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="83" t="s">
+        <v>145</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F50" s="26" t="s">
         <v>9</v>
@@ -2413,14 +2400,14 @@
       <c r="I50" s="52"/>
     </row>
     <row r="51" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="74"/>
-      <c r="B51" s="74"/>
+      <c r="A51" s="84"/>
+      <c r="B51" s="84"/>
       <c r="C51" s="76"/>
       <c r="D51" s="12" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>9</v>
@@ -2430,14 +2417,16 @@
       <c r="I51" s="67"/>
     </row>
     <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="74"/>
-      <c r="B52" s="74"/>
-      <c r="C52" s="76"/>
+      <c r="A52" s="84"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="83" t="s">
+        <v>146</v>
+      </c>
       <c r="D52" s="12" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>9</v>
@@ -2447,14 +2436,14 @@
       <c r="I52" s="67"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="74"/>
-      <c r="B53" s="74"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="84"/>
       <c r="C53" s="76"/>
       <c r="D53" s="12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>9</v>
@@ -2464,16 +2453,16 @@
       <c r="I53" s="67"/>
     </row>
     <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="74"/>
-      <c r="B54" s="74"/>
+      <c r="A54" s="84"/>
+      <c r="B54" s="84"/>
       <c r="C54" s="11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>15</v>
@@ -2483,16 +2472,16 @@
       <c r="I54" s="68"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="75" t="s">
-        <v>94</v>
+      <c r="A55" s="84"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="83" t="s">
+        <v>91</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>15</v>
@@ -2502,14 +2491,14 @@
       <c r="I55" s="68"/>
     </row>
     <row r="56" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="74"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="74"/>
+      <c r="A56" s="84"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="84"/>
       <c r="D56" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>9</v>
@@ -2519,14 +2508,14 @@
       <c r="I56" s="52"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="77"/>
-      <c r="B57" s="77"/>
-      <c r="C57" s="77"/>
+      <c r="A57" s="76"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
       <c r="D57" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>15</v>
@@ -2733,14 +2722,23 @@
       <c r="E99" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B40:B48"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="C55:C57"/>
     <mergeCell ref="C45:C46"/>
     <mergeCell ref="C47:C48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A28:A38"/>
+    <mergeCell ref="B28:B38"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C33:C35"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2755,19 +2753,11 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A38"/>
-    <mergeCell ref="B28:B38"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B40:B48"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E33:E35"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988E393A-7BB3-4BAC-B9E5-85938DE98A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AFF23D-ECFB-4123-8383-382390CDC5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="156">
   <si>
     <t>User Story</t>
   </si>
@@ -56,9 +56,6 @@
     <t>User Password is not encrypted</t>
   </si>
   <si>
-    <t>Check  DB stores hashed Passwords only  using flask_bcrypt for enhanced security</t>
-  </si>
-  <si>
     <t>Invalid</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>US002.</t>
   </si>
   <si>
-    <t>Search by name, clinic or specialty do not work</t>
-  </si>
-  <si>
     <t>US003.</t>
   </si>
   <si>
@@ -119,53 +113,6 @@
     <t>Sorted list order do not match the order of sorting expression</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Click a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>specialty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card of Homepage Navigates to the selected </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>specialty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> section of Doctors Page</t>
-    </r>
-  </si>
-  <si>
     <t>invalid</t>
   </si>
   <si>
@@ -178,9 +125,6 @@
     <t>short</t>
   </si>
   <si>
-    <t>Add a valid search expression to Doctors Page search field Displays only the MDs matching search criteria</t>
-  </si>
-  <si>
     <t>Open MD's personal Booking Page Displays the proper bookable dates</t>
   </si>
   <si>
@@ -229,9 +173,6 @@
     <t>User cannot check password misspelling</t>
   </si>
   <si>
-    <t>Check any 'Remember me' button existence</t>
-  </si>
-  <si>
     <t>Extra sensitive personal data can be accessable by outsiders</t>
   </si>
   <si>
@@ -253,30 +194,15 @@
     <t>Enter URL into browser search bar Navigates to Register Page</t>
   </si>
   <si>
-    <t>Click on any registration button Navigates to Register Page</t>
-  </si>
-  <si>
     <t>As a registered User, I want to Log in and Log out properly so that I can access my personal health details and they are  safe from outsiders as well.</t>
   </si>
   <si>
     <t>Enter URL into browser search bar Navigates to Login Page</t>
   </si>
   <si>
-    <t>Click on any Login button Navigates to Login Page</t>
-  </si>
-  <si>
     <t>Check that Leaving the site / closing browser is resulted in logged in User Logout even in case of missing Logout button use</t>
   </si>
   <si>
-    <t>Click proper button Navigates to Doctors Page both by active and passive Login button</t>
-  </si>
-  <si>
-    <t>Verify if Doctors Page sorter dropdown menu changes in sorting type Change the MDs sorted list order</t>
-  </si>
-  <si>
-    <t>Change sorting expression of the sorter dropdown menu Changes the ordered list of MDs</t>
-  </si>
-  <si>
     <t>Doctors page is unavailable via URL</t>
   </si>
   <si>
@@ -325,12 +251,6 @@
     <t>As a User, I want to check an MD's booking calendar for an appointment so that I can book a suitable one</t>
   </si>
   <si>
-    <t>Enter proper URL Opens the MD's personal Booking Page</t>
-  </si>
-  <si>
-    <t>Enter input and Book an appointment</t>
-  </si>
-  <si>
     <t>Booking does not work / invalid appointment can be booked</t>
   </si>
   <si>
@@ -346,18 +266,12 @@
     <t>Verify if general User's appointment is not saved, calendar note registered / reminder email/text sent</t>
   </si>
   <si>
-    <t>Enter '/appointments/&lt;userID&gt;' into browser search bar do not open personal Appointments Page</t>
-  </si>
-  <si>
     <t>Possible abuse of personal profile access</t>
   </si>
   <si>
     <t>Lost access to personal appointments</t>
   </si>
   <si>
-    <t>Verify if logged in User can Filter personal Appointments Page content</t>
-  </si>
-  <si>
     <t>Verify if logged in User can Modify booked appointment(s)</t>
   </si>
   <si>
@@ -367,15 +281,9 @@
     <t>Remove cancelled appointment</t>
   </si>
   <si>
-    <t>Change between 'All' / 'Upcomming' / 'Cancelled' on the basis of appointment state</t>
-  </si>
-  <si>
     <t>Unavailable filtering</t>
   </si>
   <si>
-    <t>Appointment cancellation unavailable</t>
-  </si>
-  <si>
     <t>Appointment remove unavailable</t>
   </si>
   <si>
@@ -406,18 +314,6 @@
     <t>Verify if any (general / logged in) User can Navigate to Doctors Page and required elements of the page are visible</t>
   </si>
   <si>
-    <t>Enter URL by active or passive Login button Navigates to Doctors Page</t>
-  </si>
-  <si>
-    <t>Enter URL by active or passive Login button Navigates to a specialty section</t>
-  </si>
-  <si>
-    <t>Any specialty section of the doctors page is missing / unavailable or wrong section displayed</t>
-  </si>
-  <si>
-    <t>Open Register Page Displays the proper elements of the page</t>
-  </si>
-  <si>
     <t>Open Login Page Displays the proper elements of the page</t>
   </si>
   <si>
@@ -436,9 +332,6 @@
     <t>Verify if any User can Search MDs by name/clinic/specailty in Doctors Page search field</t>
   </si>
   <si>
-    <t>Verify if Navigating to a specialty section Dislpays the required elements</t>
-  </si>
-  <si>
     <t xml:space="preserve">Open any specialty section Displays the proper elements of section </t>
   </si>
   <si>
@@ -454,9 +347,6 @@
     <t>Verify if any User can Open an MD's personal Booking Page</t>
   </si>
   <si>
-    <t>Click any Booking button Opens the MD's personal Booking Page</t>
-  </si>
-  <si>
     <t>Booking page is unavailable via button(s)</t>
   </si>
   <si>
@@ -472,27 +362,12 @@
     <t>Appointment is not saved</t>
   </si>
   <si>
-    <t>Book appointment and calendar note / reminder email/text is sent</t>
-  </si>
-  <si>
-    <t>Book appointment and it is Saved into User's profile</t>
-  </si>
-  <si>
-    <t>Book appointment and it is not Saved / available from app</t>
-  </si>
-  <si>
     <t>Leaking extra sensitive personal data</t>
   </si>
   <si>
-    <t>Login using credentials and Navigate to personal Appointments Page displays the proper User's appointments</t>
-  </si>
-  <si>
     <t>Missing page elements and appointment details</t>
   </si>
   <si>
-    <t>Open personal Appointments Page displays booked appoinment(s) separated with basicrequired elements</t>
-  </si>
-  <si>
     <t>Verify if User can Open Homepage and the required elements of the page are visible</t>
   </si>
   <si>
@@ -505,41 +380,9 @@
     <t>Verify if registered User can Log in using own valid credentials</t>
   </si>
   <si>
-    <t>Verify if registered User cannot accept 'Remember me' at Log in and cannot stay logged in</t>
-  </si>
-  <si>
     <t>Verify if any User can Navigate to a specialty section of Doctors Page via specialty cards</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Click a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>specialty</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card of Doctors Page Navigates to the selected specialty section of Doctors Page</t>
-    </r>
-  </si>
-  <si>
-    <t>Open any specialty section Displays  only the MDs with the selected specialty and in the proper sorted order</t>
-  </si>
-  <si>
     <t>As a registered User I want to Check and Modify my booked appointment(s) saved in profile so that I can customize them to fit to my schedule</t>
   </si>
   <si>
@@ -547,13 +390,130 @@
   </si>
   <si>
     <t>Verify if a logged in User can check booked appointment(s) details on personal Appointments Page after Login</t>
+  </si>
+  <si>
+    <t>Click on registration button Navigates to Register Page</t>
+  </si>
+  <si>
+    <t>Check that Register Page Displays the proper elements of the page</t>
+  </si>
+  <si>
+    <t>Check  DB stores hashed Passwords only using flask_bcrypt for enhanced security</t>
+  </si>
+  <si>
+    <t>Click on Login button Navigates to Login Page</t>
+  </si>
+  <si>
+    <t>Verify if registered User cannot accept 'Remember me' at Login and cannot stay logged in</t>
+  </si>
+  <si>
+    <t>Check no 'Remember me' button exists</t>
+  </si>
+  <si>
+    <t>Any specialty section of the doctors page is missing / unavailable or wrong section is displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open specialty section by any User entering URL </t>
+  </si>
+  <si>
+    <t>Open specialty section by any User clicking Homepage specialty card</t>
+  </si>
+  <si>
+    <t>Open specialty section by any User clicking Doctors Page specialty card</t>
+  </si>
+  <si>
+    <t>Open Doctors Page by any User entering URL into the browser search bar</t>
+  </si>
+  <si>
+    <t>Open Doctors Page by logged in User clicking navigation button(s)</t>
+  </si>
+  <si>
+    <t>Open Doctors Page by general User clicking navigation button(s)</t>
+  </si>
+  <si>
+    <t>Verify if Doctors Page filtering works and is displayed properly</t>
+  </si>
+  <si>
+    <t>Change sorting expression of the sorter dropdown menu and ordered list of MDs changes</t>
+  </si>
+  <si>
+    <t>param</t>
+  </si>
+  <si>
+    <t>Verify if Navigating to a specialty section Dislpays the required elements and filtering works</t>
+  </si>
+  <si>
+    <t>param?</t>
+  </si>
+  <si>
+    <t>Open any specialty section Displays only the MDs with the selected specialty and in the proper sorted order</t>
+  </si>
+  <si>
+    <t>Add a search expression to Doctors Page search field Displays only the MDs matching search criteria</t>
+  </si>
+  <si>
+    <t>Search by name, clinic or specialty does not work</t>
+  </si>
+  <si>
+    <t>Open MD's personal Booking Page entering url</t>
+  </si>
+  <si>
+    <t>Open MD's Booking Page by logged in User clicking any Booking button</t>
+  </si>
+  <si>
+    <t>Open MD's Booking Page by general User clicking any Booking button</t>
+  </si>
+  <si>
+    <t>Enter input by logged in User and Book an appointment</t>
+  </si>
+  <si>
+    <t>Enter input by general User and Book an appointment</t>
+  </si>
+  <si>
+    <t>Send Logged in User's appointment reminder</t>
+  </si>
+  <si>
+    <t>Save logged in User's booked appointment into User's profile</t>
+  </si>
+  <si>
+    <t>Submit general User's booked appointment without saving</t>
+  </si>
+  <si>
+    <t>Send general User's appointment reminder</t>
+  </si>
+  <si>
+    <t>Open logged in User personal Appointments Page with button</t>
+  </si>
+  <si>
+    <t>Enter logged out registered User Appointments Page url into browser search bar do not open profile</t>
+  </si>
+  <si>
+    <t>Open logged in User personal Appointments Page with url</t>
+  </si>
+  <si>
+    <t>Open personal Appointments Page displays booked appoinment(s) separated with basic required elements</t>
+  </si>
+  <si>
+    <t>Change between appointments' filtered groups display</t>
+  </si>
+  <si>
+    <t>Verify if logged in User can Filter personal appointments</t>
+  </si>
+  <si>
+    <t>Keep appointment under cancellation</t>
+  </si>
+  <si>
+    <t>Cancelling appointment unavailable</t>
+  </si>
+  <si>
+    <t>Cancelling appointment irreversible</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,6 +590,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -858,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -930,9 +898,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1074,16 +1039,34 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1101,21 +1084,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1129,12 +1124,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1471,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1488,8 +1477,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="58" t="s">
-        <v>14</v>
+      <c r="A1" s="57" t="s">
+        <v>13</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>0</v>
@@ -1504,1104 +1493,1155 @@
         <v>3</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="39" t="s">
-        <v>6</v>
+      <c r="I1" s="38" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59"/>
+      <c r="A2" s="58"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="47"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="82" t="s">
-        <v>136</v>
+      <c r="A3" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="93" t="s">
+        <v>109</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="40"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="41"/>
+    </row>
+    <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="86"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="42"/>
-    </row>
-    <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="81"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="41"/>
+      <c r="G4" s="40"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="42"/>
+      <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="21"/>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
       <c r="E5" s="20"/>
-      <c r="F5" s="28"/>
+      <c r="F5" s="27"/>
       <c r="G5" s="1"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="42"/>
+      <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="81" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="81" t="s">
+      <c r="A6" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="40"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="41"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="86"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="40"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="51"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="86"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="42"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="52"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="86"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="K9" s="53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="39"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="69"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="86"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="40"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="51"/>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="86"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="51"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="86"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="40"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="51"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="86"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="83" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="41"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="42"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="81"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="41"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="52"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="81"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="11" t="s">
+      <c r="E14" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="84" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="40"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="51"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="86"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="53"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="81"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" s="54" t="s">
-        <v>104</v>
-      </c>
-      <c r="K9" s="54" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="81"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="76"/>
-      <c r="F10" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="70"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="81"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="41"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="52"/>
-    </row>
-    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="81"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="41"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="52"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="81"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="87" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="71" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="41"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="52"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="81"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="77" t="s">
-        <v>114</v>
-      </c>
-      <c r="F14" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="52"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="81"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="78"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="41"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="52"/>
+      <c r="I15" s="51"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="60"/>
+      <c r="A16" s="59"/>
       <c r="B16" s="21"/>
       <c r="C16" s="20"/>
       <c r="D16" s="21"/>
       <c r="E16" s="20"/>
-      <c r="F16" s="49"/>
+      <c r="F16" s="48"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-      <c r="I16" s="52"/>
+      <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>138</v>
+      <c r="A17" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="41"/>
+        <v>59</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="40"/>
       <c r="H17" s="1"/>
-      <c r="I17" s="52"/>
+      <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="81"/>
-      <c r="B18" s="81"/>
-      <c r="C18" s="86"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="94"/>
       <c r="D18" s="12" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="41"/>
+        <v>8</v>
+      </c>
+      <c r="G18" s="40"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="52"/>
+      <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="81"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="12" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="43"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="53"/>
+        <v>10</v>
+      </c>
+      <c r="G19" s="42"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="81"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="83" t="s">
-        <v>139</v>
+      <c r="A20" s="86"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="76" t="s">
+        <v>112</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="86"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="77"/>
+      <c r="F21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="62"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="37"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="83"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="40"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="51"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="83"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="40"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="51"/>
+    </row>
+    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="83"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="81"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="76"/>
-      <c r="F21" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="63"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="38"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="41"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="52"/>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="F24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="40"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="51"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="41"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="52"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="78"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="41"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="52"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="78"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="83" t="s">
+      <c r="D25" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="40"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="51"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="83"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="41"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="52"/>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="78"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="82"/>
+      <c r="E26" s="93"/>
       <c r="F26" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G26" s="41"/>
+        <v>8</v>
+      </c>
+      <c r="G26" s="40"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="52"/>
+      <c r="I26" s="51"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="19"/>
       <c r="C27" s="20"/>
       <c r="D27" s="21"/>
       <c r="E27" s="20"/>
-      <c r="F27" s="49"/>
+      <c r="F27" s="48"/>
       <c r="G27" s="1"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="42"/>
+      <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="73" t="s">
+      <c r="A28" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="F28" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="40"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="41"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="95"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="40"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="41"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="95"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="77"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="41"/>
+    </row>
+    <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="95"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="40"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="41"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="95"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="40"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="41"/>
+    </row>
+    <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="95"/>
+      <c r="B33" s="95"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="40"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="41"/>
+    </row>
+    <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="95"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="87" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="63"/>
+      <c r="H34" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I34" s="41"/>
+    </row>
+    <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="95"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E35" s="88"/>
+      <c r="F35" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="40"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="41"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="95"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="77"/>
+      <c r="F36" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="40"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="41"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="95"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="40"/>
+      <c r="H37" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="41"/>
+    </row>
+    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="95"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="42"/>
+      <c r="H38" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="43"/>
+    </row>
+    <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="81"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="37"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="80" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="41"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="100"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="F42" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="40"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="41"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="100"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" s="77"/>
+      <c r="F43" s="79"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="41"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="100"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="42"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="43"/>
+    </row>
+    <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="100"/>
+      <c r="B45" s="90"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="100"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="76" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="80" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="100"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="92"/>
+      <c r="D47" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="77"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="100"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="F48" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="62"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="37"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="100"/>
+      <c r="B49" s="90"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="63"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="41"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="100"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="76" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="41"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="42"/>
-    </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="85"/>
-      <c r="B29" s="85"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="41"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="42"/>
-    </row>
-    <row r="30" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="85"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="41"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="42"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G31" s="41"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="42"/>
-    </row>
-    <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="85"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32" s="41"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="42"/>
-    </row>
-    <row r="33" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="85"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="83" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="F50" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="63"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="41"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="100"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="92"/>
+      <c r="D51" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" s="81"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="41"/>
+    </row>
+    <row r="52" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="59"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="41"/>
+    </row>
+    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="64"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="51"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="95"/>
+      <c r="B54" s="95"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="64"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="51"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="95"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="E55" s="77"/>
+      <c r="F55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="64"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="51"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="90"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="75" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="41"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="42"/>
-    </row>
-    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="84"/>
-      <c r="F34" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="41"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="42"/>
-    </row>
-    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="76"/>
-      <c r="F35" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="41"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="42"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="42"/>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="43"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="44"/>
-    </row>
-    <row r="38" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="74"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="35"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="38"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="90" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="73" t="s">
+      <c r="F56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="40"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="66"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="90"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="40"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="66"/>
+    </row>
+    <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="90"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="40"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="67"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="40"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="67"/>
+    </row>
+    <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="90"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="40"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="51"/>
+    </row>
+    <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="90"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="40"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="51"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="42"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="91"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="41"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="42"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="91"/>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="43"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="44"/>
-    </row>
-    <row r="43" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="91"/>
-      <c r="B43" s="84"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="91"/>
-      <c r="B44" s="84"/>
-      <c r="C44" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D44" s="27" t="s">
+      <c r="E62" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="91"/>
-      <c r="B45" s="84"/>
-      <c r="C45" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="63"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="38"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="91"/>
-      <c r="B46" s="84"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F46" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" s="64"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="42"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="91"/>
-      <c r="B47" s="84"/>
-      <c r="C47" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="F47" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="64"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="42"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="91"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="F48" s="74"/>
-      <c r="G48" s="64"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="42"/>
-    </row>
-    <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="60"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="42"/>
-    </row>
-    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E50" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="65"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="52"/>
-    </row>
-    <row r="51" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
-      <c r="B51" s="84"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" s="41"/>
-      <c r="H51" s="66"/>
-      <c r="I51" s="67"/>
-    </row>
-    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
-      <c r="B52" s="84"/>
-      <c r="C52" s="83" t="s">
-        <v>146</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="41"/>
-      <c r="H52" s="66"/>
-      <c r="I52" s="67"/>
-    </row>
-    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
-      <c r="B53" s="84"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" s="41"/>
-      <c r="H53" s="66"/>
-      <c r="I53" s="67"/>
-    </row>
-    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
-      <c r="B54" s="84"/>
-      <c r="C54" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G54" s="41"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="68"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
-      <c r="B55" s="84"/>
-      <c r="C55" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="41"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="68"/>
-    </row>
-    <row r="56" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
-      <c r="B56" s="84"/>
-      <c r="C56" s="84"/>
-      <c r="D56" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" s="41"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="52"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="76"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="43"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="53"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="32"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="69"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="69"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="32"/>
-    </row>
-    <row r="59" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="2"/>
-      <c r="E59" s="5"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="2"/>
-      <c r="E60" s="5"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="2"/>
-      <c r="E61" s="5"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="2"/>
-      <c r="E62" s="5"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="2"/>
+      <c r="F62" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="42"/>
+      <c r="H62" s="50"/>
+      <c r="I62" s="52"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B63" s="2"/>
-      <c r="E63" s="5"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="31"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="68"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="31"/>
+    </row>
+    <row r="64" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="2"/>
       <c r="E64" s="5"/>
-      <c r="G64" s="1"/>
+      <c r="G64" s="2"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="2"/>
       <c r="E65" s="5"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B66" s="3"/>
-      <c r="E66" s="7"/>
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="2"/>
+      <c r="E66" s="5"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B67" s="3"/>
+      <c r="B67" s="2"/>
       <c r="E67" s="5"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+      <c r="I67" s="2"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
-      <c r="E68" s="7"/>
-    </row>
-    <row r="69" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E68" s="5"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
-      <c r="E69" s="7"/>
+      <c r="E69" s="5"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
@@ -2611,14 +2651,11 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="E71" s="5"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+      <c r="B71" s="3"/>
+      <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B72" s="2"/>
+      <c r="B72" s="3"/>
       <c r="E72" s="5"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -2626,18 +2663,18 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
-      <c r="E73" s="5"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="E74" s="7"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
-      <c r="E75" s="7"/>
+      <c r="E75" s="5"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
@@ -2648,11 +2685,17 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
-      <c r="E77" s="7"/>
+      <c r="E77" s="5"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
-      <c r="E78" s="7"/>
+      <c r="E78" s="5"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
@@ -2662,54 +2705,62 @@
       <c r="B80" s="2"/>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E81" s="5"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="E82" s="7"/>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B83" s="2"/>
       <c r="E83" s="7"/>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B84" s="2"/>
       <c r="E84" s="7"/>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85" s="2"/>
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="2"/>
       <c r="E86" s="7"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87" s="2"/>
       <c r="E87" s="7"/>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E88" s="7"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E90" s="7"/>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E93" s="7"/>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E94" s="7"/>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E95" s="7"/>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E96" s="7"/>
     </row>
     <row r="97" spans="5:5" x14ac:dyDescent="0.3">
@@ -2721,24 +2772,39 @@
     <row r="99" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E99" s="7"/>
     </row>
+    <row r="100" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E100" s="7"/>
+    </row>
+    <row r="101" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E101" s="7"/>
+    </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E102" s="7"/>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E103" s="7"/>
+    </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E104" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B40:B48"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="B50:B57"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="C47:C48"/>
+  <mergeCells count="47">
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
     <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A28:A38"/>
-    <mergeCell ref="B28:B38"/>
-    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
     <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2753,11 +2819,23 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -1051,80 +1051,80 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1517,13 +1517,13 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="91" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="12" t="s">
@@ -1540,9 +1540,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="93"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="91"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1568,13 +1568,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="81" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1591,9 +1591,9 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="90"/>
+      <c r="A7" s="89"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="12" t="s">
         <v>117</v>
       </c>
@@ -1608,9 +1608,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="77"/>
+      <c r="A8" s="89"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="83"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1625,15 +1625,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="76" t="s">
+      <c r="A9" s="89"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="81" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="81" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1656,13 +1656,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="90"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="80"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="77"/>
+      <c r="E10" s="83"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1671,9 +1671,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="77"/>
+      <c r="A11" s="89"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="83"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1688,8 +1688,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="83"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="90"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1707,9 +1707,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="96" t="s">
+      <c r="A13" s="89"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="86" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1726,16 +1726,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="97"/>
+      <c r="A14" s="89"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="87"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="F14" s="93" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1743,14 +1743,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="98"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="88"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="83"/>
-      <c r="F15" s="85"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="94"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1767,13 +1767,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="81" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1790,9 +1790,9 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="94"/>
+      <c r="A18" s="89"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="82"/>
       <c r="D18" s="12" t="s">
         <v>120</v>
       </c>
@@ -1807,9 +1807,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="92"/>
+      <c r="A19" s="89"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="84"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1824,15 +1824,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="76" t="s">
+      <c r="A20" s="89"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="81" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="76" t="s">
+      <c r="E20" s="81" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1849,13 +1849,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="86"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="94"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="77"/>
+      <c r="E21" s="83"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1864,9 +1864,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="83"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="92"/>
+      <c r="A22" s="90"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="84"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1881,8 +1881,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="83"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="90"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1900,8 +1900,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="83"/>
+      <c r="A24" s="90"/>
+      <c r="B24" s="90"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1919,15 +1919,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="76" t="s">
+      <c r="A25" s="90"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="81" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="91" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1938,13 +1938,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="90"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="84"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="93"/>
+      <c r="E26" s="91"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1964,13 +1964,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="81" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -1987,16 +1987,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="95"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="90"/>
+      <c r="A29" s="79"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="80"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="76" t="s">
+      <c r="E29" s="81" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="78" t="s">
+      <c r="F29" s="97" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2004,22 +2004,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="95"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="90"/>
+      <c r="A30" s="79"/>
+      <c r="B30" s="79"/>
+      <c r="C30" s="80"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="89"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="98"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="95"/>
-      <c r="B31" s="95"/>
-      <c r="C31" s="77"/>
+      <c r="A31" s="79"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="83"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2034,9 +2034,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="95"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="91" t="s">
+      <c r="A32" s="79"/>
+      <c r="B32" s="79"/>
+      <c r="C32" s="99" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2053,9 +2053,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="95"/>
-      <c r="B33" s="95"/>
-      <c r="C33" s="77"/>
+      <c r="A33" s="79"/>
+      <c r="B33" s="79"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2070,15 +2070,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="95"/>
-      <c r="B34" s="95"/>
-      <c r="C34" s="76" t="s">
+      <c r="A34" s="79"/>
+      <c r="B34" s="79"/>
+      <c r="C34" s="81" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="87" t="s">
+      <c r="E34" s="95" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2091,13 +2091,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="95"/>
-      <c r="B35" s="95"/>
-      <c r="C35" s="94"/>
+      <c r="A35" s="79"/>
+      <c r="B35" s="79"/>
+      <c r="C35" s="82"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="88"/>
+      <c r="E35" s="96"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2106,13 +2106,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="95"/>
-      <c r="B36" s="95"/>
-      <c r="C36" s="94"/>
+      <c r="A36" s="79"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="82"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="77"/>
+      <c r="E36" s="83"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2121,9 +2121,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="95"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="76" t="s">
+      <c r="A37" s="79"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="81" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2142,9 +2142,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="95"/>
-      <c r="B38" s="95"/>
-      <c r="C38" s="77"/>
+      <c r="A38" s="79"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="83"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2161,8 +2161,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="81"/>
-      <c r="B39" s="81"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2197,13 +2197,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="99" t="s">
+      <c r="A41" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="81" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2222,16 +2222,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="100"/>
-      <c r="B42" s="95"/>
-      <c r="C42" s="94"/>
+      <c r="A42" s="77"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="82"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="76" t="s">
+      <c r="E42" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="78" t="s">
+      <c r="F42" s="97" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2239,22 +2239,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="100"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="94"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="82"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="77"/>
-      <c r="F43" s="79"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="100"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="100"/>
-      <c r="B44" s="90"/>
-      <c r="C44" s="90"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="80"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2269,9 +2269,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="100"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="77"/>
+      <c r="A45" s="77"/>
+      <c r="B45" s="80"/>
+      <c r="C45" s="83"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2292,47 +2292,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="100"/>
-      <c r="B46" s="90"/>
-      <c r="C46" s="76" t="s">
+      <c r="A46" s="77"/>
+      <c r="B46" s="80"/>
+      <c r="C46" s="81" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="76" t="s">
+      <c r="E46" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="78" t="s">
+      <c r="F46" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="80" t="s">
+      <c r="G46" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H46" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="80" t="s">
+      <c r="I46" s="78" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="100"/>
-      <c r="B47" s="90"/>
-      <c r="C47" s="92"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="84"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="77"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="100"/>
-      <c r="B48" s="90"/>
-      <c r="C48" s="76" t="s">
+      <c r="A48" s="77"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="81" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2349,9 +2349,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="100"/>
-      <c r="B49" s="90"/>
-      <c r="C49" s="77"/>
+      <c r="A49" s="77"/>
+      <c r="B49" s="80"/>
+      <c r="C49" s="83"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2366,9 +2366,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="100"/>
-      <c r="B50" s="90"/>
-      <c r="C50" s="76" t="s">
+      <c r="A50" s="77"/>
+      <c r="B50" s="80"/>
+      <c r="C50" s="81" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2377,7 +2377,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="80" t="s">
+      <c r="F50" s="78" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2385,16 +2385,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="100"/>
-      <c r="B51" s="90"/>
-      <c r="C51" s="92"/>
+      <c r="A51" s="77"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="84"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="81"/>
+      <c r="F51" s="85"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2411,13 +2411,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="76" t="s">
+      <c r="C53" s="81" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2434,13 +2434,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="95"/>
-      <c r="B54" s="95"/>
-      <c r="C54" s="94"/>
+      <c r="A54" s="79"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="82"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="76" t="s">
+      <c r="E54" s="81" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2451,13 +2451,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="95"/>
-      <c r="B55" s="95"/>
-      <c r="C55" s="94"/>
+      <c r="A55" s="79"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="82"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="77"/>
+      <c r="E55" s="83"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2466,9 +2466,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="90"/>
-      <c r="B56" s="90"/>
-      <c r="C56" s="76" t="s">
+      <c r="A56" s="80"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="81" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2485,9 +2485,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="90"/>
-      <c r="B57" s="90"/>
-      <c r="C57" s="77"/>
+      <c r="A57" s="80"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="83"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2502,8 +2502,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="90"/>
-      <c r="B58" s="90"/>
+      <c r="A58" s="80"/>
+      <c r="B58" s="80"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2521,9 +2521,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="90"/>
-      <c r="B59" s="90"/>
-      <c r="C59" s="76" t="s">
+      <c r="A59" s="80"/>
+      <c r="B59" s="80"/>
+      <c r="C59" s="81" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2540,9 +2540,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="90"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="90"/>
+      <c r="A60" s="80"/>
+      <c r="B60" s="80"/>
+      <c r="C60" s="80"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2557,9 +2557,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="90"/>
-      <c r="B61" s="90"/>
-      <c r="C61" s="90"/>
+      <c r="A61" s="80"/>
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2574,9 +2574,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="77"/>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
+      <c r="A62" s="83"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="83"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2789,22 +2789,23 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2819,23 +2820,22 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AFF23D-ECFB-4123-8383-382390CDC5FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584DC136-CD60-43F8-A514-63A7283A503B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -599,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +618,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -826,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1051,55 +1057,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1108,23 +1087,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1517,16 +1526,16 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="89" t="s">
+      <c r="B3" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="101" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -1540,9 +1549,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="89"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="91"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1568,13 +1577,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="81" t="s">
+      <c r="C6" s="76" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1591,10 +1600,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="12" t="s">
+      <c r="A7" s="86"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="101" t="s">
         <v>117</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -1608,9 +1617,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89"/>
-      <c r="B8" s="90"/>
-      <c r="C8" s="83"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="77"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1625,15 +1634,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="81" t="s">
+      <c r="A9" s="86"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="76" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="E9" s="76" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1656,13 +1665,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="89"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="80"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="90"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="83"/>
+      <c r="E10" s="77"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1671,9 +1680,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="89"/>
-      <c r="B11" s="90"/>
-      <c r="C11" s="83"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1688,8 +1697,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="89"/>
-      <c r="B12" s="90"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="83"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1707,9 +1716,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="89"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="86" t="s">
+      <c r="A13" s="86"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="96" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1726,16 +1735,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="89"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="87"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="97"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="93" t="s">
+      <c r="F14" s="84" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1743,14 +1752,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="88"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="98"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="94"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="85"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1767,13 +1776,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="76" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1790,10 +1799,10 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="89"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="12" t="s">
+      <c r="A18" s="86"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="101" t="s">
         <v>120</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -1807,9 +1816,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="89"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="84"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1824,15 +1833,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="89"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="81" t="s">
+      <c r="A20" s="86"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="76" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="81" t="s">
+      <c r="E20" s="76" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1849,13 +1858,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="89"/>
-      <c r="B21" s="90"/>
-      <c r="C21" s="82"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="94"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="83"/>
+      <c r="E21" s="77"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1864,9 +1873,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="90"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="84"/>
+      <c r="A22" s="83"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1881,8 +1890,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="90"/>
-      <c r="B23" s="90"/>
+      <c r="A23" s="83"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1900,8 +1909,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="90"/>
-      <c r="B24" s="90"/>
+      <c r="A24" s="83"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1919,15 +1928,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="90"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="81" t="s">
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="76" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="91" t="s">
+      <c r="E25" s="93" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1938,13 +1947,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="90"/>
-      <c r="B26" s="90"/>
-      <c r="C26" s="84"/>
+      <c r="A26" s="83"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="91"/>
+      <c r="E26" s="93"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1964,13 +1973,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="76" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -1987,16 +1996,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="79"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="80"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="95"/>
+      <c r="C29" s="90"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="81" t="s">
+      <c r="E29" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="97" t="s">
+      <c r="F29" s="78" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2004,22 +2013,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="79"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="80"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="95"/>
+      <c r="C30" s="90"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="83"/>
-      <c r="F30" s="98"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="89"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="79"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="83"/>
+      <c r="A31" s="95"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="77"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2034,9 +2043,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="79"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="99" t="s">
+      <c r="A32" s="95"/>
+      <c r="B32" s="95"/>
+      <c r="C32" s="91" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2053,9 +2062,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="79"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="83"/>
+      <c r="A33" s="95"/>
+      <c r="B33" s="95"/>
+      <c r="C33" s="77"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2070,15 +2079,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="79"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="81" t="s">
+      <c r="A34" s="95"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="76" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="95" t="s">
+      <c r="E34" s="87" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2091,13 +2100,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="79"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="82"/>
+      <c r="A35" s="95"/>
+      <c r="B35" s="95"/>
+      <c r="C35" s="94"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="96"/>
+      <c r="E35" s="88"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2106,13 +2115,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="79"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="82"/>
+      <c r="A36" s="95"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="94"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="83"/>
+      <c r="E36" s="77"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2121,9 +2130,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="79"/>
-      <c r="B37" s="79"/>
-      <c r="C37" s="81" t="s">
+      <c r="A37" s="95"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="76" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2142,9 +2151,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="79"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="83"/>
+      <c r="A38" s="95"/>
+      <c r="B38" s="95"/>
+      <c r="C38" s="77"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2161,8 +2170,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
+      <c r="A39" s="81"/>
+      <c r="B39" s="81"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2197,13 +2206,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="76" t="s">
+      <c r="A41" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="81" t="s">
+      <c r="C41" s="76" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2222,16 +2231,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="77"/>
-      <c r="B42" s="79"/>
-      <c r="C42" s="82"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="94"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="81" t="s">
+      <c r="E42" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="97" t="s">
+      <c r="F42" s="78" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2239,22 +2248,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="77"/>
-      <c r="B43" s="79"/>
-      <c r="C43" s="82"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="94"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="83"/>
-      <c r="F43" s="100"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="79"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="77"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="90"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2269,9 +2278,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="77"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="83"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="90"/>
+      <c r="C45" s="77"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2292,47 +2301,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="77"/>
-      <c r="B46" s="80"/>
-      <c r="C46" s="81" t="s">
+      <c r="A46" s="100"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="76" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="81" t="s">
+      <c r="E46" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="97" t="s">
+      <c r="F46" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="78" t="s">
+      <c r="G46" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="78" t="s">
+      <c r="H46" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="78" t="s">
+      <c r="I46" s="80" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="77"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="84"/>
+      <c r="A47" s="100"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="92"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="83"/>
-      <c r="F47" s="100"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
+      <c r="I47" s="77"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="77"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="81" t="s">
+      <c r="A48" s="100"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="76" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2349,9 +2358,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="77"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="83"/>
+      <c r="A49" s="100"/>
+      <c r="B49" s="90"/>
+      <c r="C49" s="77"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2366,9 +2375,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="77"/>
-      <c r="B50" s="80"/>
-      <c r="C50" s="81" t="s">
+      <c r="A50" s="100"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="76" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2377,7 +2386,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="78" t="s">
+      <c r="F50" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2385,16 +2394,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="77"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="84"/>
+      <c r="A51" s="100"/>
+      <c r="B51" s="90"/>
+      <c r="C51" s="92"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="85"/>
+      <c r="F51" s="81"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2411,13 +2420,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="78" t="s">
+      <c r="A53" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="78" t="s">
+      <c r="B53" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="76" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2434,13 +2443,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="79"/>
-      <c r="B54" s="79"/>
-      <c r="C54" s="82"/>
+      <c r="A54" s="95"/>
+      <c r="B54" s="95"/>
+      <c r="C54" s="94"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="81" t="s">
+      <c r="E54" s="76" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2451,13 +2460,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="79"/>
-      <c r="B55" s="79"/>
-      <c r="C55" s="82"/>
+      <c r="A55" s="95"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="94"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="83"/>
+      <c r="E55" s="77"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2466,9 +2475,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="80"/>
-      <c r="B56" s="80"/>
-      <c r="C56" s="81" t="s">
+      <c r="A56" s="90"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="76" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2485,9 +2494,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="80"/>
-      <c r="B57" s="80"/>
-      <c r="C57" s="83"/>
+      <c r="A57" s="90"/>
+      <c r="B57" s="90"/>
+      <c r="C57" s="77"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2502,8 +2511,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="80"/>
-      <c r="B58" s="80"/>
+      <c r="A58" s="90"/>
+      <c r="B58" s="90"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2521,9 +2530,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="80"/>
-      <c r="B59" s="80"/>
-      <c r="C59" s="81" t="s">
+      <c r="A59" s="90"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="76" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2540,9 +2549,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="80"/>
-      <c r="B60" s="80"/>
-      <c r="C60" s="80"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="90"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2557,9 +2566,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="80"/>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
+      <c r="A61" s="90"/>
+      <c r="B61" s="90"/>
+      <c r="C61" s="90"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2574,9 +2583,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="83"/>
-      <c r="B62" s="83"/>
-      <c r="C62" s="83"/>
+      <c r="A62" s="77"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2789,23 +2798,22 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2820,22 +2828,23 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584DC136-CD60-43F8-A514-63A7283A503B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19D470-567C-4E56-A854-9E32405D96CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -599,7 +599,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -624,6 +624,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -832,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1057,82 +1063,85 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1526,16 +1535,16 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="101" t="s">
+      <c r="D3" s="102" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -1549,9 +1558,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="93"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1577,13 +1586,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="82" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1600,10 +1609,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="86"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="101" t="s">
+      <c r="A7" s="90"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="102" t="s">
         <v>117</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -1617,9 +1626,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="77"/>
+      <c r="A8" s="90"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="84"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1634,15 +1643,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="86"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="76" t="s">
+      <c r="A9" s="90"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="82" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="76" t="s">
+      <c r="E9" s="82" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1665,13 +1674,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="86"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="90"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="81"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="77"/>
+      <c r="E10" s="84"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1680,9 +1689,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="86"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="77"/>
+      <c r="A11" s="90"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="84"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1697,8 +1706,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="86"/>
-      <c r="B12" s="83"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1716,9 +1725,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="86"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="96" t="s">
+      <c r="A13" s="90"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="87" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1735,16 +1744,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="86"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="97"/>
+      <c r="A14" s="90"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="F14" s="94" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1752,14 +1761,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="86"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="98"/>
+      <c r="A15" s="90"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="89"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="83"/>
-      <c r="F15" s="85"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="95"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1776,13 +1785,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="82" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1799,10 +1808,10 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="86"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="101" t="s">
+      <c r="A18" s="90"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="102" t="s">
         <v>120</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -1816,9 +1825,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="86"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="92"/>
+      <c r="A19" s="90"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1833,15 +1842,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="76" t="s">
+      <c r="A20" s="90"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="82" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="76" t="s">
+      <c r="E20" s="82" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1858,13 +1867,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="86"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="94"/>
+      <c r="A21" s="90"/>
+      <c r="B21" s="91"/>
+      <c r="C21" s="83"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="77"/>
+      <c r="E21" s="84"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1873,9 +1882,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="83"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="92"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="85"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1890,8 +1899,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="83"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="91"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1909,8 +1918,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="83"/>
+      <c r="A24" s="91"/>
+      <c r="B24" s="91"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1928,15 +1937,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="76" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="91"/>
+      <c r="C25" s="82" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="92" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1947,13 +1956,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="91"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="85"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="93"/>
+      <c r="E26" s="92"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1973,13 +1982,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="82" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -1996,16 +2005,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="95"/>
-      <c r="B29" s="95"/>
-      <c r="C29" s="90"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="80"/>
+      <c r="C29" s="81"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="76" t="s">
+      <c r="E29" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="78" t="s">
+      <c r="F29" s="98" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2013,22 +2022,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="95"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="90"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="81"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="89"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="95"/>
-      <c r="B31" s="95"/>
-      <c r="C31" s="77"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="84"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2043,9 +2052,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="95"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="91" t="s">
+      <c r="A32" s="80"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="100" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2062,9 +2071,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="95"/>
-      <c r="B33" s="95"/>
-      <c r="C33" s="77"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="80"/>
+      <c r="C33" s="84"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2079,15 +2088,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="95"/>
-      <c r="B34" s="95"/>
-      <c r="C34" s="76" t="s">
+      <c r="A34" s="80"/>
+      <c r="B34" s="80"/>
+      <c r="C34" s="82" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="87" t="s">
+      <c r="E34" s="96" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2100,13 +2109,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="95"/>
-      <c r="B35" s="95"/>
-      <c r="C35" s="94"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="83"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="88"/>
+      <c r="E35" s="97"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2115,13 +2124,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="95"/>
-      <c r="B36" s="95"/>
-      <c r="C36" s="94"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="83"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="77"/>
+      <c r="E36" s="84"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2130,9 +2139,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="95"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="76" t="s">
+      <c r="A37" s="80"/>
+      <c r="B37" s="80"/>
+      <c r="C37" s="82" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2151,9 +2160,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="95"/>
-      <c r="B38" s="95"/>
-      <c r="C38" s="77"/>
+      <c r="A38" s="80"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="84"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2170,8 +2179,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="81"/>
-      <c r="B39" s="81"/>
+      <c r="A39" s="86"/>
+      <c r="B39" s="86"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2206,13 +2215,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="99" t="s">
+      <c r="A41" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="82" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2231,16 +2240,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="100"/>
-      <c r="B42" s="95"/>
-      <c r="C42" s="94"/>
+      <c r="A42" s="78"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="83"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="76" t="s">
+      <c r="E42" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="78" t="s">
+      <c r="F42" s="98" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2248,22 +2257,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="100"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="94"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="83"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="77"/>
-      <c r="F43" s="79"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="101"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="100"/>
-      <c r="B44" s="90"/>
-      <c r="C44" s="90"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2278,9 +2287,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="100"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="77"/>
+      <c r="A45" s="78"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="84"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2301,47 +2310,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="100"/>
-      <c r="B46" s="90"/>
-      <c r="C46" s="76" t="s">
+      <c r="A46" s="78"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="82" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="76" t="s">
+      <c r="E46" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="78" t="s">
+      <c r="F46" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="80" t="s">
+      <c r="G46" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H46" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="80" t="s">
+      <c r="I46" s="79" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="100"/>
-      <c r="B47" s="90"/>
-      <c r="C47" s="92"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="81"/>
+      <c r="C47" s="85"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="77"/>
-      <c r="F47" s="79"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="101"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="100"/>
-      <c r="B48" s="90"/>
-      <c r="C48" s="76" t="s">
+      <c r="A48" s="78"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="82" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2358,9 +2367,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="100"/>
-      <c r="B49" s="90"/>
-      <c r="C49" s="77"/>
+      <c r="A49" s="78"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="84"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2375,9 +2384,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="100"/>
-      <c r="B50" s="90"/>
-      <c r="C50" s="76" t="s">
+      <c r="A50" s="78"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="82" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2386,7 +2395,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="80" t="s">
+      <c r="F50" s="79" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2394,16 +2403,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="100"/>
-      <c r="B51" s="90"/>
-      <c r="C51" s="92"/>
+      <c r="A51" s="78"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="85"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="81"/>
+      <c r="F51" s="86"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2420,13 +2429,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="76" t="s">
+      <c r="C53" s="82" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2443,13 +2452,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="95"/>
-      <c r="B54" s="95"/>
-      <c r="C54" s="94"/>
+      <c r="A54" s="80"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="83"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="76" t="s">
+      <c r="E54" s="82" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2460,13 +2469,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="95"/>
-      <c r="B55" s="95"/>
-      <c r="C55" s="94"/>
+      <c r="A55" s="80"/>
+      <c r="B55" s="80"/>
+      <c r="C55" s="83"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="77"/>
+      <c r="E55" s="84"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2475,9 +2484,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="90"/>
-      <c r="B56" s="90"/>
-      <c r="C56" s="76" t="s">
+      <c r="A56" s="81"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="82" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2494,9 +2503,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="90"/>
-      <c r="B57" s="90"/>
-      <c r="C57" s="77"/>
+      <c r="A57" s="81"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="84"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2511,8 +2520,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="90"/>
-      <c r="B58" s="90"/>
+      <c r="A58" s="81"/>
+      <c r="B58" s="81"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2530,9 +2539,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="90"/>
-      <c r="B59" s="90"/>
-      <c r="C59" s="76" t="s">
+      <c r="A59" s="81"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="82" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2549,9 +2558,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="90"/>
-      <c r="B60" s="90"/>
-      <c r="C60" s="90"/>
+      <c r="A60" s="81"/>
+      <c r="B60" s="81"/>
+      <c r="C60" s="81"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2566,9 +2575,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="90"/>
-      <c r="B61" s="90"/>
-      <c r="C61" s="90"/>
+      <c r="A61" s="81"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2583,9 +2592,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="77"/>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
+      <c r="A62" s="84"/>
+      <c r="B62" s="84"/>
+      <c r="C62" s="84"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2798,22 +2807,23 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2828,23 +2838,22 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19D470-567C-4E56-A854-9E32405D96CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D6BF9E-9ECD-4505-B62D-5820C2BBF27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1066,55 +1066,31 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1123,25 +1099,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1535,16 +1535,16 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="95" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="102" t="s">
+      <c r="D3" s="77" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -1558,9 +1558,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="95"/>
-      <c r="C4" s="92"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1586,13 +1586,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="82" t="s">
+      <c r="C6" s="78" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1609,10 +1609,10 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="102" t="s">
+      <c r="A7" s="88"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="77" t="s">
         <v>117</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -1626,9 +1626,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="84"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1643,15 +1643,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="82" t="s">
+      <c r="A9" s="88"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="78" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1674,13 +1674,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="81"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="84"/>
+      <c r="E10" s="79"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1689,9 +1689,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="84"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1706,8 +1706,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="91"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1725,9 +1725,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="87" t="s">
+      <c r="A13" s="88"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="98" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1744,16 +1744,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="90"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="88"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="93" t="s">
+      <c r="E14" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="86" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1761,14 +1761,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="90"/>
-      <c r="B15" s="91"/>
-      <c r="C15" s="89"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="91"/>
-      <c r="F15" s="95"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1785,13 +1785,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="78" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1808,10 +1808,10 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="90"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="102" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="77" t="s">
         <v>120</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -1825,9 +1825,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="90"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="85"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1842,15 +1842,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="90"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="82" t="s">
+      <c r="A20" s="88"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="78" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="78" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1867,13 +1867,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="83"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="96"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="84"/>
+      <c r="E21" s="79"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,9 +1882,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="91"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="85"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1899,8 +1899,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="91"/>
-      <c r="B23" s="91"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1918,8 +1918,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="91"/>
-      <c r="B24" s="91"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1937,15 +1937,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="91"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="82" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="78" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="92" t="s">
+      <c r="E25" s="95" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1956,13 +1956,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="85"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="92"/>
+      <c r="E26" s="95"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1982,13 +1982,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="79" t="s">
+      <c r="A28" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="82" t="s">
+      <c r="C28" s="78" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -2005,16 +2005,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="80"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="81"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="92"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="98" t="s">
+      <c r="F29" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2022,22 +2022,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="81"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="92"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="84"/>
-      <c r="F30" s="99"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="91"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="80"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="84"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2052,9 +2052,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="80"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="100" t="s">
+      <c r="A32" s="97"/>
+      <c r="B32" s="97"/>
+      <c r="C32" s="93" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2071,9 +2071,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="80"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="84"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="97"/>
+      <c r="C33" s="79"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2088,15 +2088,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="80"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="82" t="s">
+      <c r="A34" s="97"/>
+      <c r="B34" s="97"/>
+      <c r="C34" s="78" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="96" t="s">
+      <c r="E34" s="89" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2109,13 +2109,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="80"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="83"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="97"/>
+      <c r="C35" s="96"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="97"/>
+      <c r="E35" s="90"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2124,13 +2124,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="80"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="83"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="96"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="84"/>
+      <c r="E36" s="79"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2139,9 +2139,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="80"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="82" t="s">
+      <c r="A37" s="97"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="78" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2160,9 +2160,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="80"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="84"/>
+      <c r="A38" s="97"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="79"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2179,8 +2179,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="86"/>
-      <c r="B39" s="86"/>
+      <c r="A39" s="83"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2215,13 +2215,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="77" t="s">
+      <c r="A41" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="79" t="s">
+      <c r="B41" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="78" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2240,16 +2240,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="78"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="83"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="97"/>
+      <c r="C42" s="96"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="82" t="s">
+      <c r="E42" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="98" t="s">
+      <c r="F42" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2257,22 +2257,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="78"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="83"/>
+      <c r="A43" s="102"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="96"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="84"/>
-      <c r="F43" s="101"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="81"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="78"/>
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
+      <c r="A44" s="102"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="92"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2287,9 +2287,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="78"/>
-      <c r="B45" s="81"/>
-      <c r="C45" s="84"/>
+      <c r="A45" s="102"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="79"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2310,47 +2310,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="78"/>
-      <c r="B46" s="81"/>
-      <c r="C46" s="82" t="s">
+      <c r="A46" s="102"/>
+      <c r="B46" s="92"/>
+      <c r="C46" s="78" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="82" t="s">
+      <c r="E46" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="98" t="s">
+      <c r="F46" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="79" t="s">
+      <c r="G46" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="79" t="s">
+      <c r="H46" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="79" t="s">
+      <c r="I46" s="82" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="78"/>
-      <c r="B47" s="81"/>
-      <c r="C47" s="85"/>
+      <c r="A47" s="102"/>
+      <c r="B47" s="92"/>
+      <c r="C47" s="94"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="84"/>
-      <c r="F47" s="101"/>
-      <c r="G47" s="84"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="84"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="79"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="78"/>
-      <c r="B48" s="81"/>
-      <c r="C48" s="82" t="s">
+      <c r="A48" s="102"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="78" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2367,9 +2367,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="78"/>
-      <c r="B49" s="81"/>
-      <c r="C49" s="84"/>
+      <c r="A49" s="102"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="79"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2384,9 +2384,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="78"/>
-      <c r="B50" s="81"/>
-      <c r="C50" s="82" t="s">
+      <c r="A50" s="102"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="78" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2395,7 +2395,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="79" t="s">
+      <c r="F50" s="82" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2403,16 +2403,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="78"/>
-      <c r="B51" s="81"/>
-      <c r="C51" s="85"/>
+      <c r="A51" s="102"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="94"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="86"/>
+      <c r="F51" s="83"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2429,13 +2429,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="79" t="s">
+      <c r="A53" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="79" t="s">
+      <c r="B53" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="82" t="s">
+      <c r="C53" s="78" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2452,13 +2452,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="80"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="83"/>
+      <c r="A54" s="97"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="96"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="82" t="s">
+      <c r="E54" s="78" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2469,13 +2469,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="80"/>
-      <c r="B55" s="80"/>
-      <c r="C55" s="83"/>
+      <c r="A55" s="97"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="96"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="84"/>
+      <c r="E55" s="79"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2484,9 +2484,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="81"/>
-      <c r="B56" s="81"/>
-      <c r="C56" s="82" t="s">
+      <c r="A56" s="92"/>
+      <c r="B56" s="92"/>
+      <c r="C56" s="78" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2503,9 +2503,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="81"/>
-      <c r="B57" s="81"/>
-      <c r="C57" s="84"/>
+      <c r="A57" s="92"/>
+      <c r="B57" s="92"/>
+      <c r="C57" s="79"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2520,8 +2520,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="81"/>
-      <c r="B58" s="81"/>
+      <c r="A58" s="92"/>
+      <c r="B58" s="92"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2539,9 +2539,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="81"/>
-      <c r="B59" s="81"/>
-      <c r="C59" s="82" t="s">
+      <c r="A59" s="92"/>
+      <c r="B59" s="92"/>
+      <c r="C59" s="78" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2558,9 +2558,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="81"/>
-      <c r="B60" s="81"/>
-      <c r="C60" s="81"/>
+      <c r="A60" s="92"/>
+      <c r="B60" s="92"/>
+      <c r="C60" s="92"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2575,9 +2575,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="81"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
+      <c r="A61" s="92"/>
+      <c r="B61" s="92"/>
+      <c r="C61" s="92"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2592,9 +2592,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="84"/>
-      <c r="B62" s="84"/>
-      <c r="C62" s="84"/>
+      <c r="A62" s="79"/>
+      <c r="B62" s="79"/>
+      <c r="C62" s="79"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2807,23 +2807,22 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2838,22 +2837,23 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -1069,80 +1069,80 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1535,13 +1535,13 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="95" t="s">
+      <c r="C3" s="93" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="77" t="s">
@@ -1558,9 +1558,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1586,13 +1586,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="78" t="s">
+      <c r="C6" s="83" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1609,9 +1609,9 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="92"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="77" t="s">
         <v>117</v>
       </c>
@@ -1626,9 +1626,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="91"/>
+      <c r="B8" s="92"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1643,15 +1643,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="78" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="83" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="83" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1674,13 +1674,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="92"/>
+      <c r="A10" s="91"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="82"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="79"/>
+      <c r="E10" s="85"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1689,9 +1689,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="79"/>
+      <c r="A11" s="91"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1706,8 +1706,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="85"/>
+      <c r="A12" s="91"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1725,9 +1725,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="98" t="s">
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="88" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1744,16 +1744,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="99"/>
+      <c r="A14" s="91"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="89"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="86" t="s">
+      <c r="F14" s="95" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1761,14 +1761,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="100"/>
+      <c r="A15" s="91"/>
+      <c r="B15" s="92"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="87"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="96"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1785,13 +1785,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="78" t="s">
+      <c r="C17" s="83" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1808,9 +1808,9 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="96"/>
+      <c r="A18" s="91"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="84"/>
       <c r="D18" s="77" t="s">
         <v>120</v>
       </c>
@@ -1825,9 +1825,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="94"/>
+      <c r="A19" s="91"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="86"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1842,15 +1842,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="78" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="83" t="s">
         <v>112</v>
       </c>
       <c r="D20" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="83" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1867,13 +1867,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="96"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="84"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="79"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,9 +1882,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="94"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1899,8 +1899,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="85"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1918,8 +1918,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="85"/>
-      <c r="B24" s="85"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1937,15 +1937,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="78" t="s">
+      <c r="A25" s="92"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="83" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="95" t="s">
+      <c r="E25" s="93" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1956,13 +1956,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="85"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="94"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="86"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="95"/>
+      <c r="E26" s="93"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1982,13 +1982,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="82" t="s">
+      <c r="A28" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="82" t="s">
+      <c r="B28" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="78" t="s">
+      <c r="C28" s="83" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -2005,16 +2005,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="97"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="92"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="78" t="s">
+      <c r="E29" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="80" t="s">
+      <c r="F29" s="99" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2022,22 +2022,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="97"/>
-      <c r="B30" s="97"/>
-      <c r="C30" s="92"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="82"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="91"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="100"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="97"/>
-      <c r="B31" s="97"/>
-      <c r="C31" s="79"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="85"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2052,9 +2052,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="97"/>
-      <c r="B32" s="97"/>
-      <c r="C32" s="93" t="s">
+      <c r="A32" s="81"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="101" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2071,9 +2071,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="97"/>
-      <c r="B33" s="97"/>
-      <c r="C33" s="79"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="85"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2088,15 +2088,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="97"/>
-      <c r="B34" s="97"/>
-      <c r="C34" s="78" t="s">
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="83" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="89" t="s">
+      <c r="E34" s="97" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2109,13 +2109,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="97"/>
-      <c r="B35" s="97"/>
-      <c r="C35" s="96"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="84"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="90"/>
+      <c r="E35" s="98"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2124,13 +2124,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="97"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="96"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="84"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="79"/>
+      <c r="E36" s="85"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2139,9 +2139,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="97"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="78" t="s">
+      <c r="A37" s="81"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="83" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2160,9 +2160,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="97"/>
-      <c r="B38" s="97"/>
-      <c r="C38" s="79"/>
+      <c r="A38" s="81"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="85"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2179,8 +2179,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="83"/>
-      <c r="B39" s="83"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2215,13 +2215,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="101" t="s">
+      <c r="A41" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="82" t="s">
+      <c r="B41" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="78" t="s">
+      <c r="C41" s="83" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2240,16 +2240,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="102"/>
-      <c r="B42" s="97"/>
-      <c r="C42" s="96"/>
+      <c r="A42" s="79"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="84"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="78" t="s">
+      <c r="E42" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="80" t="s">
+      <c r="F42" s="99" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2257,22 +2257,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="102"/>
-      <c r="B43" s="97"/>
-      <c r="C43" s="96"/>
+      <c r="A43" s="79"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="84"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="79"/>
-      <c r="F43" s="81"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="102"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="102"/>
-      <c r="B44" s="92"/>
-      <c r="C44" s="92"/>
+      <c r="A44" s="79"/>
+      <c r="B44" s="82"/>
+      <c r="C44" s="82"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2287,9 +2287,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="102"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="79"/>
+      <c r="A45" s="79"/>
+      <c r="B45" s="82"/>
+      <c r="C45" s="85"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2310,47 +2310,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="102"/>
-      <c r="B46" s="92"/>
-      <c r="C46" s="78" t="s">
+      <c r="A46" s="79"/>
+      <c r="B46" s="82"/>
+      <c r="C46" s="83" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="78" t="s">
+      <c r="E46" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="80" t="s">
+      <c r="F46" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="82" t="s">
+      <c r="G46" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="82" t="s">
+      <c r="H46" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="82" t="s">
+      <c r="I46" s="80" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="102"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="94"/>
+      <c r="A47" s="79"/>
+      <c r="B47" s="82"/>
+      <c r="C47" s="86"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="79"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="79"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="102"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="102"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="78" t="s">
+      <c r="A48" s="79"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="83" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2367,9 +2367,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="102"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="79"/>
+      <c r="A49" s="79"/>
+      <c r="B49" s="82"/>
+      <c r="C49" s="85"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2384,9 +2384,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="102"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="78" t="s">
+      <c r="A50" s="79"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="83" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2395,7 +2395,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="82" t="s">
+      <c r="F50" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2403,16 +2403,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="102"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="94"/>
+      <c r="A51" s="79"/>
+      <c r="B51" s="82"/>
+      <c r="C51" s="86"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="83"/>
+      <c r="F51" s="87"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2429,13 +2429,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="82" t="s">
+      <c r="A53" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="82" t="s">
+      <c r="B53" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="78" t="s">
+      <c r="C53" s="83" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2452,13 +2452,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="97"/>
-      <c r="B54" s="97"/>
-      <c r="C54" s="96"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="84"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="78" t="s">
+      <c r="E54" s="83" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2469,13 +2469,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="97"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="96"/>
+      <c r="A55" s="81"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="84"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="79"/>
+      <c r="E55" s="85"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2484,9 +2484,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
-      <c r="B56" s="92"/>
-      <c r="C56" s="78" t="s">
+      <c r="A56" s="82"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="83" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2503,9 +2503,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
-      <c r="B57" s="92"/>
-      <c r="C57" s="79"/>
+      <c r="A57" s="82"/>
+      <c r="B57" s="82"/>
+      <c r="C57" s="85"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2520,8 +2520,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
-      <c r="B58" s="92"/>
+      <c r="A58" s="82"/>
+      <c r="B58" s="82"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2539,9 +2539,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="92"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="78" t="s">
+      <c r="A59" s="82"/>
+      <c r="B59" s="82"/>
+      <c r="C59" s="83" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2558,9 +2558,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="92"/>
-      <c r="B60" s="92"/>
-      <c r="C60" s="92"/>
+      <c r="A60" s="82"/>
+      <c r="B60" s="82"/>
+      <c r="C60" s="82"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2575,9 +2575,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
-      <c r="B61" s="92"/>
-      <c r="C61" s="92"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2592,9 +2592,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="79"/>
-      <c r="B62" s="79"/>
-      <c r="C62" s="79"/>
+      <c r="A62" s="85"/>
+      <c r="B62" s="85"/>
+      <c r="C62" s="85"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2807,22 +2807,23 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2837,23 +2838,22 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D6BF9E-9ECD-4505-B62D-5820C2BBF27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88501FD5-1FDE-42AD-838E-D09DB1F32EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1069,55 +1069,28 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1126,23 +1099,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1535,13 +1535,13 @@
       <c r="I2" s="46"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="91" t="s">
+      <c r="B3" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="95" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="77" t="s">
@@ -1558,9 +1558,9 @@
       <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="93"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
@@ -1586,13 +1586,13 @@
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="78" t="s">
         <v>89</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1609,9 +1609,9 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="82"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="92"/>
       <c r="D7" s="77" t="s">
         <v>117</v>
       </c>
@@ -1626,9 +1626,9 @@
       <c r="I7" s="51"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="91"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="85"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="12" t="s">
         <v>118</v>
       </c>
@@ -1643,15 +1643,15 @@
       <c r="I8" s="52"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="83" t="s">
+      <c r="A9" s="88"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="78" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="78" t="s">
         <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1674,13 +1674,13 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="82"/>
+      <c r="A10" s="88"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="85"/>
+      <c r="E10" s="79"/>
       <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
@@ -1689,9 +1689,9 @@
       <c r="I10" s="69"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="85"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="12" t="s">
         <v>42</v>
       </c>
@@ -1706,8 +1706,8 @@
       <c r="I11" s="51"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="92"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="55" t="s">
         <v>110</v>
       </c>
@@ -1725,9 +1725,9 @@
       <c r="I12" s="51"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="88" t="s">
+      <c r="A13" s="88"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="98" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="44" t="s">
@@ -1744,16 +1744,16 @@
       <c r="I13" s="51"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="89"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="94" t="s">
+      <c r="E14" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="95" t="s">
+      <c r="F14" s="86" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="40"/>
@@ -1761,14 +1761,14 @@
       <c r="I14" s="51"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="90"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="92"/>
-      <c r="F15" s="96"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="40"/>
       <c r="H15" s="1"/>
       <c r="I15" s="51"/>
@@ -1785,13 +1785,13 @@
       <c r="I16" s="51"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="78" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="12" t="s">
@@ -1808,9 +1808,9 @@
       <c r="I17" s="51"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="84"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="96"/>
       <c r="D18" s="77" t="s">
         <v>120</v>
       </c>
@@ -1825,9 +1825,9 @@
       <c r="I18" s="51"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="86"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="12" t="s">
         <v>91</v>
       </c>
@@ -1842,15 +1842,15 @@
       <c r="I19" s="52"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="83" t="s">
+      <c r="A20" s="88"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="78" t="s">
         <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1867,13 +1867,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="84"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="96"/>
       <c r="D21" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="85"/>
+      <c r="E21" s="79"/>
       <c r="F21" s="9" t="s">
         <v>14</v>
       </c>
@@ -1882,9 +1882,9 @@
       <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="86"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="12" t="s">
         <v>42</v>
       </c>
@@ -1899,8 +1899,8 @@
       <c r="I22" s="51"/>
     </row>
     <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="85"/>
       <c r="C23" s="11" t="s">
         <v>121</v>
       </c>
@@ -1918,8 +1918,8 @@
       <c r="I23" s="51"/>
     </row>
     <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="85"/>
       <c r="C24" s="11" t="s">
         <v>61</v>
       </c>
@@ -1937,15 +1937,15 @@
       <c r="I24" s="51"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="83" t="s">
+      <c r="A25" s="85"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="78" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="95" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -1956,13 +1956,13 @@
       <c r="I25" s="51"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="86"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="93"/>
+      <c r="E26" s="95"/>
       <c r="F26" s="10" t="s">
         <v>8</v>
       </c>
@@ -1982,13 +1982,13 @@
       <c r="I27" s="41"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="83" t="s">
+      <c r="C28" s="78" t="s">
         <v>90</v>
       </c>
       <c r="D28" s="12" t="s">
@@ -2005,16 +2005,16 @@
       <c r="I28" s="41"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="81"/>
-      <c r="B29" s="81"/>
-      <c r="C29" s="82"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="92"/>
       <c r="D29" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="F29" s="99" t="s">
+      <c r="F29" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G29" s="40"/>
@@ -2022,22 +2022,22 @@
       <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="81"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="82"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="92"/>
       <c r="D30" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="85"/>
-      <c r="F30" s="100"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="91"/>
       <c r="G30" s="40"/>
       <c r="H30" s="3"/>
       <c r="I30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="81"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="85"/>
+      <c r="A31" s="97"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="12" t="s">
         <v>92</v>
       </c>
@@ -2052,9 +2052,9 @@
       <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="81"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="101" t="s">
+      <c r="A32" s="97"/>
+      <c r="B32" s="97"/>
+      <c r="C32" s="93" t="s">
         <v>130</v>
       </c>
       <c r="D32" s="12" t="s">
@@ -2071,9 +2071,9 @@
       <c r="I32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="81"/>
-      <c r="B33" s="81"/>
-      <c r="C33" s="85"/>
+      <c r="A33" s="97"/>
+      <c r="B33" s="97"/>
+      <c r="C33" s="79"/>
       <c r="D33" s="12" t="s">
         <v>131</v>
       </c>
@@ -2088,15 +2088,15 @@
       <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="81"/>
-      <c r="B34" s="81"/>
-      <c r="C34" s="83" t="s">
+      <c r="A34" s="97"/>
+      <c r="B34" s="97"/>
+      <c r="C34" s="78" t="s">
         <v>113</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E34" s="97" t="s">
+      <c r="E34" s="89" t="s">
         <v>123</v>
       </c>
       <c r="F34" s="72" t="s">
@@ -2109,13 +2109,13 @@
       <c r="I34" s="41"/>
     </row>
     <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="81"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="84"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="97"/>
+      <c r="C35" s="96"/>
       <c r="D35" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="98"/>
+      <c r="E35" s="90"/>
       <c r="F35" s="72" t="s">
         <v>10</v>
       </c>
@@ -2124,13 +2124,13 @@
       <c r="I35" s="41"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="81"/>
-      <c r="B36" s="81"/>
-      <c r="C36" s="84"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="97"/>
+      <c r="C36" s="96"/>
       <c r="D36" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="85"/>
+      <c r="E36" s="79"/>
       <c r="F36" s="72" t="s">
         <v>10</v>
       </c>
@@ -2139,9 +2139,9 @@
       <c r="I36" s="41"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="81"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="83" t="s">
+      <c r="A37" s="97"/>
+      <c r="B37" s="97"/>
+      <c r="C37" s="78" t="s">
         <v>133</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -2160,9 +2160,9 @@
       <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="81"/>
-      <c r="B38" s="81"/>
-      <c r="C38" s="85"/>
+      <c r="A38" s="97"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="79"/>
       <c r="D38" s="12" t="s">
         <v>135</v>
       </c>
@@ -2179,8 +2179,8 @@
       <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
+      <c r="A39" s="83"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="32" t="s">
         <v>96</v>
       </c>
@@ -2215,13 +2215,13 @@
       <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="78" t="s">
+      <c r="A41" s="101" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="82" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="78" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -2240,16 +2240,16 @@
       <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="79"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="84"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="97"/>
+      <c r="C42" s="96"/>
       <c r="D42" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="83" t="s">
+      <c r="E42" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="F42" s="99" t="s">
+      <c r="F42" s="80" t="s">
         <v>8</v>
       </c>
       <c r="G42" s="40"/>
@@ -2257,22 +2257,22 @@
       <c r="I42" s="41"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="79"/>
-      <c r="B43" s="81"/>
-      <c r="C43" s="84"/>
+      <c r="A43" s="102"/>
+      <c r="B43" s="97"/>
+      <c r="C43" s="96"/>
       <c r="D43" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="85"/>
-      <c r="F43" s="102"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="81"/>
       <c r="G43" s="40"/>
       <c r="H43" s="3"/>
       <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="79"/>
-      <c r="B44" s="82"/>
-      <c r="C44" s="82"/>
+      <c r="A44" s="102"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="92"/>
       <c r="D44" s="12" t="s">
         <v>64</v>
       </c>
@@ -2287,9 +2287,9 @@
       <c r="I44" s="43"/>
     </row>
     <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="79"/>
-      <c r="B45" s="82"/>
-      <c r="C45" s="85"/>
+      <c r="A45" s="102"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="79"/>
       <c r="D45" s="12" t="s">
         <v>28</v>
       </c>
@@ -2310,47 +2310,47 @@
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="79"/>
-      <c r="B46" s="82"/>
-      <c r="C46" s="83" t="s">
+      <c r="A46" s="102"/>
+      <c r="B46" s="92"/>
+      <c r="C46" s="78" t="s">
         <v>104</v>
       </c>
       <c r="D46" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="83" t="s">
+      <c r="E46" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="F46" s="99" t="s">
+      <c r="F46" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="G46" s="80" t="s">
+      <c r="G46" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H46" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I46" s="80" t="s">
+      <c r="I46" s="82" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="79"/>
-      <c r="B47" s="82"/>
-      <c r="C47" s="86"/>
+      <c r="A47" s="102"/>
+      <c r="B47" s="92"/>
+      <c r="C47" s="94"/>
       <c r="D47" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="E47" s="85"/>
-      <c r="F47" s="102"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="79"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="79"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="83" t="s">
+      <c r="A48" s="102"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="78" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="26" t="s">
@@ -2367,9 +2367,9 @@
       <c r="I48" s="37"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="79"/>
-      <c r="B49" s="82"/>
-      <c r="C49" s="85"/>
+      <c r="A49" s="102"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="79"/>
       <c r="D49" s="26" t="s">
         <v>143</v>
       </c>
@@ -2384,9 +2384,9 @@
       <c r="I49" s="41"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="79"/>
-      <c r="B50" s="82"/>
-      <c r="C50" s="83" t="s">
+      <c r="A50" s="102"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="78" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="26" t="s">
@@ -2395,7 +2395,7 @@
       <c r="E50" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="F50" s="80" t="s">
+      <c r="F50" s="82" t="s">
         <v>8</v>
       </c>
       <c r="G50" s="63"/>
@@ -2403,16 +2403,16 @@
       <c r="I50" s="41"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="79"/>
-      <c r="B51" s="82"/>
-      <c r="C51" s="86"/>
+      <c r="A51" s="102"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="94"/>
       <c r="D51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="87"/>
+      <c r="F51" s="83"/>
       <c r="G51" s="63"/>
       <c r="H51" s="3"/>
       <c r="I51" s="41"/>
@@ -2429,13 +2429,13 @@
       <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="83" t="s">
+      <c r="C53" s="78" t="s">
         <v>115</v>
       </c>
       <c r="D53" s="23" t="s">
@@ -2452,13 +2452,13 @@
       <c r="I53" s="51"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="81"/>
-      <c r="B54" s="81"/>
-      <c r="C54" s="84"/>
+      <c r="A54" s="97"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="96"/>
       <c r="D54" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="E54" s="83" t="s">
+      <c r="E54" s="78" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="75" t="s">
@@ -2469,13 +2469,13 @@
       <c r="I54" s="51"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="81"/>
-      <c r="B55" s="81"/>
-      <c r="C55" s="84"/>
+      <c r="A55" s="97"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="96"/>
       <c r="D55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="85"/>
+      <c r="E55" s="79"/>
       <c r="F55" s="8" t="s">
         <v>8</v>
       </c>
@@ -2484,9 +2484,9 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="82"/>
-      <c r="B56" s="82"/>
-      <c r="C56" s="83" t="s">
+      <c r="A56" s="92"/>
+      <c r="B56" s="92"/>
+      <c r="C56" s="78" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="12" t="s">
@@ -2503,9 +2503,9 @@
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="82"/>
-      <c r="B57" s="82"/>
-      <c r="C57" s="85"/>
+      <c r="A57" s="92"/>
+      <c r="B57" s="92"/>
+      <c r="C57" s="79"/>
       <c r="D57" s="12" t="s">
         <v>85</v>
       </c>
@@ -2520,8 +2520,8 @@
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="82"/>
-      <c r="B58" s="82"/>
+      <c r="A58" s="92"/>
+      <c r="B58" s="92"/>
       <c r="C58" s="11" t="s">
         <v>152</v>
       </c>
@@ -2539,9 +2539,9 @@
       <c r="I58" s="67"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="82"/>
-      <c r="B59" s="82"/>
-      <c r="C59" s="83" t="s">
+      <c r="A59" s="92"/>
+      <c r="B59" s="92"/>
+      <c r="C59" s="78" t="s">
         <v>77</v>
       </c>
       <c r="D59" s="12" t="s">
@@ -2558,9 +2558,9 @@
       <c r="I59" s="67"/>
     </row>
     <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="82"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="82"/>
+      <c r="A60" s="92"/>
+      <c r="B60" s="92"/>
+      <c r="C60" s="92"/>
       <c r="D60" s="12" t="s">
         <v>78</v>
       </c>
@@ -2575,9 +2575,9 @@
       <c r="I60" s="51"/>
     </row>
     <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="82"/>
-      <c r="B61" s="82"/>
-      <c r="C61" s="82"/>
+      <c r="A61" s="92"/>
+      <c r="B61" s="92"/>
+      <c r="C61" s="92"/>
       <c r="D61" s="12" t="s">
         <v>153</v>
       </c>
@@ -2592,9 +2592,9 @@
       <c r="I61" s="51"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="85"/>
-      <c r="B62" s="85"/>
-      <c r="C62" s="85"/>
+      <c r="A62" s="79"/>
+      <c r="B62" s="79"/>
+      <c r="C62" s="79"/>
       <c r="D62" s="12" t="s">
         <v>79</v>
       </c>
@@ -2807,23 +2807,22 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B41:B51"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="A53:A62"/>
+    <mergeCell ref="C59:C62"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="A28:A39"/>
+    <mergeCell ref="B28:B39"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C25:C26"/>
     <mergeCell ref="B17:B26"/>
@@ -2838,22 +2837,23 @@
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
     <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88501FD5-1FDE-42AD-838E-D09DB1F32EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A6D1DD-403C-484A-868D-AFD36FB85F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
   <si>
     <t>User Story</t>
   </si>
@@ -140,24 +140,9 @@
     <t>Verify if new User can Register using own valid credentials</t>
   </si>
   <si>
-    <t>Register without Selecting a country</t>
-  </si>
-  <si>
-    <t>Register without Selecting a gender option</t>
-  </si>
-  <si>
-    <t>Register without Selecting agreement option</t>
-  </si>
-  <si>
     <t>missing</t>
   </si>
   <si>
-    <t>Verify if new User cannot Register without Selecting select options</t>
-  </si>
-  <si>
-    <t>existing email!</t>
-  </si>
-  <si>
     <t>US005.</t>
   </si>
   <si>
@@ -245,9 +230,6 @@
     <t>Enter credentials and Login</t>
   </si>
   <si>
-    <t>Enter credentials and Register</t>
-  </si>
-  <si>
     <t>As a User, I want to check an MD's booking calendar for an appointment so that I can book a suitable one</t>
   </si>
   <si>
@@ -305,9 +287,6 @@
     <t xml:space="preserve">invalid </t>
   </si>
   <si>
-    <t xml:space="preserve"> =&gt; </t>
-  </si>
-  <si>
     <t>Verify if new User can Open Register page and the required elements of the page are visible</t>
   </si>
   <si>
@@ -320,12 +299,6 @@
     <t>Open Doctors Page Displays the proper elements of this page</t>
   </si>
   <si>
-    <t xml:space="preserve"> Registration with missing details</t>
-  </si>
-  <si>
-    <t>Registration without selecting/aggreeing  options has possible legal consequences</t>
-  </si>
-  <si>
     <t>Check that Logout button works properly closing the profile</t>
   </si>
   <si>
@@ -507,6 +480,9 @@
   </si>
   <si>
     <t>Cancelling appointment irreversible</t>
+  </si>
+  <si>
+    <t>Enter credentials Select options and Register</t>
   </si>
 </sst>
 </file>
@@ -599,7 +575,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -620,12 +596,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -838,7 +808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -909,9 +879,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -969,12 +936,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -996,7 +957,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1015,12 +975,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1044,12 +998,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1066,36 +1014,24 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1108,41 +1044,78 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1478,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1495,7 +1468,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="15" t="s">
@@ -1513,124 +1486,124 @@
       <c r="F1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="37" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="58"/>
+      <c r="A2" s="54"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="46"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="77" t="s">
+      <c r="B3" s="76" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="60" t="s">
+      <c r="E3" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="40"/>
+      <c r="G3" s="39"/>
       <c r="H3" s="3"/>
-      <c r="I3" s="41"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="95"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="82"/>
       <c r="D4" s="12" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="40"/>
+      <c r="G4" s="39"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="41"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="59"/>
+      <c r="A5" s="55"/>
       <c r="B5" s="21"/>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
       <c r="E5" s="20"/>
-      <c r="F5" s="27"/>
+      <c r="F5" s="26"/>
       <c r="G5" s="1"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="41"/>
+      <c r="I5" s="40"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="88" t="s">
+      <c r="B6" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="78" t="s">
-        <v>89</v>
+      <c r="C6" s="70" t="s">
+        <v>82</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="40"/>
+      <c r="G6" s="39"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="41"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="77" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="A7" s="76"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="40"/>
+      <c r="G7" s="39"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="51"/>
+      <c r="I7" s="48"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="76"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="71"/>
       <c r="D8" s="12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>31</v>
@@ -1638,1005 +1611,973 @@
       <c r="F8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="52"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="49"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="78" t="s">
+      <c r="A9" s="76"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="76" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="D9" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="E9" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="95" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="76"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="93"/>
+      <c r="F10" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="63"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="76"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="39"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="76"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="39"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="48"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="55"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="39"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="48"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="76"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="39"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="48"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="76"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="41"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="49"/>
+    </row>
+    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="76"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="F17" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="90" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="K9" s="53" t="s">
+      <c r="I17" s="90" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="76"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="93"/>
+      <c r="F18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="56"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="36"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="74"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="39"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="69"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="51"/>
-    </row>
-    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="51"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="98" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="51"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="84" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="86" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="51"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="51"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="51"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="51"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="51"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="42"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="52"/>
-    </row>
-    <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="78" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="74"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="78" t="s">
+      <c r="D20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="39"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="48"/>
+    </row>
+    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="74"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="39"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="48"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="10" t="s">
+      <c r="G22" s="39"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="48"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="74"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="82"/>
+      <c r="F23" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="39"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="48"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="26"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="40"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="40"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="84"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="39"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="40"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="84"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="71"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="40"/>
+    </row>
+    <row r="28" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="84"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="39"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="40"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="84"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="80" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="39"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="40"/>
+    </row>
+    <row r="30" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="84"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="39"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="40"/>
+    </row>
+    <row r="31" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="84"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="57"/>
+      <c r="H31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I31" s="40"/>
+    </row>
+    <row r="32" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="84"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="78"/>
+      <c r="F32" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="40"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="84"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="71"/>
+      <c r="F33" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="39"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="40"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="84"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="70" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="39"/>
+      <c r="H34" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="I34" s="40"/>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="84"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="41"/>
+      <c r="H35" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" s="42"/>
+    </row>
+    <row r="36" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="73"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="79"/>
-      <c r="F21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="62"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="37"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="40"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="51"/>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="40"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="51"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="85"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="51"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="78" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E25" s="95" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="40"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="51"/>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="85"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="95"/>
-      <c r="F26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="51"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="41"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="82" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="40"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="41"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="97"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="40"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="41"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="97"/>
-      <c r="B30" s="97"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="26" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="36"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="86" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="41"/>
-    </row>
-    <row r="31" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="97"/>
-      <c r="B31" s="97"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="40"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="41"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="97"/>
-      <c r="B32" s="97"/>
-      <c r="C32" s="93" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="40"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="41"/>
-    </row>
-    <row r="33" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="97"/>
-      <c r="B33" s="97"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="40"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="41"/>
-    </row>
-    <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="97"/>
-      <c r="B34" s="97"/>
-      <c r="C34" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" s="89" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="63"/>
-      <c r="H34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I34" s="41"/>
-    </row>
-    <row r="35" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="97"/>
-      <c r="B35" s="97"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" s="90"/>
-      <c r="F35" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="40"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="41"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="97"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="79"/>
-      <c r="F36" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="40"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="41"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="97"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="78" t="s">
-        <v>133</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="40"/>
-      <c r="H37" s="73" t="s">
-        <v>134</v>
-      </c>
-      <c r="I37" s="41"/>
-    </row>
-    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="97"/>
-      <c r="B38" s="97"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="32" t="s">
-        <v>99</v>
+      <c r="E38" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="42"/>
-      <c r="H38" s="74" t="s">
+      <c r="G38" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="40"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="87"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="39"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="40"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="87"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="71"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="40"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="87"/>
+      <c r="B41" s="79"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="41"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="42"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="87"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="96" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="96" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="87"/>
+      <c r="B43" s="79"/>
+      <c r="C43" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="100" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="100" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="100" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="87"/>
+      <c r="B44" s="79"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="71"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="85"/>
+      <c r="H44" s="85"/>
+      <c r="I44" s="85"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="87"/>
+      <c r="B45" s="79"/>
+      <c r="C45" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F45" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="56"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="36"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="87"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="I38" s="43"/>
-    </row>
-    <row r="39" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="83"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="32" t="s">
+      <c r="E46" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="57"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="40"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="87"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="100" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="57"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="40"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="87"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F39" s="9" t="s">
+      <c r="F48" s="102"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="40"/>
+    </row>
+    <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="55"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="40"/>
+    </row>
+    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="C50" s="70" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="58"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="48"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="84"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="58"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="48"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="84"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" s="71"/>
+      <c r="F52" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="58"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="48"/>
+    </row>
+    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="79"/>
+      <c r="B53" s="79"/>
+      <c r="C53" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="39"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="60"/>
+    </row>
+    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="79"/>
+      <c r="B54" s="79"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="39"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="60"/>
+    </row>
+    <row r="55" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="79"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="37"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="82" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>101</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F41" s="9" t="s">
+      <c r="G55" s="39"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="61"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="79"/>
+      <c r="B56" s="79"/>
+      <c r="C56" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G41" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="41"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="102"/>
-      <c r="B42" s="97"/>
-      <c r="C42" s="96"/>
-      <c r="D42" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E42" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="40"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="41"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="102"/>
-      <c r="B43" s="97"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E43" s="79"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="41"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="102"/>
-      <c r="B44" s="92"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="42"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="43"/>
-    </row>
-    <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="102"/>
-      <c r="B45" s="92"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="102"/>
-      <c r="B46" s="92"/>
-      <c r="C46" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="F46" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="G46" s="82" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="82" t="s">
-        <v>25</v>
-      </c>
-      <c r="I46" s="82" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="102"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="94"/>
-      <c r="D47" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" s="79"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="79"/>
-      <c r="H47" s="79"/>
-      <c r="I47" s="79"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="102"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="62"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="37"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="102"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="79"/>
-      <c r="D49" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="F49" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="63"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="41"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="102"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="F50" s="82" t="s">
-        <v>8</v>
-      </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="41"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="102"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="94"/>
-      <c r="D51" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="83"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="41"/>
-    </row>
-    <row r="52" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="41"/>
-    </row>
-    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53" s="82" t="s">
-        <v>114</v>
-      </c>
-      <c r="C53" s="78" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="F53" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="64"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="51"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="97"/>
-      <c r="B54" s="97"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E54" s="78" t="s">
-        <v>76</v>
-      </c>
-      <c r="F54" s="75" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="64"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="51"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="97"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="E55" s="79"/>
-      <c r="F55" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G55" s="64"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="51"/>
-    </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
-      <c r="B56" s="92"/>
-      <c r="C56" s="78" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G56" s="40"/>
-      <c r="H56" s="65"/>
-      <c r="I56" s="66"/>
-    </row>
-    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
-      <c r="B57" s="92"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="61"/>
+    </row>
+    <row r="57" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="79"/>
+      <c r="B57" s="79"/>
       <c r="C57" s="79"/>
       <c r="D57" s="12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="40"/>
-      <c r="H57" s="65"/>
-      <c r="I57" s="66"/>
-    </row>
-    <row r="58" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
-      <c r="B58" s="92"/>
-      <c r="C58" s="11" t="s">
-        <v>152</v>
-      </c>
+      <c r="G57" s="39"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="48"/>
+    </row>
+    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="79"/>
+      <c r="B58" s="79"/>
+      <c r="C58" s="79"/>
       <c r="D58" s="12" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G58" s="40"/>
+        <v>10</v>
+      </c>
+      <c r="G58" s="39"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="67"/>
+      <c r="I58" s="48"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="92"/>
-      <c r="B59" s="92"/>
-      <c r="C59" s="78" t="s">
-        <v>77</v>
-      </c>
+      <c r="A59" s="71"/>
+      <c r="B59" s="71"/>
+      <c r="C59" s="71"/>
       <c r="D59" s="12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G59" s="40"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="67"/>
-    </row>
-    <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="92"/>
-      <c r="B60" s="92"/>
-      <c r="C60" s="92"/>
-      <c r="D60" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G60" s="40"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="51"/>
-    </row>
-    <row r="61" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
-      <c r="B61" s="92"/>
-      <c r="C61" s="92"/>
-      <c r="D61" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="40"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="47"/>
+      <c r="I59" s="49"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="62"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="30"/>
+    </row>
+    <row r="61" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="2"/>
+      <c r="E61" s="5"/>
+      <c r="G61" s="2"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="51"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="79"/>
-      <c r="B62" s="79"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="42"/>
-      <c r="H62" s="50"/>
-      <c r="I62" s="52"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="31"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="31"/>
-    </row>
-    <row r="64" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="2"/>
+      <c r="E62" s="5"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="2"/>
+      <c r="E63" s="5"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B64" s="2"/>
       <c r="E64" s="5"/>
-      <c r="G64" s="2"/>
+      <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B65" s="2"/>
       <c r="E65" s="5"/>
-      <c r="G65" s="1"/>
+      <c r="G65" s="2"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="E66" s="5"/>
-      <c r="G66" s="2"/>
+      <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
@@ -2645,17 +2586,14 @@
       <c r="E67" s="5"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
-      <c r="I67" s="2"/>
+      <c r="I67" s="1"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B68" s="2"/>
-      <c r="E68" s="5"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="B68" s="3"/>
+      <c r="E68" s="7"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
+      <c r="B69" s="3"/>
       <c r="E69" s="5"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -2663,17 +2601,14 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
-      <c r="E70" s="5"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B71" s="3"/>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="2"/>
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B72" s="3"/>
+      <c r="B72" s="2"/>
       <c r="E72" s="5"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -2681,11 +2616,17 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
-      <c r="E73" s="7"/>
-    </row>
-    <row r="74" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E73" s="5"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
-      <c r="E74" s="7"/>
+      <c r="E74" s="5"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
@@ -2696,17 +2637,11 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="E76" s="7"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
-      <c r="E77" s="5"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
@@ -2723,62 +2658,56 @@
       <c r="B80" s="2"/>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
-      <c r="E81" s="5"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E81" s="7"/>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="E82" s="7"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="E83" s="7"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="E84" s="7"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E86" s="7"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="2"/>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E87" s="7"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E88" s="7"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E90" s="7"/>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E93" s="7"/>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E94" s="7"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E95" s="7"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E96" s="7"/>
     </row>
     <row r="97" spans="5:5" x14ac:dyDescent="0.3">
@@ -2796,64 +2725,52 @@
     <row r="101" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E101" s="7"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E102" s="7"/>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E103" s="7"/>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E104" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B41:B51"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="B53:B62"/>
-    <mergeCell ref="A53:A62"/>
-    <mergeCell ref="C59:C62"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="A28:A39"/>
-    <mergeCell ref="B28:B39"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="C34:C36"/>
+  <mergeCells count="44">
+    <mergeCell ref="A38:A48"/>
+    <mergeCell ref="B38:B48"/>
+    <mergeCell ref="C38:C42"/>
+    <mergeCell ref="B50:B59"/>
+    <mergeCell ref="A50:A59"/>
+    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="A25:A36"/>
+    <mergeCell ref="B25:B36"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C31:C33"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B17:B26"/>
-    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B14:B23"/>
+    <mergeCell ref="E22:E23"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E17:E18"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C14:C16"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A26"/>
-    <mergeCell ref="I46:I47"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="B6:B12"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A14:A23"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="F47:F48"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E42:E43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="E54:E55"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="H43:H44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A6D1DD-403C-484A-868D-AFD36FB85F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A3F324-ABBF-4DA7-A8A3-49DDE2199884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="150">
   <si>
     <t>User Story</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Risk</t>
   </si>
   <si>
-    <t>User Password is not encrypted</t>
-  </si>
-  <si>
     <t>Invalid</t>
   </si>
   <si>
@@ -209,9 +206,6 @@
     <t>Login page is unavailable via button(s)</t>
   </si>
   <si>
-    <t>Verify if Homepage Opens properly after Login</t>
-  </si>
-  <si>
     <t>Open Doctors Page Displays MDs in - default - sorted order</t>
   </si>
   <si>
@@ -371,9 +365,6 @@
     <t>Check that Register Page Displays the proper elements of the page</t>
   </si>
   <si>
-    <t>Check  DB stores hashed Passwords only using flask_bcrypt for enhanced security</t>
-  </si>
-  <si>
     <t>Click on Login button Navigates to Login Page</t>
   </si>
   <si>
@@ -483,6 +474,21 @@
   </si>
   <si>
     <t>Enter credentials Select options and Register</t>
+  </si>
+  <si>
+    <t>Check that URL does not contian password after signup</t>
+  </si>
+  <si>
+    <t>User Password is not hasehed or masked</t>
+  </si>
+  <si>
+    <t>Check  passwords are hashed or masked  for enhanced security</t>
+  </si>
+  <si>
+    <t>Check that URL does not contian password after login</t>
+  </si>
+  <si>
+    <t>Verify if User password is handled securely</t>
   </si>
 </sst>
 </file>
@@ -575,18 +581,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -596,7 +596,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -808,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,19 +843,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -876,19 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -939,9 +927,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -957,165 +942,236 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1451,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1467,1107 +1523,1123 @@
     <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:9" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="90" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="100" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="37" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="14.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="43"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="82" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="68" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="89" t="s">
+      <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="40"/>
-    </row>
-    <row r="4" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="76"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="39"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="40"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="26"/>
+      <c r="I4" s="32"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="43"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="19"/>
       <c r="G5" s="1"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="40"/>
-    </row>
-    <row r="6" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76" t="s">
+      <c r="I5" s="32"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="90" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="31"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="90"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="31"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="39"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="90"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="70" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="40"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="90"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="104" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="66" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="90"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="84"/>
+      <c r="F10" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="51"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="90"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="31"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="39"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="90"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="60" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="31"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="39"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="90"/>
+      <c r="B13" s="112"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="84"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="39"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="43"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="39"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B15" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="101" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="31"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="39"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="90"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="31"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="39"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="90"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="33"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="40"/>
+    </row>
+    <row r="18" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="90"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="101" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="90"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="84"/>
+      <c r="F19" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="44"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="90"/>
+      <c r="B20" s="112"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="70" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="45"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="112"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="39"/>
+    </row>
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="112"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="31"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="39"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="112"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="39"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="112"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="31"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="39"/>
+    </row>
+    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="112"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="99"/>
+      <c r="F25" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="39"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="19"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="32"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="31"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="32"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="109"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="31"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="32"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="109"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="84"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="32"/>
+    </row>
+    <row r="30" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="109"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="F30" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="31"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="32"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="109"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="97" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="32"/>
+    </row>
+    <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="109"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="31"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="32"/>
+    </row>
+    <row r="33" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="109"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="92" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="45"/>
+      <c r="H33" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="I33" s="32"/>
+    </row>
+    <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="109"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E34" s="93"/>
+      <c r="F34" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="32"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="109"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="106"/>
+      <c r="D35" s="70" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="84"/>
+      <c r="F35" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="31"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="32"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="109"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" s="31"/>
+      <c r="H36" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="I36" s="32"/>
+    </row>
+    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="109"/>
+      <c r="B37" s="109"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="33"/>
+      <c r="H37" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" s="34"/>
+    </row>
+    <row r="38" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="110"/>
+      <c r="B38" s="110"/>
+      <c r="C38" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F38" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="28"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="113" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="C40" s="95" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="39"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="40"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="76"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" s="88" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="90" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="39"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="48"/>
-    </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="76"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="41"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="49"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="68" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="92" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="95" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="95" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="95" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="12" t="s">
+      <c r="H40" s="3"/>
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="114"/>
+      <c r="B41" s="109"/>
+      <c r="C41" s="116"/>
+      <c r="D41" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="32"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="114"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="116"/>
+      <c r="D42" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" s="84"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="32"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="114"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="33"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="34"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="114"/>
+      <c r="B44" s="115"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="114"/>
+      <c r="B45" s="115"/>
+      <c r="C45" s="95" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="114"/>
+      <c r="B46" s="115"/>
+      <c r="C46" s="111"/>
+      <c r="D46" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="84"/>
+      <c r="F46" s="86"/>
+      <c r="G46" s="88"/>
+      <c r="H46" s="88"/>
+      <c r="I46" s="88"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="114"/>
+      <c r="B47" s="115"/>
+      <c r="C47" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="63"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="39"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="48"/>
-    </row>
-    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="76"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="103" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="39"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="48"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="55"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="48"/>
-    </row>
-    <row r="14" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="39"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="48"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="76"/>
-      <c r="B15" s="76"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="88" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="48"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="76"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="81"/>
-      <c r="D16" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="49"/>
-    </row>
-    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="76"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="70" t="s">
+      <c r="D47" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="44"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="28"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="114"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F48" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="45"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="32"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="114"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" s="87" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="45"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="114"/>
+      <c r="B50" s="115"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="59" t="s">
+        <v>134</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="89"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="32"/>
+    </row>
+    <row r="51" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="43"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="32"/>
+    </row>
+    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="108" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="91" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="90" t="s">
-        <v>33</v>
-      </c>
-      <c r="H17" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="90" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="93"/>
-      <c r="F18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="56"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="36"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="74"/>
-      <c r="B19" s="74"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="39"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="48"/>
-    </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="74"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="96" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="39"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="48"/>
-    </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="74"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="39"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="48"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="74"/>
-      <c r="B22" s="74"/>
-      <c r="C22" s="70" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="82" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="96" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="39"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="48"/>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="82"/>
-      <c r="F23" s="96" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="48"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="40"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="40"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="39"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="40"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="71"/>
-      <c r="F27" s="98"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="40"/>
-    </row>
-    <row r="28" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
-      <c r="B28" s="84"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="40"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="84"/>
-      <c r="B29" s="84"/>
-      <c r="C29" s="80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="39"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="40"/>
-    </row>
-    <row r="30" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="84"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="39"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="40"/>
-    </row>
-    <row r="31" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="84"/>
-      <c r="B31" s="84"/>
-      <c r="C31" s="70" t="s">
+      <c r="C52" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="77" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="57"/>
-      <c r="H31" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I31" s="40"/>
-    </row>
-    <row r="32" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="84"/>
-      <c r="B32" s="84"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="78"/>
-      <c r="F32" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="40"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" s="71"/>
-      <c r="F33" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="40"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="84"/>
-      <c r="B34" s="84"/>
-      <c r="C34" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="39"/>
-      <c r="H34" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="I34" s="40"/>
-    </row>
-    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="84"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="41"/>
-      <c r="H35" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" s="42"/>
-    </row>
-    <row r="36" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="73"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="46"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="36"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="86" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="72" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="40"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="84"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="F39" s="97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="39"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="40"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" s="71"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="40"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="79"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="41"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="42"/>
-    </row>
-    <row r="42" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="79"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="69" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="96" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" s="96" t="s">
-        <v>25</v>
-      </c>
-      <c r="I42" s="96" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="87"/>
-      <c r="B43" s="79"/>
-      <c r="C43" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="70" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="97" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="100" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" s="100" t="s">
-        <v>25</v>
-      </c>
-      <c r="I43" s="100" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="87"/>
-      <c r="B44" s="79"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" s="71"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="85"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="87"/>
-      <c r="B45" s="79"/>
-      <c r="C45" s="70" t="s">
+      <c r="D52" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D45" s="25" t="s">
+      <c r="F52" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="46"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="39"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="109"/>
+      <c r="B53" s="109"/>
+      <c r="C53" s="116"/>
+      <c r="D53" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="46"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="39"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="109"/>
+      <c r="B54" s="109"/>
+      <c r="C54" s="116"/>
+      <c r="D54" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E54" s="84"/>
+      <c r="F54" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="46"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="39"/>
+    </row>
+    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="115"/>
+      <c r="B55" s="115"/>
+      <c r="C55" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F45" s="101" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="56"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="36"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="87"/>
-      <c r="B46" s="79"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F46" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="57"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="40"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="87"/>
-      <c r="B47" s="79"/>
-      <c r="C47" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="F47" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="57"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="40"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="87"/>
-      <c r="B48" s="79"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="F48" s="102"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="40"/>
-    </row>
-    <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="55"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="40"/>
-    </row>
-    <row r="50" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="23" t="s">
+      <c r="F55" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="31"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="48"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="115"/>
+      <c r="B56" s="115"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="31"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="48"/>
+    </row>
+    <row r="57" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="115"/>
+      <c r="B57" s="115"/>
+      <c r="C57" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="31" t="s">
+      <c r="E57" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="31"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="49"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="115"/>
+      <c r="B58" s="115"/>
+      <c r="C58" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="F50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="G50" s="58"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="48"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
-      <c r="B51" s="84"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="70" t="s">
+      <c r="D58" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="31"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="49"/>
+    </row>
+    <row r="59" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="115"/>
+      <c r="B59" s="115"/>
+      <c r="C59" s="96"/>
+      <c r="D59" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="F51" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="58"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="48"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
-      <c r="B52" s="84"/>
-      <c r="C52" s="83"/>
-      <c r="D52" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" s="71"/>
-      <c r="F52" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="58"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="48"/>
-    </row>
-    <row r="53" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="79"/>
-      <c r="B53" s="79"/>
-      <c r="C53" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="12" t="s">
+      <c r="E59" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F59" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="31"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="39"/>
+    </row>
+    <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="115"/>
+      <c r="B60" s="115"/>
+      <c r="C60" s="96"/>
+      <c r="D60" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="E53" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="39"/>
-      <c r="H53" s="59"/>
-      <c r="I53" s="60"/>
-    </row>
-    <row r="54" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="79"/>
-      <c r="B54" s="79"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G54" s="39"/>
-      <c r="H54" s="59"/>
-      <c r="I54" s="60"/>
-    </row>
-    <row r="55" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="79"/>
-      <c r="B55" s="79"/>
-      <c r="C55" s="11" t="s">
+      <c r="E60" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G55" s="39"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="61"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="79"/>
-      <c r="B56" s="79"/>
-      <c r="C56" s="70" t="s">
+      <c r="F60" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" s="31"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="39"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="84"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G56" s="39"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="61"/>
-    </row>
-    <row r="57" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="79"/>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="39"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="48"/>
-    </row>
-    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="79"/>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79"/>
-      <c r="D58" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="39"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="48"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="71"/>
-      <c r="B59" s="71"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="12" t="s">
+      <c r="E61" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="E59" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" s="41"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="49"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="30"/>
-    </row>
-    <row r="61" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="2"/>
-      <c r="E61" s="5"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="2"/>
-      <c r="E62" s="5"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F61" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="33"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="40"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="50"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="22"/>
+    </row>
+    <row r="63" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2"/>
       <c r="E63" s="5"/>
       <c r="G63" s="2"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="2"/>
       <c r="E64" s="5"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="2"/>
       <c r="E65" s="5"/>
       <c r="G65" s="2"/>
@@ -2579,47 +2651,47 @@
       <c r="E66" s="5"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="I66" s="2"/>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="E67" s="5"/>
-      <c r="G67" s="1"/>
+      <c r="G67" s="2"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B68" s="3"/>
-      <c r="E68" s="7"/>
+      <c r="B68" s="2"/>
+      <c r="E68" s="5"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="3"/>
+      <c r="B69" s="2"/>
       <c r="E69" s="5"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B70" s="2"/>
+      <c r="B70" s="3"/>
       <c r="E70" s="7"/>
     </row>
-    <row r="71" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="E71" s="7"/>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B71" s="3"/>
+      <c r="E71" s="5"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
-      <c r="E72" s="5"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
-      <c r="E73" s="5"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="E73" s="7"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
@@ -2637,18 +2709,21 @@
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
-      <c r="E76" s="7"/>
+      <c r="E76" s="5"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
-      <c r="E77" s="7"/>
+      <c r="E77" s="5"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
-      <c r="E78" s="5"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
@@ -2656,7 +2731,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
-      <c r="E80" s="7"/>
+      <c r="E80" s="5"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
@@ -2675,9 +2753,11 @@
       <c r="E84" s="7"/>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B85" s="2"/>
       <c r="E85" s="7"/>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B86" s="2"/>
       <c r="E86" s="7"/>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.3">
@@ -2725,52 +2805,61 @@
     <row r="101" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E101" s="7"/>
     </row>
+    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E102" s="7"/>
+    </row>
+    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E103" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="A38:A48"/>
-    <mergeCell ref="B38:B48"/>
-    <mergeCell ref="C38:C42"/>
-    <mergeCell ref="B50:B59"/>
-    <mergeCell ref="A50:A59"/>
-    <mergeCell ref="C56:C59"/>
+  <mergeCells count="47">
+    <mergeCell ref="A40:A50"/>
+    <mergeCell ref="B40:B50"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B52:B61"/>
+    <mergeCell ref="A52:A61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C55:C56"/>
     <mergeCell ref="C45:C46"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="A25:A36"/>
-    <mergeCell ref="B25:B36"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="A27:A38"/>
+    <mergeCell ref="B27:B38"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C33:C35"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B15:B25"/>
+    <mergeCell ref="B6:B13"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A15:A25"/>
+    <mergeCell ref="C18:C20"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="B6:B12"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="A14:A23"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="F49:F50"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="H45:H46"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A3F324-ABBF-4DA7-A8A3-49DDE2199884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E64008A-9B66-4259-92A7-73B3D648BA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="154">
   <si>
     <t>User Story</t>
   </si>
@@ -344,9 +344,6 @@
     <t>Verify if User can Open Login page and the required elements of the page are visible</t>
   </si>
   <si>
-    <t>Verify if registered User can Log in using own valid credentials</t>
-  </si>
-  <si>
     <t>Verify if any User can Navigate to a specialty section of Doctors Page via specialty cards</t>
   </si>
   <si>
@@ -479,16 +476,31 @@
     <t>Check that URL does not contian password after signup</t>
   </si>
   <si>
-    <t>User Password is not hasehed or masked</t>
-  </si>
-  <si>
-    <t>Check  passwords are hashed or masked  for enhanced security</t>
-  </si>
-  <si>
     <t>Check that URL does not contian password after login</t>
   </si>
   <si>
-    <t>Verify if User password is handled securely</t>
+    <t>Verify if registered User can Log in using own valid credentials and password is not endangered</t>
+  </si>
+  <si>
+    <t>Check that page does not expose password after signup</t>
+  </si>
+  <si>
+    <t>Check  passwords handling for enhanced security</t>
+  </si>
+  <si>
+    <t>User Password is endangered</t>
+  </si>
+  <si>
+    <t>User password is endangered</t>
+  </si>
+  <si>
+    <t>Check that error message does not expose password at signup</t>
+  </si>
+  <si>
+    <t>Check that error message does not expose password at login</t>
+  </si>
+  <si>
+    <t>Check that page does not expose password after login</t>
   </si>
 </sst>
 </file>
@@ -581,7 +593,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,6 +624,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -820,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1068,110 +1086,122 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1507,7 +1537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1564,13 +1594,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="115" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1587,9 +1617,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="100"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="115"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
@@ -1615,13 +1645,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="96" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="70" t="s">
@@ -1638,11 +1668,11 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="112"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
       <c r="C7" s="102"/>
       <c r="D7" s="62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>52</v>
@@ -1655,11 +1685,11 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="90"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="103"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>30</v>
@@ -1672,15 +1702,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="104" t="s">
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="96" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="83" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="101" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1697,13 +1727,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="105"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="84"/>
+      <c r="E10" s="93"/>
       <c r="F10" s="78" t="s">
         <v>13</v>
       </c>
@@ -1712,9 +1742,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="90"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="98"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="70" t="s">
         <v>36</v>
       </c>
@@ -1729,18 +1759,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="90"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="95" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="117" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="83" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="101" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="120" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1748,381 +1778,359 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="90"/>
-      <c r="B13" s="112"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="84"/>
-      <c r="F13" s="94"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="88"/>
+      <c r="F13" s="121"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="1"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="60" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="88"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
-    <row r="15" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="101" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="72" t="s">
-        <v>9</v>
-      </c>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="116" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" s="93"/>
+      <c r="F15" s="113"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="90"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="62" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="31"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="39"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="90"/>
-      <c r="B17" s="112"/>
-      <c r="C17" s="107"/>
+    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="99" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="96" t="s">
+        <v>100</v>
+      </c>
       <c r="D17" s="70" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="40"/>
-    </row>
-    <row r="18" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="90"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="101" t="s">
-        <v>101</v>
-      </c>
+      <c r="G17" s="31"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="39"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="99"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="83" t="s">
-        <v>35</v>
+        <v>107</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="F18" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="31"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="39"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="40"/>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="89" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="101" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="64" t="s">
+      <c r="H20" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="64" t="s">
+      <c r="I20" s="64" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="90"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="68" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="84"/>
-      <c r="F19" s="69" t="s">
+      <c r="E21" s="93"/>
+      <c r="F21" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="44"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="28"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="90"/>
-      <c r="B20" s="112"/>
-      <c r="C20" s="115"/>
-      <c r="D20" s="70" t="s">
+      <c r="G21" s="44"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="28"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="71" t="s">
+      <c r="F22" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="45"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="32"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="112"/>
-      <c r="B21" s="112"/>
-      <c r="C21" s="61" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="54" t="s">
+      <c r="G22" s="45"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="32"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="39"/>
-    </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="112"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="60" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="31"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="39"/>
-    </row>
-    <row r="23" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="112"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="39"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="112"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="95" t="s">
-        <v>42</v>
-      </c>
+      <c r="A24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="99" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="39"/>
-    </row>
-    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="112"/>
-      <c r="B25" s="112"/>
-      <c r="C25" s="111"/>
+        <v>145</v>
+      </c>
+      <c r="E24" s="88"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="32"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="100"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="56" t="s">
-        <v>7</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E25" s="93"/>
+      <c r="F25" s="119"/>
       <c r="G25" s="31"/>
       <c r="H25" s="1"/>
       <c r="I25" s="39"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="32"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="108" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="95" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="79" t="s">
-        <v>13</v>
+    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="100"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="31"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="39"/>
+    </row>
+    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="100"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="G27" s="31"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="32"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="109"/>
-      <c r="B28" s="109"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="85" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="114" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="56" t="s">
         <v>7</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="32"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="109"/>
-      <c r="B29" s="109"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" s="84"/>
-      <c r="F29" s="94"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="39"/>
+    </row>
+    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="100"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="114"/>
+      <c r="F29" s="56" t="s">
+        <v>7</v>
+      </c>
       <c r="G29" s="31"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="32"/>
-    </row>
-    <row r="30" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="109"/>
-      <c r="B30" s="109"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="31"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="39"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="19"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="1"/>
       <c r="H30" s="3"/>
       <c r="I30" s="32"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="109"/>
-      <c r="B31" s="109"/>
-      <c r="C31" s="97" t="s">
-        <v>118</v>
+      <c r="A31" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="89" t="s">
+        <v>81</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="79" t="s">
         <v>13</v>
       </c>
       <c r="G31" s="31"/>
       <c r="H31" s="3"/>
       <c r="I31" s="32"/>
     </row>
-    <row r="32" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="109"/>
-      <c r="B32" s="109"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="78" t="s">
-        <v>13</v>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="110" t="s">
+        <v>7</v>
       </c>
       <c r="G32" s="31"/>
       <c r="H32" s="3"/>
       <c r="I32" s="32"/>
     </row>
-    <row r="33" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="109"/>
-      <c r="B33" s="109"/>
-      <c r="C33" s="101" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="92" t="s">
-        <v>111</v>
-      </c>
-      <c r="F33" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="45"/>
-      <c r="H33" s="82" t="s">
-        <v>120</v>
-      </c>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="93"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
-    <row r="34" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="109"/>
-      <c r="B34" s="109"/>
-      <c r="C34" s="106"/>
+    <row r="34" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="92"/>
       <c r="D34" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="72" t="s">
         <v>9</v>
       </c>
       <c r="G34" s="31"/>
@@ -2130,664 +2138,724 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="109"/>
-      <c r="B35" s="109"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="70" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" s="84"/>
-      <c r="F35" s="73" t="s">
-        <v>9</v>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="112" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F35" s="78" t="s">
+        <v>13</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="109"/>
-      <c r="B36" s="109"/>
-      <c r="C36" s="101" t="s">
+    <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="87"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="31"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="32"/>
+    </row>
+    <row r="37" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="87"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="96" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="108" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="45"/>
+      <c r="H37" s="82" t="s">
+        <v>119</v>
+      </c>
+      <c r="I37" s="32"/>
+    </row>
+    <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="87"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="109"/>
+      <c r="F38" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="32"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E39" s="93"/>
+      <c r="F39" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="32"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="87"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="71" t="s">
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="97"/>
+      <c r="D41" s="68" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="33"/>
+      <c r="H41" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="34"/>
+    </row>
+    <row r="42" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="95"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="28"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="84" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="89" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F44" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="32"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="85"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" s="101" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="110" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="31"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="32"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="85"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="93"/>
+      <c r="F46" s="113"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="85"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="91"/>
+      <c r="D47" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G36" s="31"/>
-      <c r="H36" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="I36" s="32"/>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="109"/>
-      <c r="B37" s="109"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="F37" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="33"/>
-      <c r="H37" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="I37" s="34"/>
-    </row>
-    <row r="38" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="110"/>
-      <c r="B38" s="110"/>
-      <c r="C38" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="D38" s="68" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F38" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="81" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="81" t="s">
-        <v>25</v>
-      </c>
-      <c r="I38" s="81" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="28"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="113" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="108" t="s">
-        <v>61</v>
-      </c>
-      <c r="C40" s="95" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="68" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="114"/>
-      <c r="B41" s="109"/>
-      <c r="C41" s="116"/>
-      <c r="D41" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E41" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" s="85" t="s">
+      <c r="G47" s="33"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="34"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="85"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="92"/>
+      <c r="D48" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="114"/>
-      <c r="B42" s="109"/>
-      <c r="C42" s="116"/>
-      <c r="D42" s="60" t="s">
+      <c r="G48" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="85"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="89" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E42" s="84"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="32"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="114"/>
-      <c r="B43" s="115"/>
-      <c r="C43" s="96"/>
-      <c r="D43" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" s="71" t="s">
+      <c r="E49" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="110" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="105" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="105" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="85"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="94"/>
+      <c r="D50" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="93"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="92"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="92"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="85"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D51" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="44"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="28"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="85"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="G43" s="33"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="114"/>
-      <c r="B44" s="115"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" s="54" t="s">
+      <c r="G52" s="45"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="32"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="85"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F53" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="G44" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="114"/>
-      <c r="B45" s="115"/>
-      <c r="C45" s="95" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E45" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="F45" s="85" t="s">
+      <c r="G53" s="45"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="32"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="85"/>
+      <c r="B54" s="88"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="106"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="43"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="32"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="86" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="89" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F56" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="87" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="114"/>
-      <c r="B46" s="115"/>
-      <c r="C46" s="111"/>
-      <c r="D46" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E46" s="84"/>
-      <c r="F46" s="86"/>
-      <c r="G46" s="88"/>
-      <c r="H46" s="88"/>
-      <c r="I46" s="88"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="114"/>
-      <c r="B47" s="115"/>
-      <c r="C47" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F47" s="58" t="s">
+      <c r="G56" s="46"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="39"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="87"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="F57" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="46"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="39"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="87"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="93"/>
+      <c r="F58" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="44"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="28"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="114"/>
-      <c r="B48" s="115"/>
-      <c r="C48" s="88"/>
-      <c r="D48" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G48" s="45"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="32"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="114"/>
-      <c r="B49" s="115"/>
-      <c r="C49" s="95" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F49" s="87" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="45"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="32"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="114"/>
-      <c r="B50" s="115"/>
-      <c r="C50" s="111"/>
-      <c r="D50" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F50" s="89"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="32"/>
-    </row>
-    <row r="51" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="43"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="32"/>
-    </row>
-    <row r="52" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="108" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="108" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="95" t="s">
+      <c r="G58" s="46"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="39"/>
+    </row>
+    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="88"/>
+      <c r="B59" s="88"/>
+      <c r="C59" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="55" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="46"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="39"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="109"/>
-      <c r="B53" s="109"/>
-      <c r="C53" s="116"/>
-      <c r="D53" s="70" t="s">
+      <c r="D59" s="60" t="s">
         <v>137</v>
       </c>
-      <c r="E53" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" s="46"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="39"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="109"/>
-      <c r="B54" s="109"/>
-      <c r="C54" s="116"/>
-      <c r="D54" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" s="84"/>
-      <c r="F54" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="46"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="39"/>
-    </row>
-    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="115"/>
-      <c r="B55" s="115"/>
-      <c r="C55" s="95" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="E55" s="8" t="s">
+      <c r="E59" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="F55" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="31"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="48"/>
-    </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="115"/>
-      <c r="B56" s="115"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F56" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G56" s="31"/>
-      <c r="H56" s="47"/>
-      <c r="I56" s="48"/>
-    </row>
-    <row r="57" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="115"/>
-      <c r="B57" s="115"/>
-      <c r="C57" s="67" t="s">
-        <v>140</v>
-      </c>
-      <c r="D57" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F57" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G57" s="31"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="49"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="115"/>
-      <c r="B58" s="115"/>
-      <c r="C58" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="D58" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F58" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="31"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="49"/>
-    </row>
-    <row r="59" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="115"/>
-      <c r="B59" s="115"/>
-      <c r="C59" s="96"/>
-      <c r="D59" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="F59" s="54" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="31"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="39"/>
-    </row>
-    <row r="60" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="115"/>
-      <c r="B60" s="115"/>
-      <c r="C60" s="96"/>
-      <c r="D60" s="70" t="s">
-        <v>141</v>
+      <c r="H59" s="47"/>
+      <c r="I59" s="48"/>
+    </row>
+    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="88"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="60" t="s">
+        <v>77</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F60" s="71" t="s">
-        <v>9</v>
+        <v>76</v>
+      </c>
+      <c r="F60" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G60" s="31"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="39"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
-      <c r="B61" s="84"/>
-      <c r="C61" s="88"/>
+      <c r="H60" s="47"/>
+      <c r="I60" s="48"/>
+    </row>
+    <row r="61" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="88"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="67" t="s">
+        <v>139</v>
+      </c>
       <c r="D61" s="68" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="33"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="40"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="49"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="22"/>
-      <c r="B62" s="22"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="50"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="22"/>
-    </row>
-    <row r="63" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="2"/>
-      <c r="E63" s="5"/>
-      <c r="G63" s="2"/>
+      <c r="A62" s="88"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F62" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="31"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="49"/>
+    </row>
+    <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="88"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="31"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="2"/>
-      <c r="E64" s="5"/>
-      <c r="G64" s="1"/>
+      <c r="A64" s="88"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" s="31"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="2"/>
-      <c r="E65" s="5"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B66" s="2"/>
-      <c r="E66" s="5"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I64" s="39"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="93"/>
+      <c r="B65" s="93"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="33"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="40"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="50"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27"/>
+      <c r="I66" s="22"/>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="E67" s="5"/>
       <c r="G67" s="2"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="E68" s="5"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
       <c r="E69" s="5"/>
-      <c r="G69" s="1"/>
+      <c r="G69" s="2"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B70" s="3"/>
-      <c r="E70" s="7"/>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B71" s="3"/>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B70" s="2"/>
+      <c r="E70" s="5"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B71" s="2"/>
       <c r="E71" s="5"/>
-      <c r="G71" s="1"/>
+      <c r="G71" s="2"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
-      <c r="E72" s="7"/>
-    </row>
-    <row r="73" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E72" s="5"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
-      <c r="E73" s="7"/>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="2"/>
-      <c r="E74" s="5"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B75" s="2"/>
+      <c r="E73" s="5"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B74" s="3"/>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B75" s="3"/>
       <c r="E75" s="5"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
-      <c r="E77" s="5"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E77" s="7"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
-      <c r="E78" s="7"/>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E78" s="5"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
-      <c r="E79" s="7"/>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E79" s="5"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="E80" s="5"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E81" s="5"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="E82" s="7"/>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="E83" s="7"/>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
-      <c r="E84" s="7"/>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E84" s="5"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="E85" s="7"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
       <c r="E86" s="7"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B87" s="2"/>
       <c r="E87" s="7"/>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="2"/>
       <c r="E88" s="7"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="2"/>
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="2"/>
       <c r="E90" s="7"/>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E93" s="7"/>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E94" s="7"/>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E95" s="7"/>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E96" s="7"/>
     </row>
     <row r="97" spans="5:5" x14ac:dyDescent="0.3">
@@ -2811,55 +2879,69 @@
     <row r="103" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E103" s="7"/>
     </row>
+    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E104" s="7"/>
+    </row>
+    <row r="105" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E105" s="7"/>
+    </row>
+    <row r="106" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E106" s="7"/>
+    </row>
+    <row r="107" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E107" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A40:A50"/>
-    <mergeCell ref="B40:B50"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B52:B61"/>
-    <mergeCell ref="A52:A61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="A27:A38"/>
-    <mergeCell ref="B27:B38"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B15:B25"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A15:A25"/>
-    <mergeCell ref="C18:C20"/>
+  <mergeCells count="49">
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C20:C25"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="A31:A42"/>
+    <mergeCell ref="B31:B42"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="A44:A54"/>
+    <mergeCell ref="B44:B54"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="A56:A65"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E64008A-9B66-4259-92A7-73B3D648BA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9D2718-284D-441B-ADD2-79567FF9D072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1089,119 +1089,119 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1594,13 +1594,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="115" t="s">
+      <c r="C3" s="118" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1617,9 +1617,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="115"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="118"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
@@ -1645,13 +1645,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="92" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="70" t="s">
@@ -1668,9 +1668,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="102"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1685,9 +1685,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="97"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="70" t="s">
         <v>106</v>
       </c>
@@ -1702,15 +1702,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="96" t="s">
+      <c r="A9" s="97"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="92" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="101" t="s">
+      <c r="E9" s="85" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1727,13 +1727,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="102"/>
+      <c r="A10" s="97"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="93"/>
+      <c r="E10" s="86"/>
       <c r="F10" s="78" t="s">
         <v>13</v>
       </c>
@@ -1742,9 +1742,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="97"/>
+      <c r="A11" s="97"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="94"/>
       <c r="D11" s="70" t="s">
         <v>36</v>
       </c>
@@ -1759,18 +1759,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="117" t="s">
+      <c r="A12" s="97"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="99" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="85" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="102" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1778,40 +1778,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="91"/>
+      <c r="A13" s="97"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="100"/>
       <c r="D13" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="88"/>
-      <c r="F13" s="121"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="60" t="s">
+      <c r="A14" s="97"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="88"/>
-      <c r="F14" s="121"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="103"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="116" t="s">
+      <c r="A15" s="97"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="93"/>
-      <c r="F15" s="113"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="88"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1828,13 +1828,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="92" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="70" t="s">
@@ -1851,9 +1851,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="98"/>
+      <c r="A18" s="97"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="95"/>
       <c r="D18" s="62" t="s">
         <v>107</v>
       </c>
@@ -1868,9 +1868,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="104"/>
+      <c r="A19" s="97"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="96"/>
       <c r="D19" s="70" t="s">
         <v>82</v>
       </c>
@@ -1885,15 +1885,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="89" t="s">
+      <c r="A20" s="97"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="107" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="101" t="s">
+      <c r="E20" s="85" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="65" t="s">
@@ -1910,13 +1910,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="91"/>
+      <c r="A21" s="97"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="100"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="93"/>
+      <c r="E21" s="86"/>
       <c r="F21" s="69" t="s">
         <v>13</v>
       </c>
@@ -1925,9 +1925,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="91"/>
+      <c r="A22" s="97"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="100"/>
       <c r="D22" s="70" t="s">
         <v>36</v>
       </c>
@@ -1942,16 +1942,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="91"/>
+      <c r="A23" s="97"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="100"/>
       <c r="D23" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="101" t="s">
+      <c r="E23" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="F23" s="110" t="s">
+      <c r="F23" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1959,34 +1959,34 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="91"/>
+      <c r="A24" s="97"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="100"/>
       <c r="D24" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="88"/>
-      <c r="F24" s="118"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="104"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="100"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="117"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="60" t="s">
         <v>153</v>
       </c>
-      <c r="E25" s="93"/>
-      <c r="F25" s="119"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="31"/>
       <c r="H25" s="1"/>
       <c r="I25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="100"/>
-      <c r="B26" s="100"/>
+      <c r="A26" s="117"/>
+      <c r="B26" s="117"/>
       <c r="C26" s="61" t="s">
         <v>108</v>
       </c>
@@ -2004,8 +2004,8 @@
       <c r="I26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="100"/>
-      <c r="B27" s="100"/>
+      <c r="A27" s="117"/>
+      <c r="B27" s="117"/>
       <c r="C27" s="83" t="s">
         <v>108</v>
       </c>
@@ -2023,15 +2023,15 @@
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="100"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="89" t="s">
+      <c r="A28" s="117"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="107" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="114" t="s">
+      <c r="E28" s="106" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="56" t="s">
@@ -2042,13 +2042,13 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="100"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="94"/>
+      <c r="A29" s="117"/>
+      <c r="B29" s="117"/>
+      <c r="C29" s="116"/>
       <c r="D29" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="114"/>
+      <c r="E29" s="106"/>
       <c r="F29" s="56" t="s">
         <v>7</v>
       </c>
@@ -2068,13 +2068,13 @@
       <c r="I30" s="32"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="89" t="s">
+      <c r="C31" s="107" t="s">
         <v>81</v>
       </c>
       <c r="D31" s="68" t="s">
@@ -2091,16 +2091,16 @@
       <c r="I31" s="32"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="91"/>
+      <c r="A32" s="114"/>
+      <c r="B32" s="114"/>
+      <c r="C32" s="100"/>
       <c r="D32" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="101" t="s">
+      <c r="E32" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="110" t="s">
+      <c r="F32" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="31"/>
@@ -2108,22 +2108,22 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="91"/>
+      <c r="A33" s="114"/>
+      <c r="B33" s="114"/>
+      <c r="C33" s="100"/>
       <c r="D33" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="93"/>
-      <c r="F33" s="111"/>
+      <c r="E33" s="86"/>
+      <c r="F33" s="110"/>
       <c r="G33" s="31"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="92"/>
+      <c r="A34" s="114"/>
+      <c r="B34" s="114"/>
+      <c r="C34" s="90"/>
       <c r="D34" s="70" t="s">
         <v>83</v>
       </c>
@@ -2138,9 +2138,9 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="112" t="s">
+      <c r="A35" s="114"/>
+      <c r="B35" s="114"/>
+      <c r="C35" s="111" t="s">
         <v>117</v>
       </c>
       <c r="D35" s="68" t="s">
@@ -2157,9 +2157,9 @@
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="103"/>
+      <c r="A36" s="114"/>
+      <c r="B36" s="114"/>
+      <c r="C36" s="112"/>
       <c r="D36" s="68" t="s">
         <v>118</v>
       </c>
@@ -2174,9 +2174,9 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="96" t="s">
+      <c r="A37" s="114"/>
+      <c r="B37" s="114"/>
+      <c r="C37" s="92" t="s">
         <v>101</v>
       </c>
       <c r="D37" s="68" t="s">
@@ -2195,9 +2195,9 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="87"/>
-      <c r="C38" s="98"/>
+      <c r="A38" s="114"/>
+      <c r="B38" s="114"/>
+      <c r="C38" s="95"/>
       <c r="D38" s="70" t="s">
         <v>112</v>
       </c>
@@ -2210,13 +2210,13 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="98"/>
+      <c r="A39" s="114"/>
+      <c r="B39" s="114"/>
+      <c r="C39" s="95"/>
       <c r="D39" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="93"/>
+      <c r="E39" s="86"/>
       <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
@@ -2225,9 +2225,9 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="96" t="s">
+      <c r="A40" s="114"/>
+      <c r="B40" s="114"/>
+      <c r="C40" s="92" t="s">
         <v>120</v>
       </c>
       <c r="D40" s="70" t="s">
@@ -2246,9 +2246,9 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="97"/>
+      <c r="A41" s="114"/>
+      <c r="B41" s="114"/>
+      <c r="C41" s="94"/>
       <c r="D41" s="68" t="s">
         <v>122</v>
       </c>
@@ -2265,8 +2265,8 @@
       <c r="I41" s="34"/>
     </row>
     <row r="42" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="95"/>
-      <c r="B42" s="95"/>
+      <c r="A42" s="115"/>
+      <c r="B42" s="115"/>
       <c r="C42" s="80" t="s">
         <v>85</v>
       </c>
@@ -2301,13 +2301,13 @@
       <c r="I43" s="28"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="86" t="s">
+      <c r="B44" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="89" t="s">
+      <c r="C44" s="107" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="68" t="s">
@@ -2326,16 +2326,16 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="90"/>
+      <c r="A45" s="120"/>
+      <c r="B45" s="114"/>
+      <c r="C45" s="121"/>
       <c r="D45" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="101" t="s">
+      <c r="E45" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="F45" s="110" t="s">
+      <c r="F45" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="31"/>
@@ -2343,22 +2343,22 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="90"/>
+      <c r="A46" s="120"/>
+      <c r="B46" s="114"/>
+      <c r="C46" s="121"/>
       <c r="D46" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="93"/>
-      <c r="F46" s="113"/>
+      <c r="E46" s="86"/>
+      <c r="F46" s="88"/>
       <c r="G46" s="31"/>
       <c r="H46" s="3"/>
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="88"/>
-      <c r="C47" s="91"/>
+      <c r="A47" s="120"/>
+      <c r="B47" s="101"/>
+      <c r="C47" s="100"/>
       <c r="D47" s="70" t="s">
         <v>57</v>
       </c>
@@ -2373,9 +2373,9 @@
       <c r="I47" s="34"/>
     </row>
     <row r="48" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="92"/>
+      <c r="A48" s="120"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="90"/>
       <c r="D48" s="60" t="s">
         <v>27</v>
       </c>
@@ -2396,47 +2396,47 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
-      <c r="B49" s="88"/>
-      <c r="C49" s="89" t="s">
+      <c r="A49" s="120"/>
+      <c r="B49" s="101"/>
+      <c r="C49" s="107" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="101" t="s">
+      <c r="E49" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="110" t="s">
+      <c r="F49" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="105" t="s">
+      <c r="G49" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="105" t="s">
+      <c r="H49" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="105" t="s">
+      <c r="I49" s="89" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
-      <c r="B50" s="88"/>
-      <c r="C50" s="94"/>
+      <c r="A50" s="120"/>
+      <c r="B50" s="101"/>
+      <c r="C50" s="116"/>
       <c r="D50" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E50" s="93"/>
-      <c r="F50" s="113"/>
-      <c r="G50" s="92"/>
-      <c r="H50" s="92"/>
-      <c r="I50" s="92"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
-      <c r="B51" s="88"/>
-      <c r="C51" s="89" t="s">
+      <c r="A51" s="120"/>
+      <c r="B51" s="101"/>
+      <c r="C51" s="107" t="s">
         <v>65</v>
       </c>
       <c r="D51" s="59" t="s">
@@ -2453,9 +2453,9 @@
       <c r="I51" s="28"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
-      <c r="B52" s="88"/>
-      <c r="C52" s="92"/>
+      <c r="A52" s="120"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="90"/>
       <c r="D52" s="75" t="s">
         <v>130</v>
       </c>
@@ -2470,9 +2470,9 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
-      <c r="B53" s="88"/>
-      <c r="C53" s="89" t="s">
+      <c r="A53" s="120"/>
+      <c r="B53" s="101"/>
+      <c r="C53" s="107" t="s">
         <v>66</v>
       </c>
       <c r="D53" s="59" t="s">
@@ -2481,7 +2481,7 @@
       <c r="E53" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="105" t="s">
+      <c r="F53" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="45"/>
@@ -2489,16 +2489,16 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="85"/>
-      <c r="B54" s="88"/>
-      <c r="C54" s="94"/>
+      <c r="A54" s="120"/>
+      <c r="B54" s="101"/>
+      <c r="C54" s="116"/>
       <c r="D54" s="59" t="s">
         <v>133</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F54" s="106"/>
+      <c r="F54" s="91"/>
       <c r="G54" s="45"/>
       <c r="H54" s="3"/>
       <c r="I54" s="32"/>
@@ -2515,13 +2515,13 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="86" t="s">
+      <c r="A56" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="86" t="s">
+      <c r="B56" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="89" t="s">
+      <c r="C56" s="107" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="55" t="s">
@@ -2538,13 +2538,13 @@
       <c r="I56" s="39"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="87"/>
-      <c r="B57" s="87"/>
-      <c r="C57" s="90"/>
+      <c r="A57" s="114"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="121"/>
       <c r="D57" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="E57" s="101" t="s">
+      <c r="E57" s="85" t="s">
         <v>68</v>
       </c>
       <c r="F57" s="77" t="s">
@@ -2555,13 +2555,13 @@
       <c r="I57" s="39"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="87"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="90"/>
+      <c r="A58" s="114"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="121"/>
       <c r="D58" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="E58" s="93"/>
+      <c r="E58" s="86"/>
       <c r="F58" s="54" t="s">
         <v>7</v>
       </c>
@@ -2570,9 +2570,9 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="88"/>
-      <c r="C59" s="89" t="s">
+      <c r="A59" s="101"/>
+      <c r="B59" s="101"/>
+      <c r="C59" s="107" t="s">
         <v>104</v>
       </c>
       <c r="D59" s="60" t="s">
@@ -2589,9 +2589,9 @@
       <c r="I59" s="48"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="92"/>
+      <c r="A60" s="101"/>
+      <c r="B60" s="101"/>
+      <c r="C60" s="90"/>
       <c r="D60" s="60" t="s">
         <v>77</v>
       </c>
@@ -2606,8 +2606,8 @@
       <c r="I60" s="48"/>
     </row>
     <row r="61" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="88"/>
+      <c r="A61" s="101"/>
+      <c r="B61" s="101"/>
       <c r="C61" s="67" t="s">
         <v>139</v>
       </c>
@@ -2625,9 +2625,9 @@
       <c r="I61" s="49"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="88"/>
-      <c r="C62" s="89" t="s">
+      <c r="A62" s="101"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="107" t="s">
         <v>69</v>
       </c>
       <c r="D62" s="68" t="s">
@@ -2644,9 +2644,9 @@
       <c r="I62" s="49"/>
     </row>
     <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
-      <c r="B63" s="88"/>
-      <c r="C63" s="91"/>
+      <c r="A63" s="101"/>
+      <c r="B63" s="101"/>
+      <c r="C63" s="100"/>
       <c r="D63" s="60" t="s">
         <v>70</v>
       </c>
@@ -2661,9 +2661,9 @@
       <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="88"/>
-      <c r="C64" s="91"/>
+      <c r="A64" s="101"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="100"/>
       <c r="D64" s="70" t="s">
         <v>140</v>
       </c>
@@ -2678,9 +2678,9 @@
       <c r="I64" s="39"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="93"/>
-      <c r="B65" s="93"/>
-      <c r="C65" s="92"/>
+      <c r="A65" s="86"/>
+      <c r="B65" s="86"/>
+      <c r="C65" s="90"/>
       <c r="D65" s="68" t="s">
         <v>71</v>
       </c>
@@ -2893,44 +2893,6 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="B31:B42"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A29"/>
     <mergeCell ref="A44:A54"/>
     <mergeCell ref="B44:B54"/>
     <mergeCell ref="C44:C48"/>
@@ -2942,6 +2904,44 @@
     <mergeCell ref="C56:C58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A31:A42"/>
+    <mergeCell ref="B31:B42"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="F53:F54"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9D2718-284D-441B-ADD2-79567FF9D072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3CD986-8A89-4ABB-BCB7-EABF79418F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -485,9 +485,6 @@
     <t>Check that page does not expose password after signup</t>
   </si>
   <si>
-    <t>Check  passwords handling for enhanced security</t>
-  </si>
-  <si>
     <t>User Password is endangered</t>
   </si>
   <si>
@@ -501,6 +498,9 @@
   </si>
   <si>
     <t>Check that page does not expose password after login</t>
+  </si>
+  <si>
+    <t>Check  passwords masking (type="password") for enhanced security</t>
   </si>
 </sst>
 </file>
@@ -593,7 +593,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -624,12 +624,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -838,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1089,118 +1083,115 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1594,13 +1585,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="101" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1617,9 +1608,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="97"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="118"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="101"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
@@ -1645,13 +1636,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="96" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="70" t="s">
@@ -1668,9 +1659,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="97"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="93"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1685,9 +1676,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="94"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="70" t="s">
         <v>106</v>
       </c>
@@ -1702,15 +1693,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="97"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="92" t="s">
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="96" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="85" t="s">
+      <c r="E9" s="104" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1727,13 +1718,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="97"/>
-      <c r="B10" s="117"/>
-      <c r="C10" s="93"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="86"/>
+      <c r="E10" s="93"/>
       <c r="F10" s="78" t="s">
         <v>13</v>
       </c>
@@ -1742,9 +1733,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="97"/>
-      <c r="B11" s="117"/>
-      <c r="C11" s="94"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="70" t="s">
         <v>36</v>
       </c>
@@ -1759,18 +1750,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="99" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="103" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="85" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="102" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="104" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="105" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1778,40 +1769,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="97"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="100"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="91"/>
       <c r="D13" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="101"/>
-      <c r="F13" s="103"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="106"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="97"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="100"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="91"/>
       <c r="D14" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="101"/>
-      <c r="F14" s="103"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="106"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="97"/>
-      <c r="B15" s="117"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="86"/>
-      <c r="F15" s="88"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="93"/>
+      <c r="F15" s="107"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1828,13 +1819,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="97" t="s">
+      <c r="A17" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="96" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="70" t="s">
@@ -1851,9 +1842,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="97"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="95"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="62" t="s">
         <v>107</v>
       </c>
@@ -1868,9 +1859,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="97"/>
-      <c r="B19" s="117"/>
-      <c r="C19" s="96"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="118"/>
       <c r="D19" s="70" t="s">
         <v>82</v>
       </c>
@@ -1885,15 +1876,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="97"/>
-      <c r="B20" s="117"/>
-      <c r="C20" s="107" t="s">
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="89" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="85" t="s">
+      <c r="E20" s="104" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="65" t="s">
@@ -1910,13 +1901,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="97"/>
-      <c r="B21" s="117"/>
-      <c r="C21" s="100"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="91"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="86"/>
+      <c r="E21" s="93"/>
       <c r="F21" s="69" t="s">
         <v>13</v>
       </c>
@@ -1925,9 +1916,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="97"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="100"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="70" t="s">
         <v>36</v>
       </c>
@@ -1942,16 +1933,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="97"/>
-      <c r="B23" s="117"/>
-      <c r="C23" s="100"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="91"/>
       <c r="D23" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" s="85" t="s">
-        <v>150</v>
-      </c>
-      <c r="F23" s="87" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="104" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="108" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1959,34 +1950,34 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="97"/>
-      <c r="B24" s="117"/>
-      <c r="C24" s="100"/>
+      <c r="A24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="104"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="109"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="117"/>
-      <c r="B25" s="117"/>
-      <c r="C25" s="90"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="86"/>
-      <c r="F25" s="105"/>
+        <v>152</v>
+      </c>
+      <c r="E25" s="93"/>
+      <c r="F25" s="110"/>
       <c r="G25" s="31"/>
       <c r="H25" s="1"/>
       <c r="I25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="117"/>
-      <c r="B26" s="117"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="100"/>
       <c r="C26" s="61" t="s">
         <v>108</v>
       </c>
@@ -2004,8 +1995,8 @@
       <c r="I26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="117"/>
-      <c r="B27" s="117"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="100"/>
       <c r="C27" s="83" t="s">
         <v>108</v>
       </c>
@@ -2023,15 +2014,15 @@
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="117"/>
-      <c r="B28" s="117"/>
-      <c r="C28" s="107" t="s">
+      <c r="A28" s="100"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="89" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="106" t="s">
+      <c r="E28" s="111" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="56" t="s">
@@ -2042,13 +2033,13 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="117"/>
-      <c r="B29" s="117"/>
-      <c r="C29" s="116"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="94"/>
       <c r="D29" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="106"/>
+      <c r="E29" s="111"/>
       <c r="F29" s="56" t="s">
         <v>7</v>
       </c>
@@ -2068,13 +2059,13 @@
       <c r="I30" s="32"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="113" t="s">
+      <c r="A31" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="113" t="s">
+      <c r="B31" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="107" t="s">
+      <c r="C31" s="89" t="s">
         <v>81</v>
       </c>
       <c r="D31" s="68" t="s">
@@ -2091,16 +2082,16 @@
       <c r="I31" s="32"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="114"/>
-      <c r="B32" s="114"/>
-      <c r="C32" s="100"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="91"/>
       <c r="D32" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="85" t="s">
+      <c r="E32" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="87" t="s">
+      <c r="F32" s="108" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="31"/>
@@ -2108,22 +2099,22 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="114"/>
-      <c r="B33" s="114"/>
-      <c r="C33" s="100"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="86"/>
-      <c r="F33" s="110"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="114"/>
       <c r="G33" s="31"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="114"/>
-      <c r="B34" s="114"/>
-      <c r="C34" s="90"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="92"/>
       <c r="D34" s="70" t="s">
         <v>83</v>
       </c>
@@ -2138,9 +2129,9 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="114"/>
-      <c r="B35" s="114"/>
-      <c r="C35" s="111" t="s">
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="115" t="s">
         <v>117</v>
       </c>
       <c r="D35" s="68" t="s">
@@ -2157,9 +2148,9 @@
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="114"/>
-      <c r="B36" s="114"/>
-      <c r="C36" s="112"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="116"/>
       <c r="D36" s="68" t="s">
         <v>118</v>
       </c>
@@ -2174,15 +2165,15 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="114"/>
-      <c r="B37" s="114"/>
-      <c r="C37" s="92" t="s">
+      <c r="A37" s="87"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="96" t="s">
         <v>101</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="108" t="s">
+      <c r="E37" s="112" t="s">
         <v>110</v>
       </c>
       <c r="F37" s="79" t="s">
@@ -2195,13 +2186,13 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="114"/>
-      <c r="B38" s="114"/>
-      <c r="C38" s="95"/>
+      <c r="A38" s="87"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="98"/>
       <c r="D38" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="109"/>
+      <c r="E38" s="113"/>
       <c r="F38" s="73" t="s">
         <v>9</v>
       </c>
@@ -2210,13 +2201,13 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="114"/>
-      <c r="B39" s="114"/>
-      <c r="C39" s="95"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="98"/>
       <c r="D39" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="86"/>
+      <c r="E39" s="93"/>
       <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
@@ -2225,9 +2216,9 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="114"/>
-      <c r="B40" s="114"/>
-      <c r="C40" s="92" t="s">
+      <c r="A40" s="87"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="96" t="s">
         <v>120</v>
       </c>
       <c r="D40" s="70" t="s">
@@ -2246,9 +2237,9 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="114"/>
-      <c r="B41" s="114"/>
-      <c r="C41" s="94"/>
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="97"/>
       <c r="D41" s="68" t="s">
         <v>122</v>
       </c>
@@ -2265,8 +2256,8 @@
       <c r="I41" s="34"/>
     </row>
     <row r="42" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="115"/>
-      <c r="B42" s="115"/>
+      <c r="A42" s="95"/>
+      <c r="B42" s="95"/>
       <c r="C42" s="80" t="s">
         <v>85</v>
       </c>
@@ -2301,13 +2292,13 @@
       <c r="I43" s="28"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="119" t="s">
+      <c r="A44" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="113" t="s">
+      <c r="B44" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="107" t="s">
+      <c r="C44" s="89" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="68" t="s">
@@ -2326,16 +2317,16 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="120"/>
-      <c r="B45" s="114"/>
-      <c r="C45" s="121"/>
+      <c r="A45" s="85"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="90"/>
       <c r="D45" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="85" t="s">
+      <c r="E45" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="F45" s="87" t="s">
+      <c r="F45" s="108" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="31"/>
@@ -2343,22 +2334,22 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="120"/>
-      <c r="B46" s="114"/>
-      <c r="C46" s="121"/>
+      <c r="A46" s="85"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="90"/>
       <c r="D46" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="86"/>
-      <c r="F46" s="88"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="107"/>
       <c r="G46" s="31"/>
       <c r="H46" s="3"/>
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="120"/>
-      <c r="B47" s="101"/>
-      <c r="C47" s="100"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="91"/>
       <c r="D47" s="70" t="s">
         <v>57</v>
       </c>
@@ -2373,9 +2364,9 @@
       <c r="I47" s="34"/>
     </row>
     <row r="48" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="120"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="90"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="92"/>
       <c r="D48" s="60" t="s">
         <v>27</v>
       </c>
@@ -2396,47 +2387,47 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="120"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="107" t="s">
+      <c r="A49" s="85"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="89" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="85" t="s">
+      <c r="E49" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="87" t="s">
+      <c r="F49" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="89" t="s">
+      <c r="G49" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="89" t="s">
+      <c r="H49" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="89" t="s">
+      <c r="I49" s="102" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="120"/>
-      <c r="B50" s="101"/>
-      <c r="C50" s="116"/>
+      <c r="A50" s="85"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="94"/>
       <c r="D50" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E50" s="86"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="90"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="90"/>
+      <c r="E50" s="93"/>
+      <c r="F50" s="107"/>
+      <c r="G50" s="92"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="92"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="120"/>
-      <c r="B51" s="101"/>
-      <c r="C51" s="107" t="s">
+      <c r="A51" s="85"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="89" t="s">
         <v>65</v>
       </c>
       <c r="D51" s="59" t="s">
@@ -2453,9 +2444,9 @@
       <c r="I51" s="28"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="120"/>
-      <c r="B52" s="101"/>
-      <c r="C52" s="90"/>
+      <c r="A52" s="85"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="92"/>
       <c r="D52" s="75" t="s">
         <v>130</v>
       </c>
@@ -2470,9 +2461,9 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="120"/>
-      <c r="B53" s="101"/>
-      <c r="C53" s="107" t="s">
+      <c r="A53" s="85"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="89" t="s">
         <v>66</v>
       </c>
       <c r="D53" s="59" t="s">
@@ -2481,7 +2472,7 @@
       <c r="E53" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="89" t="s">
+      <c r="F53" s="102" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="45"/>
@@ -2489,16 +2480,16 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="120"/>
-      <c r="B54" s="101"/>
-      <c r="C54" s="116"/>
+      <c r="A54" s="85"/>
+      <c r="B54" s="88"/>
+      <c r="C54" s="94"/>
       <c r="D54" s="59" t="s">
         <v>133</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F54" s="91"/>
+      <c r="F54" s="120"/>
       <c r="G54" s="45"/>
       <c r="H54" s="3"/>
       <c r="I54" s="32"/>
@@ -2515,13 +2506,13 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="113" t="s">
+      <c r="A56" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="113" t="s">
+      <c r="B56" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="107" t="s">
+      <c r="C56" s="89" t="s">
         <v>103</v>
       </c>
       <c r="D56" s="55" t="s">
@@ -2538,13 +2529,13 @@
       <c r="I56" s="39"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="114"/>
-      <c r="B57" s="114"/>
-      <c r="C57" s="121"/>
+      <c r="A57" s="87"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="90"/>
       <c r="D57" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="E57" s="85" t="s">
+      <c r="E57" s="104" t="s">
         <v>68</v>
       </c>
       <c r="F57" s="77" t="s">
@@ -2555,13 +2546,13 @@
       <c r="I57" s="39"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="114"/>
-      <c r="B58" s="114"/>
-      <c r="C58" s="121"/>
+      <c r="A58" s="87"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="90"/>
       <c r="D58" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="E58" s="86"/>
+      <c r="E58" s="93"/>
       <c r="F58" s="54" t="s">
         <v>7</v>
       </c>
@@ -2570,9 +2561,9 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="101"/>
-      <c r="B59" s="101"/>
-      <c r="C59" s="107" t="s">
+      <c r="A59" s="88"/>
+      <c r="B59" s="88"/>
+      <c r="C59" s="89" t="s">
         <v>104</v>
       </c>
       <c r="D59" s="60" t="s">
@@ -2589,9 +2580,9 @@
       <c r="I59" s="48"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="101"/>
-      <c r="B60" s="101"/>
-      <c r="C60" s="90"/>
+      <c r="A60" s="88"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="92"/>
       <c r="D60" s="60" t="s">
         <v>77</v>
       </c>
@@ -2606,8 +2597,8 @@
       <c r="I60" s="48"/>
     </row>
     <row r="61" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="101"/>
-      <c r="B61" s="101"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="67" t="s">
         <v>139</v>
       </c>
@@ -2625,9 +2616,9 @@
       <c r="I61" s="49"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="101"/>
-      <c r="B62" s="101"/>
-      <c r="C62" s="107" t="s">
+      <c r="A62" s="88"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="89" t="s">
         <v>69</v>
       </c>
       <c r="D62" s="68" t="s">
@@ -2644,9 +2635,9 @@
       <c r="I62" s="49"/>
     </row>
     <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="101"/>
-      <c r="B63" s="101"/>
-      <c r="C63" s="100"/>
+      <c r="A63" s="88"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="91"/>
       <c r="D63" s="60" t="s">
         <v>70</v>
       </c>
@@ -2661,9 +2652,9 @@
       <c r="I63" s="39"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="101"/>
-      <c r="B64" s="101"/>
-      <c r="C64" s="100"/>
+      <c r="A64" s="88"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="91"/>
       <c r="D64" s="70" t="s">
         <v>140</v>
       </c>
@@ -2678,9 +2669,9 @@
       <c r="I64" s="39"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="86"/>
-      <c r="B65" s="86"/>
-      <c r="C65" s="90"/>
+      <c r="A65" s="93"/>
+      <c r="B65" s="93"/>
+      <c r="C65" s="92"/>
       <c r="D65" s="68" t="s">
         <v>71</v>
       </c>
@@ -2893,28 +2884,17 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A44:A54"/>
-    <mergeCell ref="B44:B54"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="B56:B65"/>
-    <mergeCell ref="A56:A65"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="B31:B42"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A29"/>
-    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E57:E58"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="I49:I50"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="E12:E15"/>
@@ -2931,17 +2911,28 @@
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="C31:C34"/>
     <mergeCell ref="C35:C36"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="A31:A42"/>
+    <mergeCell ref="B31:B42"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A44:A54"/>
+    <mergeCell ref="B44:B54"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="B56:B65"/>
+    <mergeCell ref="A56:A65"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="C49:C50"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3CD986-8A89-4ABB-BCB7-EABF79418F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A75385-F564-4BF4-A650-242170C97874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="152">
   <si>
     <t>User Story</t>
   </si>
@@ -485,22 +485,16 @@
     <t>Check that page does not expose password after signup</t>
   </si>
   <si>
-    <t>User Password is endangered</t>
-  </si>
-  <si>
     <t>User password is endangered</t>
   </si>
   <si>
-    <t>Check that error message does not expose password at signup</t>
-  </si>
-  <si>
-    <t>Check that error message does not expose password at login</t>
-  </si>
-  <si>
     <t>Check that page does not expose password after login</t>
   </si>
   <si>
     <t>Check  passwords masking (type="password") for enhanced security</t>
+  </si>
+  <si>
+    <t>Check Register goes via https protocol (manual)</t>
   </si>
 </sst>
 </file>
@@ -832,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1140,18 +1134,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1192,6 +1177,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1528,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1609,7 +1600,7 @@
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="99"/>
-      <c r="B4" s="119"/>
+      <c r="B4" s="116"/>
       <c r="C4" s="101"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
@@ -1661,7 +1652,7 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="99"/>
       <c r="B7" s="100"/>
-      <c r="C7" s="117"/>
+      <c r="C7" s="114"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1701,7 +1692,7 @@
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="104" t="s">
+      <c r="E9" s="103" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1720,7 +1711,7 @@
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="99"/>
       <c r="B10" s="100"/>
-      <c r="C10" s="117"/>
+      <c r="C10" s="114"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
@@ -1752,13 +1743,13 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="99"/>
       <c r="B12" s="100"/>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="104" t="s">
+      <c r="D12" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="118" t="s">
         <v>148</v>
       </c>
       <c r="F12" s="105" t="s">
@@ -1771,11 +1762,11 @@
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="99"/>
       <c r="B13" s="100"/>
-      <c r="C13" s="91"/>
+      <c r="C13" s="88"/>
       <c r="D13" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="88"/>
+        <v>147</v>
+      </c>
+      <c r="E13" s="118"/>
       <c r="F13" s="106"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
@@ -1784,11 +1775,11 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="99"/>
       <c r="B14" s="100"/>
-      <c r="C14" s="91"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="E14" s="88"/>
+        <v>151</v>
+      </c>
+      <c r="E14" s="118"/>
       <c r="F14" s="106"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
@@ -1797,11 +1788,11 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="99"/>
       <c r="B15" s="100"/>
-      <c r="C15" s="92"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="93"/>
+        <v>150</v>
+      </c>
+      <c r="E15" s="119"/>
       <c r="F15" s="107"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
@@ -1861,7 +1852,7 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="99"/>
       <c r="B19" s="100"/>
-      <c r="C19" s="118"/>
+      <c r="C19" s="115"/>
       <c r="D19" s="70" t="s">
         <v>82</v>
       </c>
@@ -1884,7 +1875,7 @@
       <c r="D20" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="104" t="s">
+      <c r="E20" s="103" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="65" t="s">
@@ -1937,12 +1928,12 @@
       <c r="B23" s="100"/>
       <c r="C23" s="91"/>
       <c r="D23" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23" s="104" t="s">
-        <v>149</v>
-      </c>
-      <c r="F23" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="105" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1954,42 +1945,36 @@
       <c r="B24" s="100"/>
       <c r="C24" s="91"/>
       <c r="D24" s="60" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E24" s="88"/>
-      <c r="F24" s="109"/>
+      <c r="F24" s="106"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="100"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="100"/>
-      <c r="C25" s="92"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" s="93"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="39"/>
-    </row>
-    <row r="26" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="E25" s="88"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="32"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="100"/>
       <c r="B26" s="100"/>
-      <c r="C26" s="61" t="s">
-        <v>108</v>
-      </c>
+      <c r="C26" s="92"/>
       <c r="D26" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" s="56" t="s">
-        <v>7</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E26" s="93"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="31"/>
       <c r="H26" s="1"/>
       <c r="I26" s="39"/>
@@ -1997,49 +1982,53 @@
     <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="100"/>
       <c r="B27" s="100"/>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="70" t="s">
-        <v>39</v>
+      <c r="D27" s="60" t="s">
+        <v>109</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="71" t="s">
-        <v>9</v>
+        <v>38</v>
+      </c>
+      <c r="F27" s="56" t="s">
+        <v>7</v>
       </c>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="100"/>
       <c r="B28" s="100"/>
-      <c r="C28" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="56" t="s">
-        <v>7</v>
+      <c r="C28" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="G28" s="31"/>
       <c r="H28" s="1"/>
       <c r="I28" s="39"/>
     </row>
-    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="100"/>
       <c r="B29" s="100"/>
-      <c r="C29" s="94"/>
+      <c r="C29" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="D29" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="111"/>
+        <v>84</v>
+      </c>
+      <c r="E29" s="108" t="s">
+        <v>38</v>
+      </c>
       <c r="F29" s="56" t="s">
         <v>7</v>
       </c>
@@ -2047,52 +2036,50 @@
       <c r="H29" s="1"/>
       <c r="I29" s="39"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="19"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="32"/>
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="100"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="108"/>
+      <c r="F30" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="31"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="31"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="1"/>
       <c r="H31" s="3"/>
       <c r="I31" s="32"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="104" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" s="108" t="s">
-        <v>7</v>
+      <c r="A32" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="86" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="89" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="68" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="79" t="s">
+        <v>13</v>
       </c>
       <c r="G32" s="31"/>
       <c r="H32" s="3"/>
@@ -2103,59 +2090,59 @@
       <c r="B33" s="87"/>
       <c r="C33" s="91"/>
       <c r="D33" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" s="93"/>
-      <c r="F33" s="114"/>
+        <v>115</v>
+      </c>
+      <c r="E33" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="105" t="s">
+        <v>7</v>
+      </c>
       <c r="G33" s="31"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
-    <row r="34" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="87"/>
       <c r="B34" s="87"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="72" t="s">
-        <v>9</v>
-      </c>
+      <c r="C34" s="91"/>
+      <c r="D34" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="93"/>
+      <c r="F34" s="111"/>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="87"/>
       <c r="B35" s="87"/>
-      <c r="C35" s="115" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>55</v>
+      <c r="C35" s="92"/>
+      <c r="D35" s="70" t="s">
+        <v>83</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="78" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F35" s="72" t="s">
+        <v>9</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
-    <row r="36" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="87"/>
       <c r="B36" s="87"/>
-      <c r="C36" s="116"/>
+      <c r="C36" s="112" t="s">
+        <v>117</v>
+      </c>
       <c r="D36" s="68" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F36" s="78" t="s">
         <v>13</v>
@@ -2164,50 +2151,52 @@
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="87"/>
       <c r="B37" s="87"/>
-      <c r="C37" s="96" t="s">
-        <v>101</v>
-      </c>
+      <c r="C37" s="113"/>
       <c r="D37" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="112" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="45"/>
-      <c r="H37" s="82" t="s">
-        <v>119</v>
-      </c>
+      <c r="G37" s="31"/>
+      <c r="H37" s="3"/>
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="87"/>
       <c r="B38" s="87"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="113"/>
-      <c r="F38" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="3"/>
+      <c r="C38" s="96" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="45"/>
+      <c r="H38" s="82" t="s">
+        <v>119</v>
+      </c>
       <c r="I38" s="32"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="87"/>
       <c r="B39" s="87"/>
       <c r="C39" s="98"/>
       <c r="D39" s="70" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="93"/>
+        <v>112</v>
+      </c>
+      <c r="E39" s="110"/>
       <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
@@ -2218,118 +2207,116 @@
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="87"/>
       <c r="B40" s="87"/>
-      <c r="C40" s="96" t="s">
-        <v>120</v>
-      </c>
+      <c r="C40" s="98"/>
       <c r="D40" s="70" t="s">
-        <v>86</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F40" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="93"/>
+      <c r="F40" s="73" t="s">
         <v>9</v>
       </c>
       <c r="G40" s="31"/>
-      <c r="H40" s="52" t="s">
-        <v>121</v>
-      </c>
+      <c r="H40" s="3"/>
       <c r="I40" s="32"/>
     </row>
-    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="87"/>
       <c r="B41" s="87"/>
-      <c r="C41" s="97"/>
-      <c r="D41" s="68" t="s">
+      <c r="C41" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="32"/>
+    </row>
+    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="87"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="97"/>
+      <c r="D42" s="68" t="s">
         <v>122</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E42" s="23" t="s">
         <v>88</v>
-      </c>
-      <c r="F41" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="33"/>
-      <c r="H41" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="I41" s="34"/>
-    </row>
-    <row r="42" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="95"/>
-      <c r="B42" s="95"/>
-      <c r="C42" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="F42" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="81" t="s">
+      <c r="G42" s="33"/>
+      <c r="H42" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="I42" s="34"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="95"/>
+      <c r="B43" s="95"/>
+      <c r="C43" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="68" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="H42" s="81" t="s">
+      <c r="H43" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="I42" s="81" t="s">
+      <c r="I43" s="81" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="28"/>
-    </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="28"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="86" t="s">
+      <c r="B45" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="89" t="s">
+      <c r="C45" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="68" t="s">
+      <c r="D45" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E45" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F44" s="69" t="s">
+      <c r="F45" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G45" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" s="104" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" s="108" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="31"/>
       <c r="H45" s="3"/>
       <c r="I45" s="32"/>
     </row>
@@ -2338,142 +2325,140 @@
       <c r="B46" s="87"/>
       <c r="C46" s="90"/>
       <c r="D46" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="93"/>
-      <c r="F46" s="107"/>
+        <v>126</v>
+      </c>
+      <c r="E46" s="103" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="105" t="s">
+        <v>7</v>
+      </c>
       <c r="G46" s="31"/>
       <c r="H46" s="3"/>
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="85"/>
-      <c r="B47" s="88"/>
-      <c r="C47" s="91"/>
-      <c r="D47" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="33"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="34"/>
-    </row>
-    <row r="48" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="87"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="93"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="85"/>
       <c r="B48" s="88"/>
-      <c r="C48" s="92"/>
-      <c r="D48" s="60" t="s">
-        <v>27</v>
+      <c r="C48" s="91"/>
+      <c r="D48" s="70" t="s">
+        <v>57</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F48" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H48" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I48" s="56" t="s">
-        <v>18</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F48" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="33"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="34"/>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="85"/>
       <c r="B49" s="88"/>
-      <c r="C49" s="89" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E49" s="104" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="108" t="s">
+      <c r="C49" s="92"/>
+      <c r="D49" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="102" t="s">
+      <c r="G49" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="102" t="s">
+      <c r="H49" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="102" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I49" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="85"/>
       <c r="B50" s="88"/>
-      <c r="C50" s="94"/>
+      <c r="C50" s="89" t="s">
+        <v>93</v>
+      </c>
       <c r="D50" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E50" s="93"/>
-      <c r="F50" s="107"/>
-      <c r="G50" s="92"/>
-      <c r="H50" s="92"/>
-      <c r="I50" s="92"/>
+        <v>128</v>
+      </c>
+      <c r="E50" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="F50" s="105" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="102" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="85"/>
       <c r="B51" s="88"/>
-      <c r="C51" s="89" t="s">
-        <v>65</v>
-      </c>
+      <c r="C51" s="94"/>
       <c r="D51" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="44"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="28"/>
+        <v>129</v>
+      </c>
+      <c r="E51" s="93"/>
+      <c r="F51" s="104"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="85"/>
       <c r="B52" s="88"/>
-      <c r="C52" s="92"/>
-      <c r="D52" s="75" t="s">
-        <v>130</v>
+      <c r="C52" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>131</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="45"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="32"/>
+        <v>95</v>
+      </c>
+      <c r="F52" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="44"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="85"/>
       <c r="B53" s="88"/>
-      <c r="C53" s="89" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>132</v>
+      <c r="C53" s="92"/>
+      <c r="D53" s="75" t="s">
+        <v>130</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F53" s="102" t="s">
-        <v>7</v>
+        <v>64</v>
+      </c>
+      <c r="F53" s="74" t="s">
+        <v>9</v>
       </c>
       <c r="G53" s="45"/>
       <c r="H53" s="3"/>
@@ -2482,64 +2467,66 @@
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="85"/>
       <c r="B54" s="88"/>
-      <c r="C54" s="94"/>
+      <c r="C54" s="89" t="s">
+        <v>66</v>
+      </c>
       <c r="D54" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="120"/>
+        <v>96</v>
+      </c>
+      <c r="F54" s="102" t="s">
+        <v>7</v>
+      </c>
       <c r="G54" s="45"/>
       <c r="H54" s="3"/>
       <c r="I54" s="32"/>
     </row>
-    <row r="55" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="43"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="1"/>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="85"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="117"/>
+      <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
     </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="86" t="s">
+    <row r="56" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="43"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="32"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="86" t="s">
+      <c r="B57" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="89" t="s">
+      <c r="C57" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D57" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="23" t="s">
+      <c r="E57" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F56" s="57" t="s">
+      <c r="F57" s="57" t="s">
         <v>7</v>
-      </c>
-      <c r="G56" s="46"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="39"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="87"/>
-      <c r="B57" s="87"/>
-      <c r="C57" s="90"/>
-      <c r="D57" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" s="104" t="s">
-        <v>68</v>
-      </c>
-      <c r="F57" s="77" t="s">
-        <v>9</v>
       </c>
       <c r="G57" s="46"/>
       <c r="H57" s="1"/>
@@ -2549,45 +2536,45 @@
       <c r="A58" s="87"/>
       <c r="B58" s="87"/>
       <c r="C58" s="90"/>
-      <c r="D58" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="93"/>
-      <c r="F58" s="54" t="s">
-        <v>7</v>
+      <c r="D58" s="70" t="s">
+        <v>136</v>
+      </c>
+      <c r="E58" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="77" t="s">
+        <v>9</v>
       </c>
       <c r="G58" s="46"/>
       <c r="H58" s="1"/>
       <c r="I58" s="39"/>
     </row>
-    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="88"/>
-      <c r="C59" s="89" t="s">
-        <v>104</v>
-      </c>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="87"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="90"/>
       <c r="D59" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>97</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E59" s="93"/>
       <c r="F59" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="31"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="48"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="88"/>
       <c r="B60" s="88"/>
-      <c r="C60" s="92"/>
+      <c r="C60" s="89" t="s">
+        <v>104</v>
+      </c>
       <c r="D60" s="60" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F60" s="54" t="s">
         <v>7</v>
@@ -2596,36 +2583,34 @@
       <c r="H60" s="47"/>
       <c r="I60" s="48"/>
     </row>
-    <row r="61" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="88"/>
       <c r="B61" s="88"/>
-      <c r="C61" s="67" t="s">
-        <v>139</v>
-      </c>
-      <c r="D61" s="68" t="s">
-        <v>138</v>
+      <c r="C61" s="92"/>
+      <c r="D61" s="60" t="s">
+        <v>77</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" s="69" t="s">
-        <v>13</v>
+        <v>76</v>
+      </c>
+      <c r="F61" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G61" s="31"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="49"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H61" s="47"/>
+      <c r="I61" s="48"/>
+    </row>
+    <row r="62" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="88"/>
       <c r="B62" s="88"/>
-      <c r="C62" s="89" t="s">
-        <v>69</v>
+      <c r="C62" s="67" t="s">
+        <v>139</v>
       </c>
       <c r="D62" s="68" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F62" s="69" t="s">
         <v>13</v>
@@ -2634,107 +2619,119 @@
       <c r="H62" s="1"/>
       <c r="I62" s="49"/>
     </row>
-    <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="88"/>
       <c r="B63" s="88"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="60" t="s">
-        <v>70</v>
+      <c r="C63" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="68" t="s">
+        <v>74</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="54" t="s">
-        <v>7</v>
+        <v>75</v>
+      </c>
+      <c r="F63" s="69" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="31"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="39"/>
+      <c r="I63" s="49"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="88"/>
       <c r="B64" s="88"/>
       <c r="C64" s="91"/>
-      <c r="D64" s="70" t="s">
-        <v>140</v>
+      <c r="D64" s="60" t="s">
+        <v>70</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="71" t="s">
-        <v>9</v>
+        <v>141</v>
+      </c>
+      <c r="F64" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G64" s="31"/>
       <c r="H64" s="1"/>
       <c r="I64" s="39"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="93"/>
-      <c r="B65" s="93"/>
-      <c r="C65" s="92"/>
-      <c r="D65" s="68" t="s">
+    <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="88"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="70" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F65" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G65" s="31"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="39"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="93"/>
+      <c r="B66" s="93"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E66" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F65" s="69" t="s">
+      <c r="F66" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="33"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="40"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="22"/>
-      <c r="B66" s="22"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="22"/>
-    </row>
-    <row r="67" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="2"/>
-      <c r="E67" s="5"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G66" s="33"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="40"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27"/>
+      <c r="I67" s="22"/>
+    </row>
+    <row r="68" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="E68" s="5"/>
-      <c r="G68" s="1"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="2"/>
+      <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
       <c r="E69" s="5"/>
-      <c r="G69" s="2"/>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="E70" s="5"/>
-      <c r="G70" s="1"/>
+      <c r="G70" s="2"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="2"/>
+      <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="E71" s="5"/>
-      <c r="G71" s="2"/>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
+      <c r="I71" s="2"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="E72" s="5"/>
-      <c r="G72" s="1"/>
+      <c r="G72" s="2"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
@@ -2746,30 +2743,30 @@
       <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="3"/>
-      <c r="E74" s="7"/>
+      <c r="B74" s="2"/>
+      <c r="E74" s="5"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B75" s="3"/>
-      <c r="E75" s="5"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="E75" s="7"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="E76" s="7"/>
-    </row>
-    <row r="77" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="3"/>
+      <c r="E76" s="5"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="E77" s="7"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
-      <c r="E78" s="5"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
@@ -2794,7 +2791,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
-      <c r="E82" s="7"/>
+      <c r="E82" s="5"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
@@ -2802,14 +2802,14 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
-      <c r="E84" s="5"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="E84" s="7"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
-      <c r="E85" s="7"/>
+      <c r="E85" s="5"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
@@ -2832,6 +2832,7 @@
       <c r="E90" s="7"/>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91" s="2"/>
       <c r="E91" s="7"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
@@ -2882,57 +2883,60 @@
     <row r="107" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E107" s="7"/>
     </row>
+    <row r="108" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E108" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E57:E58"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="F54:F55"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="I49:I50"/>
     <mergeCell ref="C12:C15"/>
+    <mergeCell ref="I50:I51"/>
     <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="E37:E39"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="A31:A42"/>
-    <mergeCell ref="B31:B42"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A32:A43"/>
+    <mergeCell ref="B32:B43"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C38:C40"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B17:B30"/>
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="A17:A30"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A44:A54"/>
-    <mergeCell ref="B44:B54"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="B56:B65"/>
-    <mergeCell ref="A56:A65"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="A45:A55"/>
+    <mergeCell ref="B45:B55"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="A57:A66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C50:C51"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A75385-F564-4BF4-A650-242170C97874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67310A35-B1AD-4D60-91EA-D01CFAB72334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -826,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1077,112 +1077,130 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1576,13 +1594,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="116" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1599,9 +1617,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="101"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="116"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
@@ -1627,13 +1645,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="93" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="70" t="s">
@@ -1650,9 +1668,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="114"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="115"/>
+      <c r="C7" s="94"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1667,9 +1685,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="97"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="115"/>
+      <c r="C8" s="95"/>
       <c r="D8" s="70" t="s">
         <v>106</v>
       </c>
@@ -1684,15 +1702,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="96" t="s">
+      <c r="A9" s="98"/>
+      <c r="B9" s="115"/>
+      <c r="C9" s="93" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="87" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1709,13 +1727,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="114"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="94"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="93"/>
+      <c r="E10" s="88"/>
       <c r="F10" s="78" t="s">
         <v>13</v>
       </c>
@@ -1724,9 +1742,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="97"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="70" t="s">
         <v>36</v>
       </c>
@@ -1741,18 +1759,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="89" t="s">
+      <c r="A12" s="98"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="123" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="118" t="s">
+      <c r="E12" s="102" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="105" t="s">
+      <c r="F12" s="120" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1760,40 +1778,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="88"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="118"/>
-      <c r="F13" s="106"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="121"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="88"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="124"/>
       <c r="D14" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="118"/>
-      <c r="F14" s="106"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="121"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="93"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="125"/>
       <c r="D15" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="119"/>
-      <c r="F15" s="107"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1810,13 +1828,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="93" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="70" t="s">
@@ -1833,9 +1851,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="98"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="96"/>
       <c r="D18" s="62" t="s">
         <v>107</v>
       </c>
@@ -1850,9 +1868,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="115"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="70" t="s">
         <v>82</v>
       </c>
@@ -1867,15 +1885,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="89" t="s">
+      <c r="A20" s="98"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="100" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="103" t="s">
+      <c r="E20" s="87" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="65" t="s">
@@ -1892,13 +1910,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="91"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="105"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="93"/>
+      <c r="E21" s="88"/>
       <c r="F21" s="69" t="s">
         <v>13</v>
       </c>
@@ -1907,9 +1925,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="91"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="105"/>
       <c r="D22" s="70" t="s">
         <v>36</v>
       </c>
@@ -1924,16 +1942,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="91"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="E23" s="103" t="s">
+      <c r="E23" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="105" t="s">
+      <c r="F23" s="84" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1941,47 +1959,47 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="91"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="105"/>
       <c r="D24" s="60" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="88"/>
-      <c r="F24" s="106"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="85"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="99"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="91"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="105"/>
       <c r="D25" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="E25" s="88"/>
-      <c r="F25" s="106"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="100"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="115"/>
+      <c r="B26" s="115"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="93"/>
-      <c r="F26" s="107"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="86"/>
       <c r="G26" s="31"/>
       <c r="H26" s="1"/>
       <c r="I26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="100"/>
-      <c r="B27" s="100"/>
+      <c r="A27" s="115"/>
+      <c r="B27" s="115"/>
       <c r="C27" s="61" t="s">
         <v>108</v>
       </c>
@@ -1999,8 +2017,8 @@
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="100"/>
-      <c r="B28" s="100"/>
+      <c r="A28" s="115"/>
+      <c r="B28" s="115"/>
       <c r="C28" s="83" t="s">
         <v>108</v>
       </c>
@@ -2018,15 +2036,15 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="100"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="89" t="s">
+      <c r="A29" s="115"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="100" t="s">
         <v>42</v>
       </c>
       <c r="D29" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="108" t="s">
+      <c r="E29" s="104" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="56" t="s">
@@ -2037,13 +2055,13 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="100"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="94"/>
+      <c r="A30" s="115"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="114"/>
       <c r="D30" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="108"/>
+      <c r="E30" s="104"/>
       <c r="F30" s="56" t="s">
         <v>7</v>
       </c>
@@ -2063,13 +2081,13 @@
       <c r="I31" s="32"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="86" t="s">
+      <c r="A32" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="89" t="s">
+      <c r="C32" s="100" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="68" t="s">
@@ -2086,16 +2104,16 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="91"/>
+      <c r="A33" s="112"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="105"/>
       <c r="D33" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="103" t="s">
+      <c r="E33" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="F33" s="105" t="s">
+      <c r="F33" s="84" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="31"/>
@@ -2103,22 +2121,22 @@
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="91"/>
+      <c r="A34" s="112"/>
+      <c r="B34" s="112"/>
+      <c r="C34" s="105"/>
       <c r="D34" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="111"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="108"/>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="92"/>
+      <c r="A35" s="112"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="91"/>
       <c r="D35" s="70" t="s">
         <v>83</v>
       </c>
@@ -2133,9 +2151,9 @@
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="112" t="s">
+      <c r="A36" s="112"/>
+      <c r="B36" s="112"/>
+      <c r="C36" s="109" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="68" t="s">
@@ -2152,9 +2170,9 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="113"/>
+      <c r="A37" s="112"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="110"/>
       <c r="D37" s="68" t="s">
         <v>118</v>
       </c>
@@ -2169,15 +2187,15 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="87"/>
-      <c r="C38" s="96" t="s">
+      <c r="A38" s="112"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="93" t="s">
         <v>101</v>
       </c>
       <c r="D38" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="109" t="s">
+      <c r="E38" s="106" t="s">
         <v>110</v>
       </c>
       <c r="F38" s="79" t="s">
@@ -2190,13 +2208,13 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="98"/>
+      <c r="A39" s="112"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="96"/>
       <c r="D39" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="110"/>
+      <c r="E39" s="107"/>
       <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
@@ -2205,13 +2223,13 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="98"/>
+      <c r="A40" s="112"/>
+      <c r="B40" s="112"/>
+      <c r="C40" s="96"/>
       <c r="D40" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="93"/>
+      <c r="E40" s="88"/>
       <c r="F40" s="73" t="s">
         <v>9</v>
       </c>
@@ -2220,9 +2238,9 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="96" t="s">
+      <c r="A41" s="112"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="93" t="s">
         <v>120</v>
       </c>
       <c r="D41" s="70" t="s">
@@ -2241,9 +2259,9 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="87"/>
-      <c r="C42" s="97"/>
+      <c r="A42" s="112"/>
+      <c r="B42" s="112"/>
+      <c r="C42" s="95"/>
       <c r="D42" s="68" t="s">
         <v>122</v>
       </c>
@@ -2260,8 +2278,8 @@
       <c r="I42" s="34"/>
     </row>
     <row r="43" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="95"/>
-      <c r="B43" s="95"/>
+      <c r="A43" s="113"/>
+      <c r="B43" s="113"/>
       <c r="C43" s="80" t="s">
         <v>85</v>
       </c>
@@ -2296,13 +2314,13 @@
       <c r="I44" s="28"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="84" t="s">
+      <c r="A45" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="86" t="s">
+      <c r="B45" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="89" t="s">
+      <c r="C45" s="100" t="s">
         <v>90</v>
       </c>
       <c r="D45" s="68" t="s">
@@ -2321,16 +2339,16 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="90"/>
+      <c r="A46" s="118"/>
+      <c r="B46" s="112"/>
+      <c r="C46" s="119"/>
       <c r="D46" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="103" t="s">
+      <c r="E46" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="F46" s="105" t="s">
+      <c r="F46" s="84" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="31"/>
@@ -2338,22 +2356,22 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="87"/>
-      <c r="C47" s="90"/>
+      <c r="A47" s="118"/>
+      <c r="B47" s="112"/>
+      <c r="C47" s="119"/>
       <c r="D47" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="93"/>
-      <c r="F47" s="104"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="89"/>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="91"/>
+      <c r="A48" s="118"/>
+      <c r="B48" s="101"/>
+      <c r="C48" s="105"/>
       <c r="D48" s="70" t="s">
         <v>57</v>
       </c>
@@ -2368,9 +2386,9 @@
       <c r="I48" s="34"/>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
-      <c r="B49" s="88"/>
-      <c r="C49" s="92"/>
+      <c r="A49" s="118"/>
+      <c r="B49" s="101"/>
+      <c r="C49" s="91"/>
       <c r="D49" s="60" t="s">
         <v>27</v>
       </c>
@@ -2391,47 +2409,47 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
-      <c r="B50" s="88"/>
-      <c r="C50" s="89" t="s">
+      <c r="A50" s="118"/>
+      <c r="B50" s="101"/>
+      <c r="C50" s="100" t="s">
         <v>93</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="103" t="s">
+      <c r="E50" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="105" t="s">
+      <c r="F50" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="102" t="s">
+      <c r="G50" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="102" t="s">
+      <c r="H50" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="102" t="s">
+      <c r="I50" s="90" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
-      <c r="B51" s="88"/>
-      <c r="C51" s="94"/>
+      <c r="A51" s="118"/>
+      <c r="B51" s="101"/>
+      <c r="C51" s="114"/>
       <c r="D51" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E51" s="93"/>
-      <c r="F51" s="104"/>
-      <c r="G51" s="92"/>
-      <c r="H51" s="92"/>
-      <c r="I51" s="92"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="89"/>
+      <c r="G51" s="91"/>
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
-      <c r="B52" s="88"/>
-      <c r="C52" s="89" t="s">
+      <c r="A52" s="118"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="100" t="s">
         <v>65</v>
       </c>
       <c r="D52" s="59" t="s">
@@ -2448,9 +2466,9 @@
       <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
-      <c r="B53" s="88"/>
-      <c r="C53" s="92"/>
+      <c r="A53" s="118"/>
+      <c r="B53" s="101"/>
+      <c r="C53" s="91"/>
       <c r="D53" s="75" t="s">
         <v>130</v>
       </c>
@@ -2465,9 +2483,9 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="85"/>
-      <c r="B54" s="88"/>
-      <c r="C54" s="89" t="s">
+      <c r="A54" s="118"/>
+      <c r="B54" s="101"/>
+      <c r="C54" s="100" t="s">
         <v>66</v>
       </c>
       <c r="D54" s="59" t="s">
@@ -2476,7 +2494,7 @@
       <c r="E54" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F54" s="102" t="s">
+      <c r="F54" s="90" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="45"/>
@@ -2484,16 +2502,16 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="85"/>
-      <c r="B55" s="88"/>
-      <c r="C55" s="94"/>
+      <c r="A55" s="118"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="114"/>
       <c r="D55" s="59" t="s">
         <v>133</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F55" s="117"/>
+      <c r="F55" s="92"/>
       <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
@@ -2510,13 +2528,13 @@
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="86" t="s">
+      <c r="B57" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="89" t="s">
+      <c r="C57" s="100" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="55" t="s">
@@ -2533,13 +2551,13 @@
       <c r="I57" s="39"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="87"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="90"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="119"/>
       <c r="D58" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="E58" s="103" t="s">
+      <c r="E58" s="87" t="s">
         <v>68</v>
       </c>
       <c r="F58" s="77" t="s">
@@ -2550,13 +2568,13 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="87"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="90"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="119"/>
       <c r="D59" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="E59" s="93"/>
+      <c r="E59" s="88"/>
       <c r="F59" s="54" t="s">
         <v>7</v>
       </c>
@@ -2565,9 +2583,9 @@
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="89" t="s">
+      <c r="A60" s="101"/>
+      <c r="B60" s="101"/>
+      <c r="C60" s="100" t="s">
         <v>104</v>
       </c>
       <c r="D60" s="60" t="s">
@@ -2584,9 +2602,9 @@
       <c r="I60" s="48"/>
     </row>
     <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="88"/>
-      <c r="C61" s="92"/>
+      <c r="A61" s="101"/>
+      <c r="B61" s="101"/>
+      <c r="C61" s="91"/>
       <c r="D61" s="60" t="s">
         <v>77</v>
       </c>
@@ -2601,8 +2619,8 @@
       <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="88"/>
+      <c r="A62" s="101"/>
+      <c r="B62" s="101"/>
       <c r="C62" s="67" t="s">
         <v>139</v>
       </c>
@@ -2620,9 +2638,9 @@
       <c r="I62" s="49"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
-      <c r="B63" s="88"/>
-      <c r="C63" s="89" t="s">
+      <c r="A63" s="101"/>
+      <c r="B63" s="101"/>
+      <c r="C63" s="100" t="s">
         <v>69</v>
       </c>
       <c r="D63" s="68" t="s">
@@ -2639,9 +2657,9 @@
       <c r="I63" s="49"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="88"/>
-      <c r="C64" s="91"/>
+      <c r="A64" s="101"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="105"/>
       <c r="D64" s="60" t="s">
         <v>70</v>
       </c>
@@ -2656,9 +2674,9 @@
       <c r="I64" s="39"/>
     </row>
     <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
-      <c r="B65" s="88"/>
-      <c r="C65" s="91"/>
+      <c r="A65" s="101"/>
+      <c r="B65" s="101"/>
+      <c r="C65" s="105"/>
       <c r="D65" s="70" t="s">
         <v>140</v>
       </c>
@@ -2673,9 +2691,9 @@
       <c r="I65" s="39"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="93"/>
-      <c r="B66" s="93"/>
-      <c r="C66" s="92"/>
+      <c r="A66" s="88"/>
+      <c r="B66" s="88"/>
+      <c r="C66" s="91"/>
       <c r="D66" s="68" t="s">
         <v>71</v>
       </c>
@@ -2888,17 +2906,28 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A45:A55"/>
+    <mergeCell ref="B45:B55"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="A57:A66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A32:A43"/>
+    <mergeCell ref="B32:B43"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="B17:B30"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A30"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="I50:I51"/>
@@ -2915,28 +2944,17 @@
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="C32:C35"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A32:A43"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B17:B30"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A45:A55"/>
-    <mergeCell ref="B45:B55"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="A57:A66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67310A35-B1AD-4D60-91EA-D01CFAB72334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3500E6-8691-4132-B7EE-D66D6FC64761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1077,7 +1077,88 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1089,118 +1170,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1594,13 +1594,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="101" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1617,9 +1617,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="116"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="101"/>
       <c r="D4" s="70" t="s">
         <v>21</v>
       </c>
@@ -1645,13 +1645,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="93" t="s">
+      <c r="C6" s="96" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="70" t="s">
@@ -1668,9 +1668,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
-      <c r="B7" s="115"/>
-      <c r="C7" s="94"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="120"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1685,9 +1685,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
-      <c r="B8" s="115"/>
-      <c r="C8" s="95"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="70" t="s">
         <v>106</v>
       </c>
@@ -1702,15 +1702,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="93" t="s">
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="96" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="114" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1727,13 +1727,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
-      <c r="B10" s="115"/>
-      <c r="C10" s="94"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="120"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="88"/>
+      <c r="E10" s="93"/>
       <c r="F10" s="78" t="s">
         <v>13</v>
       </c>
@@ -1742,9 +1742,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="98"/>
-      <c r="B11" s="115"/>
-      <c r="C11" s="95"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="70" t="s">
         <v>36</v>
       </c>
@@ -1759,18 +1759,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="123" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="103" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="109" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="122" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1778,40 +1778,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="98"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="124"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="104"/>
       <c r="D13" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="121"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="123"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="98"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="124"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="104"/>
       <c r="D14" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="121"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="123"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="98"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="125"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="103"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="124"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1828,13 +1828,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="98" t="s">
+      <c r="A17" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="96" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="70" t="s">
@@ -1851,9 +1851,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="98"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="96"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="62" t="s">
         <v>107</v>
       </c>
@@ -1868,9 +1868,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="98"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="97"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="70" t="s">
         <v>82</v>
       </c>
@@ -1885,15 +1885,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="98"/>
-      <c r="B20" s="115"/>
-      <c r="C20" s="100" t="s">
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="89" t="s">
         <v>146</v>
       </c>
       <c r="D20" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="87" t="s">
+      <c r="E20" s="114" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="65" t="s">
@@ -1910,13 +1910,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="98"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="105"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="91"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="88"/>
+      <c r="E21" s="93"/>
       <c r="F21" s="69" t="s">
         <v>13</v>
       </c>
@@ -1925,9 +1925,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="98"/>
-      <c r="B22" s="115"/>
-      <c r="C22" s="105"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="70" t="s">
         <v>36</v>
       </c>
@@ -1942,16 +1942,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="98"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="105"/>
-      <c r="D23" s="60" t="s">
+      <c r="A23" s="99"/>
+      <c r="B23" s="100"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="E23" s="87" t="s">
+      <c r="E23" s="114" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="84" t="s">
+      <c r="F23" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1959,47 +1959,47 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="98"/>
-      <c r="B24" s="115"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="60" t="s">
+      <c r="A24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="85"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="112"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="98"/>
-      <c r="B25" s="115"/>
-      <c r="C25" s="105"/>
+      <c r="A25" s="99"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="85"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="115"/>
-      <c r="B26" s="115"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="88"/>
-      <c r="F26" s="86"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="113"/>
       <c r="G26" s="31"/>
       <c r="H26" s="1"/>
       <c r="I26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
-      <c r="B27" s="115"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="100"/>
       <c r="C27" s="61" t="s">
         <v>108</v>
       </c>
@@ -2017,8 +2017,8 @@
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="115"/>
-      <c r="B28" s="115"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="100"/>
       <c r="C28" s="83" t="s">
         <v>108</v>
       </c>
@@ -2036,15 +2036,15 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="115"/>
-      <c r="B29" s="115"/>
-      <c r="C29" s="100" t="s">
+      <c r="A29" s="100"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="89" t="s">
         <v>42</v>
       </c>
       <c r="D29" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E29" s="104" t="s">
+      <c r="E29" s="116" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="56" t="s">
@@ -2055,13 +2055,13 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="115"/>
-      <c r="B30" s="115"/>
-      <c r="C30" s="114"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="94"/>
       <c r="D30" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="104"/>
+      <c r="E30" s="116"/>
       <c r="F30" s="56" t="s">
         <v>7</v>
       </c>
@@ -2081,13 +2081,13 @@
       <c r="I31" s="32"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="111" t="s">
+      <c r="A32" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="111" t="s">
+      <c r="B32" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="100" t="s">
+      <c r="C32" s="89" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="68" t="s">
@@ -2104,16 +2104,16 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="112"/>
-      <c r="B33" s="112"/>
-      <c r="C33" s="105"/>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="87" t="s">
+      <c r="E33" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="F33" s="84" t="s">
+      <c r="F33" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="31"/>
@@ -2121,22 +2121,22 @@
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="112"/>
-      <c r="B34" s="112"/>
-      <c r="C34" s="105"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="91"/>
       <c r="D34" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="88"/>
-      <c r="F34" s="108"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="119"/>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="112"/>
-      <c r="B35" s="112"/>
-      <c r="C35" s="91"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="92"/>
       <c r="D35" s="70" t="s">
         <v>83</v>
       </c>
@@ -2151,9 +2151,9 @@
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="112"/>
-      <c r="B36" s="112"/>
-      <c r="C36" s="109" t="s">
+      <c r="A36" s="87"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="106" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="68" t="s">
@@ -2170,9 +2170,9 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="112"/>
-      <c r="B37" s="112"/>
-      <c r="C37" s="110"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="107"/>
       <c r="D37" s="68" t="s">
         <v>118</v>
       </c>
@@ -2187,15 +2187,15 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="112"/>
-      <c r="B38" s="112"/>
-      <c r="C38" s="93" t="s">
+      <c r="A38" s="87"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="96" t="s">
         <v>101</v>
       </c>
       <c r="D38" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="106" t="s">
+      <c r="E38" s="117" t="s">
         <v>110</v>
       </c>
       <c r="F38" s="79" t="s">
@@ -2208,13 +2208,13 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="112"/>
-      <c r="B39" s="112"/>
-      <c r="C39" s="96"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="98"/>
       <c r="D39" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="107"/>
+      <c r="E39" s="118"/>
       <c r="F39" s="73" t="s">
         <v>9</v>
       </c>
@@ -2223,13 +2223,13 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="112"/>
-      <c r="B40" s="112"/>
-      <c r="C40" s="96"/>
+      <c r="A40" s="87"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="98"/>
       <c r="D40" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="88"/>
+      <c r="E40" s="93"/>
       <c r="F40" s="73" t="s">
         <v>9</v>
       </c>
@@ -2238,9 +2238,9 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="112"/>
-      <c r="B41" s="112"/>
-      <c r="C41" s="93" t="s">
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="96" t="s">
         <v>120</v>
       </c>
       <c r="D41" s="70" t="s">
@@ -2259,9 +2259,9 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="112"/>
-      <c r="B42" s="112"/>
-      <c r="C42" s="95"/>
+      <c r="A42" s="87"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="68" t="s">
         <v>122</v>
       </c>
@@ -2278,8 +2278,8 @@
       <c r="I42" s="34"/>
     </row>
     <row r="43" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="113"/>
-      <c r="B43" s="113"/>
+      <c r="A43" s="95"/>
+      <c r="B43" s="95"/>
       <c r="C43" s="80" t="s">
         <v>85</v>
       </c>
@@ -2314,13 +2314,13 @@
       <c r="I44" s="28"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="117" t="s">
+      <c r="A45" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="111" t="s">
+      <c r="B45" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="100" t="s">
+      <c r="C45" s="89" t="s">
         <v>90</v>
       </c>
       <c r="D45" s="68" t="s">
@@ -2339,16 +2339,16 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="118"/>
-      <c r="B46" s="112"/>
-      <c r="C46" s="119"/>
+      <c r="A46" s="85"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="90"/>
       <c r="D46" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="87" t="s">
+      <c r="E46" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="F46" s="84" t="s">
+      <c r="F46" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="31"/>
@@ -2356,22 +2356,22 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="118"/>
-      <c r="B47" s="112"/>
-      <c r="C47" s="119"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="90"/>
       <c r="D47" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="88"/>
-      <c r="F47" s="89"/>
+      <c r="E47" s="93"/>
+      <c r="F47" s="115"/>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="118"/>
-      <c r="B48" s="101"/>
-      <c r="C48" s="105"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="91"/>
       <c r="D48" s="70" t="s">
         <v>57</v>
       </c>
@@ -2386,9 +2386,9 @@
       <c r="I48" s="34"/>
     </row>
     <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="118"/>
-      <c r="B49" s="101"/>
-      <c r="C49" s="91"/>
+      <c r="A49" s="85"/>
+      <c r="B49" s="88"/>
+      <c r="C49" s="92"/>
       <c r="D49" s="60" t="s">
         <v>27</v>
       </c>
@@ -2409,47 +2409,47 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="118"/>
-      <c r="B50" s="101"/>
-      <c r="C50" s="100" t="s">
+      <c r="A50" s="85"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="89" t="s">
         <v>93</v>
       </c>
       <c r="D50" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="87" t="s">
+      <c r="E50" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="84" t="s">
+      <c r="F50" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="90" t="s">
+      <c r="G50" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="90" t="s">
+      <c r="H50" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="90" t="s">
+      <c r="I50" s="108" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="118"/>
-      <c r="B51" s="101"/>
-      <c r="C51" s="114"/>
+      <c r="A51" s="85"/>
+      <c r="B51" s="88"/>
+      <c r="C51" s="94"/>
       <c r="D51" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E51" s="88"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="91"/>
-      <c r="H51" s="91"/>
-      <c r="I51" s="91"/>
+      <c r="E51" s="93"/>
+      <c r="F51" s="115"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="118"/>
-      <c r="B52" s="101"/>
-      <c r="C52" s="100" t="s">
+      <c r="A52" s="85"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="89" t="s">
         <v>65</v>
       </c>
       <c r="D52" s="59" t="s">
@@ -2466,9 +2466,9 @@
       <c r="I52" s="28"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="118"/>
-      <c r="B53" s="101"/>
-      <c r="C53" s="91"/>
+      <c r="A53" s="85"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="92"/>
       <c r="D53" s="75" t="s">
         <v>130</v>
       </c>
@@ -2483,9 +2483,9 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="118"/>
-      <c r="B54" s="101"/>
-      <c r="C54" s="100" t="s">
+      <c r="A54" s="85"/>
+      <c r="B54" s="88"/>
+      <c r="C54" s="89" t="s">
         <v>66</v>
       </c>
       <c r="D54" s="59" t="s">
@@ -2494,7 +2494,7 @@
       <c r="E54" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F54" s="90" t="s">
+      <c r="F54" s="108" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="45"/>
@@ -2502,16 +2502,16 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="118"/>
-      <c r="B55" s="101"/>
-      <c r="C55" s="114"/>
+      <c r="A55" s="85"/>
+      <c r="B55" s="88"/>
+      <c r="C55" s="94"/>
       <c r="D55" s="59" t="s">
         <v>133</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F55" s="92"/>
+      <c r="F55" s="125"/>
       <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
@@ -2528,13 +2528,13 @@
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="111" t="s">
+      <c r="A57" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="111" t="s">
+      <c r="B57" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="100" t="s">
+      <c r="C57" s="89" t="s">
         <v>103</v>
       </c>
       <c r="D57" s="55" t="s">
@@ -2551,13 +2551,13 @@
       <c r="I57" s="39"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="112"/>
-      <c r="B58" s="112"/>
-      <c r="C58" s="119"/>
+      <c r="A58" s="87"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="90"/>
       <c r="D58" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="E58" s="87" t="s">
+      <c r="E58" s="114" t="s">
         <v>68</v>
       </c>
       <c r="F58" s="77" t="s">
@@ -2568,13 +2568,13 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="112"/>
-      <c r="B59" s="112"/>
-      <c r="C59" s="119"/>
+      <c r="A59" s="87"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="90"/>
       <c r="D59" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="E59" s="88"/>
+      <c r="E59" s="93"/>
       <c r="F59" s="54" t="s">
         <v>7</v>
       </c>
@@ -2583,9 +2583,9 @@
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="101"/>
-      <c r="B60" s="101"/>
-      <c r="C60" s="100" t="s">
+      <c r="A60" s="88"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="89" t="s">
         <v>104</v>
       </c>
       <c r="D60" s="60" t="s">
@@ -2602,9 +2602,9 @@
       <c r="I60" s="48"/>
     </row>
     <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="101"/>
-      <c r="B61" s="101"/>
-      <c r="C61" s="91"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="92"/>
       <c r="D61" s="60" t="s">
         <v>77</v>
       </c>
@@ -2619,8 +2619,8 @@
       <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="101"/>
-      <c r="B62" s="101"/>
+      <c r="A62" s="88"/>
+      <c r="B62" s="88"/>
       <c r="C62" s="67" t="s">
         <v>139</v>
       </c>
@@ -2638,9 +2638,9 @@
       <c r="I62" s="49"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="101"/>
-      <c r="B63" s="101"/>
-      <c r="C63" s="100" t="s">
+      <c r="A63" s="88"/>
+      <c r="B63" s="88"/>
+      <c r="C63" s="89" t="s">
         <v>69</v>
       </c>
       <c r="D63" s="68" t="s">
@@ -2657,9 +2657,9 @@
       <c r="I63" s="49"/>
     </row>
     <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="101"/>
-      <c r="B64" s="101"/>
-      <c r="C64" s="105"/>
+      <c r="A64" s="88"/>
+      <c r="B64" s="88"/>
+      <c r="C64" s="91"/>
       <c r="D64" s="60" t="s">
         <v>70</v>
       </c>
@@ -2674,9 +2674,9 @@
       <c r="I64" s="39"/>
     </row>
     <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="101"/>
-      <c r="B65" s="101"/>
-      <c r="C65" s="105"/>
+      <c r="A65" s="88"/>
+      <c r="B65" s="88"/>
+      <c r="C65" s="91"/>
       <c r="D65" s="70" t="s">
         <v>140</v>
       </c>
@@ -2691,9 +2691,9 @@
       <c r="I65" s="39"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
-      <c r="B66" s="88"/>
-      <c r="C66" s="91"/>
+      <c r="A66" s="93"/>
+      <c r="B66" s="93"/>
+      <c r="C66" s="92"/>
       <c r="D66" s="68" t="s">
         <v>71</v>
       </c>
@@ -2906,17 +2906,28 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A45:A55"/>
-    <mergeCell ref="B45:B55"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="A57:A66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="H50:H51"/>
     <mergeCell ref="A32:A43"/>
     <mergeCell ref="B32:B43"/>
     <mergeCell ref="C41:C42"/>
@@ -2930,31 +2941,20 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C12:C15"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E20:E21"/>
     <mergeCell ref="C20:C26"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
     <mergeCell ref="C32:C35"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="F54:F55"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="A45:A55"/>
+    <mergeCell ref="B45:B55"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="A57:A66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="C50:C51"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3500E6-8691-4132-B7EE-D66D6FC64761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FAC61-135E-4037-9643-4AD07FCF3572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="155">
   <si>
     <t>User Story</t>
   </si>
@@ -494,7 +494,16 @@
     <t>Check  passwords masking (type="password") for enhanced security</t>
   </si>
   <si>
-    <t>Check Register goes via https protocol (manual)</t>
+    <t>Check that Register goes via https protocol (manual)</t>
+  </si>
+  <si>
+    <t>Check that password is not exposed in error messages</t>
+  </si>
+  <si>
+    <t>Check that Login goes via https protocol (manual)</t>
+  </si>
+  <si>
+    <t>Check that password is note exposed in error message</t>
   </si>
 </sst>
 </file>
@@ -826,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1023,9 +1032,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1077,11 +1083,62 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1089,40 +1146,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1134,13 +1167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1149,59 +1176,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1537,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1594,13 +1579,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="109" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1617,16 +1602,16 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="70" t="s">
+      <c r="A4" s="105"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="69" t="s">
         <v>21</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="31"/>
@@ -1645,22 +1630,22 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="69" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="76" t="s">
+      <c r="F6" s="75" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="31"/>
@@ -1668,9 +1653,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="120"/>
+      <c r="A7" s="105"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1685,16 +1670,16 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="70" t="s">
+      <c r="A8" s="105"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="69" t="s">
         <v>106</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="33"/>
@@ -1702,75 +1687,75 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="96" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="108"/>
+      <c r="C9" s="90" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="114" t="s">
+      <c r="E9" s="83" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="66" t="s">
+      <c r="G9" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="66" t="s">
+      <c r="H9" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="66" t="s">
+      <c r="I9" s="64" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="68" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="78" t="s">
-        <v>13</v>
+      <c r="E10" s="84"/>
+      <c r="F10" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="G10" s="30"/>
       <c r="H10" s="27"/>
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="70" t="s">
+      <c r="A11" s="105"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="67" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="72" t="s">
-        <v>9</v>
+      <c r="F11" s="77" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="31"/>
       <c r="H11" s="1"/>
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="103" t="s">
+      <c r="A12" s="105"/>
+      <c r="B12" s="108"/>
+      <c r="C12" s="106" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="109" t="s">
+      <c r="E12" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="122" t="s">
+      <c r="F12" s="85" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1778,273 +1763,261 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="104"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="111"/>
       <c r="D13" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="109"/>
-      <c r="F13" s="123"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="117"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="109"/>
-      <c r="F14" s="123"/>
+      <c r="A14" s="105"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="95"/>
+      <c r="F14" s="117"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="105"/>
+      <c r="A15" s="105"/>
+      <c r="B15" s="108"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="110"/>
-      <c r="F15" s="124"/>
+        <v>151</v>
+      </c>
+      <c r="E15" s="95"/>
+      <c r="F15" s="117"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="1"/>
+      <c r="A16" s="105"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="96"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="1"/>
       <c r="I16" s="39"/>
     </row>
-    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="99" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="31"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="43"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="62" t="s">
-        <v>107</v>
+    <row r="18" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="105" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>46</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>7</v>
+        <v>53</v>
+      </c>
+      <c r="F18" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="1"/>
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="100"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="70" t="s">
+      <c r="A19" s="105"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="31"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="39"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="105"/>
+      <c r="B20" s="108"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="71" t="s">
+      <c r="F20" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="40"/>
-    </row>
-    <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="100"/>
-      <c r="C20" s="89" t="s">
+      <c r="G20" s="33"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="40"/>
+    </row>
+    <row r="21" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="105"/>
+      <c r="B21" s="108"/>
+      <c r="C21" s="106" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="62" t="s">
+      <c r="D21" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="114" t="s">
+      <c r="E21" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="65" t="s">
+      <c r="F21" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G21" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="64" t="s">
+      <c r="H21" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="64" t="s">
+      <c r="I21" s="64" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
-      <c r="B21" s="100"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="68" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="105"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="93"/>
-      <c r="F21" s="69" t="s">
+      <c r="E22" s="84"/>
+      <c r="F22" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="44"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="28"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="105"/>
+      <c r="B23" s="108"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="68" t="s">
         <v>13</v>
-      </c>
-      <c r="G21" s="44"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="28"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="99"/>
-      <c r="B22" s="100"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="45"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="32"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="99"/>
-      <c r="B23" s="100"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="114" t="s">
-        <v>148</v>
-      </c>
-      <c r="F23" s="111" t="s">
-        <v>7</v>
       </c>
       <c r="G23" s="45"/>
       <c r="H23" s="3"/>
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
-      <c r="B24" s="100"/>
-      <c r="C24" s="91"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="108"/>
+      <c r="C24" s="111"/>
       <c r="D24" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="88"/>
-      <c r="F24" s="112"/>
+        <v>145</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="F24" s="85" t="s">
+        <v>7</v>
+      </c>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="99"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="88"/>
-      <c r="F25" s="112"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="108"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="62" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="97"/>
+      <c r="F25" s="117"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="100"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="105"/>
+      <c r="B26" s="108"/>
+      <c r="C26" s="111"/>
       <c r="D26" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="97"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="32"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="105"/>
+      <c r="B27" s="108"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="97"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="32"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="108"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="93"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="39"/>
-    </row>
-    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="100"/>
-      <c r="B27" s="100"/>
-      <c r="C27" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="39"/>
-    </row>
-    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="100"/>
-      <c r="B28" s="100"/>
-      <c r="C28" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="71" t="s">
-        <v>9</v>
-      </c>
+      <c r="E28" s="84"/>
+      <c r="F28" s="86"/>
       <c r="G28" s="31"/>
       <c r="H28" s="1"/>
       <c r="I28" s="39"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="100"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="89" t="s">
-        <v>42</v>
+    <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="108"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="61" t="s">
+        <v>108</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="116" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="56" t="s">
@@ -2055,698 +2028,722 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="100"/>
-      <c r="B30" s="100"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="116"/>
-      <c r="F30" s="56" t="s">
-        <v>7</v>
+      <c r="A30" s="108"/>
+      <c r="B30" s="108"/>
+      <c r="C30" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G30" s="31"/>
       <c r="H30" s="1"/>
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="19"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="32"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="86" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="79" t="s">
-        <v>13</v>
+      <c r="A31" s="108"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="39"/>
+    </row>
+    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="108"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="98"/>
+      <c r="F32" s="56" t="s">
+        <v>7</v>
       </c>
       <c r="G32" s="31"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="32"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="31"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="91"/>
-      <c r="D34" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="93"/>
-      <c r="F34" s="119"/>
+      <c r="A34" s="102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="106" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="78" t="s">
+        <v>13</v>
+      </c>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
-    <row r="35" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="72" t="s">
-        <v>9</v>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="103"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="111"/>
+      <c r="D35" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="E35" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="85" t="s">
+        <v>7</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="106" t="s">
-        <v>117</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="78" t="s">
-        <v>13</v>
-      </c>
+      <c r="A36" s="103"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="111"/>
+      <c r="D36" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="84"/>
+      <c r="F36" s="101"/>
       <c r="G36" s="31"/>
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="68" t="s">
-        <v>118</v>
+    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="103"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="69" t="s">
+        <v>83</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="78" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F37" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="3"/>
       <c r="I37" s="32"/>
     </row>
-    <row r="38" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="87"/>
-      <c r="C38" s="96" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="F38" s="79" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="103"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="112" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="45"/>
-      <c r="H38" s="82" t="s">
-        <v>119</v>
-      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="3"/>
       <c r="I38" s="32"/>
     </row>
-    <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" s="118"/>
-      <c r="F39" s="73" t="s">
-        <v>9</v>
+    <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="103"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="113"/>
+      <c r="D39" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="77" t="s">
+        <v>13</v>
       </c>
       <c r="G39" s="31"/>
       <c r="H39" s="3"/>
       <c r="I39" s="32"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="70" t="s">
+    <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="103"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="99" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="45"/>
+      <c r="H40" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="103"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="100"/>
+      <c r="F41" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="32"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="103"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="93"/>
+      <c r="D42" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="93"/>
-      <c r="F40" s="73" t="s">
+      <c r="E42" s="84"/>
+      <c r="F42" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="31"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="96" t="s">
+      <c r="G42" s="31"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="32"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="103"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D41" s="70" t="s">
+      <c r="D43" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E43" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="71" t="s">
+      <c r="F43" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="52" t="s">
+      <c r="G43" s="31"/>
+      <c r="H43" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="87"/>
-      <c r="C42" s="97"/>
-      <c r="D42" s="68" t="s">
+      <c r="I43" s="32"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="103"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E44" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="69" t="s">
+      <c r="F44" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="33"/>
-      <c r="H42" s="53" t="s">
+      <c r="G44" s="33"/>
+      <c r="H44" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="I42" s="34"/>
-    </row>
-    <row r="43" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="95"/>
-      <c r="B43" s="95"/>
-      <c r="C43" s="80" t="s">
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="104"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D45" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F43" s="69" t="s">
+      <c r="F45" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G43" s="81" t="s">
+      <c r="G45" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="81" t="s">
+      <c r="H45" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I43" s="81" t="s">
+      <c r="I45" s="80" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="28"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="84" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="28"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="86" t="s">
+      <c r="B47" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="89" t="s">
+      <c r="C47" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="68" t="s">
+      <c r="D47" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F45" s="69" t="s">
+      <c r="F47" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G47" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="32"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" s="114" t="s">
-        <v>91</v>
-      </c>
-      <c r="F46" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="31"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="32"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
-      <c r="B47" s="87"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="93"/>
-      <c r="F47" s="115"/>
-      <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
-      <c r="B48" s="88"/>
-      <c r="C48" s="91"/>
-      <c r="D48" s="70" t="s">
+      <c r="A48" s="115"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="116"/>
+      <c r="D48" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="31"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="32"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="115"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="116"/>
+      <c r="D49" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" s="84"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="115"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="111"/>
+      <c r="D50" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E50" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F48" s="71" t="s">
+      <c r="F50" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="G48" s="33"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="34"/>
-    </row>
-    <row r="49" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
-      <c r="B49" s="88"/>
-      <c r="C49" s="92"/>
-      <c r="D49" s="60" t="s">
+      <c r="G50" s="33"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="34"/>
+    </row>
+    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="115"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="54" t="s">
+      <c r="F51" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="56" t="s">
+      <c r="G51" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="56" t="s">
+      <c r="H51" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="56" t="s">
+      <c r="I51" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
-      <c r="B50" s="88"/>
-      <c r="C50" s="89" t="s">
+    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="115"/>
+      <c r="B52" s="97"/>
+      <c r="C52" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D52" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="114" t="s">
+      <c r="E52" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="111" t="s">
+      <c r="F52" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="108" t="s">
+      <c r="G52" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="108" t="s">
+      <c r="H52" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="108" t="s">
+      <c r="I52" s="87" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
-      <c r="B51" s="88"/>
-      <c r="C51" s="94"/>
-      <c r="D51" s="59" t="s">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="115"/>
+      <c r="B53" s="97"/>
+      <c r="C53" s="107"/>
+      <c r="D53" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E51" s="93"/>
-      <c r="F51" s="115"/>
-      <c r="G51" s="92"/>
-      <c r="H51" s="92"/>
-      <c r="I51" s="92"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
-      <c r="B52" s="88"/>
-      <c r="C52" s="89" t="s">
+      <c r="E53" s="84"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="115"/>
+      <c r="B54" s="97"/>
+      <c r="C54" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="59" t="s">
+      <c r="D54" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E54" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F52" s="58" t="s">
+      <c r="F54" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="44"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="28"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
-      <c r="B53" s="88"/>
-      <c r="C53" s="92"/>
-      <c r="D53" s="75" t="s">
+      <c r="G54" s="44"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="28"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="115"/>
+      <c r="B55" s="97"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E55" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F53" s="74" t="s">
+      <c r="F55" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="45"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="32"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="85"/>
-      <c r="B54" s="88"/>
-      <c r="C54" s="89" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" s="108" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="32"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="85"/>
-      <c r="B55" s="88"/>
-      <c r="C55" s="94"/>
-      <c r="D55" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="125"/>
       <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
     </row>
-    <row r="56" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="43"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="1"/>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="115"/>
+      <c r="B56" s="97"/>
+      <c r="C56" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="87" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
     </row>
-    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="86" t="s">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="115"/>
+      <c r="B57" s="97"/>
+      <c r="C57" s="107"/>
+      <c r="D57" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="89"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="32"/>
+    </row>
+    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="32"/>
+    </row>
+    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="86" t="s">
+      <c r="B59" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="C57" s="89" t="s">
+      <c r="C59" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="D57" s="55" t="s">
+      <c r="D59" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E59" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F57" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="G57" s="46"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="39"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="87"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" s="114" t="s">
-        <v>68</v>
-      </c>
-      <c r="F58" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="G58" s="46"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="39"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="87"/>
-      <c r="B59" s="87"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E59" s="93"/>
-      <c r="F59" s="54" t="s">
+      <c r="F59" s="57" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="46"/>
       <c r="H59" s="1"/>
       <c r="I59" s="39"/>
     </row>
-    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="89" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F60" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="31"/>
-      <c r="H60" s="47"/>
-      <c r="I60" s="48"/>
-    </row>
-    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="88"/>
-      <c r="C61" s="92"/>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="103"/>
+      <c r="B60" s="103"/>
+      <c r="C60" s="116"/>
+      <c r="D60" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" s="46"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="39"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="103"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="116"/>
       <c r="D61" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>76</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="E61" s="84"/>
       <c r="F61" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="48"/>
-    </row>
-    <row r="62" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="88"/>
-      <c r="C62" s="67" t="s">
+      <c r="G61" s="46"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="39"/>
+    </row>
+    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="97"/>
+      <c r="B62" s="97"/>
+      <c r="C62" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F62" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="31"/>
+      <c r="H62" s="47"/>
+      <c r="I62" s="48"/>
+    </row>
+    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="97"/>
+      <c r="B63" s="97"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="31"/>
+      <c r="H63" s="47"/>
+      <c r="I63" s="48"/>
+    </row>
+    <row r="64" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="97"/>
+      <c r="B64" s="97"/>
+      <c r="C64" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="D62" s="68" t="s">
+      <c r="D64" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E64" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F62" s="69" t="s">
+      <c r="F64" s="68" t="s">
         <v>13</v>
-      </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="49"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
-      <c r="B63" s="88"/>
-      <c r="C63" s="89" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F63" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="31"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="49"/>
-    </row>
-    <row r="64" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="88"/>
-      <c r="C64" s="91"/>
-      <c r="D64" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F64" s="54" t="s">
-        <v>7</v>
       </c>
       <c r="G64" s="31"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="39"/>
-    </row>
-    <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
-      <c r="B65" s="88"/>
-      <c r="C65" s="91"/>
-      <c r="D65" s="70" t="s">
-        <v>140</v>
+      <c r="I64" s="49"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="97"/>
+      <c r="B65" s="97"/>
+      <c r="C65" s="106" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="67" t="s">
+        <v>74</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F65" s="71" t="s">
-        <v>9</v>
+        <v>75</v>
+      </c>
+      <c r="F65" s="68" t="s">
+        <v>13</v>
       </c>
       <c r="G65" s="31"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="39"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="93"/>
-      <c r="B66" s="93"/>
-      <c r="C66" s="92"/>
-      <c r="D66" s="68" t="s">
+      <c r="I65" s="49"/>
+    </row>
+    <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="97"/>
+      <c r="B66" s="97"/>
+      <c r="C66" s="111"/>
+      <c r="D66" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F66" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="31"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="39"/>
+    </row>
+    <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="97"/>
+      <c r="B67" s="97"/>
+      <c r="C67" s="111"/>
+      <c r="D67" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F67" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="31"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="39"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="84"/>
+      <c r="B68" s="84"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E68" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="69" t="s">
+      <c r="F68" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G66" s="33"/>
-      <c r="H66" s="38"/>
-      <c r="I66" s="40"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="22"/>
-      <c r="B67" s="22"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="50"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="22"/>
-    </row>
-    <row r="68" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="2"/>
-      <c r="E68" s="5"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
-      <c r="E69" s="5"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G68" s="33"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="40"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="22"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="E70" s="5"/>
       <c r="G70" s="2"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="E71" s="5"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="E72" s="5"/>
       <c r="G72" s="2"/>
@@ -2758,47 +2755,47 @@
       <c r="E73" s="5"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="I73" s="2"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="E74" s="5"/>
-      <c r="G74" s="1"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B75" s="3"/>
-      <c r="E75" s="7"/>
+      <c r="B75" s="2"/>
+      <c r="E75" s="5"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="3"/>
+      <c r="B76" s="2"/>
       <c r="E76" s="5"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="2"/>
+      <c r="B77" s="3"/>
       <c r="E77" s="7"/>
     </row>
-    <row r="78" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="2"/>
-      <c r="E78" s="7"/>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B78" s="3"/>
+      <c r="E78" s="5"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
-      <c r="E79" s="5"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
-      <c r="E80" s="5"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="E80" s="7"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
@@ -2816,18 +2813,21 @@
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
-      <c r="E83" s="7"/>
+      <c r="E83" s="5"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
-      <c r="E84" s="7"/>
+      <c r="E84" s="5"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
-      <c r="E85" s="5"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
+      <c r="E85" s="7"/>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
@@ -2835,7 +2835,10 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
-      <c r="E87" s="7"/>
+      <c r="E87" s="5"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
@@ -2854,9 +2857,11 @@
       <c r="E91" s="7"/>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92" s="2"/>
       <c r="E92" s="7"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="2"/>
       <c r="E93" s="7"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
@@ -2904,57 +2909,63 @@
     <row r="108" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E108" s="7"/>
     </row>
+    <row r="109" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E109" s="7"/>
+    </row>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E110" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="B47:B57"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="B18:B32"/>
+    <mergeCell ref="B6:B16"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="A18:A32"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="C21:C28"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H52:H53"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="I50:I51"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="H50:H51"/>
-    <mergeCell ref="A32:A43"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B17:B30"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="A45:A55"/>
-    <mergeCell ref="B45:B55"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="A57:A66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="F56:F57"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FAC61-135E-4037-9643-4AD07FCF3572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501208CA-345F-4812-91E0-418645ACF726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -835,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1083,109 +1083,118 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1579,13 +1588,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="100" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1602,9 +1611,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="105"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="109"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="69" t="s">
         <v>21</v>
       </c>
@@ -1630,13 +1639,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="105" t="s">
+      <c r="A6" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="95" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="69" t="s">
@@ -1653,9 +1662,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="105"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="91"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1670,9 +1679,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="105"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="92"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="96"/>
       <c r="D8" s="69" t="s">
         <v>106</v>
       </c>
@@ -1687,15 +1696,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="105"/>
-      <c r="B9" s="108"/>
-      <c r="C9" s="90" t="s">
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="95" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="110" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1712,13 +1721,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
-      <c r="B10" s="108"/>
-      <c r="C10" s="91"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="115"/>
       <c r="D10" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="84"/>
+      <c r="E10" s="92"/>
       <c r="F10" s="71" t="s">
         <v>9</v>
       </c>
@@ -1727,9 +1736,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="105"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="92"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="96"/>
       <c r="D11" s="67" t="s">
         <v>36</v>
       </c>
@@ -1744,18 +1753,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="105"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="106" t="s">
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="88" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="85" t="s">
+      <c r="F12" s="107" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1763,53 +1772,53 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="105"/>
-      <c r="B13" s="108"/>
-      <c r="C13" s="111"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="90"/>
       <c r="D13" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="117"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="105"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="111"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="90"/>
       <c r="D14" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="117"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="108"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="105"/>
-      <c r="B15" s="108"/>
-      <c r="C15" s="111"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="E15" s="95"/>
-      <c r="F15" s="117"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="108"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="105"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="88"/>
+      <c r="A16" s="98"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="91"/>
       <c r="D16" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E16" s="96"/>
-      <c r="F16" s="86"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="109"/>
       <c r="G16" s="31"/>
       <c r="H16" s="1"/>
       <c r="I16" s="39"/>
@@ -1826,13 +1835,13 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="105" t="s">
+      <c r="B18" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="90" t="s">
+      <c r="C18" s="95" t="s">
         <v>100</v>
       </c>
       <c r="D18" s="69" t="s">
@@ -1849,9 +1858,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="105"/>
-      <c r="B19" s="105"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="62" t="s">
         <v>107</v>
       </c>
@@ -1866,9 +1875,9 @@
       <c r="I19" s="39"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="105"/>
-      <c r="B20" s="108"/>
-      <c r="C20" s="94"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="116"/>
       <c r="D20" s="69" t="s">
         <v>82</v>
       </c>
@@ -1883,15 +1892,15 @@
       <c r="I20" s="40"/>
     </row>
     <row r="21" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="105"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="106" t="s">
+      <c r="A21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="95" t="s">
         <v>146</v>
       </c>
       <c r="D21" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="83" t="s">
+      <c r="E21" s="110" t="s">
         <v>35</v>
       </c>
       <c r="F21" s="65" t="s">
@@ -1908,13 +1917,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="105"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="111"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="115"/>
       <c r="D22" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="84"/>
+      <c r="E22" s="92"/>
       <c r="F22" s="70" t="s">
         <v>9</v>
       </c>
@@ -1923,9 +1932,9 @@
       <c r="I22" s="28"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="105"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="111"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="67" t="s">
         <v>36</v>
       </c>
@@ -1940,16 +1949,16 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="105"/>
-      <c r="B24" s="108"/>
-      <c r="C24" s="111"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="115"/>
       <c r="D24" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="83" t="s">
+      <c r="E24" s="110" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="85" t="s">
+      <c r="F24" s="118" t="s">
         <v>7</v>
       </c>
       <c r="G24" s="45"/>
@@ -1957,60 +1966,60 @@
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="105"/>
-      <c r="B25" s="108"/>
-      <c r="C25" s="111"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="115"/>
       <c r="D25" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="97"/>
-      <c r="F25" s="117"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="119"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="105"/>
-      <c r="B26" s="108"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="60" t="s">
+      <c r="A26" s="98"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="E26" s="97"/>
-      <c r="F26" s="117"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="119"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="105"/>
-      <c r="B27" s="108"/>
-      <c r="C27" s="111"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="115"/>
       <c r="D27" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="97"/>
-      <c r="F27" s="117"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="119"/>
       <c r="G27" s="45"/>
       <c r="H27" s="3"/>
       <c r="I27" s="32"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="108"/>
-      <c r="B28" s="108"/>
-      <c r="C28" s="88"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="96"/>
       <c r="D28" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="84"/>
-      <c r="F28" s="86"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="120"/>
       <c r="G28" s="31"/>
       <c r="H28" s="1"/>
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="108"/>
-      <c r="B29" s="108"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="99"/>
       <c r="C29" s="61" t="s">
         <v>108</v>
       </c>
@@ -2028,8 +2037,8 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="82" t="s">
         <v>108</v>
       </c>
@@ -2047,15 +2056,15 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="108"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="106" t="s">
+      <c r="A31" s="99"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="88" t="s">
         <v>42</v>
       </c>
       <c r="D31" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="98" t="s">
+      <c r="E31" s="111" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="56" t="s">
@@ -2066,13 +2075,13 @@
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="108"/>
-      <c r="B32" s="108"/>
-      <c r="C32" s="107"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="99"/>
+      <c r="C32" s="93"/>
       <c r="D32" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="98"/>
+      <c r="E32" s="111"/>
       <c r="F32" s="56" t="s">
         <v>7</v>
       </c>
@@ -2092,13 +2101,13 @@
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="102" t="s">
+      <c r="A34" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="106" t="s">
+      <c r="C34" s="88" t="s">
         <v>81</v>
       </c>
       <c r="D34" s="67" t="s">
@@ -2115,16 +2124,16 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="103"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="111"/>
+      <c r="A35" s="86"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="90"/>
       <c r="D35" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E35" s="83" t="s">
+      <c r="E35" s="110" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="85" t="s">
+      <c r="F35" s="107" t="s">
         <v>7</v>
       </c>
       <c r="G35" s="31"/>
@@ -2132,22 +2141,22 @@
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="103"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="111"/>
+      <c r="A36" s="86"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="90"/>
       <c r="D36" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="84"/>
-      <c r="F36" s="101"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="114"/>
       <c r="G36" s="31"/>
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="103"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="88"/>
+      <c r="A37" s="86"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="69" t="s">
         <v>83</v>
       </c>
@@ -2162,9 +2171,9 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="103"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="112" t="s">
+      <c r="A38" s="86"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="102" t="s">
         <v>117</v>
       </c>
       <c r="D38" s="67" t="s">
@@ -2181,9 +2190,9 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="103"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="113"/>
+      <c r="A39" s="86"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="103"/>
       <c r="D39" s="67" t="s">
         <v>118</v>
       </c>
@@ -2198,15 +2207,15 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="103"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="90" t="s">
+      <c r="A40" s="86"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="95" t="s">
         <v>101</v>
       </c>
       <c r="D40" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="99" t="s">
+      <c r="E40" s="112" t="s">
         <v>110</v>
       </c>
       <c r="F40" s="78" t="s">
@@ -2219,13 +2228,13 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="103"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="93"/>
+      <c r="A41" s="86"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="97"/>
       <c r="D41" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="E41" s="100"/>
+      <c r="E41" s="113"/>
       <c r="F41" s="72" t="s">
         <v>9</v>
       </c>
@@ -2234,13 +2243,13 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="103"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="93"/>
+      <c r="A42" s="86"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="97"/>
       <c r="D42" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="E42" s="84"/>
+      <c r="E42" s="92"/>
       <c r="F42" s="72" t="s">
         <v>9</v>
       </c>
@@ -2249,9 +2258,9 @@
       <c r="I42" s="32"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="103"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="90" t="s">
+      <c r="A43" s="86"/>
+      <c r="B43" s="86"/>
+      <c r="C43" s="95" t="s">
         <v>120</v>
       </c>
       <c r="D43" s="69" t="s">
@@ -2270,9 +2279,9 @@
       <c r="I43" s="32"/>
     </row>
     <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="103"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="92"/>
+      <c r="A44" s="86"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="96"/>
       <c r="D44" s="67" t="s">
         <v>122</v>
       </c>
@@ -2289,8 +2298,8 @@
       <c r="I44" s="34"/>
     </row>
     <row r="45" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="104"/>
-      <c r="B45" s="104"/>
+      <c r="A45" s="94"/>
+      <c r="B45" s="94"/>
       <c r="C45" s="79" t="s">
         <v>85</v>
       </c>
@@ -2325,13 +2334,13 @@
       <c r="I46" s="28"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="114" t="s">
+      <c r="A47" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="102" t="s">
+      <c r="B47" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="106" t="s">
+      <c r="C47" s="88" t="s">
         <v>90</v>
       </c>
       <c r="D47" s="67" t="s">
@@ -2350,16 +2359,16 @@
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="115"/>
-      <c r="B48" s="103"/>
-      <c r="C48" s="116"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="89"/>
       <c r="D48" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="83" t="s">
+      <c r="E48" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="F48" s="85" t="s">
+      <c r="F48" s="107" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="31"/>
@@ -2367,22 +2376,22 @@
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="115"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="116"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="E49" s="84"/>
-      <c r="F49" s="86"/>
+      <c r="E49" s="92"/>
+      <c r="F49" s="109"/>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="115"/>
-      <c r="B50" s="97"/>
-      <c r="C50" s="111"/>
+      <c r="A50" s="84"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="90"/>
       <c r="D50" s="69" t="s">
         <v>57</v>
       </c>
@@ -2397,9 +2406,9 @@
       <c r="I50" s="34"/>
     </row>
     <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="115"/>
-      <c r="B51" s="97"/>
-      <c r="C51" s="88"/>
+      <c r="A51" s="84"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="91"/>
       <c r="D51" s="60" t="s">
         <v>27</v>
       </c>
@@ -2420,47 +2429,47 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="115"/>
-      <c r="B52" s="97"/>
-      <c r="C52" s="106" t="s">
+      <c r="A52" s="84"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D52" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="83" t="s">
+      <c r="E52" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="85" t="s">
+      <c r="F52" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="87" t="s">
+      <c r="G52" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="H52" s="87" t="s">
+      <c r="H52" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="87" t="s">
+      <c r="I52" s="104" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="115"/>
-      <c r="B53" s="97"/>
-      <c r="C53" s="107"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="93"/>
       <c r="D53" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E53" s="84"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="88"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="88"/>
+      <c r="E53" s="92"/>
+      <c r="F53" s="109"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="115"/>
-      <c r="B54" s="97"/>
-      <c r="C54" s="106" t="s">
+      <c r="A54" s="84"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="88" t="s">
         <v>65</v>
       </c>
       <c r="D54" s="59" t="s">
@@ -2477,9 +2486,9 @@
       <c r="I54" s="28"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="115"/>
-      <c r="B55" s="97"/>
-      <c r="C55" s="88"/>
+      <c r="A55" s="84"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="91"/>
       <c r="D55" s="74" t="s">
         <v>130</v>
       </c>
@@ -2494,9 +2503,9 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="115"/>
-      <c r="B56" s="97"/>
-      <c r="C56" s="106" t="s">
+      <c r="A56" s="84"/>
+      <c r="B56" s="87"/>
+      <c r="C56" s="88" t="s">
         <v>66</v>
       </c>
       <c r="D56" s="59" t="s">
@@ -2505,7 +2514,7 @@
       <c r="E56" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F56" s="87" t="s">
+      <c r="F56" s="104" t="s">
         <v>7</v>
       </c>
       <c r="G56" s="45"/>
@@ -2513,16 +2522,16 @@
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="115"/>
-      <c r="B57" s="97"/>
-      <c r="C57" s="107"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="93"/>
       <c r="D57" s="59" t="s">
         <v>133</v>
       </c>
       <c r="E57" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F57" s="89"/>
+      <c r="F57" s="117"/>
       <c r="G57" s="45"/>
       <c r="H57" s="3"/>
       <c r="I57" s="32"/>
@@ -2539,13 +2548,13 @@
       <c r="I58" s="32"/>
     </row>
     <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="102" t="s">
+      <c r="A59" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="102" t="s">
+      <c r="B59" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="C59" s="106" t="s">
+      <c r="C59" s="88" t="s">
         <v>103</v>
       </c>
       <c r="D59" s="55" t="s">
@@ -2562,13 +2571,13 @@
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="103"/>
-      <c r="B60" s="103"/>
-      <c r="C60" s="116"/>
+      <c r="A60" s="86"/>
+      <c r="B60" s="86"/>
+      <c r="C60" s="89"/>
       <c r="D60" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="E60" s="83" t="s">
+      <c r="E60" s="110" t="s">
         <v>68</v>
       </c>
       <c r="F60" s="76" t="s">
@@ -2579,13 +2588,13 @@
       <c r="I60" s="39"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="103"/>
-      <c r="B61" s="103"/>
-      <c r="C61" s="116"/>
+      <c r="A61" s="86"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="89"/>
       <c r="D61" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="E61" s="84"/>
+      <c r="E61" s="92"/>
       <c r="F61" s="54" t="s">
         <v>7</v>
       </c>
@@ -2594,9 +2603,9 @@
       <c r="I61" s="39"/>
     </row>
     <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="97"/>
-      <c r="B62" s="97"/>
-      <c r="C62" s="106" t="s">
+      <c r="A62" s="87"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="88" t="s">
         <v>104</v>
       </c>
       <c r="D62" s="60" t="s">
@@ -2613,9 +2622,9 @@
       <c r="I62" s="48"/>
     </row>
     <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="97"/>
-      <c r="B63" s="97"/>
-      <c r="C63" s="88"/>
+      <c r="A63" s="87"/>
+      <c r="B63" s="87"/>
+      <c r="C63" s="91"/>
       <c r="D63" s="60" t="s">
         <v>77</v>
       </c>
@@ -2630,8 +2639,8 @@
       <c r="I63" s="48"/>
     </row>
     <row r="64" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="97"/>
-      <c r="B64" s="97"/>
+      <c r="A64" s="87"/>
+      <c r="B64" s="87"/>
       <c r="C64" s="66" t="s">
         <v>139</v>
       </c>
@@ -2649,9 +2658,9 @@
       <c r="I64" s="49"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="97"/>
-      <c r="B65" s="97"/>
-      <c r="C65" s="106" t="s">
+      <c r="A65" s="87"/>
+      <c r="B65" s="87"/>
+      <c r="C65" s="88" t="s">
         <v>69</v>
       </c>
       <c r="D65" s="67" t="s">
@@ -2668,9 +2677,9 @@
       <c r="I65" s="49"/>
     </row>
     <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="97"/>
-      <c r="B66" s="97"/>
-      <c r="C66" s="111"/>
+      <c r="A66" s="87"/>
+      <c r="B66" s="87"/>
+      <c r="C66" s="90"/>
       <c r="D66" s="60" t="s">
         <v>70</v>
       </c>
@@ -2685,9 +2694,9 @@
       <c r="I66" s="39"/>
     </row>
     <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="97"/>
-      <c r="B67" s="97"/>
-      <c r="C67" s="111"/>
+      <c r="A67" s="87"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="90"/>
       <c r="D67" s="69" t="s">
         <v>140</v>
       </c>
@@ -2702,9 +2711,9 @@
       <c r="I67" s="39"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
-      <c r="B68" s="84"/>
-      <c r="C68" s="88"/>
+      <c r="A68" s="92"/>
+      <c r="B68" s="92"/>
+      <c r="C68" s="91"/>
       <c r="D68" s="67" t="s">
         <v>71</v>
       </c>
@@ -2917,17 +2926,28 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A47:A57"/>
-    <mergeCell ref="B47:B57"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H52:H53"/>
     <mergeCell ref="A34:A45"/>
     <mergeCell ref="B34:B45"/>
     <mergeCell ref="C43:C44"/>
@@ -2944,28 +2964,17 @@
     <mergeCell ref="C21:C28"/>
     <mergeCell ref="C34:C37"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="B47:B57"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C52:C53"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501208CA-345F-4812-91E0-418645ACF726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E287E8-F1D1-47D1-B3E8-47F605CA9E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="154">
   <si>
     <t>User Story</t>
   </si>
@@ -495,9 +495,6 @@
   </si>
   <si>
     <t>Check that Register goes via https protocol (manual)</t>
-  </si>
-  <si>
-    <t>Check that password is not exposed in error messages</t>
   </si>
   <si>
     <t>Check that Login goes via https protocol (manual)</t>
@@ -596,7 +593,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,6 +624,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -835,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1083,119 +1086,134 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1531,7 +1549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1588,13 +1606,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="108" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="112" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="62" t="s">
@@ -1611,9 +1629,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="100"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="112"/>
       <c r="D4" s="69" t="s">
         <v>21</v>
       </c>
@@ -1639,13 +1657,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="95" t="s">
+      <c r="C6" s="90" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="69" t="s">
@@ -1662,9 +1680,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="115"/>
+      <c r="A7" s="108"/>
+      <c r="B7" s="111"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="62" t="s">
         <v>105</v>
       </c>
@@ -1679,9 +1697,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="96"/>
+      <c r="A8" s="108"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="69" t="s">
         <v>106</v>
       </c>
@@ -1696,15 +1714,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="95" t="s">
+      <c r="A9" s="108"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="90" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="110" t="s">
+      <c r="E9" s="83" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="65" t="s">
@@ -1721,13 +1739,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="115"/>
+      <c r="A10" s="108"/>
+      <c r="B10" s="111"/>
+      <c r="C10" s="91"/>
       <c r="D10" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="92"/>
+      <c r="E10" s="84"/>
       <c r="F10" s="71" t="s">
         <v>9</v>
       </c>
@@ -1736,9 +1754,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="96"/>
+      <c r="A11" s="108"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="67" t="s">
         <v>36</v>
       </c>
@@ -1753,18 +1771,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="88" t="s">
+      <c r="A12" s="108"/>
+      <c r="B12" s="111"/>
+      <c r="C12" s="123" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="107" t="s">
+      <c r="F12" s="120" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1772,301 +1790,303 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="90"/>
+      <c r="A13" s="108"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="62" t="s">
         <v>147</v>
       </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="108"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="121"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E14" s="105"/>
-      <c r="F14" s="108"/>
+      <c r="A14" s="108"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="95"/>
+      <c r="F14" s="121"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="90"/>
+      <c r="A15" s="108"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="125"/>
       <c r="D15" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="108"/>
+        <v>150</v>
+      </c>
+      <c r="E15" s="96"/>
+      <c r="F15" s="122"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="98"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="106"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="31"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="39"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="1"/>
+    <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="108" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="31"/>
       <c r="H17" s="1"/>
       <c r="I17" s="39"/>
     </row>
-    <row r="18" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>46</v>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="108"/>
+      <c r="B18" s="108"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="62" t="s">
+        <v>107</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>9</v>
+        <v>54</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>7</v>
       </c>
       <c r="G18" s="31"/>
       <c r="H18" s="1"/>
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="98"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="62" t="s">
-        <v>107</v>
+      <c r="A19" s="108"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="69" t="s">
+        <v>82</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="40"/>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="108"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="90" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="39"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="98"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="70" t="s">
+      <c r="G20" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="108"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="84"/>
+      <c r="F21" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="40"/>
-    </row>
-    <row r="21" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="98"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="62" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="65" t="s">
+      <c r="G21" s="44"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="28"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="108"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="45"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="32"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="108"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="97" t="s">
         <v>7</v>
-      </c>
-      <c r="G21" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21" s="64" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="98"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="92"/>
-      <c r="F22" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="44"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="28"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="98"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="68" t="s">
-        <v>13</v>
       </c>
       <c r="G23" s="45"/>
       <c r="H23" s="3"/>
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="98"/>
-      <c r="B24" s="99"/>
-      <c r="C24" s="115"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="110" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="118" t="s">
-        <v>7</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E24" s="100"/>
+      <c r="F24" s="98"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="98"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="115"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="111"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="119"/>
+        <v>153</v>
+      </c>
+      <c r="E25" s="100"/>
+      <c r="F25" s="98"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="115"/>
+      <c r="A26" s="108"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="62" t="s">
-        <v>154</v>
-      </c>
-      <c r="E26" s="87"/>
-      <c r="F26" s="119"/>
+        <v>152</v>
+      </c>
+      <c r="E26" s="100"/>
+      <c r="F26" s="98"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="98"/>
-      <c r="B27" s="99"/>
-      <c r="C27" s="115"/>
+      <c r="A27" s="111"/>
+      <c r="B27" s="111"/>
+      <c r="C27" s="92"/>
       <c r="D27" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="E27" s="87"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="32"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="99"/>
-      <c r="B28" s="99"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="92"/>
-      <c r="F28" s="120"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="39"/>
+    </row>
+    <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="111"/>
+      <c r="B28" s="111"/>
+      <c r="C28" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="56" t="s">
+        <v>7</v>
+      </c>
       <c r="G28" s="31"/>
       <c r="H28" s="1"/>
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="99"/>
-      <c r="B29" s="99"/>
-      <c r="C29" s="61" t="s">
+      <c r="A29" s="111"/>
+      <c r="B29" s="111"/>
+      <c r="C29" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="60" t="s">
-        <v>109</v>
+      <c r="D29" s="69" t="s">
+        <v>39</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="56" t="s">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="F29" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G29" s="31"/>
       <c r="H29" s="1"/>
       <c r="I29" s="39"/>
     </row>
-    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="82" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="70" t="s">
-        <v>9</v>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="111"/>
+      <c r="B30" s="111"/>
+      <c r="C30" s="109" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="101" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="56" t="s">
+        <v>7</v>
       </c>
       <c r="G30" s="31"/>
       <c r="H30" s="1"/>
       <c r="I30" s="39"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="99"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="88" t="s">
-        <v>42</v>
-      </c>
+    <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="111"/>
+      <c r="B31" s="111"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="111" t="s">
-        <v>38</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E31" s="101"/>
       <c r="F31" s="56" t="s">
         <v>7</v>
       </c>
@@ -2074,113 +2094,115 @@
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
-    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="99"/>
-      <c r="B32" s="99"/>
-      <c r="C32" s="93"/>
-      <c r="D32" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="111"/>
-      <c r="F32" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="31"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="39"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="19"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="1"/>
+      <c r="A33" s="105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="109" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="31"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="88" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="67" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="78" t="s">
-        <v>13</v>
+      <c r="A34" s="106"/>
+      <c r="B34" s="106"/>
+      <c r="C34" s="114"/>
+      <c r="D34" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="85" t="s">
+        <v>7</v>
       </c>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="90"/>
+      <c r="A35" s="106"/>
+      <c r="B35" s="106"/>
+      <c r="C35" s="114"/>
       <c r="D35" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="110" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="107" t="s">
-        <v>7</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E35" s="84"/>
+      <c r="F35" s="104"/>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="86"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" s="92"/>
-      <c r="F36" s="114"/>
+    <row r="36" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="106"/>
+      <c r="B36" s="106"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="71" t="s">
+        <v>9</v>
+      </c>
       <c r="G36" s="31"/>
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="86"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="91"/>
-      <c r="D37" s="69" t="s">
-        <v>83</v>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="106"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="115" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="67" t="s">
+        <v>55</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="71" t="s">
-        <v>9</v>
+        <v>56</v>
+      </c>
+      <c r="F37" s="77" t="s">
+        <v>13</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="3"/>
       <c r="I37" s="32"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="86"/>
-      <c r="B38" s="86"/>
-      <c r="C38" s="102" t="s">
-        <v>117</v>
-      </c>
+    <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="106"/>
+      <c r="B38" s="106"/>
+      <c r="C38" s="116"/>
       <c r="D38" s="67" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F38" s="77" t="s">
         <v>13</v>
@@ -2189,52 +2211,50 @@
       <c r="H38" s="3"/>
       <c r="I38" s="32"/>
     </row>
-    <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="86"/>
-      <c r="B39" s="86"/>
-      <c r="C39" s="103"/>
+    <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="106"/>
+      <c r="B39" s="106"/>
+      <c r="C39" s="90" t="s">
+        <v>101</v>
+      </c>
       <c r="D39" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="3"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="81" t="s">
+        <v>119</v>
+      </c>
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="86"/>
-      <c r="B40" s="86"/>
-      <c r="C40" s="95" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" s="112" t="s">
-        <v>110</v>
-      </c>
-      <c r="F40" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="45"/>
-      <c r="H40" s="81" t="s">
-        <v>119</v>
-      </c>
+      <c r="A40" s="106"/>
+      <c r="B40" s="106"/>
+      <c r="C40" s="93"/>
+      <c r="D40" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="103"/>
+      <c r="F40" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="3"/>
       <c r="I40" s="32"/>
     </row>
-    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="86"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="97"/>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="106"/>
+      <c r="B41" s="106"/>
+      <c r="C41" s="93"/>
       <c r="D41" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="113"/>
+        <v>113</v>
+      </c>
+      <c r="E41" s="84"/>
       <c r="F41" s="72" t="s">
         <v>9</v>
       </c>
@@ -2243,376 +2263,378 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="86"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="97"/>
+      <c r="A42" s="106"/>
+      <c r="B42" s="106"/>
+      <c r="C42" s="90" t="s">
+        <v>120</v>
+      </c>
       <c r="D42" s="69" t="s">
-        <v>113</v>
-      </c>
-      <c r="E42" s="92"/>
-      <c r="F42" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="31"/>
-      <c r="H42" s="3"/>
+      <c r="H42" s="52" t="s">
+        <v>121</v>
+      </c>
       <c r="I42" s="32"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="86"/>
-      <c r="B43" s="86"/>
-      <c r="C43" s="95" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="69" t="s">
-        <v>86</v>
+    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="106"/>
+      <c r="B43" s="106"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="67" t="s">
+        <v>122</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="33"/>
+      <c r="H43" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="I43" s="32"/>
-    </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="86"/>
-      <c r="B44" s="86"/>
-      <c r="C44" s="96"/>
+      <c r="I43" s="34"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="107"/>
+      <c r="B44" s="107"/>
+      <c r="C44" s="79" t="s">
+        <v>85</v>
+      </c>
       <c r="D44" s="67" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>88</v>
+        <v>123</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="F44" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="33"/>
-      <c r="H44" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="94"/>
-      <c r="B45" s="94"/>
-      <c r="C45" s="79" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="68" t="s">
+      <c r="G44" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="28"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="109" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="80" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="80" t="s">
-        <v>25</v>
-      </c>
-      <c r="I45" s="80" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="28"/>
+      <c r="G46" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="67" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>10</v>
-      </c>
+      <c r="A47" s="118"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="119"/>
+      <c r="D47" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="84"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="89"/>
+      <c r="A48" s="118"/>
+      <c r="B48" s="106"/>
+      <c r="C48" s="119"/>
       <c r="D48" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="110" t="s">
-        <v>91</v>
-      </c>
-      <c r="F48" s="107" t="s">
-        <v>7</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E48" s="84"/>
+      <c r="F48" s="86"/>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="84"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="92"/>
-      <c r="F49" s="109"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="32"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="84"/>
-      <c r="B50" s="87"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="69" t="s">
+      <c r="A49" s="118"/>
+      <c r="B49" s="100"/>
+      <c r="C49" s="114"/>
+      <c r="D49" s="69" t="s">
         <v>57</v>
       </c>
+      <c r="E49" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="33"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="34"/>
+    </row>
+    <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="118"/>
+      <c r="B50" s="100"/>
+      <c r="C50" s="88"/>
+      <c r="D50" s="60" t="s">
+        <v>27</v>
+      </c>
       <c r="E50" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="118"/>
+      <c r="B51" s="100"/>
+      <c r="C51" s="109" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E51" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" s="85" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="87" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="87" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="118"/>
+      <c r="B52" s="100"/>
+      <c r="C52" s="110"/>
+      <c r="D52" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" s="84"/>
+      <c r="F52" s="86"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="118"/>
+      <c r="B53" s="100"/>
+      <c r="C53" s="109" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="44"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="28"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="118"/>
+      <c r="B54" s="100"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F54" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="33"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="34"/>
-    </row>
-    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
-      <c r="B51" s="87"/>
-      <c r="C51" s="91"/>
-      <c r="D51" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F51" s="54" t="s">
+      <c r="G54" s="45"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="118"/>
+      <c r="B55" s="100"/>
+      <c r="C55" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" s="87" t="s">
         <v>7</v>
-      </c>
-      <c r="G51" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
-      <c r="B52" s="87"/>
-      <c r="C52" s="88" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" s="110" t="s">
-        <v>62</v>
-      </c>
-      <c r="F52" s="107" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="104" t="s">
-        <v>17</v>
-      </c>
-      <c r="H52" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52" s="104" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
-      <c r="B53" s="87"/>
-      <c r="C53" s="93"/>
-      <c r="D53" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E53" s="92"/>
-      <c r="F53" s="109"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="91"/>
-      <c r="I53" s="91"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
-      <c r="B54" s="87"/>
-      <c r="C54" s="88" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="44"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="28"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
-      <c r="B55" s="87"/>
-      <c r="C55" s="91"/>
-      <c r="D55" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F55" s="73" t="s">
-        <v>9</v>
       </c>
       <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
-      <c r="B56" s="87"/>
-      <c r="C56" s="88" t="s">
-        <v>66</v>
-      </c>
+      <c r="A56" s="118"/>
+      <c r="B56" s="100"/>
+      <c r="C56" s="110"/>
       <c r="D56" s="59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" s="104" t="s">
-        <v>7</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="F56" s="89"/>
       <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="84"/>
-      <c r="B57" s="87"/>
-      <c r="C57" s="93"/>
-      <c r="D57" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="117"/>
-      <c r="G57" s="45"/>
+    <row r="57" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="43"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="1"/>
       <c r="H57" s="3"/>
       <c r="I57" s="32"/>
     </row>
-    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="32"/>
-    </row>
-    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="85" t="s">
+    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="85" t="s">
+      <c r="B58" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="C59" s="88" t="s">
+      <c r="C58" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="D59" s="55" t="s">
+      <c r="D58" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E58" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="57" t="s">
+      <c r="F58" s="57" t="s">
         <v>7</v>
+      </c>
+      <c r="G58" s="46"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="39"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="106"/>
+      <c r="B59" s="106"/>
+      <c r="C59" s="119"/>
+      <c r="D59" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="76" t="s">
+        <v>9</v>
       </c>
       <c r="G59" s="46"/>
       <c r="H59" s="1"/>
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="86"/>
-      <c r="B60" s="86"/>
-      <c r="C60" s="89"/>
-      <c r="D60" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E60" s="110" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="76" t="s">
-        <v>9</v>
+      <c r="A60" s="106"/>
+      <c r="B60" s="106"/>
+      <c r="C60" s="119"/>
+      <c r="D60" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" s="84"/>
+      <c r="F60" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G60" s="46"/>
       <c r="H60" s="1"/>
       <c r="I60" s="39"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="86"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="89"/>
+    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="100"/>
+      <c r="B61" s="100"/>
+      <c r="C61" s="109" t="s">
+        <v>104</v>
+      </c>
       <c r="D61" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E61" s="92"/>
+        <v>137</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="F61" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="46"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="39"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="47"/>
+      <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="87"/>
-      <c r="B62" s="87"/>
-      <c r="C62" s="88" t="s">
-        <v>104</v>
-      </c>
+      <c r="A62" s="100"/>
+      <c r="B62" s="100"/>
+      <c r="C62" s="88"/>
       <c r="D62" s="60" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F62" s="54" t="s">
         <v>7</v>
@@ -2621,34 +2643,36 @@
       <c r="H62" s="47"/>
       <c r="I62" s="48"/>
     </row>
-    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="87"/>
-      <c r="B63" s="87"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="60" t="s">
-        <v>77</v>
+    <row r="63" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="100"/>
+      <c r="B63" s="100"/>
+      <c r="C63" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D63" s="67" t="s">
+        <v>138</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F63" s="54" t="s">
-        <v>7</v>
+        <v>72</v>
+      </c>
+      <c r="F63" s="68" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="31"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="48"/>
-    </row>
-    <row r="64" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="87"/>
-      <c r="B64" s="87"/>
-      <c r="C64" s="66" t="s">
-        <v>139</v>
+      <c r="H63" s="1"/>
+      <c r="I63" s="49"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="100"/>
+      <c r="B64" s="100"/>
+      <c r="C64" s="109" t="s">
+        <v>69</v>
       </c>
       <c r="D64" s="67" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F64" s="68" t="s">
         <v>13</v>
@@ -2657,119 +2681,107 @@
       <c r="H64" s="1"/>
       <c r="I64" s="49"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="87"/>
-      <c r="B65" s="87"/>
-      <c r="C65" s="88" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" s="67" t="s">
-        <v>74</v>
+    <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="100"/>
+      <c r="B65" s="100"/>
+      <c r="C65" s="114"/>
+      <c r="D65" s="60" t="s">
+        <v>70</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="68" t="s">
-        <v>13</v>
+        <v>141</v>
+      </c>
+      <c r="F65" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G65" s="31"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="49"/>
+      <c r="I65" s="39"/>
     </row>
     <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="87"/>
-      <c r="B66" s="87"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="60" t="s">
-        <v>70</v>
+      <c r="A66" s="100"/>
+      <c r="B66" s="100"/>
+      <c r="C66" s="114"/>
+      <c r="D66" s="69" t="s">
+        <v>140</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F66" s="54" t="s">
-        <v>7</v>
+        <v>142</v>
+      </c>
+      <c r="F66" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G66" s="31"/>
       <c r="H66" s="1"/>
       <c r="I66" s="39"/>
     </row>
-    <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="87"/>
-      <c r="B67" s="87"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="69" t="s">
-        <v>140</v>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="84"/>
+      <c r="B67" s="84"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="67" t="s">
+        <v>71</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F67" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="G67" s="31"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="39"/>
+        <v>73</v>
+      </c>
+      <c r="F67" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="33"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="40"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="92"/>
-      <c r="B68" s="92"/>
-      <c r="C68" s="91"/>
-      <c r="D68" s="67" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F68" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="33"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="40"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="22"/>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="50"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="22"/>
+    </row>
+    <row r="69" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="2"/>
+      <c r="E69" s="5"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="E70" s="5"/>
-      <c r="G70" s="2"/>
+      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
+      <c r="I70" s="2"/>
     </row>
     <row r="71" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="E71" s="5"/>
-      <c r="G71" s="1"/>
+      <c r="G71" s="2"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="2"/>
-    </row>
-    <row r="72" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="E72" s="5"/>
-      <c r="G72" s="2"/>
+      <c r="G72" s="1"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
+      <c r="I72" s="2"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
       <c r="E73" s="5"/>
-      <c r="G73" s="1"/>
+      <c r="G73" s="2"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="2"/>
+      <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="E74" s="5"/>
-      <c r="G74" s="2"/>
+      <c r="G74" s="1"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
@@ -2781,30 +2793,30 @@
       <c r="I75" s="1"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="B76" s="3"/>
+      <c r="E76" s="7"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
-      <c r="E77" s="7"/>
+      <c r="E77" s="5"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="3"/>
-      <c r="E78" s="5"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B78" s="2"/>
+      <c r="E78" s="7"/>
+    </row>
+    <row r="79" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="E79" s="7"/>
     </row>
-    <row r="80" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
-      <c r="E80" s="7"/>
+      <c r="E80" s="5"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
@@ -2829,10 +2841,7 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
-      <c r="E84" s="5"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
+      <c r="E84" s="7"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
@@ -2840,14 +2849,14 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
-      <c r="E86" s="7"/>
+      <c r="E86" s="5"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
-      <c r="E87" s="5"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
+      <c r="E87" s="7"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
@@ -2870,7 +2879,6 @@
       <c r="E92" s="7"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="2"/>
       <c r="E93" s="7"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
@@ -2921,60 +2929,57 @@
     <row r="109" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E109" s="7"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E110" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="A46:A56"/>
+    <mergeCell ref="B46:B56"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="A58:A67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="A33:A44"/>
+    <mergeCell ref="B33:B44"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B17:B31"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A31"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="H51:H52"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="A34:A45"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="B18:B32"/>
-    <mergeCell ref="B6:B16"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="A18:A32"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C21:C28"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A47:A57"/>
-    <mergeCell ref="B47:B57"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="F55:F56"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E287E8-F1D1-47D1-B3E8-47F605CA9E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF198D3A-1754-4379-94B3-9703F478D307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -368,9 +368,6 @@
     <t>Verify if registered User cannot accept 'Remember me' at Login and cannot stay logged in</t>
   </si>
   <si>
-    <t>Check no 'Remember me' button exists</t>
-  </si>
-  <si>
     <t>Any specialty section of the doctors page is missing / unavailable or wrong section is displayed</t>
   </si>
   <si>
@@ -494,13 +491,88 @@
     <t>Check  passwords masking (type="password") for enhanced security</t>
   </si>
   <si>
-    <t>Check that Register goes via https protocol (manual)</t>
-  </si>
-  <si>
-    <t>Check that Login goes via https protocol (manual)</t>
-  </si>
-  <si>
     <t>Check that password is note exposed in error message</t>
+  </si>
+  <si>
+    <r>
+      <t>Check that Login goes via https protocol (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MANUAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Check that Register goes via https protocol (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MANUAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Check no 'Remember me' button exists (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MANUAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -838,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1020,9 +1092,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1086,133 +1155,145 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1606,22 +1687,22 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="61" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="31"/>
@@ -1629,16 +1710,16 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="108"/>
-      <c r="B4" s="113"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="69" t="s">
+      <c r="A4" s="97"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="31"/>
@@ -1657,22 +1738,22 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="68" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="74" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="31"/>
@@ -1680,16 +1761,16 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="108"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="62" t="s">
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="61" t="s">
         <v>105</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="63" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="31"/>
@@ -1697,16 +1778,16 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="108"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="69" t="s">
+      <c r="A8" s="97"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="68" t="s">
         <v>106</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="33"/>
@@ -1714,39 +1795,39 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="108"/>
-      <c r="B9" s="111"/>
-      <c r="C9" s="90" t="s">
+      <c r="A9" s="97"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" s="83" t="s">
+      <c r="D9" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="65" t="s">
+      <c r="F9" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="64" t="s">
+      <c r="I9" s="63" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="108"/>
-      <c r="B10" s="111"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="69" t="s">
+      <c r="A10" s="97"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="71" t="s">
+      <c r="E10" s="91"/>
+      <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="30"/>
@@ -1754,16 +1835,16 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="108"/>
-      <c r="B11" s="111"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="67" t="s">
+      <c r="A11" s="97"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="76" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="31"/>
@@ -1771,18 +1852,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="108"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="123" t="s">
+      <c r="A12" s="97"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="95" t="s">
-        <v>148</v>
-      </c>
-      <c r="F12" s="120" t="s">
+      <c r="D12" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="108" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="121" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1790,40 +1871,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="108"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="95"/>
-      <c r="F13" s="121"/>
+      <c r="A13" s="97"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="108"/>
+      <c r="F13" s="122"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="108"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="62" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="121"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="108"/>
+      <c r="F14" s="122"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="108"/>
-      <c r="B15" s="111"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="96"/>
-      <c r="F15" s="122"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="109"/>
+      <c r="F15" s="123"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1840,22 +1921,22 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="108" t="s">
+      <c r="A17" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C17" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="68" t="s">
         <v>46</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="71" t="s">
+      <c r="F17" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="31"/>
@@ -1863,16 +1944,16 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="108"/>
-      <c r="B18" s="108"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="62" t="s">
+      <c r="A18" s="97"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="61" t="s">
         <v>107</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="64" t="s">
         <v>7</v>
       </c>
       <c r="G18" s="31"/>
@@ -1880,16 +1961,16 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="108"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="69" t="s">
+      <c r="A19" s="97"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="68" t="s">
         <v>82</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="70" t="s">
+      <c r="F19" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G19" s="33"/>
@@ -1897,39 +1978,39 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="108"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="90" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="62" t="s">
+      <c r="A20" s="97"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="94" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="65" t="s">
+      <c r="F20" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="64" t="s">
+      <c r="H20" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="64" t="s">
+      <c r="I20" s="63" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="108"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="69" t="s">
+      <c r="A21" s="97"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="84"/>
-      <c r="F21" s="70" t="s">
+      <c r="E21" s="91"/>
+      <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G21" s="44"/>
@@ -1937,16 +2018,16 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="108"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="67" t="s">
+      <c r="A22" s="97"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="68" t="s">
+      <c r="F22" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G22" s="45"/>
@@ -1954,16 +2035,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="108"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="91"/>
-      <c r="D23" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="83" t="s">
-        <v>148</v>
-      </c>
-      <c r="F23" s="97" t="s">
+      <c r="A23" s="97"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="113" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23" s="110" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -1971,70 +2052,70 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="108"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="91"/>
-      <c r="D24" s="62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="100"/>
-      <c r="F24" s="98"/>
+      <c r="A24" s="97"/>
+      <c r="B24" s="98"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="86"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="108"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="62" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="100"/>
-      <c r="F25" s="98"/>
+      <c r="A25" s="97"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="86"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="108"/>
-      <c r="B26" s="111"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="62" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" s="100"/>
-      <c r="F26" s="98"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="86"/>
+      <c r="F26" s="111"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="111"/>
-      <c r="B27" s="111"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="84"/>
-      <c r="F27" s="99"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="91"/>
+      <c r="F27" s="112"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="111"/>
-      <c r="B28" s="111"/>
-      <c r="C28" s="61" t="s">
+      <c r="A28" s="98"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="60" t="s">
-        <v>109</v>
+      <c r="D28" s="126" t="s">
+        <v>153</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="56" t="s">
+      <c r="F28" s="125" t="s">
         <v>7</v>
       </c>
       <c r="G28" s="31"/>
@@ -2042,18 +2123,18 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="111"/>
-      <c r="B29" s="111"/>
-      <c r="C29" s="82" t="s">
+      <c r="A29" s="98"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="68" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="31"/>
@@ -2061,18 +2142,18 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="111"/>
-      <c r="B30" s="111"/>
-      <c r="C30" s="109" t="s">
+      <c r="A30" s="98"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="101" t="s">
+      <c r="E30" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="128" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2080,13 +2161,13 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="111"/>
-      <c r="B31" s="111"/>
-      <c r="C31" s="110"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="98"/>
+      <c r="C31" s="92"/>
       <c r="D31" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="101"/>
+      <c r="E31" s="116"/>
       <c r="F31" s="56" t="s">
         <v>7</v>
       </c>
@@ -2106,22 +2187,22 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="105" t="s">
+      <c r="A33" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="109" t="s">
+      <c r="C33" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="67" t="s">
-        <v>114</v>
+      <c r="D33" s="66" t="s">
+        <v>113</v>
       </c>
       <c r="E33" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="78" t="s">
+      <c r="F33" s="77" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="31"/>
@@ -2129,16 +2210,16 @@
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="106"/>
-      <c r="B34" s="106"/>
-      <c r="C34" s="114"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="89"/>
       <c r="D34" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" s="83" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="114" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2146,29 +2227,29 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="106"/>
-      <c r="B35" s="106"/>
-      <c r="C35" s="114"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="89"/>
       <c r="D35" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" s="84"/>
-      <c r="F35" s="104"/>
+        <v>115</v>
+      </c>
+      <c r="E35" s="91"/>
+      <c r="F35" s="119"/>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="106"/>
-      <c r="B36" s="106"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="69" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="68" t="s">
         <v>83</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="71" t="s">
+      <c r="F36" s="70" t="s">
         <v>9</v>
       </c>
       <c r="G36" s="31"/>
@@ -2176,18 +2257,18 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="106"/>
-      <c r="B37" s="106"/>
-      <c r="C37" s="115" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="67" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="105" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="66" t="s">
         <v>55</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="77" t="s">
+      <c r="F37" s="76" t="s">
         <v>13</v>
       </c>
       <c r="G37" s="31"/>
@@ -2195,16 +2276,16 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="106"/>
-      <c r="B38" s="106"/>
-      <c r="C38" s="116"/>
-      <c r="D38" s="67" t="s">
-        <v>118</v>
+      <c r="A38" s="85"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="106"/>
+      <c r="D38" s="66" t="s">
+        <v>117</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="77" t="s">
+      <c r="F38" s="76" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="31"/>
@@ -2212,35 +2293,35 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="106"/>
-      <c r="B39" s="106"/>
-      <c r="C39" s="90" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="D39" s="67" t="s">
+      <c r="D39" s="66" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="117" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="45"/>
+      <c r="H39" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="I39" s="32"/>
+    </row>
+    <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="F39" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="45"/>
-      <c r="H39" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="I39" s="32"/>
-    </row>
-    <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="106"/>
-      <c r="B40" s="106"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="103"/>
-      <c r="F40" s="72" t="s">
+      <c r="E40" s="118"/>
+      <c r="F40" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G40" s="31"/>
@@ -2248,14 +2329,14 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="106"/>
-      <c r="B41" s="106"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="69" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="84"/>
-      <c r="F41" s="72" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="91"/>
+      <c r="F41" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G41" s="31"/>
@@ -2263,67 +2344,67 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="106"/>
-      <c r="B42" s="106"/>
-      <c r="C42" s="90" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="69" t="s">
+      <c r="A42" s="85"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="68" t="s">
         <v>86</v>
       </c>
       <c r="E42" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="70" t="s">
+      <c r="F42" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="31"/>
       <c r="H42" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="32"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="85"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="66" t="s">
         <v>121</v>
-      </c>
-      <c r="I42" s="32"/>
-    </row>
-    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="106"/>
-      <c r="B43" s="106"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="67" t="s">
-        <v>122</v>
       </c>
       <c r="E43" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="68" t="s">
+      <c r="F43" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G43" s="33"/>
       <c r="H43" s="53" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="79" t="s">
+      <c r="A44" s="93"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="67" t="s">
+      <c r="D44" s="66" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F44" s="68" t="s">
+      <c r="F44" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="80" t="s">
+      <c r="G44" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H44" s="80" t="s">
+      <c r="H44" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="80" t="s">
+      <c r="I44" s="79" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2339,22 +2420,22 @@
       <c r="I45" s="28"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="117" t="s">
+      <c r="A46" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="105" t="s">
+      <c r="B46" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="109" t="s">
+      <c r="C46" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="67" t="s">
-        <v>125</v>
+      <c r="D46" s="66" t="s">
+        <v>124</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F46" s="68" t="s">
+      <c r="F46" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G46" s="31" t="s">
@@ -2364,16 +2445,16 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="118"/>
-      <c r="B47" s="106"/>
-      <c r="C47" s="119"/>
+      <c r="A47" s="83"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="88"/>
       <c r="D47" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="F47" s="85" t="s">
+      <c r="F47" s="114" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="31"/>
@@ -2381,29 +2462,29 @@
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="118"/>
-      <c r="B48" s="106"/>
-      <c r="C48" s="119"/>
+      <c r="A48" s="83"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="88"/>
       <c r="D48" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="E48" s="84"/>
-      <c r="F48" s="86"/>
+        <v>126</v>
+      </c>
+      <c r="E48" s="91"/>
+      <c r="F48" s="115"/>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="118"/>
-      <c r="B49" s="100"/>
-      <c r="C49" s="114"/>
-      <c r="D49" s="69" t="s">
+      <c r="A49" s="83"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="68" t="s">
         <v>57</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="70" t="s">
+      <c r="F49" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G49" s="33"/>
@@ -2411,9 +2492,9 @@
       <c r="I49" s="34"/>
     </row>
     <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="118"/>
-      <c r="B50" s="100"/>
-      <c r="C50" s="88"/>
+      <c r="A50" s="83"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="90"/>
       <c r="D50" s="60" t="s">
         <v>27</v>
       </c>
@@ -2434,51 +2515,51 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="118"/>
-      <c r="B51" s="100"/>
-      <c r="C51" s="109" t="s">
+      <c r="A51" s="83"/>
+      <c r="B51" s="86"/>
+      <c r="C51" s="87" t="s">
         <v>93</v>
       </c>
       <c r="D51" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="E51" s="113" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" s="114" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="107" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="107" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="83"/>
+      <c r="B52" s="86"/>
+      <c r="C52" s="92"/>
+      <c r="D52" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="F51" s="85" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="87" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="118"/>
-      <c r="B52" s="100"/>
-      <c r="C52" s="110"/>
-      <c r="D52" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E52" s="84"/>
-      <c r="F52" s="86"/>
-      <c r="G52" s="88"/>
-      <c r="H52" s="88"/>
-      <c r="I52" s="88"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="115"/>
+      <c r="G52" s="90"/>
+      <c r="H52" s="90"/>
+      <c r="I52" s="90"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="118"/>
-      <c r="B53" s="100"/>
-      <c r="C53" s="109" t="s">
+      <c r="A53" s="83"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="87" t="s">
         <v>65</v>
       </c>
       <c r="D53" s="59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E53" s="18" t="s">
         <v>95</v>
@@ -2491,16 +2572,16 @@
       <c r="I53" s="28"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="118"/>
-      <c r="B54" s="100"/>
-      <c r="C54" s="88"/>
-      <c r="D54" s="74" t="s">
-        <v>130</v>
+      <c r="A54" s="83"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="73" t="s">
+        <v>129</v>
       </c>
       <c r="E54" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F54" s="73" t="s">
+      <c r="F54" s="72" t="s">
         <v>9</v>
       </c>
       <c r="G54" s="45"/>
@@ -2508,18 +2589,18 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="118"/>
-      <c r="B55" s="100"/>
-      <c r="C55" s="109" t="s">
+      <c r="A55" s="83"/>
+      <c r="B55" s="86"/>
+      <c r="C55" s="87" t="s">
         <v>66</v>
       </c>
       <c r="D55" s="59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E55" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F55" s="87" t="s">
+      <c r="F55" s="107" t="s">
         <v>7</v>
       </c>
       <c r="G55" s="45"/>
@@ -2527,16 +2608,16 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="118"/>
-      <c r="B56" s="100"/>
-      <c r="C56" s="110"/>
+      <c r="A56" s="83"/>
+      <c r="B56" s="86"/>
+      <c r="C56" s="92"/>
       <c r="D56" s="59" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F56" s="89"/>
+      <c r="F56" s="124"/>
       <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
@@ -2553,17 +2634,17 @@
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="105" t="s">
+      <c r="A58" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="105" t="s">
+      <c r="B58" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="109" t="s">
+      <c r="C58" s="87" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E58" s="23" t="s">
         <v>67</v>
@@ -2576,16 +2657,16 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="106"/>
-      <c r="B59" s="106"/>
-      <c r="C59" s="119"/>
-      <c r="D59" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" s="83" t="s">
+      <c r="A59" s="85"/>
+      <c r="B59" s="85"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="F59" s="76" t="s">
+      <c r="F59" s="75" t="s">
         <v>9</v>
       </c>
       <c r="G59" s="46"/>
@@ -2593,13 +2674,13 @@
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="106"/>
-      <c r="B60" s="106"/>
-      <c r="C60" s="119"/>
+      <c r="A60" s="85"/>
+      <c r="B60" s="85"/>
+      <c r="C60" s="88"/>
       <c r="D60" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E60" s="84"/>
+        <v>133</v>
+      </c>
+      <c r="E60" s="91"/>
       <c r="F60" s="54" t="s">
         <v>7</v>
       </c>
@@ -2608,13 +2689,13 @@
       <c r="I60" s="39"/>
     </row>
     <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="100"/>
-      <c r="B61" s="100"/>
-      <c r="C61" s="109" t="s">
+      <c r="A61" s="86"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="87" t="s">
         <v>104</v>
       </c>
       <c r="D61" s="60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>97</v>
@@ -2627,9 +2708,9 @@
       <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="100"/>
-      <c r="B62" s="100"/>
-      <c r="C62" s="88"/>
+      <c r="A62" s="86"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="90"/>
       <c r="D62" s="60" t="s">
         <v>77</v>
       </c>
@@ -2644,18 +2725,18 @@
       <c r="I62" s="48"/>
     </row>
     <row r="63" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="100"/>
-      <c r="B63" s="100"/>
-      <c r="C63" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="D63" s="67" t="s">
+      <c r="A63" s="86"/>
+      <c r="B63" s="86"/>
+      <c r="C63" s="65" t="s">
         <v>138</v>
+      </c>
+      <c r="D63" s="66" t="s">
+        <v>137</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F63" s="68" t="s">
+      <c r="F63" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G63" s="31"/>
@@ -2663,18 +2744,18 @@
       <c r="I63" s="49"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="100"/>
-      <c r="B64" s="100"/>
-      <c r="C64" s="109" t="s">
+      <c r="A64" s="86"/>
+      <c r="B64" s="86"/>
+      <c r="C64" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="D64" s="67" t="s">
+      <c r="D64" s="66" t="s">
         <v>74</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="68" t="s">
+      <c r="F64" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G64" s="31"/>
@@ -2682,14 +2763,14 @@
       <c r="I64" s="49"/>
     </row>
     <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="100"/>
-      <c r="B65" s="100"/>
-      <c r="C65" s="114"/>
+      <c r="A65" s="86"/>
+      <c r="B65" s="86"/>
+      <c r="C65" s="89"/>
       <c r="D65" s="60" t="s">
         <v>70</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" s="54" t="s">
         <v>7</v>
@@ -2699,16 +2780,16 @@
       <c r="I65" s="39"/>
     </row>
     <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="100"/>
-      <c r="B66" s="100"/>
-      <c r="C66" s="114"/>
-      <c r="D66" s="69" t="s">
-        <v>140</v>
+      <c r="A66" s="86"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="89"/>
+      <c r="D66" s="68" t="s">
+        <v>139</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F66" s="70" t="s">
+        <v>141</v>
+      </c>
+      <c r="F66" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G66" s="31"/>
@@ -2716,16 +2797,16 @@
       <c r="I66" s="39"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
-      <c r="B67" s="84"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="67" t="s">
+      <c r="A67" s="91"/>
+      <c r="B67" s="91"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="66" t="s">
         <v>71</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="68" t="s">
+      <c r="F67" s="67" t="s">
         <v>13</v>
       </c>
       <c r="G67" s="33"/>
@@ -2931,17 +3012,28 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A46:A56"/>
-    <mergeCell ref="B46:B56"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="A58:A67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="H51:H52"/>
     <mergeCell ref="A33:A44"/>
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="C42:C43"/>
@@ -2958,28 +3050,17 @@
     <mergeCell ref="C20:C27"/>
     <mergeCell ref="C33:C36"/>
     <mergeCell ref="C37:C38"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="A46:A56"/>
+    <mergeCell ref="B46:B56"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="A58:A67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C51:C52"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF198D3A-1754-4379-94B3-9703F478D307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D12922-FC7A-48E0-A2F5-9E9A6880961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -910,7 +910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1155,145 +1155,139 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1687,13 +1681,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="115" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1710,9 +1704,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="97"/>
-      <c r="B4" s="100"/>
-      <c r="C4" s="99"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="115"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1738,13 +1732,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="97" t="s">
+      <c r="A6" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="90" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1761,9 +1755,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="104"/>
+      <c r="A7" s="111"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="61" t="s">
         <v>105</v>
       </c>
@@ -1778,9 +1772,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97"/>
-      <c r="B8" s="98"/>
-      <c r="C8" s="95"/>
+      <c r="A8" s="111"/>
+      <c r="B8" s="114"/>
+      <c r="C8" s="92"/>
       <c r="D8" s="68" t="s">
         <v>106</v>
       </c>
@@ -1795,15 +1789,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="97"/>
-      <c r="B9" s="98"/>
-      <c r="C9" s="94" t="s">
+      <c r="A9" s="111"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="90" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="113" t="s">
+      <c r="E9" s="83" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1820,13 +1814,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="97"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="104"/>
+      <c r="A10" s="111"/>
+      <c r="B10" s="114"/>
+      <c r="C10" s="91"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="91"/>
+      <c r="E10" s="84"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1835,9 +1829,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="95"/>
+      <c r="A11" s="111"/>
+      <c r="B11" s="114"/>
+      <c r="C11" s="92"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1852,18 +1846,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="101" t="s">
+      <c r="A12" s="111"/>
+      <c r="B12" s="114"/>
+      <c r="C12" s="117" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="108" t="s">
+      <c r="E12" s="98" t="s">
         <v>147</v>
       </c>
-      <c r="F12" s="121" t="s">
+      <c r="F12" s="95" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1871,40 +1865,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="97"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="102"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="114"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="108"/>
-      <c r="F13" s="122"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="96"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="97"/>
-      <c r="B14" s="98"/>
-      <c r="C14" s="102"/>
+      <c r="A14" s="111"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="108"/>
-      <c r="F14" s="122"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="96"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="97"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="103"/>
+      <c r="A15" s="111"/>
+      <c r="B15" s="114"/>
+      <c r="C15" s="119"/>
       <c r="D15" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="109"/>
-      <c r="F15" s="123"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="97"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1921,13 +1915,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="97" t="s">
+      <c r="A17" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="90" t="s">
         <v>100</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1944,9 +1938,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="97"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="96"/>
+      <c r="A18" s="111"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="61" t="s">
         <v>107</v>
       </c>
@@ -1961,9 +1955,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="97"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="120"/>
+      <c r="A19" s="111"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="94"/>
       <c r="D19" s="68" t="s">
         <v>82</v>
       </c>
@@ -1978,15 +1972,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="97"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="94" t="s">
+      <c r="A20" s="111"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="90" t="s">
         <v>145</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="113" t="s">
+      <c r="E20" s="83" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2003,13 +1997,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="97"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="104"/>
+      <c r="A21" s="111"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="91"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="91"/>
+      <c r="E21" s="84"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2018,9 +2012,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="97"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="104"/>
+      <c r="A22" s="111"/>
+      <c r="B22" s="114"/>
+      <c r="C22" s="91"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2035,16 +2029,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="97"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="104"/>
+      <c r="A23" s="111"/>
+      <c r="B23" s="114"/>
+      <c r="C23" s="91"/>
       <c r="D23" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E23" s="113" t="s">
+      <c r="E23" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="F23" s="110" t="s">
+      <c r="F23" s="100" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2052,70 +2046,70 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="97"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="104"/>
+      <c r="A24" s="111"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="91"/>
       <c r="D24" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E24" s="86"/>
-      <c r="F24" s="111"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="101"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="97"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="104"/>
+      <c r="A25" s="111"/>
+      <c r="B25" s="114"/>
+      <c r="C25" s="91"/>
       <c r="D25" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="86"/>
-      <c r="F25" s="111"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="97"/>
-      <c r="B26" s="98"/>
-      <c r="C26" s="104"/>
+      <c r="A26" s="111"/>
+      <c r="B26" s="114"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="E26" s="86"/>
-      <c r="F26" s="111"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="101"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="98"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="95"/>
+      <c r="A27" s="114"/>
+      <c r="B27" s="114"/>
+      <c r="C27" s="92"/>
       <c r="D27" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="91"/>
-      <c r="F27" s="112"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="102"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="98"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="127" t="s">
+      <c r="A28" s="114"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="126" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="126" t="s">
+      <c r="D28" s="61" t="s">
         <v>153</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="125" t="s">
+      <c r="F28" s="63" t="s">
         <v>7</v>
       </c>
       <c r="G28" s="31"/>
@@ -2123,8 +2117,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="98"/>
-      <c r="B29" s="98"/>
+      <c r="A29" s="114"/>
+      <c r="B29" s="114"/>
       <c r="C29" s="81" t="s">
         <v>108</v>
       </c>
@@ -2142,18 +2136,18 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="98"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="87" t="s">
+      <c r="A30" s="114"/>
+      <c r="B30" s="114"/>
+      <c r="C30" s="112" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="116" t="s">
+      <c r="E30" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="128" t="s">
+      <c r="F30" s="82" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2161,13 +2155,13 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="98"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="92"/>
+      <c r="A31" s="114"/>
+      <c r="B31" s="114"/>
+      <c r="C31" s="113"/>
       <c r="D31" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="116"/>
+      <c r="E31" s="104"/>
       <c r="F31" s="56" t="s">
         <v>7</v>
       </c>
@@ -2187,13 +2181,13 @@
       <c r="I32" s="32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="84" t="s">
+      <c r="B33" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="87" t="s">
+      <c r="C33" s="112" t="s">
         <v>81</v>
       </c>
       <c r="D33" s="66" t="s">
@@ -2210,16 +2204,16 @@
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="89"/>
+      <c r="A34" s="109"/>
+      <c r="B34" s="109"/>
+      <c r="C34" s="120"/>
       <c r="D34" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="113" t="s">
+      <c r="E34" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="114" t="s">
+      <c r="F34" s="85" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2227,22 +2221,22 @@
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="89"/>
+      <c r="A35" s="109"/>
+      <c r="B35" s="109"/>
+      <c r="C35" s="120"/>
       <c r="D35" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="E35" s="91"/>
-      <c r="F35" s="119"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="107"/>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="90"/>
+      <c r="A36" s="109"/>
+      <c r="B36" s="109"/>
+      <c r="C36" s="88"/>
       <c r="D36" s="68" t="s">
         <v>83</v>
       </c>
@@ -2257,9 +2251,9 @@
       <c r="I36" s="32"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="105" t="s">
+      <c r="A37" s="109"/>
+      <c r="B37" s="109"/>
+      <c r="C37" s="121" t="s">
         <v>116</v>
       </c>
       <c r="D37" s="66" t="s">
@@ -2276,9 +2270,9 @@
       <c r="I37" s="32"/>
     </row>
     <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="85"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="106"/>
+      <c r="A38" s="109"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="122"/>
       <c r="D38" s="66" t="s">
         <v>117</v>
       </c>
@@ -2293,15 +2287,15 @@
       <c r="I38" s="32"/>
     </row>
     <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="94" t="s">
+      <c r="A39" s="109"/>
+      <c r="B39" s="109"/>
+      <c r="C39" s="90" t="s">
         <v>101</v>
       </c>
       <c r="D39" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="117" t="s">
+      <c r="E39" s="105" t="s">
         <v>109</v>
       </c>
       <c r="F39" s="77" t="s">
@@ -2314,13 +2308,13 @@
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="96"/>
+      <c r="A40" s="109"/>
+      <c r="B40" s="109"/>
+      <c r="C40" s="93"/>
       <c r="D40" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="118"/>
+      <c r="E40" s="106"/>
       <c r="F40" s="71" t="s">
         <v>9</v>
       </c>
@@ -2329,13 +2323,13 @@
       <c r="I40" s="32"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="85"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="96"/>
+      <c r="A41" s="109"/>
+      <c r="B41" s="109"/>
+      <c r="C41" s="93"/>
       <c r="D41" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="E41" s="91"/>
+      <c r="E41" s="84"/>
       <c r="F41" s="71" t="s">
         <v>9</v>
       </c>
@@ -2344,9 +2338,9 @@
       <c r="I41" s="32"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="94" t="s">
+      <c r="A42" s="109"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="90" t="s">
         <v>119</v>
       </c>
       <c r="D42" s="68" t="s">
@@ -2365,9 +2359,9 @@
       <c r="I42" s="32"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="95"/>
+      <c r="A43" s="109"/>
+      <c r="B43" s="109"/>
+      <c r="C43" s="92"/>
       <c r="D43" s="66" t="s">
         <v>121</v>
       </c>
@@ -2384,8 +2378,8 @@
       <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="93"/>
-      <c r="B44" s="93"/>
+      <c r="A44" s="110"/>
+      <c r="B44" s="110"/>
       <c r="C44" s="78" t="s">
         <v>85</v>
       </c>
@@ -2420,13 +2414,13 @@
       <c r="I45" s="28"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="82" t="s">
+      <c r="A46" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="84" t="s">
+      <c r="B46" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="87" t="s">
+      <c r="C46" s="112" t="s">
         <v>90</v>
       </c>
       <c r="D46" s="66" t="s">
@@ -2445,16 +2439,16 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="83"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="88"/>
+      <c r="A47" s="124"/>
+      <c r="B47" s="109"/>
+      <c r="C47" s="125"/>
       <c r="D47" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="113" t="s">
+      <c r="E47" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="F47" s="114" t="s">
+      <c r="F47" s="85" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="31"/>
@@ -2462,22 +2456,22 @@
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="83"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="88"/>
+      <c r="A48" s="124"/>
+      <c r="B48" s="109"/>
+      <c r="C48" s="125"/>
       <c r="D48" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="91"/>
-      <c r="F48" s="115"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="86"/>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="83"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="89"/>
+      <c r="A49" s="124"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="120"/>
       <c r="D49" s="68" t="s">
         <v>57</v>
       </c>
@@ -2492,9 +2486,9 @@
       <c r="I49" s="34"/>
     </row>
     <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="83"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="90"/>
+      <c r="A50" s="124"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="88"/>
       <c r="D50" s="60" t="s">
         <v>27</v>
       </c>
@@ -2515,47 +2509,47 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="83"/>
-      <c r="B51" s="86"/>
-      <c r="C51" s="87" t="s">
+      <c r="A51" s="124"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="112" t="s">
         <v>93</v>
       </c>
       <c r="D51" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="E51" s="113" t="s">
+      <c r="E51" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="F51" s="114" t="s">
+      <c r="F51" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="107" t="s">
+      <c r="G51" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="107" t="s">
+      <c r="H51" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="I51" s="107" t="s">
+      <c r="I51" s="87" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="83"/>
-      <c r="B52" s="86"/>
-      <c r="C52" s="92"/>
+      <c r="A52" s="124"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="113"/>
       <c r="D52" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="91"/>
-      <c r="F52" s="115"/>
-      <c r="G52" s="90"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="90"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="86"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="83"/>
-      <c r="B53" s="86"/>
-      <c r="C53" s="87" t="s">
+      <c r="A53" s="124"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="112" t="s">
         <v>65</v>
       </c>
       <c r="D53" s="59" t="s">
@@ -2572,9 +2566,9 @@
       <c r="I53" s="28"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="83"/>
-      <c r="B54" s="86"/>
-      <c r="C54" s="90"/>
+      <c r="A54" s="124"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="88"/>
       <c r="D54" s="73" t="s">
         <v>129</v>
       </c>
@@ -2589,9 +2583,9 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="83"/>
-      <c r="B55" s="86"/>
-      <c r="C55" s="87" t="s">
+      <c r="A55" s="124"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="112" t="s">
         <v>66</v>
       </c>
       <c r="D55" s="59" t="s">
@@ -2600,7 +2594,7 @@
       <c r="E55" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F55" s="107" t="s">
+      <c r="F55" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G55" s="45"/>
@@ -2608,16 +2602,16 @@
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="83"/>
-      <c r="B56" s="86"/>
-      <c r="C56" s="92"/>
+      <c r="A56" s="124"/>
+      <c r="B56" s="103"/>
+      <c r="C56" s="113"/>
       <c r="D56" s="59" t="s">
         <v>132</v>
       </c>
       <c r="E56" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F56" s="124"/>
+      <c r="F56" s="89"/>
       <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
@@ -2634,13 +2628,13 @@
       <c r="I57" s="32"/>
     </row>
     <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="108" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="112" t="s">
         <v>103</v>
       </c>
       <c r="D58" s="55" t="s">
@@ -2657,13 +2651,13 @@
       <c r="I58" s="39"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="85"/>
-      <c r="B59" s="85"/>
-      <c r="C59" s="88"/>
+      <c r="A59" s="109"/>
+      <c r="B59" s="109"/>
+      <c r="C59" s="125"/>
       <c r="D59" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="113" t="s">
+      <c r="E59" s="83" t="s">
         <v>68</v>
       </c>
       <c r="F59" s="75" t="s">
@@ -2674,13 +2668,13 @@
       <c r="I59" s="39"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="85"/>
-      <c r="B60" s="85"/>
-      <c r="C60" s="88"/>
+      <c r="A60" s="109"/>
+      <c r="B60" s="109"/>
+      <c r="C60" s="125"/>
       <c r="D60" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="E60" s="91"/>
+      <c r="E60" s="84"/>
       <c r="F60" s="54" t="s">
         <v>7</v>
       </c>
@@ -2689,9 +2683,9 @@
       <c r="I60" s="39"/>
     </row>
     <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="86"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="87" t="s">
+      <c r="A61" s="103"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="112" t="s">
         <v>104</v>
       </c>
       <c r="D61" s="60" t="s">
@@ -2708,9 +2702,9 @@
       <c r="I61" s="48"/>
     </row>
     <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="86"/>
-      <c r="B62" s="86"/>
-      <c r="C62" s="90"/>
+      <c r="A62" s="103"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="88"/>
       <c r="D62" s="60" t="s">
         <v>77</v>
       </c>
@@ -2725,8 +2719,8 @@
       <c r="I62" s="48"/>
     </row>
     <row r="63" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="86"/>
-      <c r="B63" s="86"/>
+      <c r="A63" s="103"/>
+      <c r="B63" s="103"/>
       <c r="C63" s="65" t="s">
         <v>138</v>
       </c>
@@ -2744,9 +2738,9 @@
       <c r="I63" s="49"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="86"/>
-      <c r="B64" s="86"/>
-      <c r="C64" s="87" t="s">
+      <c r="A64" s="103"/>
+      <c r="B64" s="103"/>
+      <c r="C64" s="112" t="s">
         <v>69</v>
       </c>
       <c r="D64" s="66" t="s">
@@ -2763,9 +2757,9 @@
       <c r="I64" s="49"/>
     </row>
     <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="86"/>
-      <c r="B65" s="86"/>
-      <c r="C65" s="89"/>
+      <c r="A65" s="103"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="120"/>
       <c r="D65" s="60" t="s">
         <v>70</v>
       </c>
@@ -2780,9 +2774,9 @@
       <c r="I65" s="39"/>
     </row>
     <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="86"/>
-      <c r="B66" s="86"/>
-      <c r="C66" s="89"/>
+      <c r="A66" s="103"/>
+      <c r="B66" s="103"/>
+      <c r="C66" s="120"/>
       <c r="D66" s="68" t="s">
         <v>139</v>
       </c>
@@ -2797,9 +2791,9 @@
       <c r="I66" s="39"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
-      <c r="B67" s="91"/>
-      <c r="C67" s="90"/>
+      <c r="A67" s="84"/>
+      <c r="B67" s="84"/>
+      <c r="C67" s="88"/>
       <c r="D67" s="66" t="s">
         <v>71</v>
       </c>
@@ -3012,28 +3006,17 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="A46:A56"/>
+    <mergeCell ref="B46:B56"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="A58:A67"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C51:C52"/>
     <mergeCell ref="A33:A44"/>
     <mergeCell ref="B33:B44"/>
     <mergeCell ref="C42:C43"/>
@@ -3050,17 +3033,28 @@
     <mergeCell ref="C20:C27"/>
     <mergeCell ref="C33:C36"/>
     <mergeCell ref="C37:C38"/>
-    <mergeCell ref="A46:A56"/>
-    <mergeCell ref="B46:B56"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="A58:A67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="F55:F56"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D12922-FC7A-48E0-A2F5-9E9A6880961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272B1BF-0106-4A46-AB48-E2AE94F230DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="155">
   <si>
     <t>User Story</t>
   </si>
@@ -291,9 +291,6 @@
   </si>
   <si>
     <t>Open Doctors Page Displays the proper elements of this page</t>
-  </si>
-  <si>
-    <t>Check that Logout button works properly closing the profile</t>
   </si>
   <si>
     <t>Verify if any User can Search MDs by name/clinic/specailty in Doctors Page search field</t>
@@ -573,6 +570,12 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Check that Logout button Navigates back to app HomePage and Sign in button is displayed</t>
+  </si>
+  <si>
+    <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic Home subNavbar</t>
   </si>
 </sst>
 </file>
@@ -910,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1155,7 +1158,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1248,6 +1251,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1282,12 +1288,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1624,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1687,8 +1687,8 @@
       <c r="B3" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="115" t="s">
-        <v>98</v>
+      <c r="C3" s="116" t="s">
+        <v>97</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>20</v>
@@ -1705,8 +1705,8 @@
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="111"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="115"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="116"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="111"/>
-      <c r="B7" s="114"/>
+      <c r="B7" s="115"/>
       <c r="C7" s="91"/>
       <c r="D7" s="61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>52</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="111"/>
-      <c r="B8" s="114"/>
+      <c r="B8" s="115"/>
       <c r="C8" s="92"/>
       <c r="D8" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>30</v>
@@ -1790,12 +1790,12 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="111"/>
-      <c r="B9" s="114"/>
+      <c r="B9" s="115"/>
       <c r="C9" s="90" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E9" s="83" t="s">
         <v>34</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="111"/>
-      <c r="B10" s="114"/>
+      <c r="B10" s="115"/>
       <c r="C10" s="91"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="111"/>
-      <c r="B11" s="114"/>
+      <c r="B11" s="115"/>
       <c r="C11" s="92"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
@@ -1847,15 +1847,15 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="111"/>
-      <c r="B12" s="114"/>
-      <c r="C12" s="117" t="s">
-        <v>99</v>
+      <c r="B12" s="115"/>
+      <c r="C12" s="118" t="s">
+        <v>98</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E12" s="98" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F12" s="95" t="s">
         <v>7</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="111"/>
-      <c r="B13" s="114"/>
-      <c r="C13" s="118"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="119"/>
       <c r="D13" s="61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E13" s="98"/>
       <c r="F13" s="96"/>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="111"/>
-      <c r="B14" s="114"/>
-      <c r="C14" s="118"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="119"/>
       <c r="D14" s="61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E14" s="98"/>
       <c r="F14" s="96"/>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="111"/>
-      <c r="B15" s="114"/>
-      <c r="C15" s="119"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E15" s="99"/>
       <c r="F15" s="97"/>
@@ -1922,7 +1922,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="68" t="s">
         <v>46</v>
@@ -1942,7 +1942,7 @@
       <c r="B18" s="111"/>
       <c r="C18" s="93"/>
       <c r="D18" s="61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>54</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="111"/>
-      <c r="B19" s="114"/>
+      <c r="B19" s="115"/>
       <c r="C19" s="94"/>
       <c r="D19" s="68" t="s">
         <v>82</v>
@@ -1973,9 +1973,9 @@
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="111"/>
-      <c r="B20" s="114"/>
+      <c r="B20" s="115"/>
       <c r="C20" s="90" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>60</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="111"/>
-      <c r="B21" s="114"/>
+      <c r="B21" s="115"/>
       <c r="C21" s="91"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="111"/>
-      <c r="B22" s="114"/>
+      <c r="B22" s="115"/>
       <c r="C22" s="91"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="111"/>
-      <c r="B23" s="114"/>
+      <c r="B23" s="115"/>
       <c r="C23" s="91"/>
       <c r="D23" s="61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" s="83" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F23" s="100" t="s">
         <v>7</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="111"/>
-      <c r="B24" s="114"/>
+      <c r="B24" s="115"/>
       <c r="C24" s="91"/>
       <c r="D24" s="61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E24" s="103"/>
       <c r="F24" s="101"/>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="111"/>
-      <c r="B25" s="114"/>
+      <c r="B25" s="115"/>
       <c r="C25" s="91"/>
       <c r="D25" s="61" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E25" s="103"/>
       <c r="F25" s="101"/>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="111"/>
-      <c r="B26" s="114"/>
+      <c r="B26" s="115"/>
       <c r="C26" s="91"/>
       <c r="D26" s="61" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E26" s="103"/>
       <c r="F26" s="101"/>
@@ -2085,11 +2085,11 @@
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="114"/>
-      <c r="B27" s="114"/>
+      <c r="A27" s="115"/>
+      <c r="B27" s="115"/>
       <c r="C27" s="92"/>
       <c r="D27" s="61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E27" s="84"/>
       <c r="F27" s="102"/>
@@ -2098,13 +2098,13 @@
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="114"/>
-      <c r="B28" s="114"/>
-      <c r="C28" s="126" t="s">
-        <v>108</v>
+      <c r="A28" s="115"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="82" t="s">
+        <v>107</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>38</v>
@@ -2117,10 +2117,10 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="114"/>
-      <c r="B29" s="114"/>
+      <c r="A29" s="115"/>
+      <c r="B29" s="115"/>
       <c r="C29" s="81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" s="68" t="s">
         <v>39</v>
@@ -2135,19 +2135,19 @@
       <c r="H29" s="1"/>
       <c r="I29" s="39"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="114"/>
-      <c r="B30" s="114"/>
+    <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="115"/>
+      <c r="B30" s="115"/>
       <c r="C30" s="112" t="s">
         <v>42</v>
       </c>
       <c r="D30" s="68" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="E30" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="82" t="s">
+      <c r="F30" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2155,66 +2155,62 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="114"/>
-      <c r="B31" s="114"/>
+      <c r="A31" s="115"/>
+      <c r="B31" s="115"/>
       <c r="C31" s="113"/>
       <c r="D31" s="60" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="E31" s="104"/>
-      <c r="F31" s="56" t="s">
-        <v>7</v>
-      </c>
+      <c r="F31" s="88"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="19"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="32"/>
+    <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="115"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="114"/>
+      <c r="D32" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="104"/>
+      <c r="F32" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="31"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="108" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="112" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="66" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="31"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="1"/>
       <c r="H33" s="3"/>
       <c r="I33" s="32"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="109"/>
-      <c r="B34" s="109"/>
-      <c r="C34" s="120"/>
-      <c r="D34" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" s="85" t="s">
-        <v>7</v>
+      <c r="A34" s="108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="112" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="77" t="s">
+        <v>13</v>
       </c>
       <c r="G34" s="31"/>
       <c r="H34" s="3"/>
@@ -2223,61 +2219,61 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="109"/>
       <c r="B35" s="109"/>
-      <c r="C35" s="120"/>
+      <c r="C35" s="121"/>
       <c r="D35" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="84"/>
-      <c r="F35" s="107"/>
+        <v>113</v>
+      </c>
+      <c r="E35" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="85" t="s">
+        <v>7</v>
+      </c>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
-    <row r="36" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="109"/>
       <c r="B36" s="109"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="70" t="s">
-        <v>9</v>
-      </c>
+      <c r="C36" s="121"/>
+      <c r="D36" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="84"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="31"/>
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="109"/>
       <c r="B37" s="109"/>
-      <c r="C37" s="121" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="66" t="s">
-        <v>55</v>
+      <c r="C37" s="88"/>
+      <c r="D37" s="68" t="s">
+        <v>83</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="76" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F37" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G37" s="31"/>
       <c r="H37" s="3"/>
       <c r="I37" s="32"/>
     </row>
-    <row r="38" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="109"/>
       <c r="B38" s="109"/>
-      <c r="C38" s="122"/>
+      <c r="C38" s="122" t="s">
+        <v>115</v>
+      </c>
       <c r="D38" s="66" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F38" s="76" t="s">
         <v>13</v>
@@ -2286,50 +2282,52 @@
       <c r="H38" s="3"/>
       <c r="I38" s="32"/>
     </row>
-    <row r="39" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="109"/>
       <c r="B39" s="109"/>
-      <c r="C39" s="90" t="s">
-        <v>101</v>
-      </c>
+      <c r="C39" s="123"/>
       <c r="D39" s="66" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="105" t="s">
-        <v>109</v>
-      </c>
-      <c r="F39" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="45"/>
-      <c r="H39" s="80" t="s">
-        <v>118</v>
-      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="3"/>
       <c r="I39" s="32"/>
     </row>
     <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="109"/>
       <c r="B40" s="109"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" s="106"/>
-      <c r="F40" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="31"/>
-      <c r="H40" s="3"/>
+      <c r="C40" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="105" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="45"/>
+      <c r="H40" s="80" t="s">
+        <v>117</v>
+      </c>
       <c r="I40" s="32"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="109"/>
       <c r="B41" s="109"/>
       <c r="C41" s="93"/>
       <c r="D41" s="68" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="84"/>
+        <v>110</v>
+      </c>
+      <c r="E41" s="106"/>
       <c r="F41" s="71" t="s">
         <v>9</v>
       </c>
@@ -2340,328 +2338,326 @@
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="109"/>
       <c r="B42" s="109"/>
-      <c r="C42" s="90" t="s">
-        <v>119</v>
-      </c>
+      <c r="C42" s="93"/>
       <c r="D42" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" s="84"/>
+      <c r="F42" s="71" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="31"/>
-      <c r="H42" s="52" t="s">
-        <v>120</v>
-      </c>
+      <c r="H42" s="3"/>
       <c r="I42" s="32"/>
     </row>
-    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="109"/>
       <c r="B43" s="109"/>
-      <c r="C43" s="92"/>
-      <c r="D43" s="66" t="s">
-        <v>121</v>
+      <c r="C43" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="68" t="s">
+        <v>85</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="33"/>
-      <c r="H43" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="31"/>
+      <c r="H43" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="32"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="109"/>
+      <c r="B44" s="109"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="110"/>
-      <c r="B44" s="110"/>
-      <c r="C44" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" s="66" t="s">
-        <v>122</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>123</v>
+      <c r="E44" s="23" t="s">
+        <v>87</v>
       </c>
       <c r="F44" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G44" s="79" t="s">
+      <c r="G44" s="33"/>
+      <c r="H44" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="110"/>
+      <c r="B45" s="110"/>
+      <c r="C45" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H44" s="79" t="s">
+      <c r="H45" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="79" t="s">
+      <c r="I45" s="79" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="28"/>
-    </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="123" t="s">
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="28"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="108" t="s">
+      <c r="B47" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="112" t="s">
-        <v>90</v>
-      </c>
-      <c r="D46" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" s="8" t="s">
+      <c r="C47" s="112" t="s">
         <v>89</v>
       </c>
-      <c r="F46" s="67" t="s">
+      <c r="D47" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G47" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="32"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="124"/>
-      <c r="B47" s="109"/>
-      <c r="C47" s="125"/>
-      <c r="D47" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="83" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" s="85" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="124"/>
+      <c r="A48" s="125"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="125"/>
+      <c r="C48" s="113"/>
       <c r="D48" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="84"/>
-      <c r="F48" s="86"/>
+        <v>124</v>
+      </c>
+      <c r="E48" s="83" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" s="85" t="s">
+        <v>7</v>
+      </c>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="124"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="68" t="s">
+      <c r="A49" s="125"/>
+      <c r="B49" s="109"/>
+      <c r="C49" s="113"/>
+      <c r="D49" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="E49" s="84"/>
+      <c r="F49" s="86"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="125"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="121"/>
+      <c r="D50" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E50" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="69" t="s">
+      <c r="F50" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G49" s="33"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="34"/>
-    </row>
-    <row r="50" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="124"/>
-      <c r="B50" s="103"/>
-      <c r="C50" s="88"/>
-      <c r="D50" s="60" t="s">
+      <c r="G50" s="33"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="34"/>
+    </row>
+    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="125"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E51" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="125"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="F50" s="54" t="s">
+      <c r="D52" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="E52" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="56" t="s">
+      <c r="G52" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="H50" s="56" t="s">
+      <c r="H52" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="124"/>
-      <c r="B51" s="103"/>
-      <c r="C51" s="112" t="s">
-        <v>93</v>
-      </c>
-      <c r="D51" s="59" t="s">
+      <c r="I52" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="125"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="114"/>
+      <c r="D53" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="E51" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="F51" s="85" t="s">
+      <c r="E53" s="84"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="125"/>
+      <c r="B54" s="103"/>
+      <c r="C54" s="112" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="87" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="87" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="124"/>
-      <c r="B52" s="103"/>
-      <c r="C52" s="113"/>
-      <c r="D52" s="59" t="s">
+      <c r="G54" s="44"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="28"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="125"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="84"/>
-      <c r="F52" s="86"/>
-      <c r="G52" s="88"/>
-      <c r="H52" s="88"/>
-      <c r="I52" s="88"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="124"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="112" t="s">
-        <v>65</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F53" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" s="44"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="28"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="124"/>
-      <c r="B54" s="103"/>
-      <c r="C54" s="88"/>
-      <c r="D54" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="E54" s="18" t="s">
+      <c r="E55" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F54" s="72" t="s">
+      <c r="F55" s="72" t="s">
         <v>9</v>
-      </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="32"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="124"/>
-      <c r="B55" s="103"/>
-      <c r="C55" s="112" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="87" t="s">
-        <v>7</v>
       </c>
       <c r="G55" s="45"/>
       <c r="H55" s="3"/>
       <c r="I55" s="32"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="124"/>
+      <c r="A56" s="125"/>
       <c r="B56" s="103"/>
-      <c r="C56" s="113"/>
+      <c r="C56" s="112" t="s">
+        <v>66</v>
+      </c>
       <c r="D56" s="59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="89"/>
+        <v>95</v>
+      </c>
+      <c r="F56" s="87" t="s">
+        <v>7</v>
+      </c>
       <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
     </row>
-    <row r="57" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="43"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="1"/>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="125"/>
+      <c r="B57" s="103"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="89"/>
+      <c r="G57" s="45"/>
       <c r="H57" s="3"/>
       <c r="I57" s="32"/>
     </row>
-    <row r="58" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="108" t="s">
+    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="43"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="32"/>
+    </row>
+    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="108" t="s">
+      <c r="B59" s="108" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59" s="112" t="s">
         <v>102</v>
       </c>
-      <c r="C58" s="112" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="23" t="s">
+      <c r="D59" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="E59" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F58" s="57" t="s">
+      <c r="F59" s="57" t="s">
         <v>7</v>
-      </c>
-      <c r="G58" s="46"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="39"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="109"/>
-      <c r="B59" s="109"/>
-      <c r="C59" s="125"/>
-      <c r="D59" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59" s="75" t="s">
-        <v>9</v>
       </c>
       <c r="G59" s="46"/>
       <c r="H59" s="1"/>
@@ -2670,46 +2666,46 @@
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="109"/>
       <c r="B60" s="109"/>
-      <c r="C60" s="125"/>
-      <c r="D60" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E60" s="84"/>
-      <c r="F60" s="54" t="s">
-        <v>7</v>
+      <c r="C60" s="113"/>
+      <c r="D60" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="75" t="s">
+        <v>9</v>
       </c>
       <c r="G60" s="46"/>
       <c r="H60" s="1"/>
       <c r="I60" s="39"/>
     </row>
-    <row r="61" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="103"/>
-      <c r="B61" s="103"/>
-      <c r="C61" s="112" t="s">
-        <v>104</v>
-      </c>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="109"/>
+      <c r="B61" s="109"/>
+      <c r="C61" s="113"/>
       <c r="D61" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>97</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E61" s="84"/>
       <c r="F61" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="47"/>
-      <c r="I61" s="48"/>
+      <c r="G61" s="46"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="39"/>
     </row>
     <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A62" s="103"/>
       <c r="B62" s="103"/>
-      <c r="C62" s="88"/>
+      <c r="C62" s="112" t="s">
+        <v>103</v>
+      </c>
       <c r="D62" s="60" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F62" s="54" t="s">
         <v>7</v>
@@ -2718,36 +2714,34 @@
       <c r="H62" s="47"/>
       <c r="I62" s="48"/>
     </row>
-    <row r="63" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A63" s="103"/>
       <c r="B63" s="103"/>
-      <c r="C63" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63" s="66" t="s">
-        <v>137</v>
+      <c r="C63" s="88"/>
+      <c r="D63" s="60" t="s">
+        <v>77</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F63" s="67" t="s">
-        <v>13</v>
+        <v>76</v>
+      </c>
+      <c r="F63" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G63" s="31"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="49"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H63" s="47"/>
+      <c r="I63" s="48"/>
+    </row>
+    <row r="64" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="103"/>
       <c r="B64" s="103"/>
-      <c r="C64" s="112" t="s">
-        <v>69</v>
+      <c r="C64" s="65" t="s">
+        <v>137</v>
       </c>
       <c r="D64" s="66" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F64" s="67" t="s">
         <v>13</v>
@@ -2756,107 +2750,119 @@
       <c r="H64" s="1"/>
       <c r="I64" s="49"/>
     </row>
-    <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="103"/>
       <c r="B65" s="103"/>
-      <c r="C65" s="120"/>
-      <c r="D65" s="60" t="s">
-        <v>70</v>
+      <c r="C65" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="66" t="s">
+        <v>74</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F65" s="54" t="s">
-        <v>7</v>
+        <v>75</v>
+      </c>
+      <c r="F65" s="67" t="s">
+        <v>13</v>
       </c>
       <c r="G65" s="31"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="39"/>
+      <c r="I65" s="49"/>
     </row>
     <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="103"/>
       <c r="B66" s="103"/>
-      <c r="C66" s="120"/>
-      <c r="D66" s="68" t="s">
+      <c r="C66" s="121"/>
+      <c r="D66" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E66" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F66" s="69" t="s">
-        <v>9</v>
+      <c r="F66" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G66" s="31"/>
       <c r="H66" s="1"/>
       <c r="I66" s="39"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
-      <c r="B67" s="84"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="66" t="s">
+    <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="103"/>
+      <c r="B67" s="103"/>
+      <c r="C67" s="121"/>
+      <c r="D67" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="31"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="39"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="84"/>
+      <c r="B68" s="84"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E68" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="67" t="s">
+      <c r="F68" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G67" s="33"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="40"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="22"/>
-      <c r="B68" s="22"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="50"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="22"/>
-    </row>
-    <row r="69" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="2"/>
-      <c r="E69" s="5"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G68" s="33"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="40"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="22"/>
+    </row>
+    <row r="70" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="E70" s="5"/>
-      <c r="G70" s="1"/>
+      <c r="G70" s="2"/>
       <c r="H70" s="1"/>
-      <c r="I70" s="2"/>
+      <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="E71" s="5"/>
-      <c r="G71" s="2"/>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="E72" s="5"/>
-      <c r="G72" s="1"/>
+      <c r="G72" s="2"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="2"/>
+      <c r="I72" s="1"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
       <c r="E73" s="5"/>
-      <c r="G73" s="2"/>
+      <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="I73" s="2"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="E74" s="5"/>
-      <c r="G74" s="1"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
@@ -2868,30 +2874,30 @@
       <c r="I75" s="1"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="3"/>
-      <c r="E76" s="7"/>
+      <c r="B76" s="2"/>
+      <c r="E76" s="5"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
-      <c r="E77" s="5"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="2"/>
-      <c r="E78" s="7"/>
-    </row>
-    <row r="79" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="3"/>
+      <c r="E78" s="5"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="E79" s="7"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
-      <c r="E80" s="5"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="E80" s="7"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
@@ -2916,7 +2922,10 @@
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
-      <c r="E84" s="7"/>
+      <c r="E84" s="5"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
@@ -2924,14 +2933,14 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
-      <c r="E86" s="5"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
+      <c r="E86" s="7"/>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
-      <c r="E87" s="7"/>
+      <c r="E87" s="5"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
@@ -2954,6 +2963,7 @@
       <c r="E92" s="7"/>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="2"/>
       <c r="E93" s="7"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
@@ -3004,57 +3014,61 @@
     <row r="109" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E109" s="7"/>
     </row>
+    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E110" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A46:A56"/>
-    <mergeCell ref="B46:B56"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="A58:A67"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="A33:A44"/>
-    <mergeCell ref="B33:B44"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C39:C41"/>
+  <mergeCells count="50">
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="B47:B57"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="B34:B45"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C40:C42"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B17:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B17:B32"/>
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A31"/>
+    <mergeCell ref="A17:A32"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C33:C36"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="I52:I53"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="F23:F27"/>
     <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="E30:E32"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="E40:E42"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="F56:F57"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7272B1BF-0106-4A46-AB48-E2AE94F230DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257B7C42-CF05-4218-AB56-8A91003E933E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="156">
   <si>
     <t>User Story</t>
   </si>
@@ -576,6 +576,9 @@
   </si>
   <si>
     <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic Home subNavbar</t>
+  </si>
+  <si>
+    <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic Home</t>
   </si>
 </sst>
 </file>
@@ -913,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1161,38 +1164,119 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1206,88 +1290,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1624,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1681,13 +1693,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="100" t="s">
         <v>97</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1704,9 +1716,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="111"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="116"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1732,13 +1744,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="111" t="s">
+      <c r="B6" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="95" t="s">
         <v>80</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1755,9 +1767,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="111"/>
-      <c r="B7" s="115"/>
-      <c r="C7" s="91"/>
+      <c r="A7" s="98"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="61" t="s">
         <v>104</v>
       </c>
@@ -1772,9 +1784,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="111"/>
-      <c r="B8" s="115"/>
-      <c r="C8" s="92"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="96"/>
       <c r="D8" s="68" t="s">
         <v>105</v>
       </c>
@@ -1789,15 +1801,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="111"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="90" t="s">
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="95" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="83" t="s">
+      <c r="E9" s="114" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1814,13 +1826,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="111"/>
-      <c r="B10" s="115"/>
-      <c r="C10" s="91"/>
+      <c r="A10" s="98"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="84"/>
+      <c r="E10" s="92"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1829,9 +1841,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="111"/>
-      <c r="B11" s="115"/>
-      <c r="C11" s="92"/>
+      <c r="A11" s="98"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="96"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1846,18 +1858,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="111"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="118" t="s">
+      <c r="A12" s="98"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="102" t="s">
         <v>98</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="98" t="s">
+      <c r="E12" s="109" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="95" t="s">
+      <c r="F12" s="122" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1865,40 +1877,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="111"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="119"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="103"/>
       <c r="D13" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="96"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="123"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="111"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="119"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="103"/>
       <c r="D14" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="98"/>
-      <c r="F14" s="96"/>
+      <c r="E14" s="109"/>
+      <c r="F14" s="123"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="111"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="120"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="99"/>
-      <c r="F15" s="97"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="124"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1915,13 +1927,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="111" t="s">
+      <c r="B17" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C17" s="95" t="s">
         <v>99</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1938,9 +1950,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="111"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="93"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="61" t="s">
         <v>106</v>
       </c>
@@ -1955,9 +1967,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="111"/>
-      <c r="B19" s="115"/>
-      <c r="C19" s="94"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="68" t="s">
         <v>82</v>
       </c>
@@ -1972,15 +1984,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="111"/>
-      <c r="B20" s="115"/>
-      <c r="C20" s="90" t="s">
+      <c r="A20" s="98"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="95" t="s">
         <v>144</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="114" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -1997,13 +2009,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="111"/>
-      <c r="B21" s="115"/>
-      <c r="C21" s="91"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="105"/>
       <c r="D21" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="84"/>
+      <c r="E21" s="92"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2012,9 +2024,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="111"/>
-      <c r="B22" s="115"/>
-      <c r="C22" s="91"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="105"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2029,16 +2041,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="111"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="91"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="E23" s="83" t="s">
+      <c r="E23" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="F23" s="100" t="s">
+      <c r="F23" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2046,60 +2058,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="111"/>
-      <c r="B24" s="115"/>
-      <c r="C24" s="91"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="105"/>
       <c r="D24" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E24" s="103"/>
-      <c r="F24" s="101"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="112"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="111"/>
-      <c r="B25" s="115"/>
-      <c r="C25" s="91"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="105"/>
       <c r="D25" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="103"/>
-      <c r="F25" s="101"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="111"/>
-      <c r="B26" s="115"/>
-      <c r="C26" s="91"/>
+      <c r="A26" s="98"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="105"/>
       <c r="D26" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="103"/>
-      <c r="F26" s="101"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="112"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="115"/>
-      <c r="B27" s="115"/>
-      <c r="C27" s="92"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="96"/>
       <c r="D27" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E27" s="84"/>
-      <c r="F27" s="102"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="113"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="115"/>
-      <c r="B28" s="115"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="82" t="s">
         <v>107</v>
       </c>
@@ -2117,8 +2129,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="115"/>
-      <c r="B29" s="115"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="99"/>
       <c r="C29" s="81" t="s">
         <v>107</v>
       </c>
@@ -2136,18 +2148,18 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="115"/>
-      <c r="B30" s="115"/>
-      <c r="C30" s="112" t="s">
+      <c r="A30" s="99"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="104" t="s">
+      <c r="E30" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="87" t="s">
+      <c r="F30" s="126" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2155,142 +2167,138 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="115"/>
-      <c r="B31" s="115"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="60" t="s">
+      <c r="A31" s="99"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="E31" s="104"/>
-      <c r="F31" s="88"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="127"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="115"/>
-      <c r="B32" s="115"/>
-      <c r="C32" s="114"/>
-      <c r="D32" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="104"/>
-      <c r="F32" s="56" t="s">
-        <v>7</v>
-      </c>
+      <c r="A32" s="99"/>
+      <c r="B32" s="99"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="E32" s="117"/>
+      <c r="F32" s="128"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="19"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="32"/>
+    <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="99"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="117"/>
+      <c r="F33" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="31"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="108" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="108" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="112" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="31"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="1"/>
       <c r="H34" s="3"/>
       <c r="I34" s="32"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="109"/>
-      <c r="B35" s="109"/>
-      <c r="C35" s="121"/>
-      <c r="D35" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="85" t="s">
-        <v>7</v>
+      <c r="A35" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="88" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="77" t="s">
+        <v>13</v>
       </c>
       <c r="G35" s="31"/>
       <c r="H35" s="3"/>
       <c r="I35" s="32"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="109"/>
-      <c r="B36" s="109"/>
-      <c r="C36" s="121"/>
+      <c r="A36" s="86"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="90"/>
       <c r="D36" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="84"/>
-      <c r="F36" s="107"/>
+        <v>113</v>
+      </c>
+      <c r="E36" s="114" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="115" t="s">
+        <v>7</v>
+      </c>
       <c r="G36" s="31"/>
       <c r="H36" s="3"/>
       <c r="I36" s="32"/>
     </row>
-    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="109"/>
-      <c r="B37" s="109"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="70" t="s">
-        <v>9</v>
-      </c>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="86"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="E37" s="92"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="31"/>
       <c r="H37" s="3"/>
       <c r="I37" s="32"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="109"/>
-      <c r="B38" s="109"/>
-      <c r="C38" s="122" t="s">
-        <v>115</v>
-      </c>
-      <c r="D38" s="66" t="s">
-        <v>55</v>
+    <row r="38" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="86"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="91"/>
+      <c r="D38" s="68" t="s">
+        <v>83</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="76" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F38" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G38" s="31"/>
       <c r="H38" s="3"/>
       <c r="I38" s="32"/>
     </row>
-    <row r="39" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="109"/>
-      <c r="B39" s="109"/>
-      <c r="C39" s="123"/>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="86"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="106" t="s">
+        <v>115</v>
+      </c>
       <c r="D39" s="66" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F39" s="76" t="s">
         <v>13</v>
@@ -2299,50 +2307,52 @@
       <c r="H39" s="3"/>
       <c r="I39" s="32"/>
     </row>
-    <row r="40" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="109"/>
-      <c r="B40" s="109"/>
-      <c r="C40" s="90" t="s">
+    <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="86"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="107"/>
+      <c r="D40" s="66" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="86"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="66" t="s">
+      <c r="D41" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="E40" s="105" t="s">
+      <c r="E41" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="F40" s="77" t="s">
+      <c r="F41" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="45"/>
-      <c r="H40" s="80" t="s">
+      <c r="G41" s="45"/>
+      <c r="H41" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="109"/>
-      <c r="B41" s="109"/>
-      <c r="C41" s="93"/>
-      <c r="D41" s="68" t="s">
+      <c r="I41" s="32"/>
+    </row>
+    <row r="42" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="86"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="97"/>
+      <c r="D42" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="E41" s="106"/>
-      <c r="F41" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="109"/>
-      <c r="B42" s="109"/>
-      <c r="C42" s="93"/>
-      <c r="D42" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" s="84"/>
+      <c r="E42" s="119"/>
       <c r="F42" s="71" t="s">
         <v>9</v>
       </c>
@@ -2351,378 +2361,376 @@
       <c r="I42" s="32"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="109"/>
-      <c r="B43" s="109"/>
-      <c r="C43" s="90" t="s">
+      <c r="A43" s="86"/>
+      <c r="B43" s="86"/>
+      <c r="C43" s="97"/>
+      <c r="D43" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="E43" s="92"/>
+      <c r="F43" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="31"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="32"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="86"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="95" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="68" t="s">
+      <c r="D44" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="23" t="s">
+      <c r="E44" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F43" s="69" t="s">
+      <c r="F44" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="52" t="s">
+      <c r="G44" s="31"/>
+      <c r="H44" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="I43" s="32"/>
-    </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="109"/>
-      <c r="B44" s="109"/>
-      <c r="C44" s="92"/>
-      <c r="D44" s="66" t="s">
+      <c r="I44" s="32"/>
+    </row>
+    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="86"/>
+      <c r="B45" s="86"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E45" s="23" t="s">
         <v>87</v>
-      </c>
-      <c r="F44" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="33"/>
-      <c r="H44" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="34"/>
-    </row>
-    <row r="45" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="110"/>
-      <c r="B45" s="110"/>
-      <c r="C45" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="D45" s="66" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>122</v>
       </c>
       <c r="F45" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="79" t="s">
+      <c r="G45" s="33"/>
+      <c r="H45" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="I45" s="34"/>
+    </row>
+    <row r="46" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="94"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="79" t="s">
+      <c r="H46" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="I45" s="79" t="s">
+      <c r="I46" s="79" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="28"/>
-    </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="124" t="s">
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="28"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="108" t="s">
+      <c r="B48" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="112" t="s">
+      <c r="C48" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="66" t="s">
+      <c r="D48" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E48" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F47" s="67" t="s">
+      <c r="F48" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G48" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="32"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="125"/>
-      <c r="B48" s="109"/>
-      <c r="C48" s="113"/>
-      <c r="D48" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="F48" s="85" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="125"/>
-      <c r="B49" s="109"/>
-      <c r="C49" s="113"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="86"/>
+      <c r="C49" s="89"/>
       <c r="D49" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="E49" s="84"/>
-      <c r="F49" s="86"/>
+        <v>124</v>
+      </c>
+      <c r="E49" s="114" t="s">
+        <v>90</v>
+      </c>
+      <c r="F49" s="115" t="s">
+        <v>7</v>
+      </c>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="125"/>
-      <c r="B50" s="103"/>
-      <c r="C50" s="121"/>
-      <c r="D50" s="68" t="s">
+      <c r="A50" s="84"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="92"/>
+      <c r="F50" s="116"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="32"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="84"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="69" t="s">
+      <c r="F51" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G50" s="33"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="34"/>
-    </row>
-    <row r="51" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="125"/>
-      <c r="B51" s="103"/>
-      <c r="C51" s="88"/>
-      <c r="D51" s="60" t="s">
+      <c r="G51" s="33"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="34"/>
+    </row>
+    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="84"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="91"/>
+      <c r="D52" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E52" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F51" s="54" t="s">
+      <c r="F52" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="56" t="s">
+      <c r="G52" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H51" s="56" t="s">
+      <c r="H52" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I51" s="56" t="s">
+      <c r="I52" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="125"/>
-      <c r="B52" s="103"/>
-      <c r="C52" s="112" t="s">
+    <row r="53" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="84"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="59" t="s">
+      <c r="D53" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="E52" s="83" t="s">
+      <c r="E53" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="85" t="s">
+      <c r="F53" s="115" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="87" t="s">
+      <c r="G53" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="H52" s="87" t="s">
+      <c r="H53" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="87" t="s">
+      <c r="I53" s="108" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="125"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="114"/>
-      <c r="D53" s="59" t="s">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="84"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="93"/>
+      <c r="D54" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="E53" s="84"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="88"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="88"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="125"/>
-      <c r="B54" s="103"/>
-      <c r="C54" s="112" t="s">
+      <c r="E54" s="92"/>
+      <c r="F54" s="116"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="91"/>
+      <c r="I54" s="91"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="84"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="D54" s="59" t="s">
+      <c r="D55" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="E54" s="18" t="s">
+      <c r="E55" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F54" s="58" t="s">
+      <c r="F55" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="44"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="28"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="125"/>
-      <c r="B55" s="103"/>
-      <c r="C55" s="88"/>
-      <c r="D55" s="73" t="s">
+      <c r="G55" s="44"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="28"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="84"/>
+      <c r="B56" s="87"/>
+      <c r="C56" s="91"/>
+      <c r="D56" s="73" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E56" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F55" s="72" t="s">
+      <c r="F56" s="72" t="s">
         <v>9</v>
-      </c>
-      <c r="G55" s="45"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="32"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="125"/>
-      <c r="B56" s="103"/>
-      <c r="C56" s="112" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="87" t="s">
-        <v>7</v>
       </c>
       <c r="G56" s="45"/>
       <c r="H56" s="3"/>
       <c r="I56" s="32"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="125"/>
-      <c r="B57" s="103"/>
-      <c r="C57" s="114"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="88" t="s">
+        <v>66</v>
+      </c>
       <c r="D57" s="59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F57" s="89"/>
+        <v>95</v>
+      </c>
+      <c r="F57" s="108" t="s">
+        <v>7</v>
+      </c>
       <c r="G57" s="45"/>
       <c r="H57" s="3"/>
       <c r="I57" s="32"/>
     </row>
-    <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="1"/>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="84"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="125"/>
+      <c r="G58" s="45"/>
       <c r="H58" s="3"/>
       <c r="I58" s="32"/>
     </row>
-    <row r="59" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="108" t="s">
+    <row r="59" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="43"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="32"/>
+    </row>
+    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="108" t="s">
+      <c r="B60" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="C59" s="112" t="s">
+      <c r="C60" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="55" t="s">
+      <c r="D60" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="E59" s="23" t="s">
+      <c r="E60" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F59" s="57" t="s">
+      <c r="F60" s="57" t="s">
         <v>7</v>
-      </c>
-      <c r="G59" s="46"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="39"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="109"/>
-      <c r="B60" s="109"/>
-      <c r="C60" s="113"/>
-      <c r="D60" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="E60" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="75" t="s">
-        <v>9</v>
       </c>
       <c r="G60" s="46"/>
       <c r="H60" s="1"/>
       <c r="I60" s="39"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="109"/>
-      <c r="B61" s="109"/>
-      <c r="C61" s="113"/>
-      <c r="D61" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" s="84"/>
-      <c r="F61" s="54" t="s">
-        <v>7</v>
+      <c r="A61" s="86"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="E61" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="F61" s="75" t="s">
+        <v>9</v>
       </c>
       <c r="G61" s="46"/>
       <c r="H61" s="1"/>
       <c r="I61" s="39"/>
     </row>
-    <row r="62" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="103"/>
-      <c r="B62" s="103"/>
-      <c r="C62" s="112" t="s">
-        <v>103</v>
-      </c>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="86"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="89"/>
       <c r="D62" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>96</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="E62" s="92"/>
       <c r="F62" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="31"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="48"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="39"/>
     </row>
     <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="103"/>
-      <c r="B63" s="103"/>
-      <c r="C63" s="88"/>
+      <c r="A63" s="87"/>
+      <c r="B63" s="87"/>
+      <c r="C63" s="88" t="s">
+        <v>103</v>
+      </c>
       <c r="D63" s="60" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="F63" s="54" t="s">
         <v>7</v>
@@ -2731,36 +2739,34 @@
       <c r="H63" s="47"/>
       <c r="I63" s="48"/>
     </row>
-    <row r="64" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="103"/>
-      <c r="B64" s="103"/>
-      <c r="C64" s="65" t="s">
+    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="87"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="31"/>
+      <c r="H64" s="47"/>
+      <c r="I64" s="48"/>
+    </row>
+    <row r="65" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="87"/>
+      <c r="B65" s="87"/>
+      <c r="C65" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="D64" s="66" t="s">
+      <c r="D65" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E65" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="F64" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G64" s="31"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="49"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="103"/>
-      <c r="B65" s="103"/>
-      <c r="C65" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" s="66" t="s">
-        <v>74</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="F65" s="67" t="s">
         <v>13</v>
@@ -2769,107 +2775,119 @@
       <c r="H65" s="1"/>
       <c r="I65" s="49"/>
     </row>
-    <row r="66" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="103"/>
-      <c r="B66" s="103"/>
-      <c r="C66" s="121"/>
-      <c r="D66" s="60" t="s">
-        <v>70</v>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="87"/>
+      <c r="B66" s="87"/>
+      <c r="C66" s="88" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" s="66" t="s">
+        <v>74</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F66" s="54" t="s">
-        <v>7</v>
+        <v>75</v>
+      </c>
+      <c r="F66" s="67" t="s">
+        <v>13</v>
       </c>
       <c r="G66" s="31"/>
       <c r="H66" s="1"/>
-      <c r="I66" s="39"/>
+      <c r="I66" s="49"/>
     </row>
     <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="103"/>
-      <c r="B67" s="103"/>
-      <c r="C67" s="121"/>
-      <c r="D67" s="68" t="s">
-        <v>138</v>
+      <c r="A67" s="87"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="60" t="s">
+        <v>70</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F67" s="69" t="s">
-        <v>9</v>
+        <v>139</v>
+      </c>
+      <c r="F67" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G67" s="31"/>
       <c r="H67" s="1"/>
       <c r="I67" s="39"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
-      <c r="B68" s="84"/>
-      <c r="C68" s="88"/>
-      <c r="D68" s="66" t="s">
+    <row r="68" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="87"/>
+      <c r="B68" s="87"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F68" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="31"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="39"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="92"/>
+      <c r="B69" s="92"/>
+      <c r="C69" s="91"/>
+      <c r="D69" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E69" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F68" s="67" t="s">
+      <c r="F69" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G68" s="33"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="40"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="22"/>
-      <c r="B69" s="22"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="22"/>
-    </row>
-    <row r="70" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="2"/>
-      <c r="E70" s="5"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G69" s="33"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="40"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="22"/>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="E71" s="5"/>
-      <c r="G71" s="1"/>
+      <c r="G71" s="2"/>
       <c r="H71" s="1"/>
-      <c r="I71" s="2"/>
+      <c r="I71" s="1"/>
     </row>
     <row r="72" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="E72" s="5"/>
-      <c r="G72" s="2"/>
+      <c r="G72" s="1"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
       <c r="E73" s="5"/>
-      <c r="G73" s="1"/>
+      <c r="G73" s="2"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="2"/>
+      <c r="I73" s="1"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="E74" s="5"/>
-      <c r="G74" s="2"/>
+      <c r="G74" s="1"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="I74" s="2"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
       <c r="E75" s="5"/>
-      <c r="G75" s="1"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
@@ -2881,30 +2899,30 @@
       <c r="I76" s="1"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="3"/>
-      <c r="E77" s="7"/>
+      <c r="B77" s="2"/>
+      <c r="E77" s="5"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
-      <c r="E78" s="5"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
+      <c r="E78" s="7"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="2"/>
-      <c r="E79" s="7"/>
-    </row>
-    <row r="80" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="3"/>
+      <c r="E79" s="5"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
-      <c r="E81" s="5"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
+      <c r="E81" s="7"/>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
@@ -2929,7 +2947,10 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
-      <c r="E85" s="7"/>
+      <c r="E85" s="5"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
@@ -2937,14 +2958,14 @@
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
-      <c r="E87" s="5"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
+      <c r="E87" s="7"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
-      <c r="E88" s="7"/>
+      <c r="E88" s="5"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="2"/>
@@ -2967,6 +2988,7 @@
       <c r="E93" s="7"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="2"/>
       <c r="E94" s="7"/>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
@@ -3017,58 +3039,61 @@
     <row r="110" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E110" s="7"/>
     </row>
+    <row r="111" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E111" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A47:A57"/>
-    <mergeCell ref="B47:B57"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="A34:A45"/>
-    <mergeCell ref="B34:B45"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B17:B32"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A32"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="I52:I53"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E40:E42"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="F57:F58"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B17:B33"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="A17:A33"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="B48:B58"/>
+    <mergeCell ref="C48:C52"/>
+    <mergeCell ref="B60:B69"/>
+    <mergeCell ref="A60:A69"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C53:C54"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257B7C42-CF05-4218-AB56-8A91003E933E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F061720B-4D6A-4640-A511-76BB522E0686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="165">
   <si>
     <t>User Story</t>
   </si>
@@ -167,22 +167,13 @@
     <t>US006.</t>
   </si>
   <si>
-    <t>Verify if logged in User can Log out properly</t>
-  </si>
-  <si>
     <t xml:space="preserve">As a User, I want to Navigate to Doctors Page so that I can Search for an MD and decide if it worth to book an appointment </t>
   </si>
   <si>
     <t>Enter URL into browser search bar Navigates to Register Page</t>
   </si>
   <si>
-    <t>As a registered User, I want to Log in and Log out properly so that I can access my personal health details and they are  safe from outsiders as well.</t>
-  </si>
-  <si>
     <t>Enter URL into browser search bar Navigates to Login Page</t>
-  </si>
-  <si>
-    <t>Check that Leaving the site / closing browser is resulted in logged in User Logout even in case of missing Logout button use</t>
   </si>
   <si>
     <t>Doctors page is unavailable via URL</t>
@@ -572,13 +563,49 @@
     </r>
   </si>
   <si>
-    <t>Check that Logout button Navigates back to app HomePage and Sign in button is displayed</t>
-  </si>
-  <si>
-    <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic Home subNavbar</t>
-  </si>
-  <si>
     <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic Home</t>
+  </si>
+  <si>
+    <t>Verify if logged-in User can Log out properly using Logout button</t>
+  </si>
+  <si>
+    <t>As a registered User, I want to Log in so that I can access my personal health details.</t>
+  </si>
+  <si>
+    <t>US007</t>
+  </si>
+  <si>
+    <t>As a registered User, I want to Log out properly so that my personal health details are  safe from outsiders.</t>
+  </si>
+  <si>
+    <t>Verify if logged-in User is Logged-out properly in case leaving the page without Logout button usage</t>
+  </si>
+  <si>
+    <t>Check that Logout button Navigates back to app logged-out HomePage and Sign in button is displayed</t>
+  </si>
+  <si>
+    <t>Check that Logout after having appointments booked is resulted in unavailability of booked appointments' content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check that Closing the browser and Opening the app in 'incognito' mode Navigates to logged-out HomePage and Sign in button is displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check that Closing the browser and Opening the app without 'incognito' mode  Navigates to logged-out HomePage and Sign in button is displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check that Leaving app by opening a new page in 'incognito' browser and returning to app Opens logged-out Home and Sign in button is displayed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check that Leaving app by opening a new page without 'incognito' and returning to app Opens logged-out Home and Sign in button is displayed </t>
+  </si>
+  <si>
+    <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic subNavbar</t>
+  </si>
+  <si>
+    <t>Check that above steps are resulted in the disappearence of booked appointments button from Clinic subNavbar</t>
+  </si>
+  <si>
+    <t>Check that above steps are resulted in the disappearence of booked appointments button from Clinic Home</t>
   </si>
 </sst>
 </file>
@@ -671,7 +698,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,6 +735,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -916,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1164,24 +1197,36 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1191,9 +1236,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1278,6 +1320,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1293,13 +1338,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1636,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1693,20 +1735,20 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="98" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="100" t="s">
-        <v>97</v>
+      <c r="B3" s="101" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="103" t="s">
+        <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F3" s="62" t="s">
         <v>7</v>
@@ -1716,9 +1758,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="100"/>
+      <c r="A4" s="101"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1744,20 +1786,20 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="101" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="95" t="s">
-        <v>80</v>
+      <c r="C6" s="98" t="s">
+        <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F6" s="74" t="s">
         <v>9</v>
@@ -1767,14 +1809,14 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="105"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="108"/>
       <c r="D7" s="61" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F7" s="63" t="s">
         <v>7</v>
@@ -1784,11 +1826,11 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="98"/>
-      <c r="B8" s="99"/>
-      <c r="C8" s="96"/>
+      <c r="A8" s="101"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="68" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>30</v>
@@ -1801,15 +1843,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
-      <c r="B9" s="99"/>
-      <c r="C9" s="95" t="s">
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="98" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="117" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1822,17 +1864,17 @@
         <v>24</v>
       </c>
       <c r="I9" s="63" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
-      <c r="B10" s="99"/>
-      <c r="C10" s="105"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="108"/>
       <c r="D10" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="92"/>
+        <v>60</v>
+      </c>
+      <c r="E10" s="88"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1841,9 +1883,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="98"/>
-      <c r="B11" s="99"/>
-      <c r="C11" s="96"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="99"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1858,18 +1900,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="102" t="s">
-        <v>98</v>
+      <c r="A12" s="101"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="105" t="s">
+        <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="109" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="112" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="126" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1877,40 +1919,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="98"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="103"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="106"/>
       <c r="D13" s="61" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="109"/>
-      <c r="F13" s="123"/>
+        <v>142</v>
+      </c>
+      <c r="E13" s="112"/>
+      <c r="F13" s="127"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="98"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="103"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="106"/>
       <c r="D14" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="109"/>
-      <c r="F14" s="123"/>
+        <v>148</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="127"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="98"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="104"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="107"/>
       <c r="D15" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="110"/>
-      <c r="F15" s="124"/>
+        <v>145</v>
+      </c>
+      <c r="E15" s="113"/>
+      <c r="F15" s="128"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1927,20 +1969,20 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="98" t="s">
+      <c r="A17" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>99</v>
+      <c r="B17" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="98" t="s">
+        <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F17" s="70" t="s">
         <v>9</v>
@@ -1950,14 +1992,14 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="98"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="97"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="61" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F18" s="64" t="s">
         <v>7</v>
@@ -1967,11 +2009,11 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="98"/>
-      <c r="B19" s="99"/>
-      <c r="C19" s="121"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="125"/>
       <c r="D19" s="68" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>30</v>
@@ -1984,15 +2026,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="98"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="95" t="s">
-        <v>144</v>
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="98" t="s">
+        <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="114" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="117" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2009,13 +2051,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="98"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="105"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="108"/>
       <c r="D21" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="92"/>
+        <v>75</v>
+      </c>
+      <c r="E21" s="88"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2024,9 +2066,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="98"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="105"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="108"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2041,16 +2083,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="98"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="105"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="108"/>
       <c r="D23" s="61" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="117" t="s">
         <v>143</v>
       </c>
-      <c r="E23" s="114" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="111" t="s">
+      <c r="F23" s="114" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2058,65 +2100,65 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="98"/>
-      <c r="B24" s="99"/>
-      <c r="C24" s="105"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="87"/>
+      <c r="C24" s="108"/>
       <c r="D24" s="61" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E24" s="87"/>
-      <c r="F24" s="112"/>
+      <c r="F24" s="115"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="98"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="105"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="87"/>
+      <c r="C25" s="108"/>
       <c r="D25" s="61" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E25" s="87"/>
-      <c r="F25" s="112"/>
+      <c r="F25" s="115"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="98"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="105"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="108"/>
       <c r="D26" s="61" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E26" s="87"/>
-      <c r="F26" s="112"/>
+      <c r="F26" s="115"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="99"/>
-      <c r="B27" s="99"/>
-      <c r="C27" s="96"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="61" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="92"/>
-      <c r="F27" s="113"/>
+        <v>145</v>
+      </c>
+      <c r="E27" s="88"/>
+      <c r="F27" s="116"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="99"/>
-      <c r="B28" s="99"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="87"/>
       <c r="C28" s="82" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>38</v>
@@ -2129,10 +2171,10 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="99"/>
-      <c r="B29" s="99"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="81" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D29" s="68" t="s">
         <v>39</v>
@@ -2148,18 +2190,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="88" t="s">
-        <v>42</v>
+      <c r="A30" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="83" t="s">
+        <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="117" t="s">
+        <v>156</v>
+      </c>
+      <c r="E30" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="126" t="s">
+      <c r="F30" s="124" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2167,933 +2213,1082 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="99"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="89"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="84"/>
       <c r="D31" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="E31" s="117"/>
-      <c r="F31" s="127"/>
+        <v>162</v>
+      </c>
+      <c r="E31" s="120"/>
+      <c r="F31" s="84"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="99"/>
-      <c r="B32" s="99"/>
-      <c r="C32" s="89"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="84"/>
       <c r="D32" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="117"/>
-      <c r="F32" s="128"/>
+        <v>150</v>
+      </c>
+      <c r="E32" s="120"/>
+      <c r="F32" s="84"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="99"/>
-      <c r="B33" s="99"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="117"/>
-      <c r="F33" s="56" t="s">
-        <v>7</v>
-      </c>
+      <c r="A33" s="87"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="131" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="120"/>
+      <c r="F33" s="85"/>
       <c r="G33" s="31"/>
       <c r="H33" s="1"/>
       <c r="I33" s="39"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="19"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="32"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="88" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="77" t="s">
+    <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="87"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="89" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" s="120"/>
+      <c r="F34" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="39"/>
+    </row>
+    <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="87"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="E35" s="120"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="39"/>
+    </row>
+    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="87"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="120"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="39"/>
+    </row>
+    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="87"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="120"/>
+      <c r="F37" s="92"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="39"/>
+    </row>
+    <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="87"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="60" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="120"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="39"/>
+    </row>
+    <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="87"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="E39" s="120"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="39"/>
+    </row>
+    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="87"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="120"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="39"/>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="87"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" s="120"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="39"/>
+    </row>
+    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="87"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="60" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="120"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="39"/>
+    </row>
+    <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="87"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E43" s="120"/>
+      <c r="F43" s="92"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="39"/>
+    </row>
+    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="88"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="88"/>
+      <c r="D44" s="131" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" s="120"/>
+      <c r="F44" s="97"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="39"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="19"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="32"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="86" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="86" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="D46" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="31"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="32"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="86"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" s="115" t="s">
+      <c r="G46" s="31"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="92"/>
+      <c r="B47" s="92"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="117" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="31"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="32"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="86"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="E37" s="92"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="32"/>
-    </row>
-    <row r="38" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="86"/>
-      <c r="B38" s="86"/>
-      <c r="C38" s="91"/>
-      <c r="D38" s="68" t="s">
-        <v>83</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="32"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="86"/>
-      <c r="B39" s="86"/>
-      <c r="C39" s="106" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" s="66" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F39" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="32"/>
-    </row>
-    <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="86"/>
-      <c r="B40" s="86"/>
-      <c r="C40" s="107"/>
-      <c r="D40" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="31"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="86"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="95" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="66" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" s="118" t="s">
-        <v>108</v>
-      </c>
-      <c r="F41" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="45"/>
-      <c r="H41" s="80" t="s">
-        <v>117</v>
-      </c>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="86"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="97"/>
-      <c r="D42" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" s="119"/>
-      <c r="F42" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="31"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="32"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="86"/>
-      <c r="B43" s="86"/>
-      <c r="C43" s="97"/>
-      <c r="D43" s="68" t="s">
+      <c r="G47" s="31"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="92"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="E43" s="92"/>
-      <c r="F43" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="31"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="32"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="86"/>
-      <c r="B44" s="86"/>
-      <c r="C44" s="95" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F44" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="31"/>
-      <c r="H44" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="86"/>
-      <c r="B45" s="86"/>
-      <c r="C45" s="96"/>
-      <c r="D45" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="33"/>
-      <c r="H45" s="53" t="s">
-        <v>119</v>
-      </c>
-      <c r="I45" s="34"/>
-    </row>
-    <row r="46" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="94"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="66" t="s">
-        <v>121</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="I46" s="79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="28"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="88" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" s="66" t="s">
-        <v>123</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F48" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>10</v>
-      </c>
+      <c r="E48" s="88"/>
+      <c r="F48" s="123"/>
+      <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="84"/>
-      <c r="B49" s="86"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" s="114" t="s">
-        <v>90</v>
-      </c>
-      <c r="F49" s="115" t="s">
-        <v>7</v>
+    <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="92"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="84"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" s="92"/>
-      <c r="F50" s="116"/>
+      <c r="A50" s="92"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="76" t="s">
+        <v>13</v>
+      </c>
       <c r="G50" s="31"/>
       <c r="H50" s="3"/>
       <c r="I50" s="32"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
-      <c r="B51" s="87"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="69" t="s">
+    <row r="51" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="92"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="31"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="32"/>
+    </row>
+    <row r="52" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="92"/>
+      <c r="B52" s="92"/>
+      <c r="C52" s="98" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="E52" s="121" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="45"/>
+      <c r="H52" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" s="32"/>
+    </row>
+    <row r="53" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="92"/>
+      <c r="B53" s="92"/>
+      <c r="C53" s="100"/>
+      <c r="D53" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="122"/>
+      <c r="F53" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G51" s="33"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="34"/>
-    </row>
-    <row r="52" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
-      <c r="B52" s="87"/>
-      <c r="C52" s="91"/>
-      <c r="D52" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F52" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H52" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52" s="56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
-      <c r="B53" s="87"/>
-      <c r="C53" s="88" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="114" t="s">
-        <v>62</v>
-      </c>
-      <c r="F53" s="115" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" s="108" t="s">
-        <v>17</v>
-      </c>
-      <c r="H53" s="108" t="s">
-        <v>24</v>
-      </c>
-      <c r="I53" s="108" t="s">
+      <c r="G53" s="31"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="32"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="92"/>
+      <c r="B54" s="92"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="E54" s="88"/>
+      <c r="F54" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G54" s="31"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="92"/>
+      <c r="B55" s="92"/>
+      <c r="C55" s="98" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F55" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="31"/>
+      <c r="H55" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="I55" s="32"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="92"/>
+      <c r="B56" s="92"/>
+      <c r="C56" s="99"/>
+      <c r="D56" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="33"/>
+      <c r="H56" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="I56" s="34"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="97"/>
+      <c r="B57" s="97"/>
+      <c r="C57" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="66" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F57" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" s="79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="25"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="28"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="86" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
-      <c r="B54" s="87"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E54" s="92"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="91"/>
-      <c r="H54" s="91"/>
-      <c r="I54" s="91"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
-      <c r="B55" s="87"/>
-      <c r="C55" s="88" t="s">
-        <v>65</v>
-      </c>
-      <c r="D55" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="44"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="28"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
-      <c r="B56" s="87"/>
-      <c r="C56" s="91"/>
-      <c r="D56" s="73" t="s">
-        <v>128</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F56" s="72" t="s">
-        <v>9</v>
-      </c>
-      <c r="G56" s="45"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="32"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="84"/>
-      <c r="B57" s="87"/>
-      <c r="C57" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="108" t="s">
-        <v>7</v>
-      </c>
-      <c r="G57" s="45"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="32"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="84"/>
-      <c r="B58" s="87"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F58" s="125"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="32"/>
-    </row>
-    <row r="59" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="43"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="1"/>
+      <c r="C59" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="31" t="s">
+        <v>10</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="I59" s="32"/>
     </row>
-    <row r="60" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="85" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="85" t="s">
-        <v>101</v>
-      </c>
-      <c r="C60" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" s="55" t="s">
-        <v>133</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F60" s="57" t="s">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="91"/>
+      <c r="B60" s="92"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="G60" s="46"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="39"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="86"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="E61" s="114" t="s">
-        <v>68</v>
-      </c>
-      <c r="F61" s="75" t="s">
+      <c r="A61" s="91"/>
+      <c r="B61" s="92"/>
+      <c r="C61" s="93"/>
+      <c r="D61" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E61" s="88"/>
+      <c r="F61" s="119"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="32"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="91"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="94"/>
+      <c r="D62" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G61" s="46"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="39"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="86"/>
-      <c r="B62" s="86"/>
-      <c r="C62" s="89"/>
-      <c r="D62" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E62" s="92"/>
-      <c r="F62" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G62" s="46"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="39"/>
-    </row>
-    <row r="63" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="87"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="34"/>
+    </row>
+    <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="91"/>
       <c r="B63" s="87"/>
-      <c r="C63" s="88" t="s">
-        <v>103</v>
-      </c>
+      <c r="C63" s="95"/>
       <c r="D63" s="60" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F63" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="31"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="48"/>
-    </row>
-    <row r="64" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="87"/>
+      <c r="G63" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="91"/>
       <c r="B64" s="87"/>
-      <c r="C64" s="91"/>
-      <c r="D64" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="F64" s="54" t="s">
+      <c r="C64" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="117" t="s">
+        <v>59</v>
+      </c>
+      <c r="F64" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="31"/>
-      <c r="H64" s="47"/>
-      <c r="I64" s="48"/>
-    </row>
-    <row r="65" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="87"/>
+      <c r="G64" s="111" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="111" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="91"/>
       <c r="B65" s="87"/>
-      <c r="C65" s="65" t="s">
+      <c r="C65" s="96"/>
+      <c r="D65" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="88"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="95"/>
+      <c r="H65" s="95"/>
+      <c r="I65" s="95"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="91"/>
+      <c r="B66" s="87"/>
+      <c r="C66" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F66" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="44"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="28"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="91"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F67" s="72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="45"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="32"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="91"/>
+      <c r="B68" s="87"/>
+      <c r="C68" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="E68" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F68" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="G68" s="45"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="32"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="91"/>
+      <c r="B69" s="87"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F69" s="129"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="32"/>
+    </row>
+    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="43"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="32"/>
+    </row>
+    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" s="46"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="39"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="92"/>
+      <c r="B72" s="92"/>
+      <c r="C72" s="93"/>
+      <c r="D72" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="F72" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" s="46"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="39"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="92"/>
+      <c r="B73" s="92"/>
+      <c r="C73" s="93"/>
+      <c r="D73" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" s="88"/>
+      <c r="F73" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G73" s="46"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="39"/>
+    </row>
+    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="87"/>
+      <c r="B74" s="87"/>
+      <c r="C74" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F74" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74" s="31"/>
+      <c r="H74" s="47"/>
+      <c r="I74" s="48"/>
+    </row>
+    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="87"/>
+      <c r="B75" s="87"/>
+      <c r="C75" s="95"/>
+      <c r="D75" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F75" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75" s="31"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="48"/>
+    </row>
+    <row r="76" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="87"/>
+      <c r="B76" s="87"/>
+      <c r="C76" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F76" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="31"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="49"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="87"/>
+      <c r="B77" s="87"/>
+      <c r="C77" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="31"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="49"/>
+    </row>
+    <row r="78" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="87"/>
+      <c r="B78" s="87"/>
+      <c r="C78" s="94"/>
+      <c r="D78" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="31"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="39"/>
+    </row>
+    <row r="79" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="87"/>
+      <c r="B79" s="87"/>
+      <c r="C79" s="94"/>
+      <c r="D79" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D65" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F65" s="67" t="s">
+      <c r="F79" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="31"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="39"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="88"/>
+      <c r="B80" s="88"/>
+      <c r="C80" s="95"/>
+      <c r="D80" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F80" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G65" s="31"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="49"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="87"/>
-      <c r="B66" s="87"/>
-      <c r="C66" s="88" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" s="66" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F66" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="31"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="49"/>
-    </row>
-    <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="87"/>
-      <c r="B67" s="87"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="F67" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="31"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="39"/>
-    </row>
-    <row r="68" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="87"/>
-      <c r="B68" s="87"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="68" t="s">
-        <v>138</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F68" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="31"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="39"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="92"/>
-      <c r="B69" s="92"/>
-      <c r="C69" s="91"/>
-      <c r="D69" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F69" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="33"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="40"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="22"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="22"/>
-    </row>
-    <row r="71" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="2"/>
-      <c r="E71" s="5"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="2"/>
-      <c r="E72" s="5"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="2"/>
-    </row>
-    <row r="73" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="2"/>
-      <c r="E73" s="5"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B74" s="2"/>
-      <c r="E74" s="5"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="2"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B75" s="2"/>
-      <c r="E75" s="5"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="2"/>
-      <c r="E77" s="5"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="3"/>
-      <c r="E78" s="7"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="3"/>
-      <c r="E79" s="5"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="2"/>
-      <c r="E80" s="7"/>
-    </row>
-    <row r="81" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="2"/>
-      <c r="E81" s="7"/>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G80" s="33"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="40"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="22"/>
+      <c r="B81" s="22"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="22"/>
+    </row>
+    <row r="82" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="E82" s="5"/>
-      <c r="G82" s="1"/>
+      <c r="G82" s="2"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="E83" s="5"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I83" s="2"/>
+    </row>
+    <row r="84" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="E84" s="5"/>
-      <c r="G84" s="1"/>
+      <c r="G84" s="2"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="E85" s="5"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I85" s="2"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
-      <c r="E86" s="7"/>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E86" s="5"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
-      <c r="E87" s="7"/>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E87" s="5"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
       <c r="E88" s="5"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="2"/>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="3"/>
       <c r="E89" s="7"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="2"/>
-      <c r="E90" s="7"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="3"/>
+      <c r="E90" s="5"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B91" s="2"/>
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
       <c r="E92" s="7"/>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
-      <c r="E93" s="7"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E93" s="5"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
-      <c r="E94" s="7"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E95" s="7"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E96" s="7"/>
-    </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E94" s="5"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B95" s="2"/>
+      <c r="E95" s="5"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B96" s="2"/>
+      <c r="E96" s="5"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B97" s="2"/>
       <c r="E97" s="7"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B98" s="2"/>
       <c r="E98" s="7"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E99" s="7"/>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99" s="2"/>
+      <c r="E99" s="5"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B100" s="2"/>
       <c r="E100" s="7"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B101" s="2"/>
       <c r="E101" s="7"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102" s="2"/>
       <c r="E102" s="7"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103" s="2"/>
       <c r="E103" s="7"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B104" s="2"/>
       <c r="E104" s="7"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B105" s="2"/>
       <c r="E105" s="7"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E106" s="7"/>
     </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E107" s="7"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E108" s="7"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E109" s="7"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E110" s="7"/>
     </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E111" s="7"/>
     </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E112" s="7"/>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E113" s="7"/>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E114" s="7"/>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E115" s="7"/>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E116" s="7"/>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E117" s="7"/>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E118" s="7"/>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E119" s="7"/>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E120" s="7"/>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E121" s="7"/>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E122" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="F57:F58"/>
+  <mergeCells count="54">
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="F68:F69"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="F12:F15"/>
-    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I64:I65"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="F23:F27"/>
     <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="E30:E44"/>
     <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="F34:F44"/>
+    <mergeCell ref="A46:A57"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="C52:C54"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="B17:B33"/>
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A17:A33"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="B48:B58"/>
-    <mergeCell ref="C48:C52"/>
-    <mergeCell ref="B60:B69"/>
-    <mergeCell ref="A60:A69"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A59:A69"/>
+    <mergeCell ref="B59:B69"/>
+    <mergeCell ref="C59:C63"/>
+    <mergeCell ref="B71:B80"/>
+    <mergeCell ref="A71:A80"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="B30:B44"/>
+    <mergeCell ref="A30:A44"/>
+    <mergeCell ref="C34:C44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F061720B-4D6A-4640-A511-76BB522E0686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60DF65E-3669-4091-A1B6-3240D522E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="164">
   <si>
     <t>User Story</t>
   </si>
@@ -593,12 +593,6 @@
     <t xml:space="preserve">Check that Closing the browser and Opening the app without 'incognito' mode  Navigates to logged-out HomePage and Sign in button is displayed </t>
   </si>
   <si>
-    <t xml:space="preserve">Check that Leaving app by opening a new page in 'incognito' browser and returning to app Opens logged-out Home and Sign in button is displayed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check that Leaving app by opening a new page without 'incognito' and returning to app Opens logged-out Home and Sign in button is displayed </t>
-  </si>
-  <si>
     <t>Check that Logout is resulted in the disappearence of 'My appointments' button from Clinic subNavbar</t>
   </si>
   <si>
@@ -606,6 +600,9 @@
   </si>
   <si>
     <t>Check that above steps are resulted in the disappearence of booked appointments button from Clinic Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check that Leaving app by opening a new page in the browser and returning to app later Opens logged-out Home and Sign in button is displayed </t>
   </si>
 </sst>
 </file>
@@ -1197,151 +1194,151 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1678,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1735,13 +1732,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="118" t="s">
         <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1758,9 +1755,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="101"/>
-      <c r="B4" s="104"/>
-      <c r="C4" s="103"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="118"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1786,13 +1783,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="91" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1809,9 +1806,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="108"/>
+      <c r="A7" s="116"/>
+      <c r="B7" s="117"/>
+      <c r="C7" s="92"/>
       <c r="D7" s="61" t="s">
         <v>101</v>
       </c>
@@ -1826,9 +1823,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="101"/>
-      <c r="B8" s="102"/>
-      <c r="C8" s="99"/>
+      <c r="A8" s="116"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="68" t="s">
         <v>102</v>
       </c>
@@ -1843,15 +1840,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="101"/>
-      <c r="B9" s="102"/>
-      <c r="C9" s="98" t="s">
+      <c r="A9" s="116"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="91" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="117" t="s">
+      <c r="E9" s="84" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1868,13 +1865,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="101"/>
-      <c r="B10" s="102"/>
-      <c r="C10" s="108"/>
+      <c r="A10" s="116"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="92"/>
       <c r="D10" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="88"/>
+      <c r="E10" s="85"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1883,9 +1880,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="101"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="99"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1900,18 +1897,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="101"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="105" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="120" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="112" t="s">
+      <c r="E12" s="99" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="126" t="s">
+      <c r="F12" s="96" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1919,40 +1916,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="101"/>
-      <c r="B13" s="102"/>
-      <c r="C13" s="106"/>
+      <c r="A13" s="116"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="121"/>
       <c r="D13" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="112"/>
-      <c r="F13" s="127"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="97"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="101"/>
-      <c r="B14" s="102"/>
-      <c r="C14" s="106"/>
+      <c r="A14" s="116"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="112"/>
-      <c r="F14" s="127"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="97"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="101"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="107"/>
+      <c r="A15" s="116"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="122"/>
       <c r="D15" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="113"/>
-      <c r="F15" s="128"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="98"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1969,13 +1966,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="115" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="91" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1992,9 +1989,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="87"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="100"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="104"/>
+      <c r="C18" s="94"/>
       <c r="D18" s="61" t="s">
         <v>103</v>
       </c>
@@ -2009,9 +2006,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="87"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="125"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="95"/>
       <c r="D19" s="68" t="s">
         <v>79</v>
       </c>
@@ -2026,15 +2023,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87"/>
-      <c r="B20" s="87"/>
-      <c r="C20" s="98" t="s">
+      <c r="A20" s="104"/>
+      <c r="B20" s="104"/>
+      <c r="C20" s="91" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="117" t="s">
+      <c r="E20" s="84" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2051,13 +2048,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
-      <c r="B21" s="87"/>
-      <c r="C21" s="108"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="92"/>
       <c r="D21" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="88"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2066,9 +2063,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="108"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2083,16 +2080,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
-      <c r="B23" s="87"/>
-      <c r="C23" s="108"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="117" t="s">
+      <c r="E23" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="114" t="s">
+      <c r="F23" s="101" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2100,60 +2097,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
-      <c r="B24" s="87"/>
-      <c r="C24" s="108"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="92"/>
       <c r="D24" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="87"/>
-      <c r="F24" s="115"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
-      <c r="B25" s="87"/>
-      <c r="C25" s="108"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="87"/>
-      <c r="F25" s="115"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="102"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
-      <c r="B26" s="87"/>
-      <c r="C26" s="108"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="87"/>
-      <c r="F26" s="115"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="102"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
-      <c r="B27" s="87"/>
-      <c r="C27" s="99"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="93"/>
       <c r="D27" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="88"/>
-      <c r="F27" s="116"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="103"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
-      <c r="B28" s="87"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="104"/>
       <c r="C28" s="82" t="s">
         <v>104</v>
       </c>
@@ -2171,8 +2168,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
-      <c r="B29" s="88"/>
+      <c r="A29" s="85"/>
+      <c r="B29" s="85"/>
       <c r="C29" s="81" t="s">
         <v>104</v>
       </c>
@@ -2190,22 +2187,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="83" t="s">
+      <c r="C30" s="131" t="s">
         <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="120" t="s">
+      <c r="E30" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="124" t="s">
+      <c r="F30" s="109" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2213,55 +2210,55 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="87"/>
-      <c r="B31" s="87"/>
-      <c r="C31" s="84"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="61" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="120"/>
-      <c r="F31" s="84"/>
+        <v>160</v>
+      </c>
+      <c r="E31" s="105"/>
+      <c r="F31" s="110"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
-      <c r="B32" s="87"/>
-      <c r="C32" s="84"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="110"/>
       <c r="D32" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="120"/>
-      <c r="F32" s="84"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
-      <c r="B33" s="87"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="131" t="s">
+      <c r="A33" s="104"/>
+      <c r="B33" s="104"/>
+      <c r="C33" s="111"/>
+      <c r="D33" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="120"/>
-      <c r="F33" s="85"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="111"/>
       <c r="G33" s="31"/>
       <c r="H33" s="1"/>
       <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
-      <c r="B34" s="87"/>
-      <c r="C34" s="89" t="s">
+      <c r="A34" s="104"/>
+      <c r="B34" s="104"/>
+      <c r="C34" s="123" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="E34" s="120"/>
-      <c r="F34" s="111" t="s">
+      <c r="E34" s="105"/>
+      <c r="F34" s="88" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2269,227 +2266,231 @@
       <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
-      <c r="B35" s="87"/>
-      <c r="C35" s="93"/>
+      <c r="A35" s="104"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="129"/>
       <c r="D35" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="120"/>
-      <c r="F35" s="130"/>
+        <v>161</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="112"/>
       <c r="G35" s="31"/>
       <c r="H35" s="1"/>
       <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
+      <c r="A36" s="104"/>
+      <c r="B36" s="104"/>
+      <c r="C36" s="104"/>
       <c r="D36" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="120"/>
-      <c r="F36" s="92"/>
+        <v>162</v>
+      </c>
+      <c r="E36" s="105"/>
+      <c r="F36" s="113"/>
       <c r="G36" s="31"/>
       <c r="H36" s="1"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
-      <c r="B37" s="87"/>
-      <c r="C37" s="87"/>
+      <c r="A37" s="104"/>
+      <c r="B37" s="104"/>
+      <c r="C37" s="104"/>
       <c r="D37" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="120"/>
-      <c r="F37" s="92"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="113"/>
       <c r="G37" s="31"/>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
+      <c r="A38" s="104"/>
+      <c r="B38" s="104"/>
+      <c r="C38" s="104"/>
       <c r="D38" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="120"/>
-      <c r="F38" s="92"/>
+        <v>161</v>
+      </c>
+      <c r="E38" s="105"/>
+      <c r="F38" s="113"/>
       <c r="G38" s="31"/>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
+      <c r="A39" s="104"/>
+      <c r="B39" s="104"/>
+      <c r="C39" s="104"/>
       <c r="D39" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" s="120"/>
-      <c r="F39" s="92"/>
+        <v>162</v>
+      </c>
+      <c r="E39" s="105"/>
+      <c r="F39" s="113"/>
       <c r="G39" s="31"/>
       <c r="H39" s="1"/>
       <c r="I39" s="39"/>
     </row>
-    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40" s="120"/>
-      <c r="F40" s="92"/>
+    <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="104"/>
+      <c r="B40" s="104"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="E40" s="105"/>
+      <c r="F40" s="113"/>
       <c r="G40" s="31"/>
       <c r="H40" s="1"/>
       <c r="I40" s="39"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="87"/>
-      <c r="C41" s="87"/>
+      <c r="A41" s="104"/>
+      <c r="B41" s="104"/>
+      <c r="C41" s="104"/>
       <c r="D41" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="120"/>
-      <c r="F41" s="92"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="113"/>
       <c r="G41" s="31"/>
       <c r="H41" s="1"/>
       <c r="I41" s="39"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="A42" s="104"/>
+      <c r="B42" s="104"/>
+      <c r="C42" s="104"/>
       <c r="D42" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" s="120"/>
-      <c r="F42" s="92"/>
+        <v>162</v>
+      </c>
+      <c r="E42" s="105"/>
+      <c r="F42" s="113"/>
       <c r="G42" s="31"/>
       <c r="H42" s="1"/>
       <c r="I42" s="39"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="87"/>
-      <c r="B43" s="87"/>
-      <c r="C43" s="87"/>
-      <c r="D43" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" s="120"/>
-      <c r="F43" s="92"/>
+      <c r="A43" s="85"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="83" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" s="105"/>
+      <c r="F43" s="114"/>
       <c r="G43" s="31"/>
       <c r="H43" s="1"/>
       <c r="I43" s="39"/>
     </row>
-    <row r="44" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="88"/>
-      <c r="B44" s="88"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="131" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="120"/>
-      <c r="F44" s="97"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="39"/>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="19"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="1"/>
+      <c r="A45" s="115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="115" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="123" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="31"/>
       <c r="H45" s="3"/>
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="86" t="s">
-        <v>33</v>
-      </c>
-      <c r="B46" s="86" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" s="66" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="77" t="s">
-        <v>13</v>
+      <c r="A46" s="113"/>
+      <c r="B46" s="113"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="84" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" s="86" t="s">
+        <v>7</v>
       </c>
       <c r="G46" s="31"/>
       <c r="H46" s="3"/>
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="92"/>
-      <c r="B47" s="92"/>
-      <c r="C47" s="94"/>
+      <c r="A47" s="113"/>
+      <c r="B47" s="113"/>
+      <c r="C47" s="124"/>
       <c r="D47" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="E47" s="117" t="s">
-        <v>46</v>
-      </c>
-      <c r="F47" s="118" t="s">
-        <v>7</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E47" s="85"/>
+      <c r="F47" s="108"/>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="92"/>
-      <c r="B48" s="92"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" s="88"/>
-      <c r="F48" s="123"/>
+    <row r="48" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="113"/>
+      <c r="B48" s="113"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="68" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="70" t="s">
+        <v>9</v>
+      </c>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
-    <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="92"/>
-      <c r="B49" s="92"/>
-      <c r="C49" s="95"/>
-      <c r="D49" s="68" t="s">
-        <v>80</v>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="113"/>
+      <c r="B49" s="113"/>
+      <c r="C49" s="125" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="66" t="s">
+        <v>52</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" s="70" t="s">
-        <v>9</v>
+        <v>53</v>
+      </c>
+      <c r="F49" s="76" t="s">
+        <v>13</v>
       </c>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="92"/>
-      <c r="B50" s="92"/>
-      <c r="C50" s="109" t="s">
-        <v>112</v>
-      </c>
+    <row r="50" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="113"/>
+      <c r="B50" s="113"/>
+      <c r="C50" s="126"/>
       <c r="D50" s="66" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F50" s="76" t="s">
         <v>13</v>
@@ -2498,52 +2499,50 @@
       <c r="H50" s="3"/>
       <c r="I50" s="32"/>
     </row>
-    <row r="51" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="92"/>
-      <c r="B51" s="92"/>
-      <c r="C51" s="110"/>
+    <row r="51" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="113"/>
+      <c r="B51" s="113"/>
+      <c r="C51" s="91" t="s">
+        <v>97</v>
+      </c>
       <c r="D51" s="66" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="F51" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="31"/>
-      <c r="H51" s="3"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="80" t="s">
+        <v>114</v>
+      </c>
       <c r="I51" s="32"/>
     </row>
     <row r="52" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
-      <c r="B52" s="92"/>
-      <c r="C52" s="98" t="s">
-        <v>97</v>
-      </c>
-      <c r="D52" s="66" t="s">
-        <v>106</v>
-      </c>
-      <c r="E52" s="121" t="s">
-        <v>105</v>
-      </c>
-      <c r="F52" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="45"/>
-      <c r="H52" s="80" t="s">
-        <v>114</v>
-      </c>
+      <c r="A52" s="113"/>
+      <c r="B52" s="113"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="107"/>
+      <c r="F52" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" s="31"/>
+      <c r="H52" s="3"/>
       <c r="I52" s="32"/>
     </row>
-    <row r="53" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
-      <c r="B53" s="92"/>
-      <c r="C53" s="100"/>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="113"/>
+      <c r="B53" s="113"/>
+      <c r="C53" s="94"/>
       <c r="D53" s="68" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="122"/>
+        <v>108</v>
+      </c>
+      <c r="E53" s="85"/>
       <c r="F53" s="71" t="s">
         <v>9</v>
       </c>
@@ -2552,376 +2551,378 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
-      <c r="B54" s="92"/>
-      <c r="C54" s="100"/>
+      <c r="A54" s="113"/>
+      <c r="B54" s="113"/>
+      <c r="C54" s="91" t="s">
+        <v>115</v>
+      </c>
       <c r="D54" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="E54" s="88"/>
-      <c r="F54" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F54" s="69" t="s">
         <v>9</v>
       </c>
       <c r="G54" s="31"/>
-      <c r="H54" s="3"/>
+      <c r="H54" s="52" t="s">
+        <v>116</v>
+      </c>
       <c r="I54" s="32"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="92"/>
-      <c r="B55" s="92"/>
-      <c r="C55" s="98" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" s="68" t="s">
-        <v>82</v>
+    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="113"/>
+      <c r="B55" s="113"/>
+      <c r="C55" s="93"/>
+      <c r="D55" s="66" t="s">
+        <v>117</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F55" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G55" s="31"/>
-      <c r="H55" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="33"/>
+      <c r="H55" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="I55" s="32"/>
-    </row>
-    <row r="56" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="92"/>
-      <c r="B56" s="92"/>
-      <c r="C56" s="99"/>
+      <c r="I55" s="34"/>
+    </row>
+    <row r="56" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="114"/>
+      <c r="B56" s="114"/>
+      <c r="C56" s="78" t="s">
+        <v>81</v>
+      </c>
       <c r="D56" s="66" t="s">
-        <v>117</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>84</v>
+        <v>118</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="F56" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G56" s="33"/>
-      <c r="H56" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="I56" s="34"/>
-    </row>
-    <row r="57" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="97"/>
-      <c r="B57" s="97"/>
-      <c r="C57" s="78" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F57" s="67" t="s">
+      <c r="G56" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="25"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="28"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="127" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="123" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="I57" s="79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="25"/>
-      <c r="I58" s="28"/>
+      <c r="G58" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="32"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="D59" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F59" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="31" t="s">
-        <v>10</v>
-      </c>
+      <c r="A59" s="128"/>
+      <c r="B59" s="113"/>
+      <c r="C59" s="129"/>
+      <c r="D59" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="84" t="s">
+        <v>87</v>
+      </c>
+      <c r="F59" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="31"/>
       <c r="H59" s="3"/>
       <c r="I59" s="32"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="91"/>
-      <c r="B60" s="92"/>
-      <c r="C60" s="93"/>
+      <c r="A60" s="128"/>
+      <c r="B60" s="113"/>
+      <c r="C60" s="129"/>
       <c r="D60" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="F60" s="118" t="s">
-        <v>7</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="E60" s="85"/>
+      <c r="F60" s="87"/>
       <c r="G60" s="31"/>
       <c r="H60" s="3"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="91"/>
-      <c r="B61" s="92"/>
-      <c r="C61" s="93"/>
-      <c r="D61" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="E61" s="88"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="32"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="91"/>
-      <c r="B62" s="87"/>
-      <c r="C62" s="94"/>
-      <c r="D62" s="68" t="s">
+      <c r="A61" s="128"/>
+      <c r="B61" s="104"/>
+      <c r="C61" s="124"/>
+      <c r="D61" s="68" t="s">
         <v>54</v>
       </c>
+      <c r="E61" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G61" s="33"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="34"/>
+    </row>
+    <row r="62" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="128"/>
+      <c r="B62" s="104"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="60" t="s">
+        <v>27</v>
+      </c>
       <c r="E62" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="H62" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="128"/>
+      <c r="B63" s="104"/>
+      <c r="C63" s="123" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="88" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="128"/>
+      <c r="B64" s="104"/>
+      <c r="C64" s="130"/>
+      <c r="D64" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="85"/>
+      <c r="F64" s="87"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="89"/>
+      <c r="I64" s="89"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="128"/>
+      <c r="B65" s="104"/>
+      <c r="C65" s="123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="F65" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="G65" s="44"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="28"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="128"/>
+      <c r="B66" s="104"/>
+      <c r="C66" s="89"/>
+      <c r="D66" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G62" s="33"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="34"/>
-    </row>
-    <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="91"/>
-      <c r="B63" s="87"/>
-      <c r="C63" s="95"/>
-      <c r="D63" s="60" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F63" s="54" t="s">
+      <c r="G66" s="45"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="32"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="128"/>
+      <c r="B67" s="104"/>
+      <c r="C67" s="123" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F67" s="88" t="s">
         <v>7</v>
-      </c>
-      <c r="G63" s="56" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="I63" s="56" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="91"/>
-      <c r="B64" s="87"/>
-      <c r="C64" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="E64" s="117" t="s">
-        <v>59</v>
-      </c>
-      <c r="F64" s="118" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" s="111" t="s">
-        <v>17</v>
-      </c>
-      <c r="H64" s="111" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="111" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
-      <c r="B65" s="87"/>
-      <c r="C65" s="96"/>
-      <c r="D65" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="E65" s="88"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="95"/>
-      <c r="H65" s="95"/>
-      <c r="I65" s="95"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="91"/>
-      <c r="B66" s="87"/>
-      <c r="C66" s="89" t="s">
-        <v>62</v>
-      </c>
-      <c r="D66" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F66" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" s="44"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="28"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
-      <c r="B67" s="87"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="F67" s="72" t="s">
-        <v>9</v>
       </c>
       <c r="G67" s="45"/>
       <c r="H67" s="3"/>
       <c r="I67" s="32"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="91"/>
-      <c r="B68" s="87"/>
-      <c r="C68" s="89" t="s">
-        <v>63</v>
-      </c>
+      <c r="A68" s="128"/>
+      <c r="B68" s="104"/>
+      <c r="C68" s="130"/>
       <c r="D68" s="59" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F68" s="111" t="s">
-        <v>7</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F68" s="90"/>
       <c r="G68" s="45"/>
       <c r="H68" s="3"/>
       <c r="I68" s="32"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="91"/>
-      <c r="B69" s="87"/>
-      <c r="C69" s="96"/>
-      <c r="D69" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F69" s="129"/>
-      <c r="G69" s="45"/>
+    <row r="69" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="43"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="1"/>
       <c r="H69" s="3"/>
       <c r="I69" s="32"/>
     </row>
-    <row r="70" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="43"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="32"/>
-    </row>
-    <row r="71" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="86" t="s">
+    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="B71" s="86" t="s">
+      <c r="B70" s="115" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="89" t="s">
+      <c r="C70" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="D71" s="55" t="s">
+      <c r="D70" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E70" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F71" s="57" t="s">
+      <c r="F70" s="57" t="s">
         <v>7</v>
+      </c>
+      <c r="G70" s="46"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="39"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="113"/>
+      <c r="B71" s="113"/>
+      <c r="C71" s="129"/>
+      <c r="D71" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="F71" s="75" t="s">
+        <v>9</v>
       </c>
       <c r="G71" s="46"/>
       <c r="H71" s="1"/>
       <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="92"/>
-      <c r="B72" s="92"/>
-      <c r="C72" s="93"/>
-      <c r="D72" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E72" s="117" t="s">
-        <v>65</v>
-      </c>
-      <c r="F72" s="75" t="s">
-        <v>9</v>
+      <c r="A72" s="113"/>
+      <c r="B72" s="113"/>
+      <c r="C72" s="129"/>
+      <c r="D72" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="E72" s="85"/>
+      <c r="F72" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G72" s="46"/>
       <c r="H72" s="1"/>
       <c r="I72" s="39"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="92"/>
-      <c r="B73" s="92"/>
-      <c r="C73" s="93"/>
+    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="104"/>
+      <c r="B73" s="104"/>
+      <c r="C73" s="123" t="s">
+        <v>100</v>
+      </c>
       <c r="D73" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E73" s="88"/>
+        <v>132</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="F73" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="46"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="39"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="47"/>
+      <c r="I73" s="48"/>
     </row>
     <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="87"/>
-      <c r="B74" s="87"/>
-      <c r="C74" s="89" t="s">
-        <v>100</v>
-      </c>
+      <c r="A74" s="104"/>
+      <c r="B74" s="104"/>
+      <c r="C74" s="89"/>
       <c r="D74" s="60" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="F74" s="54" t="s">
         <v>7</v>
@@ -2930,34 +2931,36 @@
       <c r="H74" s="47"/>
       <c r="I74" s="48"/>
     </row>
-    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="87"/>
-      <c r="B75" s="87"/>
-      <c r="C75" s="95"/>
-      <c r="D75" s="60" t="s">
-        <v>74</v>
+    <row r="75" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="104"/>
+      <c r="B75" s="104"/>
+      <c r="C75" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" s="66" t="s">
+        <v>133</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F75" s="54" t="s">
-        <v>7</v>
+        <v>69</v>
+      </c>
+      <c r="F75" s="67" t="s">
+        <v>13</v>
       </c>
       <c r="G75" s="31"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="48"/>
-    </row>
-    <row r="76" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="87"/>
-      <c r="B76" s="87"/>
-      <c r="C76" s="65" t="s">
-        <v>134</v>
+      <c r="H75" s="1"/>
+      <c r="I75" s="49"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="104"/>
+      <c r="B76" s="104"/>
+      <c r="C76" s="123" t="s">
+        <v>66</v>
       </c>
       <c r="D76" s="66" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F76" s="67" t="s">
         <v>13</v>
@@ -2966,182 +2969,167 @@
       <c r="H76" s="1"/>
       <c r="I76" s="49"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="87"/>
-      <c r="B77" s="87"/>
-      <c r="C77" s="89" t="s">
-        <v>66</v>
-      </c>
-      <c r="D77" s="66" t="s">
-        <v>71</v>
+    <row r="77" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="104"/>
+      <c r="B77" s="104"/>
+      <c r="C77" s="124"/>
+      <c r="D77" s="60" t="s">
+        <v>67</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F77" s="67" t="s">
-        <v>13</v>
+        <v>136</v>
+      </c>
+      <c r="F77" s="54" t="s">
+        <v>7</v>
       </c>
       <c r="G77" s="31"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="49"/>
+      <c r="I77" s="39"/>
     </row>
     <row r="78" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="87"/>
-      <c r="B78" s="87"/>
-      <c r="C78" s="94"/>
-      <c r="D78" s="60" t="s">
-        <v>67</v>
+      <c r="A78" s="104"/>
+      <c r="B78" s="104"/>
+      <c r="C78" s="124"/>
+      <c r="D78" s="68" t="s">
+        <v>135</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F78" s="54" t="s">
-        <v>7</v>
+        <v>137</v>
+      </c>
+      <c r="F78" s="69" t="s">
+        <v>9</v>
       </c>
       <c r="G78" s="31"/>
       <c r="H78" s="1"/>
       <c r="I78" s="39"/>
     </row>
-    <row r="79" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="87"/>
-      <c r="B79" s="87"/>
-      <c r="C79" s="94"/>
-      <c r="D79" s="68" t="s">
-        <v>135</v>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="85"/>
+      <c r="B79" s="85"/>
+      <c r="C79" s="89"/>
+      <c r="D79" s="66" t="s">
+        <v>68</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F79" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="G79" s="31"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="39"/>
+        <v>70</v>
+      </c>
+      <c r="F79" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="33"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="88"/>
-      <c r="B80" s="88"/>
-      <c r="C80" s="95"/>
-      <c r="D80" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="F80" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="33"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="40"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="22"/>
-      <c r="B81" s="22"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="22"/>
-    </row>
-    <row r="82" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="22"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="22"/>
+    </row>
+    <row r="81" spans="2:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="2"/>
+      <c r="E81" s="5"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="E82" s="5"/>
-      <c r="G82" s="2"/>
+      <c r="G82" s="1"/>
       <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-    </row>
-    <row r="83" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I82" s="2"/>
+    </row>
+    <row r="83" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="E83" s="5"/>
-      <c r="G83" s="1"/>
+      <c r="G83" s="2"/>
       <c r="H83" s="1"/>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="E84" s="5"/>
-      <c r="G84" s="2"/>
+      <c r="G84" s="1"/>
       <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I84" s="2"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="E85" s="5"/>
-      <c r="G85" s="1"/>
+      <c r="G85" s="2"/>
       <c r="H85" s="1"/>
-      <c r="I85" s="2"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
       <c r="E86" s="5"/>
-      <c r="G86" s="2"/>
+      <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
       <c r="E87" s="5"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="2"/>
-      <c r="E88" s="5"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="3"/>
+      <c r="E88" s="7"/>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
-      <c r="E89" s="7"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="3"/>
-      <c r="E90" s="5"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E89" s="5"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="2"/>
+      <c r="E90" s="7"/>
+    </row>
+    <row r="91" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="2"/>
       <c r="E91" s="7"/>
     </row>
-    <row r="92" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
-      <c r="E92" s="7"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E92" s="5"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
       <c r="E93" s="5"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
       <c r="E94" s="5"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="2"/>
       <c r="E95" s="5"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B96" s="2"/>
-      <c r="E96" s="5"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="E96" s="7"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97" s="2"/>
@@ -3149,14 +3137,14 @@
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98" s="2"/>
-      <c r="E98" s="7"/>
+      <c r="E98" s="5"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99" s="2"/>
-      <c r="E99" s="5"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="E99" s="7"/>
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100" s="2"/>
@@ -3179,7 +3167,6 @@
       <c r="E104" s="7"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B105" s="2"/>
       <c r="E105" s="7"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.3">
@@ -3230,39 +3217,26 @@
     <row r="121" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E121" s="7"/>
     </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E122" s="7"/>
-    </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="I64:I65"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="E30:E44"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="F34:F44"/>
-    <mergeCell ref="A46:A57"/>
-    <mergeCell ref="B46:B57"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="C34:C43"/>
+    <mergeCell ref="A58:A68"/>
+    <mergeCell ref="B58:B68"/>
+    <mergeCell ref="C58:C62"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A70:A79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A45:A56"/>
+    <mergeCell ref="B45:B56"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C51:C53"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B6:B15"/>
     <mergeCell ref="A6:A15"/>
@@ -3270,25 +3244,35 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A59:A69"/>
-    <mergeCell ref="B59:B69"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="B71:B80"/>
-    <mergeCell ref="A71:A80"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="C30:C33"/>
     <mergeCell ref="B17:B29"/>
     <mergeCell ref="A17:A29"/>
-    <mergeCell ref="B30:B44"/>
-    <mergeCell ref="A30:A44"/>
-    <mergeCell ref="C34:C44"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="E30:E43"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="F34:F43"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="F67:F68"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60DF65E-3669-4091-A1B6-3240D522E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B941E0B0-D78A-402E-B414-F00DD9F5FD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -1197,37 +1197,133 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1242,103 +1338,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1732,13 +1732,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="101" t="s">
         <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1755,9 +1755,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="116"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="118"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="101"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1783,13 +1783,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="116" t="s">
+      <c r="A6" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="96" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1806,9 +1806,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="116"/>
-      <c r="B7" s="117"/>
-      <c r="C7" s="92"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="106"/>
       <c r="D7" s="61" t="s">
         <v>101</v>
       </c>
@@ -1823,9 +1823,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="116"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="93"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="68" t="s">
         <v>102</v>
       </c>
@@ -1840,15 +1840,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="116"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="91" t="s">
+      <c r="A9" s="99"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="96" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="84" t="s">
+      <c r="E9" s="118" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1865,13 +1865,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="116"/>
-      <c r="B10" s="117"/>
-      <c r="C10" s="92"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="106"/>
       <c r="D10" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="85"/>
+      <c r="E10" s="86"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1880,9 +1880,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="116"/>
-      <c r="B11" s="117"/>
-      <c r="C11" s="93"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1897,18 +1897,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="116"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="120" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="103" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="113" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="96" t="s">
+      <c r="F12" s="128" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1916,40 +1916,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="116"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="121"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="104"/>
       <c r="D13" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="99"/>
-      <c r="F13" s="97"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="129"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="116"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="121"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="104"/>
       <c r="D14" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="99"/>
-      <c r="F14" s="97"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="129"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="116"/>
-      <c r="B15" s="117"/>
-      <c r="C15" s="122"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="98"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="130"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1966,13 +1966,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="96" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1989,9 +1989,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="104"/>
-      <c r="B18" s="104"/>
-      <c r="C18" s="94"/>
+      <c r="A18" s="85"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="61" t="s">
         <v>103</v>
       </c>
@@ -2006,9 +2006,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="104"/>
-      <c r="B19" s="104"/>
-      <c r="C19" s="95"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="127"/>
       <c r="D19" s="68" t="s">
         <v>79</v>
       </c>
@@ -2023,15 +2023,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="104"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="91" t="s">
+      <c r="A20" s="85"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="96" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="84" t="s">
+      <c r="E20" s="118" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2048,13 +2048,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="104"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="92"/>
+      <c r="A21" s="85"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="106"/>
       <c r="D21" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="85"/>
+      <c r="E21" s="86"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2063,9 +2063,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="104"/>
-      <c r="B22" s="104"/>
-      <c r="C22" s="92"/>
+      <c r="A22" s="85"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="106"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2080,16 +2080,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="104"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="92"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="84" t="s">
+      <c r="E23" s="118" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="101" t="s">
+      <c r="F23" s="115" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2097,60 +2097,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="104"/>
-      <c r="B24" s="104"/>
-      <c r="C24" s="92"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="106"/>
       <c r="D24" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="104"/>
-      <c r="F24" s="102"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="116"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="104"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="92"/>
+      <c r="A25" s="85"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="106"/>
       <c r="D25" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="104"/>
-      <c r="F25" s="102"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="104"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="92"/>
+      <c r="A26" s="85"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="106"/>
       <c r="D26" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="104"/>
-      <c r="F26" s="102"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="93"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="97"/>
       <c r="D27" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="85"/>
-      <c r="F27" s="103"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="117"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="104"/>
-      <c r="B28" s="104"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="85"/>
       <c r="C28" s="82" t="s">
         <v>104</v>
       </c>
@@ -2168,8 +2168,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="85"/>
-      <c r="B29" s="85"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="86"/>
       <c r="C29" s="81" t="s">
         <v>104</v>
       </c>
@@ -2187,22 +2187,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="115" t="s">
+      <c r="A30" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="115" t="s">
+      <c r="B30" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="131" t="s">
+      <c r="C30" s="109" t="s">
         <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="105" t="s">
+      <c r="E30" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="109" t="s">
+      <c r="F30" s="125" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2210,55 +2210,55 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="104"/>
-      <c r="B31" s="104"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="85"/>
       <c r="C31" s="110"/>
       <c r="D31" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="105"/>
+      <c r="E31" s="121"/>
       <c r="F31" s="110"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="104"/>
-      <c r="B32" s="104"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="85"/>
       <c r="C32" s="110"/>
       <c r="D32" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="105"/>
+      <c r="E32" s="121"/>
       <c r="F32" s="110"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="104"/>
-      <c r="B33" s="104"/>
+      <c r="A33" s="85"/>
+      <c r="B33" s="85"/>
       <c r="C33" s="111"/>
       <c r="D33" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="105"/>
+      <c r="E33" s="121"/>
       <c r="F33" s="111"/>
       <c r="G33" s="31"/>
       <c r="H33" s="1"/>
       <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="104"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="123" t="s">
+      <c r="A34" s="85"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="87" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="88" t="s">
+      <c r="E34" s="121"/>
+      <c r="F34" s="112" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2266,118 +2266,118 @@
       <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="104"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="129"/>
-      <c r="D35" s="60" t="s">
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="105"/>
-      <c r="F35" s="112"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="126"/>
       <c r="G35" s="31"/>
       <c r="H35" s="1"/>
       <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="104"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="60" t="s">
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="85"/>
+      <c r="D36" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="113"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="91"/>
       <c r="G36" s="31"/>
       <c r="H36" s="1"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="104"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="104"/>
+      <c r="A37" s="85"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="105"/>
-      <c r="F37" s="113"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="91"/>
       <c r="G37" s="31"/>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="104"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="60" t="s">
+      <c r="A38" s="85"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="105"/>
-      <c r="F38" s="113"/>
+      <c r="E38" s="121"/>
+      <c r="F38" s="91"/>
       <c r="G38" s="31"/>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="104"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="104"/>
-      <c r="D39" s="60" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E39" s="105"/>
-      <c r="F39" s="113"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="91"/>
       <c r="G39" s="31"/>
       <c r="H39" s="1"/>
       <c r="I39" s="39"/>
     </row>
     <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="104"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="104"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
       <c r="D40" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="105"/>
-      <c r="F40" s="113"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="91"/>
       <c r="G40" s="31"/>
       <c r="H40" s="1"/>
       <c r="I40" s="39"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="104"/>
-      <c r="B41" s="104"/>
-      <c r="C41" s="104"/>
+      <c r="A41" s="85"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="85"/>
       <c r="D41" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="105"/>
-      <c r="F41" s="113"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="91"/>
       <c r="G41" s="31"/>
       <c r="H41" s="1"/>
       <c r="I41" s="39"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="104"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="104"/>
+      <c r="A42" s="85"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="85"/>
       <c r="D42" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="105"/>
-      <c r="F42" s="113"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="91"/>
       <c r="G42" s="31"/>
       <c r="H42" s="1"/>
       <c r="I42" s="39"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
+      <c r="A43" s="86"/>
+      <c r="B43" s="86"/>
+      <c r="C43" s="86"/>
       <c r="D43" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E43" s="105"/>
-      <c r="F43" s="114"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="95"/>
       <c r="G43" s="31"/>
       <c r="H43" s="1"/>
       <c r="I43" s="39"/>
@@ -2394,13 +2394,13 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="115" t="s">
+      <c r="A45" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="115" t="s">
+      <c r="B45" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="123" t="s">
+      <c r="C45" s="87" t="s">
         <v>78</v>
       </c>
       <c r="D45" s="66" t="s">
@@ -2417,16 +2417,16 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="113"/>
-      <c r="B46" s="113"/>
-      <c r="C46" s="124"/>
+      <c r="A46" s="91"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="92"/>
       <c r="D46" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="E46" s="84" t="s">
+      <c r="E46" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="86" t="s">
+      <c r="F46" s="119" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="31"/>
@@ -2434,22 +2434,22 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="113"/>
-      <c r="B47" s="113"/>
-      <c r="C47" s="124"/>
+      <c r="A47" s="91"/>
+      <c r="B47" s="91"/>
+      <c r="C47" s="92"/>
       <c r="D47" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="85"/>
-      <c r="F47" s="108"/>
+      <c r="E47" s="86"/>
+      <c r="F47" s="124"/>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="113"/>
-      <c r="B48" s="113"/>
-      <c r="C48" s="89"/>
+      <c r="A48" s="91"/>
+      <c r="B48" s="91"/>
+      <c r="C48" s="93"/>
       <c r="D48" s="68" t="s">
         <v>80</v>
       </c>
@@ -2464,9 +2464,9 @@
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="113"/>
-      <c r="B49" s="113"/>
-      <c r="C49" s="125" t="s">
+      <c r="A49" s="91"/>
+      <c r="B49" s="91"/>
+      <c r="C49" s="107" t="s">
         <v>112</v>
       </c>
       <c r="D49" s="66" t="s">
@@ -2483,9 +2483,9 @@
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="113"/>
-      <c r="B50" s="113"/>
-      <c r="C50" s="126"/>
+      <c r="A50" s="91"/>
+      <c r="B50" s="91"/>
+      <c r="C50" s="108"/>
       <c r="D50" s="66" t="s">
         <v>113</v>
       </c>
@@ -2500,15 +2500,15 @@
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="113"/>
-      <c r="B51" s="113"/>
-      <c r="C51" s="91" t="s">
+      <c r="A51" s="91"/>
+      <c r="B51" s="91"/>
+      <c r="C51" s="96" t="s">
         <v>97</v>
       </c>
       <c r="D51" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="E51" s="106" t="s">
+      <c r="E51" s="122" t="s">
         <v>105</v>
       </c>
       <c r="F51" s="77" t="s">
@@ -2521,13 +2521,13 @@
       <c r="I51" s="32"/>
     </row>
     <row r="52" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="113"/>
-      <c r="B52" s="113"/>
-      <c r="C52" s="94"/>
+      <c r="A52" s="91"/>
+      <c r="B52" s="91"/>
+      <c r="C52" s="98"/>
       <c r="D52" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="107"/>
+      <c r="E52" s="123"/>
       <c r="F52" s="71" t="s">
         <v>9</v>
       </c>
@@ -2536,13 +2536,13 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="113"/>
-      <c r="B53" s="113"/>
-      <c r="C53" s="94"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="91"/>
+      <c r="C53" s="98"/>
       <c r="D53" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="85"/>
+      <c r="E53" s="86"/>
       <c r="F53" s="71" t="s">
         <v>9</v>
       </c>
@@ -2551,9 +2551,9 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="113"/>
-      <c r="B54" s="113"/>
-      <c r="C54" s="91" t="s">
+      <c r="A54" s="91"/>
+      <c r="B54" s="91"/>
+      <c r="C54" s="96" t="s">
         <v>115</v>
       </c>
       <c r="D54" s="68" t="s">
@@ -2572,9 +2572,9 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="113"/>
-      <c r="B55" s="113"/>
-      <c r="C55" s="93"/>
+      <c r="A55" s="91"/>
+      <c r="B55" s="91"/>
+      <c r="C55" s="97"/>
       <c r="D55" s="66" t="s">
         <v>117</v>
       </c>
@@ -2591,8 +2591,8 @@
       <c r="I55" s="34"/>
     </row>
     <row r="56" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="114"/>
-      <c r="B56" s="114"/>
+      <c r="A56" s="95"/>
+      <c r="B56" s="95"/>
       <c r="C56" s="78" t="s">
         <v>81</v>
       </c>
@@ -2627,13 +2627,13 @@
       <c r="I57" s="28"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="127" t="s">
+      <c r="A58" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="115" t="s">
+      <c r="B58" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="123" t="s">
+      <c r="C58" s="87" t="s">
         <v>86</v>
       </c>
       <c r="D58" s="66" t="s">
@@ -2652,16 +2652,16 @@
       <c r="I58" s="32"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="128"/>
-      <c r="B59" s="113"/>
-      <c r="C59" s="129"/>
+      <c r="A59" s="90"/>
+      <c r="B59" s="91"/>
+      <c r="C59" s="88"/>
       <c r="D59" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="E59" s="84" t="s">
+      <c r="E59" s="118" t="s">
         <v>87</v>
       </c>
-      <c r="F59" s="86" t="s">
+      <c r="F59" s="119" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="31"/>
@@ -2669,22 +2669,22 @@
       <c r="I59" s="32"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="128"/>
-      <c r="B60" s="113"/>
-      <c r="C60" s="129"/>
+      <c r="A60" s="90"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="88"/>
       <c r="D60" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="E60" s="85"/>
-      <c r="F60" s="87"/>
+      <c r="E60" s="86"/>
+      <c r="F60" s="120"/>
       <c r="G60" s="31"/>
       <c r="H60" s="3"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="128"/>
-      <c r="B61" s="104"/>
-      <c r="C61" s="124"/>
+      <c r="A61" s="90"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="92"/>
       <c r="D61" s="68" t="s">
         <v>54</v>
       </c>
@@ -2699,9 +2699,9 @@
       <c r="I61" s="34"/>
     </row>
     <row r="62" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="128"/>
-      <c r="B62" s="104"/>
-      <c r="C62" s="89"/>
+      <c r="A62" s="90"/>
+      <c r="B62" s="85"/>
+      <c r="C62" s="93"/>
       <c r="D62" s="60" t="s">
         <v>27</v>
       </c>
@@ -2722,47 +2722,47 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="128"/>
-      <c r="B63" s="104"/>
-      <c r="C63" s="123" t="s">
+      <c r="A63" s="90"/>
+      <c r="B63" s="85"/>
+      <c r="C63" s="87" t="s">
         <v>89</v>
       </c>
       <c r="D63" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="E63" s="84" t="s">
+      <c r="E63" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="86" t="s">
+      <c r="F63" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="88" t="s">
+      <c r="G63" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="88" t="s">
+      <c r="H63" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="88" t="s">
+      <c r="I63" s="112" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="128"/>
-      <c r="B64" s="104"/>
-      <c r="C64" s="130"/>
+      <c r="A64" s="90"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="94"/>
       <c r="D64" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E64" s="85"/>
-      <c r="F64" s="87"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="89"/>
-      <c r="I64" s="89"/>
+      <c r="E64" s="86"/>
+      <c r="F64" s="120"/>
+      <c r="G64" s="93"/>
+      <c r="H64" s="93"/>
+      <c r="I64" s="93"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="128"/>
-      <c r="B65" s="104"/>
-      <c r="C65" s="123" t="s">
+      <c r="A65" s="90"/>
+      <c r="B65" s="85"/>
+      <c r="C65" s="87" t="s">
         <v>62</v>
       </c>
       <c r="D65" s="59" t="s">
@@ -2779,9 +2779,9 @@
       <c r="I65" s="28"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="128"/>
-      <c r="B66" s="104"/>
-      <c r="C66" s="89"/>
+      <c r="A66" s="90"/>
+      <c r="B66" s="85"/>
+      <c r="C66" s="93"/>
       <c r="D66" s="73" t="s">
         <v>125</v>
       </c>
@@ -2796,9 +2796,9 @@
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="128"/>
-      <c r="B67" s="104"/>
-      <c r="C67" s="123" t="s">
+      <c r="A67" s="90"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="87" t="s">
         <v>63</v>
       </c>
       <c r="D67" s="59" t="s">
@@ -2807,7 +2807,7 @@
       <c r="E67" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F67" s="88" t="s">
+      <c r="F67" s="112" t="s">
         <v>7</v>
       </c>
       <c r="G67" s="45"/>
@@ -2815,16 +2815,16 @@
       <c r="I67" s="32"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="128"/>
-      <c r="B68" s="104"/>
-      <c r="C68" s="130"/>
+      <c r="A68" s="90"/>
+      <c r="B68" s="85"/>
+      <c r="C68" s="94"/>
       <c r="D68" s="59" t="s">
         <v>128</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F68" s="90"/>
+      <c r="F68" s="131"/>
       <c r="G68" s="45"/>
       <c r="H68" s="3"/>
       <c r="I68" s="32"/>
@@ -2841,13 +2841,13 @@
       <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="115" t="s">
+      <c r="A70" s="84" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="115" t="s">
+      <c r="B70" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="123" t="s">
+      <c r="C70" s="87" t="s">
         <v>99</v>
       </c>
       <c r="D70" s="55" t="s">
@@ -2864,13 +2864,13 @@
       <c r="I70" s="39"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="113"/>
-      <c r="B71" s="113"/>
-      <c r="C71" s="129"/>
+      <c r="A71" s="91"/>
+      <c r="B71" s="91"/>
+      <c r="C71" s="88"/>
       <c r="D71" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="E71" s="84" t="s">
+      <c r="E71" s="118" t="s">
         <v>65</v>
       </c>
       <c r="F71" s="75" t="s">
@@ -2881,13 +2881,13 @@
       <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="113"/>
-      <c r="B72" s="113"/>
-      <c r="C72" s="129"/>
+      <c r="A72" s="91"/>
+      <c r="B72" s="91"/>
+      <c r="C72" s="88"/>
       <c r="D72" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="E72" s="85"/>
+      <c r="E72" s="86"/>
       <c r="F72" s="54" t="s">
         <v>7</v>
       </c>
@@ -2896,9 +2896,9 @@
       <c r="I72" s="39"/>
     </row>
     <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="104"/>
-      <c r="B73" s="104"/>
-      <c r="C73" s="123" t="s">
+      <c r="A73" s="85"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="87" t="s">
         <v>100</v>
       </c>
       <c r="D73" s="60" t="s">
@@ -2915,9 +2915,9 @@
       <c r="I73" s="48"/>
     </row>
     <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="104"/>
-      <c r="B74" s="104"/>
-      <c r="C74" s="89"/>
+      <c r="A74" s="85"/>
+      <c r="B74" s="85"/>
+      <c r="C74" s="93"/>
       <c r="D74" s="60" t="s">
         <v>74</v>
       </c>
@@ -2932,8 +2932,8 @@
       <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="104"/>
-      <c r="B75" s="104"/>
+      <c r="A75" s="85"/>
+      <c r="B75" s="85"/>
       <c r="C75" s="65" t="s">
         <v>134</v>
       </c>
@@ -2951,9 +2951,9 @@
       <c r="I75" s="49"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="104"/>
-      <c r="B76" s="104"/>
-      <c r="C76" s="123" t="s">
+      <c r="A76" s="85"/>
+      <c r="B76" s="85"/>
+      <c r="C76" s="87" t="s">
         <v>66</v>
       </c>
       <c r="D76" s="66" t="s">
@@ -2970,9 +2970,9 @@
       <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="104"/>
-      <c r="B77" s="104"/>
-      <c r="C77" s="124"/>
+      <c r="A77" s="85"/>
+      <c r="B77" s="85"/>
+      <c r="C77" s="92"/>
       <c r="D77" s="60" t="s">
         <v>67</v>
       </c>
@@ -2987,9 +2987,9 @@
       <c r="I77" s="39"/>
     </row>
     <row r="78" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="104"/>
-      <c r="B78" s="104"/>
-      <c r="C78" s="124"/>
+      <c r="A78" s="85"/>
+      <c r="B78" s="85"/>
+      <c r="C78" s="92"/>
       <c r="D78" s="68" t="s">
         <v>135</v>
       </c>
@@ -3004,9 +3004,9 @@
       <c r="I78" s="39"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="85"/>
-      <c r="B79" s="85"/>
-      <c r="C79" s="89"/>
+      <c r="A79" s="86"/>
+      <c r="B79" s="86"/>
+      <c r="C79" s="93"/>
       <c r="D79" s="66" t="s">
         <v>68</v>
       </c>
@@ -3219,35 +3219,16 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="A30:A43"/>
-    <mergeCell ref="C34:C43"/>
-    <mergeCell ref="A58:A68"/>
-    <mergeCell ref="B58:B68"/>
-    <mergeCell ref="C58:C62"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A70:A79"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="A45:A56"/>
-    <mergeCell ref="B45:B56"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
     <mergeCell ref="A17:A29"/>
     <mergeCell ref="I63:I64"/>
     <mergeCell ref="E12:E15"/>
@@ -3263,16 +3244,35 @@
     <mergeCell ref="H63:H64"/>
     <mergeCell ref="F30:F33"/>
     <mergeCell ref="F34:F43"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A70:A79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="C34:C43"/>
+    <mergeCell ref="A58:A68"/>
+    <mergeCell ref="B58:B68"/>
+    <mergeCell ref="C58:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="A45:A56"/>
+    <mergeCell ref="B45:B56"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C51:C53"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B941E0B0-D78A-402E-B414-F00DD9F5FD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547F750D-F582-4B23-BC18-676B90D08B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="164">
   <si>
     <t>User Story</t>
   </si>
@@ -602,7 +602,7 @@
     <t>Check that above steps are resulted in the disappearence of booked appointments button from Clinic Home</t>
   </si>
   <si>
-    <t xml:space="preserve">Check that Leaving app by opening a new page in the browser and returning to app later Opens logged-out Home and Sign in button is displayed </t>
+    <t>Check that Leaving app by opening a new page in the browser and returning to app later Opens logged-out Home</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1197,18 +1197,141 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1218,127 +1341,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1732,13 +1738,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="123" t="s">
         <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1755,9 +1761,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="101"/>
+      <c r="A4" s="121"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="123"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1783,13 +1789,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="92" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1806,9 +1812,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="106"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="61" t="s">
         <v>101</v>
       </c>
@@ -1823,9 +1829,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="97"/>
+      <c r="A8" s="121"/>
+      <c r="B8" s="122"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="68" t="s">
         <v>102</v>
       </c>
@@ -1840,15 +1846,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="96" t="s">
+      <c r="A9" s="121"/>
+      <c r="B9" s="122"/>
+      <c r="C9" s="92" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="118" t="s">
+      <c r="E9" s="85" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1865,9 +1871,9 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="106"/>
+      <c r="A10" s="121"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="68" t="s">
         <v>60</v>
       </c>
@@ -1880,9 +1886,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100"/>
-      <c r="C11" s="97"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="94"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1897,18 +1903,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="103" t="s">
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="125" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="113" t="s">
+      <c r="E12" s="102" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="128" t="s">
+      <c r="F12" s="97" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1916,40 +1922,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="104"/>
+      <c r="A13" s="121"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="126"/>
       <c r="D13" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="113"/>
-      <c r="F13" s="129"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="98"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="104"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="113"/>
-      <c r="F14" s="129"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="98"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="100"/>
-      <c r="C15" s="105"/>
+      <c r="A15" s="121"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="127"/>
       <c r="D15" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="114"/>
-      <c r="F15" s="130"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="99"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1966,13 +1972,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="100" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="96" t="s">
+      <c r="C17" s="92" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1989,9 +1995,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="85"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="98"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="95"/>
       <c r="D18" s="61" t="s">
         <v>103</v>
       </c>
@@ -2006,9 +2012,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="127"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="96"/>
       <c r="D19" s="68" t="s">
         <v>79</v>
       </c>
@@ -2023,15 +2029,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="85"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="96" t="s">
+      <c r="A20" s="101"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="92" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="118" t="s">
+      <c r="E20" s="85" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2048,9 +2054,9 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="85"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="106"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="68" t="s">
         <v>75</v>
       </c>
@@ -2063,9 +2069,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="106"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2080,16 +2086,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="85"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="106"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="118" t="s">
+      <c r="E23" s="85" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="115" t="s">
+      <c r="F23" s="104" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2097,60 +2103,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="85"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="106"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="93"/>
       <c r="D24" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="116"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="105"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
-      <c r="B25" s="85"/>
-      <c r="C25" s="106"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="93"/>
       <c r="D25" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="116"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="85"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="106"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="85"/>
-      <c r="F26" s="116"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="85"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="97"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="94"/>
       <c r="D27" s="61" t="s">
         <v>145</v>
       </c>
       <c r="E27" s="86"/>
-      <c r="F27" s="117"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
-      <c r="B28" s="85"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="82" t="s">
         <v>104</v>
       </c>
@@ -2187,22 +2193,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="100" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="109" t="s">
+      <c r="C30" s="120" t="s">
         <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="121" t="s">
+      <c r="E30" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="125" t="s">
+      <c r="F30" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2210,55 +2216,57 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="110"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="112"/>
       <c r="D31" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="E31" s="121"/>
-      <c r="F31" s="110"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="101"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="85"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="110"/>
+      <c r="A32" s="101"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="112"/>
       <c r="D32" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="121"/>
-      <c r="F32" s="110"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="86"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="85"/>
-      <c r="B33" s="85"/>
-      <c r="C33" s="111"/>
+      <c r="A33" s="101"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="113"/>
       <c r="D33" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="121"/>
-      <c r="F33" s="111"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="84" t="s">
+        <v>9</v>
+      </c>
       <c r="G33" s="31"/>
       <c r="H33" s="1"/>
       <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="87" t="s">
+      <c r="A34" s="101"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="120" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="E34" s="121"/>
-      <c r="F34" s="112" t="s">
+      <c r="E34" s="107"/>
+      <c r="F34" s="111" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2266,105 +2274,105 @@
       <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="88"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="101"/>
+      <c r="C35" s="132"/>
       <c r="D35" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="121"/>
-      <c r="F35" s="126"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="101"/>
       <c r="G35" s="31"/>
       <c r="H35" s="1"/>
       <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="101"/>
+      <c r="C36" s="112"/>
       <c r="D36" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E36" s="121"/>
-      <c r="F36" s="91"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="101"/>
       <c r="G36" s="31"/>
       <c r="H36" s="1"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="112"/>
       <c r="D37" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="121"/>
-      <c r="F37" s="91"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="101"/>
       <c r="G37" s="31"/>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="85"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="85"/>
+      <c r="A38" s="101"/>
+      <c r="B38" s="101"/>
+      <c r="C38" s="112"/>
       <c r="D38" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="121"/>
-      <c r="F38" s="91"/>
+      <c r="E38" s="107"/>
+      <c r="F38" s="101"/>
       <c r="G38" s="31"/>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
+      <c r="A39" s="101"/>
+      <c r="B39" s="101"/>
+      <c r="C39" s="112"/>
       <c r="D39" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E39" s="121"/>
-      <c r="F39" s="91"/>
+      <c r="E39" s="107"/>
+      <c r="F39" s="101"/>
       <c r="G39" s="31"/>
       <c r="H39" s="1"/>
       <c r="I39" s="39"/>
     </row>
     <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="85"/>
-      <c r="D40" s="61" t="s">
+      <c r="A40" s="101"/>
+      <c r="B40" s="101"/>
+      <c r="C40" s="112"/>
+      <c r="D40" s="68" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="121"/>
-      <c r="F40" s="91"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="101"/>
       <c r="G40" s="31"/>
       <c r="H40" s="1"/>
       <c r="I40" s="39"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="85"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="60" t="s">
+      <c r="A41" s="101"/>
+      <c r="B41" s="101"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E41" s="121"/>
-      <c r="F41" s="91"/>
+      <c r="E41" s="107"/>
+      <c r="F41" s="101"/>
       <c r="G41" s="31"/>
       <c r="H41" s="1"/>
       <c r="I41" s="39"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="60" t="s">
+      <c r="A42" s="101"/>
+      <c r="B42" s="101"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="E42" s="121"/>
-      <c r="F42" s="91"/>
+      <c r="E42" s="107"/>
+      <c r="F42" s="101"/>
       <c r="G42" s="31"/>
       <c r="H42" s="1"/>
       <c r="I42" s="39"/>
@@ -2372,12 +2380,14 @@
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="86"/>
       <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
+      <c r="C43" s="113"/>
       <c r="D43" s="83" t="s">
         <v>157</v>
       </c>
-      <c r="E43" s="121"/>
-      <c r="F43" s="95"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="133" t="s">
+        <v>9</v>
+      </c>
       <c r="G43" s="31"/>
       <c r="H43" s="1"/>
       <c r="I43" s="39"/>
@@ -2394,13 +2404,13 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="84" t="s">
+      <c r="A45" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="84" t="s">
+      <c r="B45" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C45" s="87" t="s">
+      <c r="C45" s="116" t="s">
         <v>78</v>
       </c>
       <c r="D45" s="66" t="s">
@@ -2417,16 +2427,16 @@
       <c r="I45" s="32"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="91"/>
-      <c r="B46" s="91"/>
-      <c r="C46" s="92"/>
+      <c r="A46" s="114"/>
+      <c r="B46" s="114"/>
+      <c r="C46" s="117"/>
       <c r="D46" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="E46" s="118" t="s">
+      <c r="E46" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="F46" s="119" t="s">
+      <c r="F46" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="31"/>
@@ -2434,22 +2444,22 @@
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="91"/>
-      <c r="B47" s="91"/>
-      <c r="C47" s="92"/>
+      <c r="A47" s="114"/>
+      <c r="B47" s="114"/>
+      <c r="C47" s="117"/>
       <c r="D47" s="59" t="s">
         <v>111</v>
       </c>
       <c r="E47" s="86"/>
-      <c r="F47" s="124"/>
+      <c r="F47" s="110"/>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="91"/>
-      <c r="B48" s="91"/>
-      <c r="C48" s="93"/>
+      <c r="A48" s="114"/>
+      <c r="B48" s="114"/>
+      <c r="C48" s="90"/>
       <c r="D48" s="68" t="s">
         <v>80</v>
       </c>
@@ -2464,9 +2474,9 @@
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="91"/>
-      <c r="B49" s="91"/>
-      <c r="C49" s="107" t="s">
+      <c r="A49" s="114"/>
+      <c r="B49" s="114"/>
+      <c r="C49" s="118" t="s">
         <v>112</v>
       </c>
       <c r="D49" s="66" t="s">
@@ -2483,9 +2493,9 @@
       <c r="I49" s="32"/>
     </row>
     <row r="50" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="91"/>
-      <c r="B50" s="91"/>
-      <c r="C50" s="108"/>
+      <c r="A50" s="114"/>
+      <c r="B50" s="114"/>
+      <c r="C50" s="119"/>
       <c r="D50" s="66" t="s">
         <v>113</v>
       </c>
@@ -2500,15 +2510,15 @@
       <c r="I50" s="32"/>
     </row>
     <row r="51" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="91"/>
-      <c r="B51" s="91"/>
-      <c r="C51" s="96" t="s">
+      <c r="A51" s="114"/>
+      <c r="B51" s="114"/>
+      <c r="C51" s="92" t="s">
         <v>97</v>
       </c>
       <c r="D51" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="E51" s="122" t="s">
+      <c r="E51" s="108" t="s">
         <v>105</v>
       </c>
       <c r="F51" s="77" t="s">
@@ -2521,13 +2531,13 @@
       <c r="I51" s="32"/>
     </row>
     <row r="52" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="91"/>
-      <c r="B52" s="91"/>
-      <c r="C52" s="98"/>
+      <c r="A52" s="114"/>
+      <c r="B52" s="114"/>
+      <c r="C52" s="95"/>
       <c r="D52" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="123"/>
+      <c r="E52" s="109"/>
       <c r="F52" s="71" t="s">
         <v>9</v>
       </c>
@@ -2536,9 +2546,9 @@
       <c r="I52" s="32"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="91"/>
-      <c r="B53" s="91"/>
-      <c r="C53" s="98"/>
+      <c r="A53" s="114"/>
+      <c r="B53" s="114"/>
+      <c r="C53" s="95"/>
       <c r="D53" s="68" t="s">
         <v>108</v>
       </c>
@@ -2551,9 +2561,9 @@
       <c r="I53" s="32"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="91"/>
-      <c r="B54" s="91"/>
-      <c r="C54" s="96" t="s">
+      <c r="A54" s="114"/>
+      <c r="B54" s="114"/>
+      <c r="C54" s="92" t="s">
         <v>115</v>
       </c>
       <c r="D54" s="68" t="s">
@@ -2572,9 +2582,9 @@
       <c r="I54" s="32"/>
     </row>
     <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="91"/>
-      <c r="B55" s="91"/>
-      <c r="C55" s="97"/>
+      <c r="A55" s="114"/>
+      <c r="B55" s="114"/>
+      <c r="C55" s="94"/>
       <c r="D55" s="66" t="s">
         <v>117</v>
       </c>
@@ -2591,8 +2601,8 @@
       <c r="I55" s="34"/>
     </row>
     <row r="56" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="95"/>
-      <c r="B56" s="95"/>
+      <c r="A56" s="115"/>
+      <c r="B56" s="115"/>
       <c r="C56" s="78" t="s">
         <v>81</v>
       </c>
@@ -2627,13 +2637,13 @@
       <c r="I57" s="28"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="89" t="s">
+      <c r="A58" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="116" t="s">
         <v>86</v>
       </c>
       <c r="D58" s="66" t="s">
@@ -2652,16 +2662,16 @@
       <c r="I58" s="32"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="90"/>
-      <c r="B59" s="91"/>
-      <c r="C59" s="88"/>
+      <c r="A59" s="131"/>
+      <c r="B59" s="114"/>
+      <c r="C59" s="129"/>
       <c r="D59" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="E59" s="118" t="s">
+      <c r="E59" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="F59" s="119" t="s">
+      <c r="F59" s="87" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="31"/>
@@ -2669,22 +2679,22 @@
       <c r="I59" s="32"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="90"/>
-      <c r="B60" s="91"/>
-      <c r="C60" s="88"/>
+      <c r="A60" s="131"/>
+      <c r="B60" s="114"/>
+      <c r="C60" s="129"/>
       <c r="D60" s="60" t="s">
         <v>122</v>
       </c>
       <c r="E60" s="86"/>
-      <c r="F60" s="120"/>
+      <c r="F60" s="88"/>
       <c r="G60" s="31"/>
       <c r="H60" s="3"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="90"/>
-      <c r="B61" s="85"/>
-      <c r="C61" s="92"/>
+      <c r="A61" s="131"/>
+      <c r="B61" s="101"/>
+      <c r="C61" s="117"/>
       <c r="D61" s="68" t="s">
         <v>54</v>
       </c>
@@ -2699,9 +2709,9 @@
       <c r="I61" s="34"/>
     </row>
     <row r="62" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="90"/>
-      <c r="B62" s="85"/>
-      <c r="C62" s="93"/>
+      <c r="A62" s="131"/>
+      <c r="B62" s="101"/>
+      <c r="C62" s="90"/>
       <c r="D62" s="60" t="s">
         <v>27</v>
       </c>
@@ -2722,47 +2732,47 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="90"/>
-      <c r="B63" s="85"/>
-      <c r="C63" s="87" t="s">
+      <c r="A63" s="131"/>
+      <c r="B63" s="101"/>
+      <c r="C63" s="116" t="s">
         <v>89</v>
       </c>
       <c r="D63" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="E63" s="118" t="s">
+      <c r="E63" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="119" t="s">
+      <c r="F63" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="112" t="s">
+      <c r="G63" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="112" t="s">
+      <c r="H63" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="112" t="s">
+      <c r="I63" s="89" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="90"/>
-      <c r="B64" s="85"/>
-      <c r="C64" s="94"/>
+      <c r="A64" s="131"/>
+      <c r="B64" s="101"/>
+      <c r="C64" s="128"/>
       <c r="D64" s="59" t="s">
         <v>124</v>
       </c>
       <c r="E64" s="86"/>
-      <c r="F64" s="120"/>
-      <c r="G64" s="93"/>
-      <c r="H64" s="93"/>
-      <c r="I64" s="93"/>
+      <c r="F64" s="88"/>
+      <c r="G64" s="90"/>
+      <c r="H64" s="90"/>
+      <c r="I64" s="90"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="90"/>
-      <c r="B65" s="85"/>
-      <c r="C65" s="87" t="s">
+      <c r="A65" s="131"/>
+      <c r="B65" s="101"/>
+      <c r="C65" s="116" t="s">
         <v>62</v>
       </c>
       <c r="D65" s="59" t="s">
@@ -2779,9 +2789,9 @@
       <c r="I65" s="28"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="90"/>
-      <c r="B66" s="85"/>
-      <c r="C66" s="93"/>
+      <c r="A66" s="131"/>
+      <c r="B66" s="101"/>
+      <c r="C66" s="90"/>
       <c r="D66" s="73" t="s">
         <v>125</v>
       </c>
@@ -2796,9 +2806,9 @@
       <c r="I66" s="32"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="90"/>
-      <c r="B67" s="85"/>
-      <c r="C67" s="87" t="s">
+      <c r="A67" s="131"/>
+      <c r="B67" s="101"/>
+      <c r="C67" s="116" t="s">
         <v>63</v>
       </c>
       <c r="D67" s="59" t="s">
@@ -2807,7 +2817,7 @@
       <c r="E67" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F67" s="112" t="s">
+      <c r="F67" s="89" t="s">
         <v>7</v>
       </c>
       <c r="G67" s="45"/>
@@ -2815,16 +2825,16 @@
       <c r="I67" s="32"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="90"/>
-      <c r="B68" s="85"/>
-      <c r="C68" s="94"/>
+      <c r="A68" s="131"/>
+      <c r="B68" s="101"/>
+      <c r="C68" s="128"/>
       <c r="D68" s="59" t="s">
         <v>128</v>
       </c>
       <c r="E68" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F68" s="131"/>
+      <c r="F68" s="91"/>
       <c r="G68" s="45"/>
       <c r="H68" s="3"/>
       <c r="I68" s="32"/>
@@ -2841,13 +2851,13 @@
       <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="84" t="s">
+      <c r="A70" s="100" t="s">
         <v>153</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="87" t="s">
+      <c r="C70" s="116" t="s">
         <v>99</v>
       </c>
       <c r="D70" s="55" t="s">
@@ -2864,13 +2874,13 @@
       <c r="I70" s="39"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
-      <c r="B71" s="91"/>
-      <c r="C71" s="88"/>
+      <c r="A71" s="114"/>
+      <c r="B71" s="114"/>
+      <c r="C71" s="129"/>
       <c r="D71" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="E71" s="118" t="s">
+      <c r="E71" s="85" t="s">
         <v>65</v>
       </c>
       <c r="F71" s="75" t="s">
@@ -2881,9 +2891,9 @@
       <c r="I71" s="39"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="91"/>
-      <c r="B72" s="91"/>
-      <c r="C72" s="88"/>
+      <c r="A72" s="114"/>
+      <c r="B72" s="114"/>
+      <c r="C72" s="129"/>
       <c r="D72" s="60" t="s">
         <v>129</v>
       </c>
@@ -2896,9 +2906,9 @@
       <c r="I72" s="39"/>
     </row>
     <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="85"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="87" t="s">
+      <c r="A73" s="101"/>
+      <c r="B73" s="101"/>
+      <c r="C73" s="116" t="s">
         <v>100</v>
       </c>
       <c r="D73" s="60" t="s">
@@ -2915,9 +2925,9 @@
       <c r="I73" s="48"/>
     </row>
     <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="85"/>
-      <c r="B74" s="85"/>
-      <c r="C74" s="93"/>
+      <c r="A74" s="101"/>
+      <c r="B74" s="101"/>
+      <c r="C74" s="90"/>
       <c r="D74" s="60" t="s">
         <v>74</v>
       </c>
@@ -2932,8 +2942,8 @@
       <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="85"/>
-      <c r="B75" s="85"/>
+      <c r="A75" s="101"/>
+      <c r="B75" s="101"/>
       <c r="C75" s="65" t="s">
         <v>134</v>
       </c>
@@ -2951,9 +2961,9 @@
       <c r="I75" s="49"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="85"/>
-      <c r="B76" s="85"/>
-      <c r="C76" s="87" t="s">
+      <c r="A76" s="101"/>
+      <c r="B76" s="101"/>
+      <c r="C76" s="116" t="s">
         <v>66</v>
       </c>
       <c r="D76" s="66" t="s">
@@ -2970,9 +2980,9 @@
       <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="85"/>
-      <c r="B77" s="85"/>
-      <c r="C77" s="92"/>
+      <c r="A77" s="101"/>
+      <c r="B77" s="101"/>
+      <c r="C77" s="117"/>
       <c r="D77" s="60" t="s">
         <v>67</v>
       </c>
@@ -2987,9 +2997,9 @@
       <c r="I77" s="39"/>
     </row>
     <row r="78" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="85"/>
-      <c r="B78" s="85"/>
-      <c r="C78" s="92"/>
+      <c r="A78" s="101"/>
+      <c r="B78" s="101"/>
+      <c r="C78" s="117"/>
       <c r="D78" s="68" t="s">
         <v>135</v>
       </c>
@@ -3006,7 +3016,7 @@
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="86"/>
       <c r="B79" s="86"/>
-      <c r="C79" s="93"/>
+      <c r="C79" s="90"/>
       <c r="D79" s="66" t="s">
         <v>68</v>
       </c>
@@ -3219,16 +3229,36 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="F67:F68"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="F34:F42"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="B70:B79"/>
+    <mergeCell ref="A70:A79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A58:A68"/>
+    <mergeCell ref="B58:B68"/>
+    <mergeCell ref="C58:C62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B6:B15"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="C34:C43"/>
+    <mergeCell ref="A45:A56"/>
+    <mergeCell ref="B45:B56"/>
+    <mergeCell ref="C54:C55"/>
     <mergeCell ref="A17:A29"/>
     <mergeCell ref="I63:I64"/>
     <mergeCell ref="E12:E15"/>
@@ -3242,37 +3272,17 @@
     <mergeCell ref="E46:E47"/>
     <mergeCell ref="F46:F47"/>
     <mergeCell ref="H63:H64"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="F34:F43"/>
     <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B6:B15"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A70:A79"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="A30:A43"/>
-    <mergeCell ref="C34:C43"/>
-    <mergeCell ref="A58:A68"/>
-    <mergeCell ref="B58:B68"/>
-    <mergeCell ref="C58:C62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="A45:A56"/>
-    <mergeCell ref="B45:B56"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:F64"/>
+    <mergeCell ref="G63:G64"/>
+    <mergeCell ref="F67:F68"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/User Stories.xlsx
+++ b/User Stories.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\job_hunt\Pet Projects\kdt-pom-Selenium-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547F750D-F582-4B23-BC18-676B90D08B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36AC4C5-BC7D-4781-A206-D210606BFA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="169">
   <si>
     <t>User Story</t>
   </si>
@@ -572,9 +572,6 @@
     <t>As a registered User, I want to Log in so that I can access my personal health details.</t>
   </si>
   <si>
-    <t>US007</t>
-  </si>
-  <si>
     <t>As a registered User, I want to Log out properly so that my personal health details are  safe from outsiders.</t>
   </si>
   <si>
@@ -603,6 +600,24 @@
   </si>
   <si>
     <t>Check that Leaving app by opening a new page in the browser and returning to app later Opens logged-out Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As a User, I want to Open the Clinic Home so that I can see basic site profile and available services</t>
+  </si>
+  <si>
+    <t>Verify if User can Open Clinic Home and the required elements of the page are visible</t>
+  </si>
+  <si>
+    <t>Enter URL into browser search bar Opens Clinic Home</t>
+  </si>
+  <si>
+    <t>Check Clinic Home elements exist</t>
+  </si>
+  <si>
+    <t>US007.</t>
+  </si>
+  <si>
+    <t>US008.</t>
   </si>
 </sst>
 </file>
@@ -946,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1200,39 +1215,138 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1245,106 +1359,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1681,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="2" customWidth="1"/>
@@ -1738,13 +1759,13 @@
       <c r="I2" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="123" t="s">
+      <c r="C3" s="107" t="s">
         <v>94</v>
       </c>
       <c r="D3" s="61" t="s">
@@ -1761,9 +1782,9 @@
       <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="121"/>
-      <c r="B4" s="124"/>
-      <c r="C4" s="123"/>
+      <c r="A4" s="105"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="107"/>
       <c r="D4" s="68" t="s">
         <v>21</v>
       </c>
@@ -1789,13 +1810,13 @@
       <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="86" t="s">
         <v>77</v>
       </c>
       <c r="D6" s="68" t="s">
@@ -1812,9 +1833,9 @@
       <c r="I6" s="32"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="121"/>
-      <c r="B7" s="122"/>
-      <c r="C7" s="93"/>
+      <c r="A7" s="105"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="128"/>
       <c r="D7" s="61" t="s">
         <v>101</v>
       </c>
@@ -1829,9 +1850,9 @@
       <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="121"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="94"/>
+      <c r="A8" s="105"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="114"/>
       <c r="D8" s="68" t="s">
         <v>102</v>
       </c>
@@ -1846,15 +1867,15 @@
       <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="121"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="92" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="106"/>
+      <c r="C9" s="86" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="85" t="s">
+      <c r="E9" s="121" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="64" t="s">
@@ -1871,13 +1892,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="121"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="93"/>
+      <c r="A10" s="105"/>
+      <c r="B10" s="106"/>
+      <c r="C10" s="128"/>
       <c r="D10" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="86"/>
+      <c r="E10" s="90"/>
       <c r="F10" s="70" t="s">
         <v>9</v>
       </c>
@@ -1886,9 +1907,9 @@
       <c r="I10" s="51"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="121"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="94"/>
+      <c r="A11" s="105"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="114"/>
       <c r="D11" s="66" t="s">
         <v>36</v>
       </c>
@@ -1903,18 +1924,18 @@
       <c r="I11" s="39"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="121"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="125" t="s">
+      <c r="A12" s="105"/>
+      <c r="B12" s="106"/>
+      <c r="C12" s="109" t="s">
         <v>95</v>
       </c>
       <c r="D12" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="116" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="97" t="s">
+      <c r="F12" s="130" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="31"/>
@@ -1922,40 +1943,40 @@
       <c r="I12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="121"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="126"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="110"/>
       <c r="D13" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="102"/>
-      <c r="F13" s="98"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="131"/>
       <c r="G13" s="31"/>
       <c r="H13" s="1"/>
       <c r="I13" s="39"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="121"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="126"/>
+      <c r="A14" s="105"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="110"/>
       <c r="D14" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="E14" s="102"/>
-      <c r="F14" s="98"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="131"/>
       <c r="G14" s="31"/>
       <c r="H14" s="1"/>
       <c r="I14" s="39"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="127"/>
+      <c r="A15" s="105"/>
+      <c r="B15" s="106"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="103"/>
-      <c r="F15" s="99"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="132"/>
       <c r="G15" s="31"/>
       <c r="H15" s="1"/>
       <c r="I15" s="39"/>
@@ -1972,13 +1993,13 @@
       <c r="I16" s="39"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="100" t="s">
+      <c r="B17" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="86" t="s">
         <v>96</v>
       </c>
       <c r="D17" s="68" t="s">
@@ -1995,9 +2016,9 @@
       <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="101"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="95"/>
+      <c r="A18" s="89"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="61" t="s">
         <v>103</v>
       </c>
@@ -2012,9 +2033,9 @@
       <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="101"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="96"/>
+      <c r="A19" s="89"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="129"/>
       <c r="D19" s="68" t="s">
         <v>79</v>
       </c>
@@ -2029,15 +2050,15 @@
       <c r="I19" s="40"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="101"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="92" t="s">
+      <c r="A20" s="89"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="86" t="s">
         <v>141</v>
       </c>
       <c r="D20" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="85" t="s">
+      <c r="E20" s="121" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="64" t="s">
@@ -2054,13 +2075,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="101"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="93"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="128"/>
       <c r="D21" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="E21" s="86"/>
+      <c r="E21" s="90"/>
       <c r="F21" s="69" t="s">
         <v>9</v>
       </c>
@@ -2069,9 +2090,9 @@
       <c r="I21" s="28"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="101"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="93"/>
+      <c r="A22" s="89"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="128"/>
       <c r="D22" s="66" t="s">
         <v>36</v>
       </c>
@@ -2086,16 +2107,16 @@
       <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="101"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="93"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="128"/>
       <c r="D23" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="85" t="s">
+      <c r="E23" s="121" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="104" t="s">
+      <c r="F23" s="118" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="45"/>
@@ -2103,60 +2124,60 @@
       <c r="I23" s="32"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="101"/>
-      <c r="B24" s="101"/>
-      <c r="C24" s="93"/>
+      <c r="A24" s="89"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="128"/>
       <c r="D24" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="105"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="45"/>
       <c r="H24" s="3"/>
       <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="101"/>
-      <c r="B25" s="101"/>
-      <c r="C25" s="93"/>
+      <c r="A25" s="89"/>
+      <c r="B25" s="89"/>
+      <c r="C25" s="128"/>
       <c r="D25" s="61" t="s">
         <v>146</v>
       </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="105"/>
+      <c r="E25" s="89"/>
+      <c r="F25" s="119"/>
       <c r="G25" s="45"/>
       <c r="H25" s="3"/>
       <c r="I25" s="32"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="101"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="93"/>
+      <c r="A26" s="89"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="128"/>
       <c r="D26" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="101"/>
-      <c r="F26" s="105"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="119"/>
       <c r="G26" s="45"/>
       <c r="H26" s="3"/>
       <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="101"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="94"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="114"/>
       <c r="D27" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="86"/>
-      <c r="F27" s="106"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="120"/>
       <c r="G27" s="31"/>
       <c r="H27" s="1"/>
       <c r="I27" s="39"/>
     </row>
     <row r="28" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="101"/>
-      <c r="B28" s="101"/>
+      <c r="A28" s="89"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="82" t="s">
         <v>104</v>
       </c>
@@ -2174,8 +2195,8 @@
       <c r="I28" s="39"/>
     </row>
     <row r="29" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
-      <c r="B29" s="86"/>
+      <c r="A29" s="90"/>
+      <c r="B29" s="90"/>
       <c r="C29" s="81" t="s">
         <v>104</v>
       </c>
@@ -2193,22 +2214,22 @@
       <c r="I29" s="39"/>
     </row>
     <row r="30" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="100" t="s">
+      <c r="A30" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="100" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="120" t="s">
+      <c r="B30" s="91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="102" t="s">
         <v>151</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30" s="107" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="111" t="s">
+      <c r="F30" s="88" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="31"/>
@@ -2216,39 +2237,39 @@
       <c r="I30" s="39"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="101"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="112"/>
+      <c r="A31" s="89"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="103"/>
       <c r="D31" s="61" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="107"/>
-      <c r="F31" s="101"/>
+        <v>159</v>
+      </c>
+      <c r="E31" s="124"/>
+      <c r="F31" s="89"/>
       <c r="G31" s="31"/>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
     </row>
     <row r="32" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="101"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="112"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="103"/>
       <c r="D32" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E32" s="107"/>
-      <c r="F32" s="86"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="90"/>
       <c r="G32" s="31"/>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
     </row>
     <row r="33" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="101"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="113"/>
+      <c r="A33" s="89"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="104"/>
       <c r="D33" s="83" t="s">
-        <v>157</v>
-      </c>
-      <c r="E33" s="107"/>
+        <v>156</v>
+      </c>
+      <c r="E33" s="124"/>
       <c r="F33" s="84" t="s">
         <v>9</v>
       </c>
@@ -2257,16 +2278,16 @@
       <c r="I33" s="39"/>
     </row>
     <row r="34" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="101"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="120" t="s">
-        <v>155</v>
+      <c r="A34" s="89"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="102" t="s">
+        <v>154</v>
       </c>
       <c r="D34" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="E34" s="107"/>
-      <c r="F34" s="111" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="124"/>
+      <c r="F34" s="88" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="31"/>
@@ -2274,118 +2295,118 @@
       <c r="I34" s="39"/>
     </row>
     <row r="35" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="101"/>
-      <c r="B35" s="101"/>
-      <c r="C35" s="132"/>
+      <c r="A35" s="89"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="E35" s="107"/>
-      <c r="F35" s="101"/>
+        <v>160</v>
+      </c>
+      <c r="E35" s="124"/>
+      <c r="F35" s="89"/>
       <c r="G35" s="31"/>
       <c r="H35" s="1"/>
       <c r="I35" s="39"/>
     </row>
     <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="101"/>
-      <c r="B36" s="101"/>
-      <c r="C36" s="112"/>
+      <c r="A36" s="89"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="103"/>
       <c r="D36" s="61" t="s">
-        <v>162</v>
-      </c>
-      <c r="E36" s="107"/>
-      <c r="F36" s="101"/>
+        <v>161</v>
+      </c>
+      <c r="E36" s="124"/>
+      <c r="F36" s="89"/>
       <c r="G36" s="31"/>
       <c r="H36" s="1"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="101"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="112"/>
+      <c r="A37" s="89"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="103"/>
       <c r="D37" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="107"/>
-      <c r="F37" s="101"/>
+        <v>158</v>
+      </c>
+      <c r="E37" s="124"/>
+      <c r="F37" s="89"/>
       <c r="G37" s="31"/>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="101"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="112"/>
+      <c r="A38" s="89"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="103"/>
       <c r="D38" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" s="107"/>
-      <c r="F38" s="101"/>
+        <v>160</v>
+      </c>
+      <c r="E38" s="124"/>
+      <c r="F38" s="89"/>
       <c r="G38" s="31"/>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
     </row>
     <row r="39" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="101"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="112"/>
+      <c r="A39" s="89"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="103"/>
       <c r="D39" s="61" t="s">
-        <v>162</v>
-      </c>
-      <c r="E39" s="107"/>
-      <c r="F39" s="101"/>
+        <v>161</v>
+      </c>
+      <c r="E39" s="124"/>
+      <c r="F39" s="89"/>
       <c r="G39" s="31"/>
       <c r="H39" s="1"/>
       <c r="I39" s="39"/>
     </row>
     <row r="40" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="101"/>
-      <c r="B40" s="101"/>
-      <c r="C40" s="112"/>
+      <c r="A40" s="89"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="103"/>
       <c r="D40" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="E40" s="107"/>
-      <c r="F40" s="101"/>
+        <v>162</v>
+      </c>
+      <c r="E40" s="124"/>
+      <c r="F40" s="89"/>
       <c r="G40" s="31"/>
       <c r="H40" s="1"/>
       <c r="I40" s="39"/>
     </row>
     <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="101"/>
-      <c r="B41" s="101"/>
-      <c r="C41" s="112"/>
+      <c r="A41" s="89"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="103"/>
       <c r="D41" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="E41" s="107"/>
-      <c r="F41" s="101"/>
+        <v>160</v>
+      </c>
+      <c r="E41" s="124"/>
+      <c r="F41" s="89"/>
       <c r="G41" s="31"/>
       <c r="H41" s="1"/>
       <c r="I41" s="39"/>
     </row>
     <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="101"/>
-      <c r="B42" s="101"/>
-      <c r="C42" s="112"/>
+      <c r="A42" s="89"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="103"/>
       <c r="D42" s="61" t="s">
-        <v>162</v>
-      </c>
-      <c r="E42" s="107"/>
-      <c r="F42" s="101"/>
+        <v>161</v>
+      </c>
+      <c r="E42" s="124"/>
+      <c r="F42" s="89"/>
       <c r="G42" s="31"/>
       <c r="H42" s="1"/>
       <c r="I42" s="39"/>
     </row>
     <row r="43" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="86"/>
-      <c r="B43" s="86"/>
-      <c r="C43" s="113"/>
+      <c r="A43" s="90"/>
+      <c r="B43" s="90"/>
+      <c r="C43" s="104"/>
       <c r="D43" s="83" t="s">
-        <v>157</v>
-      </c>
-      <c r="E43" s="107"/>
-      <c r="F43" s="133" t="s">
+        <v>156</v>
+      </c>
+      <c r="E43" s="124"/>
+      <c r="F43" s="85" t="s">
         <v>9</v>
       </c>
       <c r="G43" s="31"/>
@@ -2404,753 +2425,782 @@
       <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="100" t="s">
+      <c r="A45" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="100" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="116" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" s="66" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="31"/>
+      <c r="B45" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="135" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" s="134" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="1"/>
       <c r="H45" s="3"/>
       <c r="I45" s="32"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="114"/>
-      <c r="B46" s="114"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="E46" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="F46" s="87" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="31"/>
+    <row r="46" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="90"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="1"/>
       <c r="H46" s="3"/>
       <c r="I46" s="32"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="114"/>
-      <c r="B47" s="114"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="86"/>
-      <c r="F47" s="110"/>
+      <c r="A47" s="91" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="93" t="s">
+        <v>78</v>
+      </c>
+      <c r="D47" s="66" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="77" t="s">
+        <v>13</v>
+      </c>
       <c r="G47" s="31"/>
       <c r="H47" s="3"/>
       <c r="I47" s="32"/>
     </row>
-    <row r="48" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="114"/>
-      <c r="B48" s="114"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="68" t="s">
-        <v>80</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="70" t="s">
-        <v>9</v>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="92"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="F48" s="122" t="s">
+        <v>7</v>
       </c>
       <c r="G48" s="31"/>
       <c r="H48" s="3"/>
       <c r="I48" s="32"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="114"/>
-      <c r="B49" s="114"/>
-      <c r="C49" s="118" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F49" s="76" t="s">
-        <v>13</v>
-      </c>
+      <c r="A49" s="92"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="90"/>
+      <c r="F49" s="127"/>
       <c r="G49" s="31"/>
       <c r="H49" s="3"/>
       <c r="I49" s="32"/>
     </row>
-    <row r="50" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="114"/>
-      <c r="B50" s="114"/>
-      <c r="C50" s="119"/>
-      <c r="D50" s="66" t="s">
-        <v>113</v>
+    <row r="50" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="92"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="95"/>
+      <c r="D50" s="68" t="s">
+        <v>80</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="76" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F50" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="G50" s="31"/>
       <c r="H50" s="3"/>
       <c r="I50" s="32"/>
     </row>
-    <row r="51" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="114"/>
-      <c r="B51" s="114"/>
-      <c r="C51" s="92" t="s">
-        <v>97</v>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="92"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="100" t="s">
+        <v>112</v>
       </c>
       <c r="D51" s="66" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="108" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="45"/>
-      <c r="H51" s="80" t="s">
-        <v>114</v>
-      </c>
+      <c r="G51" s="31"/>
+      <c r="H51" s="3"/>
       <c r="I51" s="32"/>
     </row>
-    <row r="52" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="114"/>
-      <c r="B52" s="114"/>
-      <c r="C52" s="95"/>
-      <c r="D52" s="68" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="71" t="s">
-        <v>9</v>
+    <row r="52" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="92"/>
+      <c r="B52" s="92"/>
+      <c r="C52" s="101"/>
+      <c r="D52" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="76" t="s">
+        <v>13</v>
       </c>
       <c r="G52" s="31"/>
       <c r="H52" s="3"/>
       <c r="I52" s="32"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="114"/>
-      <c r="B53" s="114"/>
-      <c r="C53" s="95"/>
-      <c r="D53" s="68" t="s">
+    <row r="53" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="92"/>
+      <c r="B53" s="92"/>
+      <c r="C53" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="E53" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="F53" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="45"/>
+      <c r="H53" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="32"/>
+    </row>
+    <row r="54" spans="1:9" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="92"/>
+      <c r="B54" s="92"/>
+      <c r="C54" s="87"/>
+      <c r="D54" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="E54" s="126"/>
+      <c r="F54" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="G54" s="31"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="92"/>
+      <c r="B55" s="92"/>
+      <c r="C55" s="87"/>
+      <c r="D55" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="86"/>
-      <c r="F53" s="71" t="s">
+      <c r="E55" s="90"/>
+      <c r="F55" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="32"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="114"/>
-      <c r="B54" s="114"/>
-      <c r="C54" s="92" t="s">
+      <c r="G55" s="31"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="32"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="92"/>
+      <c r="B56" s="92"/>
+      <c r="C56" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="68" t="s">
+      <c r="D56" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="E56" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="F54" s="69" t="s">
+      <c r="F56" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="52" t="s">
+      <c r="G56" s="31"/>
+      <c r="H56" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="32"/>
-    </row>
-    <row r="55" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="114"/>
-      <c r="B55" s="114"/>
-      <c r="C55" s="94"/>
-      <c r="D55" s="66" t="s">
+      <c r="I56" s="32"/>
+    </row>
+    <row r="57" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="92"/>
+      <c r="B57" s="92"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E57" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="F55" s="67" t="s">
+      <c r="F57" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G55" s="33"/>
-      <c r="H55" s="53" t="s">
+      <c r="G57" s="33"/>
+      <c r="H57" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="I55" s="34"/>
-    </row>
-    <row r="56" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="115"/>
-      <c r="B56" s="115"/>
-      <c r="C56" s="78" t="s">
+      <c r="I57" s="34"/>
+    </row>
+    <row r="58" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="113"/>
+      <c r="B58" s="113"/>
+      <c r="C58" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="66" t="s">
+      <c r="D58" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E58" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="F56" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="I56" s="79" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="25"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="28"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="130" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="100" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="116" t="s">
-        <v>86</v>
-      </c>
-      <c r="D58" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="F58" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G58" s="31" t="s">
+      <c r="G58" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" s="79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="25"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="28"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="B60" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="93" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F60" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="32"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="131"/>
-      <c r="B59" s="114"/>
-      <c r="C59" s="129"/>
-      <c r="D59" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="E59" s="85" t="s">
-        <v>87</v>
-      </c>
-      <c r="F59" s="87" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="31"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="32"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="131"/>
-      <c r="B60" s="114"/>
-      <c r="C60" s="129"/>
-      <c r="D60" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="E60" s="86"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="31"/>
       <c r="H60" s="3"/>
       <c r="I60" s="32"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="131"/>
-      <c r="B61" s="101"/>
-      <c r="C61" s="117"/>
-      <c r="D61" s="68" t="s">
+      <c r="A61" s="99"/>
+      <c r="B61" s="92"/>
+      <c r="C61" s="97"/>
+      <c r="D61" s="60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="121" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" s="122" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="31"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="32"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="99"/>
+      <c r="B62" s="92"/>
+      <c r="C62" s="97"/>
+      <c r="D62" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E62" s="90"/>
+      <c r="F62" s="123"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="32"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="99"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="94"/>
+      <c r="D63" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E63" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="69" t="s">
+      <c r="F63" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="G61" s="33"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="34"/>
-    </row>
-    <row r="62" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="131"/>
-      <c r="B62" s="101"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="60" t="s">
+      <c r="G63" s="33"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="34"/>
+    </row>
+    <row r="64" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="99"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E64" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F62" s="54" t="s">
+      <c r="F64" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="56" t="s">
+      <c r="G64" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H62" s="56" t="s">
+      <c r="H64" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="I62" s="56" t="s">
+      <c r="I64" s="56" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="131"/>
-      <c r="B63" s="101"/>
-      <c r="C63" s="116" t="s">
+    <row r="65" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="99"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="93" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="59" t="s">
+      <c r="D65" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="E63" s="85" t="s">
+      <c r="E65" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="F63" s="87" t="s">
+      <c r="F65" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="89" t="s">
+      <c r="G65" s="115" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="89" t="s">
+      <c r="H65" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="89" t="s">
+      <c r="I65" s="115" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="131"/>
-      <c r="B64" s="101"/>
-      <c r="C64" s="128"/>
-      <c r="D64" s="59" t="s">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="99"/>
+      <c r="B66" s="89"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E64" s="86"/>
-      <c r="F64" s="88"/>
-      <c r="G64" s="90"/>
-      <c r="H64" s="90"/>
-      <c r="I64" s="90"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="131"/>
-      <c r="B65" s="101"/>
-      <c r="C65" s="116" t="s">
+      <c r="E66" s="90"/>
+      <c r="F66" s="123"/>
+      <c r="G66" s="95"/>
+      <c r="H66" s="95"/>
+      <c r="I66" s="95"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="99"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="D65" s="59" t="s">
+      <c r="D67" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E67" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F65" s="58" t="s">
+      <c r="F67" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G65" s="44"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="28"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="131"/>
-      <c r="B66" s="101"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="73" t="s">
+      <c r="G67" s="44"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="28"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="99"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="18" t="s">
+      <c r="E68" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F66" s="72" t="s">
+      <c r="F68" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="G66" s="45"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="32"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="131"/>
-      <c r="B67" s="101"/>
-      <c r="C67" s="116" t="s">
-        <v>63</v>
-      </c>
-      <c r="D67" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F67" s="89" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="45"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="32"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="131"/>
-      <c r="B68" s="101"/>
-      <c r="C68" s="128"/>
-      <c r="D68" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F68" s="91"/>
       <c r="G68" s="45"/>
       <c r="H68" s="3"/>
       <c r="I68" s="32"/>
     </row>
-    <row r="69" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="43"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="1"/>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="99"/>
+      <c r="B69" s="89"/>
+      <c r="C69" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F69" s="115" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" s="45"/>
       <c r="H69" s="3"/>
       <c r="I69" s="32"/>
     </row>
-    <row r="70" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="100" t="s">
-        <v>153</v>
-      </c>
-      <c r="B70" s="100" t="s">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="99"/>
+      <c r="B70" s="89"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E70" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F70" s="133"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="32"/>
+    </row>
+    <row r="71" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="43"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="32"/>
+    </row>
+    <row r="72" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="91" t="s">
+        <v>168</v>
+      </c>
+      <c r="B72" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="C70" s="116" t="s">
+      <c r="C72" s="93" t="s">
         <v>99</v>
       </c>
-      <c r="D70" s="55" t="s">
+      <c r="D72" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="E70" s="23" t="s">
+      <c r="E72" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F70" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" s="46"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="39"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="114"/>
-      <c r="B71" s="114"/>
-      <c r="C71" s="129"/>
-      <c r="D71" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E71" s="85" t="s">
-        <v>65</v>
-      </c>
-      <c r="F71" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="G71" s="46"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="39"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="114"/>
-      <c r="B72" s="114"/>
-      <c r="C72" s="129"/>
-      <c r="D72" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72" s="86"/>
-      <c r="F72" s="54" t="s">
+      <c r="F72" s="57" t="s">
         <v>7</v>
       </c>
       <c r="G72" s="46"/>
       <c r="H72" s="1"/>
       <c r="I72" s="39"/>
     </row>
-    <row r="73" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="101"/>
-      <c r="B73" s="101"/>
-      <c r="C73" s="116" t="s">
-        <v>100</v>
-      </c>
-      <c r="D73" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F73" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="G73" s="31"/>
-      <c r="H73" s="47"/>
-      <c r="I73" s="48"/>
-    </row>
-    <row r="74" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="101"/>
-      <c r="B74" s="101"/>
-      <c r="C74" s="90"/>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="92"/>
+      <c r="B73" s="92"/>
+      <c r="C73" s="97"/>
+      <c r="D73" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E73" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="G73" s="46"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="39"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="92"/>
+      <c r="B74" s="92"/>
+      <c r="C74" s="97"/>
       <c r="D74" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>73</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E74" s="90"/>
       <c r="F74" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G74" s="31"/>
-      <c r="H74" s="47"/>
-      <c r="I74" s="48"/>
-    </row>
-    <row r="75" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="101"/>
-      <c r="B75" s="101"/>
-      <c r="C75" s="65" t="s">
+      <c r="G74" s="46"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="39"/>
+    </row>
+    <row r="75" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="89"/>
+      <c r="B75" s="89"/>
+      <c r="C75" s="93" t="s">
+        <v>100</v>
+      </c>
+      <c r="D75" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F75" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75" s="31"/>
+      <c r="H75" s="47"/>
+      <c r="I75" s="48"/>
+    </row>
+    <row r="76" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="89"/>
+      <c r="B76" s="89"/>
+      <c r="C76" s="95"/>
+      <c r="D76" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F76" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76" s="31"/>
+      <c r="H76" s="47"/>
+      <c r="I76" s="48"/>
+    </row>
+    <row r="77" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="89"/>
+      <c r="B77" s="89"/>
+      <c r="C77" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="D75" s="66" t="s">
+      <c r="D77" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E77" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F75" s="67" t="s">
+      <c r="F77" s="67" t="s">
         <v>13</v>
-      </c>
-      <c r="G75" s="31"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="49"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="101"/>
-      <c r="B76" s="101"/>
-      <c r="C76" s="116" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F76" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="31"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="49"/>
-    </row>
-    <row r="77" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="101"/>
-      <c r="B77" s="101"/>
-      <c r="C77" s="117"/>
-      <c r="D77" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="F77" s="54" t="s">
-        <v>7</v>
       </c>
       <c r="G77" s="31"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="39"/>
-    </row>
-    <row r="78" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="101"/>
-      <c r="B78" s="101"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="68" t="s">
-        <v>135</v>
+      <c r="I77" s="49"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="89"/>
+      <c r="B78" s="89"/>
+      <c r="C78" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="D78" s="66" t="s">
+        <v>71</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F78" s="69" t="s">
-        <v>9</v>
+        <v>72</v>
+      </c>
+      <c r="F78" s="67" t="s">
+        <v>13</v>
       </c>
       <c r="G78" s="31"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="39"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="86"/>
-      <c r="B79" s="86"/>
-      <c r="C79" s="90"/>
-      <c r="D79" s="66" t="s">
+      <c r="I78" s="49"/>
+    </row>
+    <row r="79" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="89"/>
+      <c r="B79" s="89"/>
+      <c r="C79" s="94"/>
+      <c r="D79" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F79" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="31"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="39"/>
+    </row>
+    <row r="80" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="89"/>
+      <c r="B80" s="89"/>
+      <c r="C80" s="94"/>
+      <c r="D80" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F80" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="G80" s="31"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="39"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="90"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E81" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F79" s="67" t="s">
+      <c r="F81" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="G79" s="33"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="40"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="22"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="22"/>
-    </row>
-    <row r="81" spans="2:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="2"/>
-      <c r="E81" s="5"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="2"/>
-      <c r="E82" s="5"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="2:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G81" s="33"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="40"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="22"/>
+      <c r="B82" s="22"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="22"/>
+    </row>
+    <row r="83" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="E83" s="5"/>
       <c r="G83" s="2"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="E84" s="5"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="E85" s="5"/>
       <c r="G85" s="2"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
       <c r="E86" s="5"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I86" s="2"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
       <c r="E87" s="5"/>
-      <c r="G87" s="1"/>
+      <c r="G87" s="2"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="3"/>
-      <c r="E88" s="7"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="3"/>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="2"/>
+      <c r="E88" s="5"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="2"/>
       <c r="E89" s="5"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="2"/>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B90" s="3"/>
       <c r="E90" s="7"/>
     </row>
-    <row r="91" spans="2:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="2"/>
-      <c r="E91" s="7"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B91" s="3"/>
+      <c r="E91" s="5"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
-      <c r="E92" s="5"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E92" s="7"/>
+    </row>
+    <row r="93" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
-      <c r="E93" s="5"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E93" s="7"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
       <c r="E94" s="5"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B95" s="2"/>
       <c r="E95" s="5"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B96" s="2"/>
-      <c r="E96" s="7"/>
+      <c r="E96" s="5"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B97" s="2"/>
-      <c r="E97" s="7"/>
+      <c r="E97" s="5"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B98" s="2"/>
-      <c r="E98" s="5"/>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="E98" s="7"/>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B99" s="2"/>
@@ -3158,7 +3208,10 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B100" s="2"/>
-      <c r="E100" s="7"/>
+      <c r="E100" s="5"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B101" s="2"/>
@@ -3177,9 +3230,11 @@
       <c r="E104" s="7"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B105" s="2"/>
       <c r="E105" s="7"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B106" s="2"/>
       <c r="E106" s="7"/>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.3">
@@ -3227,24 +3282,44 @@
     <row r="121" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E121" s="7"/>
     </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E122" s="7"/>
+    </row>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E123" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="F34:F42"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="B70:B79"/>
-    <mergeCell ref="A70:A79"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A58:A68"/>
-    <mergeCell ref="B58:B68"/>
-    <mergeCell ref="C58:C62"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="C49:C50"/>
+  <mergeCells count="57">
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="E30:E43"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="A17:A29"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="C30:C33"/>
     <mergeCell ref="B17:B29"/>
     <mergeCell ref="A3:A4"/>
@@ -3256,33 +3331,22 @@
     <mergeCell ref="B30:B43"/>
     <mergeCell ref="A30:A43"/>
     <mergeCell ref="C34:C43"/>
-    <mergeCell ref="A45:A56"/>
-    <mergeCell ref="B45:B56"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="A17:A29"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F23:F27"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="E30:E43"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="E51:E53"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:F64"/>
-    <mergeCell ref="G63:G64"/>
-    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="F34:F42"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="B72:B81"/>
+    <mergeCell ref="A72:A81"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="C72:C74"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="A60:A70"/>
+    <mergeCell ref="B60:B70"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C51:C52"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
